--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.11</v>
       </c>
-      <c r="G2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>
@@ -969,152 +969,152 @@
         <v>5.8</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="Q3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S3" t="n">
         <v>1.96</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H5" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="I5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S5" t="n">
         <v>2.56</v>
       </c>
-      <c r="J5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.4</v>
-      </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="W5" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1399,46 +1399,46 @@
         <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC5" t="n">
         <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK5" t="n">
         <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>16.5</v>
+        <v>1.9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.4</v>
+        <v>1.9</v>
       </c>
       <c r="AR5" t="n">
-        <v>11</v>
+        <v>1.72</v>
       </c>
       <c r="AS5" t="n">
-        <v>19.5</v>
+        <v>1.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>12.5</v>
+        <v>1.73</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.4</v>
+        <v>1.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.800000000000001</v>
+        <v>1.66</v>
       </c>
       <c r="AW5" t="n">
-        <v>16.5</v>
+        <v>1.77</v>
       </c>
       <c r="AX5" t="n">
-        <v>19.5</v>
+        <v>1.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>11</v>
+        <v>1.71</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11.5</v>
+        <v>1.72</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>1.81</v>
       </c>
       <c r="BB5" t="n">
-        <v>44</v>
+        <v>1.85</v>
       </c>
       <c r="BC5" t="n">
-        <v>26</v>
+        <v>1.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>28</v>
+        <v>1.83</v>
       </c>
       <c r="BE5" t="n">
-        <v>44</v>
+        <v>1.86</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>
@@ -1551,19 +1551,19 @@
         <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.41</v>
       </c>
       <c r="P6" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="Q6" t="n">
         <v>2.24</v>
@@ -1575,128 +1575,128 @@
         <v>4.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z6" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AA6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC6" t="n">
         <v>7.6</v>
       </c>
       <c r="AD6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR6" t="n">
         <v>11</v>
       </c>
-      <c r="AE6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>630</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP6" t="n">
+      <c r="AS6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV6" t="n">
         <v>10</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AW6" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AY6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BB6" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="BC6" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BD6" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BE6" t="n">
         <v>42</v>
       </c>
       <c r="BF6" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BG6" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>1.62</v>
       </c>
       <c r="J7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L7" t="n">
         <v>1.01</v>
       </c>
-      <c r="K7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.05</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
         <v>2.96</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Q9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="K10" t="n">
-        <v>710</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="K11" t="n">
         <v>4.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>
@@ -2703,16 +2703,16 @@
         <v>6.2</v>
       </c>
       <c r="H12" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="I12" t="n">
         <v>2.14</v>
       </c>
       <c r="J12" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>1.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>
@@ -2897,16 +2897,16 @@
         <v>3.35</v>
       </c>
       <c r="H13" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J13" t="n">
         <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,16 +2921,16 @@
         <v>1.37</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q13" t="n">
         <v>2.12</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T13" t="n">
         <v>1.85</v>
@@ -2945,73 +2945,73 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AB13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AC13" t="n">
         <v>7.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF13" t="n">
         <v>23</v>
       </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK13" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN13" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AO13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR13" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AS13" t="n">
         <v>21</v>
       </c>
       <c r="AT13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU13" t="n">
         <v>6.8</v>
@@ -3020,25 +3020,25 @@
         <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AX13" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="AY13" t="n">
         <v>13</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BD13" t="n">
         <v>29</v>
@@ -3047,14 +3047,14 @@
         <v>38</v>
       </c>
       <c r="BF13" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BG13" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>
@@ -3121,16 +3121,16 @@
         <v>1.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T14" t="n">
         <v>2.52</v>
       </c>
       <c r="U14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3139,10 +3139,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3151,61 +3151,61 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AD14" t="n">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AF14" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="AG14" t="n">
         <v>11</v>
       </c>
       <c r="AH14" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AK14" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AL14" t="n">
-        <v>300</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AN14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ14" t="n">
         <v>19.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.5</v>
+        <v>55</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU14" t="n">
         <v>12</v>
@@ -3214,7 +3214,7 @@
         <v>26</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.3</v>
+        <v>48</v>
       </c>
       <c r="AX14" t="n">
         <v>6.4</v>
@@ -3223,32 +3223,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF14" t="n">
         <v>5.9</v>
       </c>
-      <c r="BA14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>6</v>
-      </c>
       <c r="BG14" t="n">
-        <v>4.5</v>
+        <v>55</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.54</v>
+        <v>6.2</v>
       </c>
       <c r="G15" t="n">
         <v>6.8</v>
       </c>
       <c r="H15" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="I15" t="n">
         <v>1.64</v>
@@ -3294,7 +3294,7 @@
         <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.27</v>
+        <v>2.18</v>
       </c>
       <c r="G17" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="J17" t="n">
-        <v>2.44</v>
+        <v>2.78</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>3.2</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.07</v>
+        <v>1.42</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="I18" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="J18" t="n">
-        <v>1.02</v>
+        <v>1.8</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>3.4</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-02-28 12:42:17</t>
+          <t>2026-02-28 15:09:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,10 +763,10 @@
         <v>1.46</v>
       </c>
       <c r="H2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="J2" t="n">
         <v>4.7</v>
@@ -775,13 +775,13 @@
         <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
         <v>1.29</v>
@@ -811,7 +811,7 @@
         <v>3.15</v>
       </c>
       <c r="X2" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
         <v>34</v>
@@ -850,7 +850,7 @@
         <v>13</v>
       </c>
       <c r="AK2" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AL2" t="n">
         <v>55</v>
@@ -859,13 +859,13 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.6</v>
@@ -874,19 +874,19 @@
         <v>5.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT2" t="n">
         <v>6.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX2" t="n">
         <v>6</v>
@@ -895,32 +895,32 @@
         <v>3.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA2" t="n">
         <v>5.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-02-28 15:09:09</t>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>
@@ -951,34 +951,34 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="G3" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.6</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P3" t="n">
         <v>1.72</v>
@@ -987,134 +987,134 @@
         <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
-        <v>1.96</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-02-28 15:09:09</t>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>
@@ -1163,34 +1163,34 @@
         <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.93</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
         <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>1.89</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="V4" t="n">
         <v>1.31</v>
@@ -1199,116 +1199,116 @@
         <v>1.84</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF4" t="n">
         <v>11</v>
       </c>
-      <c r="AR4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-02-28 15:09:09</t>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>3.2</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H5" t="n">
         <v>2.1</v>
       </c>
       <c r="I5" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
@@ -1363,19 +1363,19 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S5" t="n">
         <v>2.56</v>
@@ -1384,34 +1384,34 @@
         <v>1.55</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AA5" t="n">
         <v>32</v>
       </c>
       <c r="AB5" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
         <v>25</v>
@@ -1420,89 +1420,89 @@
         <v>32</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ5" t="n">
         <v>70</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
         <v>80</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.72</v>
+        <v>4.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.73</v>
+        <v>4.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.9</v>
+        <v>3.65</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.66</v>
+        <v>3.9</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.77</v>
+        <v>4.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.71</v>
+        <v>4.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.72</v>
+        <v>4.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.81</v>
+        <v>4.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.85</v>
+        <v>5.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.83</v>
+        <v>4.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.86</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.9</v>
+        <v>3.95</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-02-28 15:09:09</t>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H6" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="I6" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
@@ -1566,7 +1566,7 @@
         <v>1.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R6" t="n">
         <v>1.29</v>
@@ -1575,31 +1575,31 @@
         <v>4.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V6" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="W6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X6" t="n">
         <v>11</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z6" t="n">
         <v>11.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC6" t="n">
         <v>7.6</v>
@@ -1611,10 +1611,10 @@
         <v>24</v>
       </c>
       <c r="AF6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AG6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH6" t="n">
         <v>21</v>
@@ -1623,22 +1623,22 @@
         <v>44</v>
       </c>
       <c r="AJ6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL6" t="n">
         <v>75</v>
       </c>
       <c r="AM6" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AO6" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AP6" t="n">
         <v>10.5</v>
@@ -1647,10 +1647,10 @@
         <v>7.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT6" t="n">
         <v>12.5</v>
@@ -1662,13 +1662,13 @@
         <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX6" t="n">
         <v>26</v>
       </c>
       <c r="AY6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>18.5</v>
@@ -1683,7 +1683,7 @@
         <v>50</v>
       </c>
       <c r="BD6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BE6" t="n">
         <v>42</v>
@@ -1692,11 +1692,11 @@
         <v>60</v>
       </c>
       <c r="BG6" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-02-28 15:09:09</t>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>6.8</v>
       </c>
       <c r="G7" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H7" t="n">
         <v>1.5</v>
@@ -1745,7 +1745,7 @@
         <v>4.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
@@ -1763,134 +1763,134 @@
         <v>1.86</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
         <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="U7" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="V7" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AA7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>290</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>200</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY7" t="n">
         <v>21</v>
       </c>
-      <c r="AB7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>95</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>1.79</v>
+        <v>20</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.82</v>
+        <v>4.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.89</v>
+        <v>4.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.89</v>
+        <v>4.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.89</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.89</v>
+        <v>4.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.89</v>
+        <v>4.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.89</v>
+        <v>6.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-02-28 15:09:09</t>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="G8" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="J8" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-02-28 15:09:09</t>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>
@@ -2115,177 +2115,177 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-02-28 15:09:09</t>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,184 +2295,184 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="J10" t="n">
-        <v>2.28</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>1.29</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-02-28 15:09:09</t>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="G11" t="n">
-        <v>3.5</v>
+        <v>2.42</v>
       </c>
       <c r="H11" t="n">
-        <v>2.72</v>
+        <v>4.3</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="K11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX11" t="n">
         <v>4.5</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-02-28 15:09:09</t>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Amiens</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ESTAC Troyes</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.95</v>
+        <v>2.76</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="H12" t="n">
-        <v>1.71</v>
+        <v>2.94</v>
       </c>
       <c r="I12" t="n">
-        <v>2.14</v>
+        <v>3.45</v>
       </c>
       <c r="J12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.25</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA12" t="n">
         <v>5.2</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-02-28 15:09:09</t>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Amiens</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>ESTAC Troyes</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="G13" t="n">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="H13" t="n">
-        <v>2.44</v>
+        <v>1.86</v>
       </c>
       <c r="I13" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="O13" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="S13" t="n">
-        <v>3.95</v>
+        <v>1.96</v>
       </c>
       <c r="T13" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X13" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>2.1</v>
       </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AR13" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
-        <v>21</v>
+        <v>2.32</v>
       </c>
       <c r="AT13" t="n">
-        <v>10.5</v>
+        <v>2.28</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>10.5</v>
+        <v>2.1</v>
       </c>
       <c r="AW13" t="n">
-        <v>21</v>
+        <v>2.34</v>
       </c>
       <c r="AX13" t="n">
-        <v>19.5</v>
+        <v>2.42</v>
       </c>
       <c r="AY13" t="n">
-        <v>13</v>
+        <v>2.32</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16</v>
+        <v>2.32</v>
       </c>
       <c r="BA13" t="n">
-        <v>36</v>
+        <v>2.42</v>
       </c>
       <c r="BB13" t="n">
-        <v>29</v>
+        <v>2.54</v>
       </c>
       <c r="BC13" t="n">
-        <v>34</v>
+        <v>2.54</v>
       </c>
       <c r="BD13" t="n">
-        <v>29</v>
+        <v>2.54</v>
       </c>
       <c r="BE13" t="n">
-        <v>38</v>
+        <v>2.54</v>
       </c>
       <c r="BF13" t="n">
-        <v>34</v>
+        <v>2.54</v>
       </c>
       <c r="BG13" t="n">
-        <v>20</v>
+        <v>2.54</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-02-28 15:09:09</t>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.33</v>
+        <v>1.81</v>
       </c>
       <c r="G14" t="n">
-        <v>1.34</v>
+        <v>1.89</v>
       </c>
       <c r="H14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF14" t="n">
         <v>12</v>
       </c>
-      <c r="I14" t="n">
+      <c r="AG14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>75</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF14" t="n">
         <v>13</v>
       </c>
-      <c r="J14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>330</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>340</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>34</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BG14" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-02-28 15:09:09</t>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="G15" t="n">
-        <v>6.8</v>
+        <v>3.4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.63</v>
+        <v>2.44</v>
       </c>
       <c r="I15" t="n">
-        <v>1.64</v>
+        <v>2.46</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-02-28 15:09:09</t>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.07</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-02-28 15:09:09</t>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.18</v>
+        <v>6.2</v>
       </c>
       <c r="G17" t="n">
-        <v>2.44</v>
+        <v>6.8</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4</v>
+        <v>1.63</v>
       </c>
       <c r="I17" t="n">
-        <v>4.9</v>
+        <v>1.64</v>
       </c>
       <c r="J17" t="n">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P17" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.96</v>
+        <v>2.06</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-02-28 15:09:09</t>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,36 +3847,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3894,7 +3894,7 @@
         <v>1.07</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,201 +4024,589 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-02-28 15:09:09</t>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>19:15:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Velez Sarsfield</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-02-28 17:32:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>19:15:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CA Platense</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K20" t="n">
+        <v>950</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-02-28 17:32:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Sportivo San Lorenzo</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Libertad</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>1.07</v>
       </c>
-      <c r="Q19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>2026-02-28 15:09:09</t>
+      <c r="Q21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-02-28 17:32:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -775,7 +775,7 @@
         <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.66</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H3" t="n">
         <v>2.66</v>
@@ -981,7 +981,7 @@
         <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q3" t="n">
         <v>2.1</v>
@@ -993,16 +993,16 @@
         <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U3" t="n">
         <v>1.89</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
         <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
         <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q5" t="n">
         <v>1.63</v>
@@ -1498,11 +1498,11 @@
         <v>4.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.95</v>
+        <v>9</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>4.3</v>
       </c>
       <c r="G6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H6" t="n">
         <v>2.02</v>
@@ -1557,7 +1557,7 @@
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O6" t="n">
         <v>1.41</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>1.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="J7" t="n">
         <v>4.1</v>
@@ -1769,10 +1769,10 @@
         <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="U7" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
         <v>2.62</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.56</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H8" t="n">
         <v>2.9</v>
@@ -1963,16 +1963,16 @@
         <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V8" t="n">
         <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -2118,13 +2118,13 @@
         <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="H9" t="n">
         <v>3.35</v>
       </c>
       <c r="I9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>2.84</v>
@@ -2154,16 +2154,16 @@
         <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="U9" t="n">
         <v>1.7</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
         <v>1.6</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -2312,13 +2312,13 @@
         <v>1.99</v>
       </c>
       <c r="G10" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="H10" t="n">
         <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J10" t="n">
         <v>3.8</v>
@@ -2351,13 +2351,13 @@
         <v>2.26</v>
       </c>
       <c r="T10" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="U10" t="n">
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
         <v>1.83</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G11" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
         <v>2.84</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2530,7 +2530,7 @@
         <v>2.22</v>
       </c>
       <c r="O11" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="P11" t="n">
         <v>1.38</v>
@@ -2548,43 +2548,43 @@
         <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V11" t="n">
         <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="X11" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AA11" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AD11" t="n">
         <v>23</v>
       </c>
       <c r="AE11" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AF11" t="n">
         <v>15</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
         <v>32</v>
@@ -2593,7 +2593,7 @@
         <v>170</v>
       </c>
       <c r="AJ11" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK11" t="n">
         <v>48</v>
@@ -2608,7 +2608,7 @@
         <v>55</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP11" t="n">
         <v>5.1</v>
@@ -2617,10 +2617,10 @@
         <v>7.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.2</v>
+        <v>2.94</v>
       </c>
       <c r="AT11" t="n">
         <v>4.6</v>
@@ -2632,41 +2632,41 @@
         <v>15.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AY11" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="BF11" t="n">
-        <v>30</v>
+        <v>2.86</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H12" t="n">
         <v>2.94</v>
@@ -2709,7 +2709,7 @@
         <v>3.45</v>
       </c>
       <c r="J12" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K12" t="n">
         <v>3.25</v>
@@ -2721,25 +2721,25 @@
         <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q12" t="n">
         <v>2.62</v>
       </c>
       <c r="R12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
         <v>5.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
         <v>1.75</v>
@@ -2760,7 +2760,7 @@
         <v>23</v>
       </c>
       <c r="AA12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB12" t="n">
         <v>9.4</v>
@@ -2787,7 +2787,7 @@
         <v>90</v>
       </c>
       <c r="AJ12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK12" t="n">
         <v>50</v>
@@ -2802,10 +2802,10 @@
         <v>60</v>
       </c>
       <c r="AO12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ12" t="n">
         <v>7.6</v>
@@ -2814,7 +2814,7 @@
         <v>16.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT12" t="n">
         <v>7</v>
@@ -2826,7 +2826,7 @@
         <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX12" t="n">
         <v>14.5</v>
@@ -2838,29 +2838,29 @@
         <v>19.5</v>
       </c>
       <c r="BA12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG12" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="G13" t="n">
         <v>5.6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="I13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K13" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2915,7 +2915,7 @@
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>1.03</v>
+        <v>1.87</v>
       </c>
       <c r="O13" t="n">
         <v>1.3</v>
@@ -2939,31 +2939,31 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y13" t="n">
         <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AA13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB13" t="n">
         <v>22</v>
       </c>
       <c r="AC13" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD13" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE13" t="n">
         <v>30</v>
@@ -2999,7 +2999,7 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AQ13" t="n">
         <v>2.1</v>
@@ -3017,7 +3017,7 @@
         <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AW13" t="n">
         <v>2.34</v>
@@ -3029,10 +3029,10 @@
         <v>2.32</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BB13" t="n">
         <v>2.54</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -3088,13 +3088,13 @@
         <v>1.81</v>
       </c>
       <c r="G14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H14" t="n">
         <v>5.2</v>
       </c>
       <c r="I14" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J14" t="n">
         <v>3.4</v>
@@ -3109,7 +3109,7 @@
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O14" t="n">
         <v>1.38</v>
@@ -3133,16 +3133,16 @@
         <v>1.7</v>
       </c>
       <c r="V14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X14" t="n">
         <v>12.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
         <v>48</v>
@@ -3199,22 +3199,22 @@
         <v>11.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AS14" t="n">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
         <v>5.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
         <v>7.8</v>
@@ -3223,32 +3223,32 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
         <v>13</v>
       </c>
       <c r="BG14" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H15" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I15" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="J15" t="n">
         <v>3.4</v>
@@ -3327,7 +3327,7 @@
         <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W15" t="n">
         <v>1.42</v>
@@ -3339,7 +3339,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
         <v>34</v>
@@ -3354,10 +3354,10 @@
         <v>11.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG15" t="n">
         <v>14</v>
@@ -3426,7 +3426,7 @@
         <v>50</v>
       </c>
       <c r="BC15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BD15" t="n">
         <v>46</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -3479,10 +3479,10 @@
         <v>1.34</v>
       </c>
       <c r="H16" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="I16" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="J16" t="n">
         <v>5.7</v>
@@ -3497,13 +3497,13 @@
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
         <v>1.92</v>
@@ -3515,16 +3515,16 @@
         <v>3.35</v>
       </c>
       <c r="T16" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="U16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="X16" t="n">
         <v>16.5</v>
@@ -3533,7 +3533,7 @@
         <v>34</v>
       </c>
       <c r="Z16" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA16" t="n">
         <v>740</v>
@@ -3548,7 +3548,7 @@
         <v>48</v>
       </c>
       <c r="AE16" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AF16" t="n">
         <v>6.8</v>
@@ -3557,7 +3557,7 @@
         <v>10.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
@@ -3566,13 +3566,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AK16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AN16" t="n">
         <v>6.4</v>
@@ -3584,10 +3584,10 @@
         <v>15.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AR16" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AS16" t="n">
         <v>110</v>
@@ -3602,10 +3602,10 @@
         <v>42</v>
       </c>
       <c r="AW16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY16" t="n">
         <v>10</v>
@@ -3617,16 +3617,16 @@
         <v>48</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
       </c>
       <c r="BD16" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE16" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BF16" t="n">
         <v>6</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
         <v>6.8</v>
@@ -3688,10 +3688,10 @@
         <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
         <v>1.36</v>
@@ -3706,13 +3706,13 @@
         <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="V17" t="n">
         <v>2.56</v>
@@ -3742,10 +3742,10 @@
         <v>10</v>
       </c>
       <c r="AE17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AG17" t="n">
         <v>25</v>
@@ -3757,19 +3757,19 @@
         <v>50</v>
       </c>
       <c r="AJ17" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AK17" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AL17" t="n">
         <v>120</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN17" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AO17" t="n">
         <v>12</v>
@@ -3778,7 +3778,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AR17" t="n">
         <v>8.199999999999999</v>
@@ -3793,44 +3793,44 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW17" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY17" t="n">
         <v>21</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BB17" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BC17" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF17" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG17" t="n">
         <v>9</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -3879,152 +3879,152 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P18" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q18" t="n">
         <v>1.01</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G19" t="n">
         <v>2.42</v>
@@ -4070,19 +4070,19 @@
         <v>2.78</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P19" t="n">
         <v>1.41</v>
@@ -4091,134 +4091,134 @@
         <v>2.96</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -4255,10 +4255,10 @@
         <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I20" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
         <v>1.03</v>
@@ -4267,152 +4267,152 @@
         <v>950</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q20" t="n">
         <v>1.01</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-02-28 17:32:45</t>
+          <t>2026-02-28 19:54:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>2.66</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H3" t="n">
         <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J3" t="n">
         <v>2.9</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1178,7 +1178,7 @@
         <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
@@ -1187,10 +1187,10 @@
         <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
         <v>1.31</v>
@@ -1253,10 +1253,10 @@
         <v>60</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
         <v>21</v>
@@ -1265,13 +1265,13 @@
         <v>4.1</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AW4" t="n">
         <v>4</v>
@@ -1280,19 +1280,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
         <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.75</v>
+        <v>18.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.65</v>
+        <v>16</v>
       </c>
       <c r="BD4" t="n">
         <v>3.9</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
         <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
         <v>1.63</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G6" t="n">
         <v>4.5</v>
@@ -1545,10 +1545,10 @@
         <v>2.06</v>
       </c>
       <c r="J6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.47</v>
@@ -1581,7 +1581,7 @@
         <v>1.96</v>
       </c>
       <c r="V6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="W6" t="n">
         <v>1.28</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
         <v>1.29</v>
@@ -1817,7 +1817,7 @@
         <v>48</v>
       </c>
       <c r="AJ7" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AK7" t="n">
         <v>150</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G8" t="n">
         <v>3.1</v>
@@ -1930,7 +1930,7 @@
         <v>2.9</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -1954,22 +1954,22 @@
         <v>1.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W8" t="n">
         <v>1.48</v>
@@ -1978,16 +1978,16 @@
         <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC8" t="n">
         <v>1000</v>
@@ -1996,13 +1996,13 @@
         <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF8" t="n">
         <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH8" t="n">
         <v>1000</v>
@@ -2011,13 +2011,13 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK8" t="n">
         <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -2118,13 +2118,13 @@
         <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H9" t="n">
         <v>3.35</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
         <v>2.84</v>
@@ -2154,7 +2154,7 @@
         <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="T9" t="n">
         <v>2.04</v>
@@ -2250,7 +2250,7 @@
         <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.85</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
         <v>4.4</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -2327,34 +2327,34 @@
         <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>2.34</v>
+        <v>4.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
         <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
         <v>1.35</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G11" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H11" t="n">
         <v>4.1</v>
@@ -2554,7 +2554,7 @@
         <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X11" t="n">
         <v>970</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="G12" t="n">
         <v>3.05</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="G13" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="H13" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="J13" t="n">
         <v>3.6</v>
       </c>
       <c r="K13" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2915,49 +2915,49 @@
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>1.87</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="V13" t="n">
         <v>1.96</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V13" t="n">
-        <v>2</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="X13" t="n">
         <v>970</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z13" t="n">
         <v>970</v>
       </c>
       <c r="AA13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AB13" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AC13" t="n">
         <v>970</v>
@@ -2966,95 +2966,95 @@
         <v>970</v>
       </c>
       <c r="AE13" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AF13" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AG13" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BE13" t="n">
         <v>2.18</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.54</v>
-      </c>
       <c r="BF13" t="n">
-        <v>2.54</v>
+        <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.54</v>
+        <v>10.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>1.81</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H14" t="n">
         <v>5.2</v>
@@ -3103,7 +3103,7 @@
         <v>3.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M14" t="n">
         <v>1.08</v>
@@ -3124,7 +3124,7 @@
         <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
         <v>1.93</v>
@@ -3133,7 +3133,7 @@
         <v>1.7</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
         <v>2.1</v>
@@ -3199,7 +3199,7 @@
         <v>11.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
         <v>1.01</v>
@@ -3208,7 +3208,7 @@
         <v>5.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -3288,28 +3288,28 @@
         <v>2.46</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J15" t="n">
         <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L15" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O15" t="n">
         <v>1.37</v>
       </c>
       <c r="P15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q15" t="n">
         <v>2.12</v>
@@ -3327,7 +3327,7 @@
         <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W15" t="n">
         <v>1.42</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -3479,19 +3479,19 @@
         <v>1.34</v>
       </c>
       <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="n">
         <v>13</v>
       </c>
-      <c r="I16" t="n">
-        <v>14</v>
-      </c>
       <c r="J16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K16" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M16" t="n">
         <v>1.06</v>
@@ -3500,31 +3500,31 @@
         <v>4.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
         <v>3.35</v>
       </c>
       <c r="T16" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="U16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W16" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="X16" t="n">
         <v>16.5</v>
@@ -3533,13 +3533,13 @@
         <v>34</v>
       </c>
       <c r="Z16" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA16" t="n">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="AB16" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AC16" t="n">
         <v>12.5</v>
@@ -3548,10 +3548,10 @@
         <v>48</v>
       </c>
       <c r="AE16" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AF16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AG16" t="n">
         <v>10.5</v>
@@ -3560,7 +3560,7 @@
         <v>40</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ16" t="n">
         <v>9.800000000000001</v>
@@ -3569,16 +3569,16 @@
         <v>16</v>
       </c>
       <c r="AL16" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM16" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AN16" t="n">
         <v>6.4</v>
       </c>
       <c r="AO16" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AP16" t="n">
         <v>15.5</v>
@@ -3593,7 +3593,7 @@
         <v>110</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU16" t="n">
         <v>11.5</v>
@@ -3617,16 +3617,16 @@
         <v>48</v>
       </c>
       <c r="BB16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE16" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BF16" t="n">
         <v>6</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
         <v>1.83</v>
       </c>
       <c r="V17" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="W17" t="n">
         <v>1.17</v>
@@ -3727,10 +3727,10 @@
         <v>7.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA17" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AB17" t="n">
         <v>19</v>
@@ -3787,19 +3787,19 @@
         <v>14</v>
       </c>
       <c r="AT17" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AU17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW17" t="n">
         <v>16.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY17" t="n">
         <v>21</v>
@@ -3811,26 +3811,26 @@
         <v>36</v>
       </c>
       <c r="BB17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC17" t="n">
         <v>12</v>
       </c>
-      <c r="BC17" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BD17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BE17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG17" t="n">
         <v>9</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -3969,52 +3969,52 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
         <v>1.01</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G19" t="n">
         <v>2.42</v>
@@ -4079,10 +4079,10 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.41</v>
+        <v>2.32</v>
       </c>
       <c r="O19" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="P19" t="n">
         <v>1.41</v>
@@ -4097,10 +4097,10 @@
         <v>2.96</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="U19" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="V19" t="n">
         <v>1.25</v>
@@ -4109,116 +4109,116 @@
         <v>1.7</v>
       </c>
       <c r="X19" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AD19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH19" t="n">
         <v>29</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>40</v>
-      </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ19" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.53</v>
+        <v>6.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.88</v>
+        <v>9</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.88</v>
+        <v>19</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.88</v>
+        <v>7.8</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.55</v>
+        <v>5.7</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.58</v>
+        <v>6.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.76</v>
+        <v>17</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.88</v>
+        <v>7.6</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.88</v>
+        <v>10.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.7</v>
+        <v>11</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.79</v>
+        <v>6.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.88</v>
+        <v>7.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.81</v>
+        <v>6.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.88</v>
+        <v>6.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.88</v>
+        <v>7.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.88</v>
+        <v>8</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.88</v>
+        <v>6.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.88</v>
+        <v>7.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -4255,13 +4255,13 @@
         <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I20" t="n">
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K20" t="n">
         <v>950</v>
@@ -4282,7 +4282,7 @@
         <v>1.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R20" t="n">
         <v>1.08</v>
@@ -4357,52 +4357,52 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>
@@ -4461,16 +4461,16 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P21" t="n">
         <v>1.24</v>
@@ -4479,134 +4479,134 @@
         <v>1.01</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-02-28 19:54:27</t>
+          <t>2026-02-28 22:14:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BH25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,7 +775,7 @@
         <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -790,7 +790,7 @@
         <v>1.99</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="R2" t="n">
         <v>1.38</v>
@@ -826,13 +826,13 @@
         <v>8.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD2" t="n">
         <v>46</v>
       </c>
       <c r="AE2" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
         <v>9</v>
@@ -847,7 +847,7 @@
         <v>190</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AK2" t="n">
         <v>970</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AR2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS2" t="n">
         <v>5.1</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>5.3</v>
       </c>
       <c r="AT2" t="n">
         <v>6.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AX2" t="n">
         <v>6</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AZ2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD2" t="n">
         <v>4.7</v>
       </c>
-      <c r="BA2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BE2" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF2" t="n">
         <v>5.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J3" t="n">
         <v>2.9</v>
@@ -981,7 +981,7 @@
         <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q3" t="n">
         <v>2.1</v>
@@ -1002,7 +1002,7 @@
         <v>1.47</v>
       </c>
       <c r="W3" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>3.75</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J4" t="n">
         <v>3.45</v>
@@ -1163,7 +1163,7 @@
         <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1178,7 +1178,7 @@
         <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
@@ -1187,10 +1187,10 @@
         <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V4" t="n">
         <v>1.31</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>4.4</v>
       </c>
       <c r="G6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H6" t="n">
         <v>2.02</v>
@@ -1689,14 +1689,14 @@
         <v>42</v>
       </c>
       <c r="BF6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BG6" t="n">
         <v>16.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
@@ -1730,28 +1730,28 @@
         <v>6.8</v>
       </c>
       <c r="G7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
         <v>4.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
         <v>1.29</v>
@@ -1769,10 +1769,10 @@
         <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="U7" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="V7" t="n">
         <v>2.62</v>
@@ -1781,7 +1781,7 @@
         <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y7" t="n">
         <v>9.4</v>
@@ -1796,7 +1796,7 @@
         <v>28</v>
       </c>
       <c r="AC7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
         <v>12</v>
@@ -1859,7 +1859,7 @@
         <v>14.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AY7" t="n">
         <v>21</v>
@@ -1868,29 +1868,29 @@
         <v>20</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BG7" t="n">
         <v>6.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>2.58</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="I8" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -1942,10 +1942,10 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>1.64</v>
+        <v>2.84</v>
       </c>
       <c r="O8" t="n">
         <v>1.44</v>
@@ -1957,134 +1957,134 @@
         <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U8" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="V8" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL8" t="n">
         <v>60</v>
       </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>75</v>
-      </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.27</v>
+        <v>8.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.34</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.26</v>
+        <v>7.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.4</v>
+        <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.37</v>
+        <v>7.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.4</v>
+        <v>14.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.3</v>
+        <v>11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.4</v>
+        <v>17</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.37</v>
+        <v>7.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.38</v>
+        <v>7.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.4</v>
+        <v>7.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>2.84</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.49</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
         <v>2.6</v>
@@ -2145,10 +2145,10 @@
         <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="R9" t="n">
         <v>1.19</v>
@@ -2157,13 +2157,13 @@
         <v>4.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
         <v>1.6</v>
@@ -2250,7 +2250,7 @@
         <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.4</v>
+        <v>3.85</v>
       </c>
       <c r="AZ9" t="n">
         <v>4.4</v>
@@ -2262,13 +2262,13 @@
         <v>4.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD9" t="n">
         <v>4.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF9" t="n">
         <v>4.7</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M10" t="n">
         <v>1.03</v>
@@ -2342,137 +2342,137 @@
         <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="T10" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="U10" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="V10" t="n">
         <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.24</v>
+        <v>2.68</v>
       </c>
       <c r="G11" t="n">
-        <v>2.44</v>
+        <v>3.05</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>2.98</v>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="J11" t="n">
         <v>2.84</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="P11" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="X11" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AA11" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AE11" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AF11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH11" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI11" t="n">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="AJ11" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AK11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AL11" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO11" t="n">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AQ11" t="n">
         <v>7.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.4</v>
+        <v>16.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.94</v>
+        <v>5.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AV11" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG11" t="n">
         <v>5.2</v>
       </c>
-      <c r="AY11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.98</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
@@ -2688,160 +2688,160 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>3.05</v>
+        <v>2.48</v>
       </c>
       <c r="H12" t="n">
-        <v>2.94</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="J12" t="n">
         <v>2.84</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="O12" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="S12" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="W12" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="X12" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="AC12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AE12" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AF12" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AI12" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AJ12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK12" t="n">
         <v>55</v>
       </c>
-      <c r="AK12" t="n">
-        <v>50</v>
-      </c>
       <c r="AL12" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AM12" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
         <v>60</v>
       </c>
       <c r="AO12" t="n">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.2</v>
+        <v>3.25</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.6</v>
+        <v>3.85</v>
       </c>
       <c r="AR12" t="n">
-        <v>16.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>12.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX12" t="n">
-        <v>14.5</v>
+        <v>3.95</v>
       </c>
       <c r="AY12" t="n">
-        <v>11.5</v>
+        <v>4.1</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19.5</v>
+        <v>4.8</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BC12" t="n">
         <v>5</v>
@@ -2856,18 +2856,18 @@
         <v>5.1</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Amiens</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ESTAC Troyes</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="G13" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9</v>
+        <v>2.46</v>
       </c>
       <c r="I13" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="J13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N13" t="n">
         <v>3.6</v>
       </c>
-      <c r="K13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.5</v>
-      </c>
       <c r="O13" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="P13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="R13" t="n">
         <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="U13" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="W13" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="X13" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE13" t="n">
         <v>28</v>
       </c>
-      <c r="AB13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>23</v>
-      </c>
       <c r="AF13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA13" t="n">
         <v>38</v>
       </c>
-      <c r="AG13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.1</v>
-      </c>
       <c r="BB13" t="n">
-        <v>2.16</v>
+        <v>50</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.16</v>
+        <v>34</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.16</v>
+        <v>46</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.18</v>
+        <v>38</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BG13" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Amiens</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>ESTAC Troyes</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.81</v>
+        <v>4.2</v>
       </c>
       <c r="G14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H14" t="n">
         <v>1.91</v>
       </c>
-      <c r="H14" t="n">
-        <v>5.2</v>
-      </c>
       <c r="I14" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L14" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="T14" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="V14" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1</v>
+        <v>1.26</v>
       </c>
       <c r="X14" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
         <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>48</v>
+        <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>190</v>
+        <v>24</v>
       </c>
       <c r="AB14" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="AF14" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AG14" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="AJ14" t="n">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="AK14" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="AL14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN14" t="n">
         <v>60</v>
       </c>
-      <c r="AM14" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>20</v>
-      </c>
       <c r="AO14" t="n">
-        <v>170</v>
+        <v>970</v>
       </c>
       <c r="AP14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF14" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>13</v>
-      </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.25</v>
+        <v>1.81</v>
       </c>
       <c r="G15" t="n">
-        <v>3.35</v>
+        <v>1.9</v>
       </c>
       <c r="H15" t="n">
-        <v>2.46</v>
+        <v>5.2</v>
       </c>
       <c r="I15" t="n">
-        <v>2.48</v>
+        <v>5.8</v>
       </c>
       <c r="J15" t="n">
         <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.6</v>
+        <v>2.72</v>
       </c>
       <c r="O15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P15" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="U15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W15" t="n">
         <v>2.1</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.42</v>
       </c>
       <c r="X15" t="n">
         <v>12.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="AA15" t="n">
-        <v>34</v>
+        <v>190</v>
       </c>
       <c r="AB15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF15" t="n">
         <v>12</v>
       </c>
-      <c r="AC15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD15" t="n">
+      <c r="AG15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>11.5</v>
       </c>
-      <c r="AE15" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>9</v>
-      </c>
       <c r="AR15" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>20</v>
+        <v>7.8</v>
       </c>
       <c r="AY15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF15" t="n">
         <v>13</v>
       </c>
-      <c r="AZ15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>34</v>
-      </c>
       <c r="BG15" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         <v>1.33</v>
       </c>
       <c r="G16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I16" t="n">
         <v>13</v>
       </c>
       <c r="J16" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K16" t="n">
         <v>5.8</v>
@@ -3497,13 +3497,13 @@
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
         <v>1.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
         <v>1.9</v>
@@ -3518,7 +3518,7 @@
         <v>2.42</v>
       </c>
       <c r="U16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V16" t="n">
         <v>1.08</v>
@@ -3557,7 +3557,7 @@
         <v>10.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI16" t="n">
         <v>230</v>
@@ -3575,7 +3575,7 @@
         <v>270</v>
       </c>
       <c r="AN16" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO16" t="n">
         <v>440</v>
@@ -3626,7 +3626,7 @@
         <v>44</v>
       </c>
       <c r="BE16" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BF16" t="n">
         <v>6</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O17" t="n">
         <v>1.36</v>
@@ -3709,7 +3709,7 @@
         <v>3.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U17" t="n">
         <v>1.83</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N19" t="n">
         <v>2.32</v>
@@ -4091,10 +4091,10 @@
         <v>2.96</v>
       </c>
       <c r="R19" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S19" t="n">
-        <v>2.96</v>
+        <v>6.2</v>
       </c>
       <c r="T19" t="n">
         <v>2.28</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
@@ -4255,13 +4255,13 @@
         <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="I20" t="n">
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K20" t="n">
         <v>950</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-02-28 22:14:55</t>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>
@@ -4551,62 +4551,838 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-01 00:35:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Tigres FC Zipaquira</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Real Cartagena</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-03-01 00:35:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X23" t="n">
         <v>10</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="Y23" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ23" t="n">
         <v>7</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="AR23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-03-01 00:35:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X24" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>290</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>220</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF24" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AS21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>65</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>42</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>2026-02-28 22:14:55</t>
+      <c r="BG24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-03-01 00:35:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Independiente (Ecu)</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-01 00:35:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH25"/>
+  <dimension ref="A1:BH27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Armenian Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Gandzasar Kapan</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FC Noah</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="G2" t="n">
-        <v>1.46</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>8.6</v>
+        <v>1.02</v>
       </c>
       <c r="I2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>3.85</v>
+        <v>1.08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>1.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.84</v>
+        <v>1.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>1.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -942,186 +942,186 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FK IMT Novi Beograd</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.66</v>
+        <v>1.43</v>
       </c>
       <c r="G3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W3" t="n">
         <v>3.15</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.43</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
       </c>
       <c r="Y3" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK3" t="n">
         <v>970</v>
       </c>
-      <c r="Z3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA3" t="n">
+      <c r="AL3" t="n">
         <v>55</v>
       </c>
-      <c r="AB3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>60</v>
-      </c>
       <c r="AM3" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>40</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO3" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.55</v>
+        <v>6.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Omonia</t>
+          <t>FK IMT Novi Beograd</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Apollon Limassol</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>2.66</v>
       </c>
       <c r="G4" t="n">
-        <v>2.18</v>
+        <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>3.75</v>
+        <v>2.66</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.89</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.1</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>1.84</v>
+        <v>1.43</v>
       </c>
       <c r="X4" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AF4" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
         <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AL4" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.5</v>
+        <v>40</v>
       </c>
       <c r="AO4" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>3.65</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.5</v>
+        <v>3.55</v>
       </c>
       <c r="AR4" t="n">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="AS4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX4" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AY4" t="n">
-        <v>7.8</v>
+        <v>3.75</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="BA4" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>18.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>16</v>
+        <v>4.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,186 +1330,186 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Manisa FK</t>
+          <t>Omonia</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>Apollon Limassol</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.2</v>
+        <v>2.02</v>
       </c>
       <c r="G5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.9</v>
       </c>
-      <c r="H5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L5" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.75</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.36</v>
+        <v>1.84</v>
       </c>
       <c r="X5" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Z5" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AA5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>32</v>
       </c>
-      <c r="AB5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>70</v>
-      </c>
       <c r="AK5" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AL5" t="n">
         <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>18.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW5" t="n">
         <v>4</v>
       </c>
-      <c r="AR5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV5" t="n">
+      <c r="AX5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD5" t="n">
         <v>3.9</v>
       </c>
-      <c r="AW5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BE5" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="BG5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Manisa FK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="H6" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="I6" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.22</v>
+        <v>1.68</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="S6" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.99</v>
+        <v>1.55</v>
       </c>
       <c r="U6" t="n">
-        <v>1.96</v>
+        <v>2.36</v>
       </c>
       <c r="V6" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="W6" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AA6" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AB6" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF6" t="n">
         <v>32</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AI6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL6" t="n">
         <v>44</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>75</v>
-      </c>
       <c r="AM6" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AN6" t="n">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="AO6" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>21</v>
+        <v>4.7</v>
       </c>
       <c r="AT6" t="n">
-        <v>12.5</v>
+        <v>4.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>3.65</v>
       </c>
       <c r="AV6" t="n">
-        <v>10</v>
+        <v>3.9</v>
       </c>
       <c r="AW6" t="n">
-        <v>21</v>
+        <v>4.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>26</v>
+        <v>4.7</v>
       </c>
       <c r="AY6" t="n">
-        <v>16.5</v>
+        <v>4.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18.5</v>
+        <v>4.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>40</v>
+        <v>4.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>80</v>
+        <v>5.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>50</v>
+        <v>4.9</v>
       </c>
       <c r="BD6" t="n">
-        <v>65</v>
+        <v>4.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>42</v>
+        <v>5.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>65</v>
+        <v>4.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>16.5</v>
+        <v>9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="G7" t="n">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="I7" t="n">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="O7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.29</v>
       </c>
-      <c r="P7" t="n">
+      <c r="S7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V7" t="n">
-        <v>2.62</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="X7" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="Z7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AA7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC7" t="n">
+      <c r="AE7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AP7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AQ7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB7" t="n">
         <v>80</v>
       </c>
-      <c r="AG7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>280</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>200</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BC7" t="n">
-        <v>4.9</v>
+        <v>50</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.8</v>
+        <v>65</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>42</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.9</v>
+        <v>65</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.6</v>
+        <v>16.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wisla Plock</t>
+          <t>Rapid Bucharest</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.58</v>
+        <v>6.8</v>
       </c>
       <c r="G8" t="n">
-        <v>2.94</v>
+        <v>8.4</v>
       </c>
       <c r="H8" t="n">
-        <v>2.98</v>
+        <v>1.51</v>
       </c>
       <c r="I8" t="n">
-        <v>3.35</v>
+        <v>1.61</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>2.84</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>2.62</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD8" t="n">
         <v>12</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AE8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>280</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>200</v>
+      </c>
+      <c r="AO8" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AP8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY8" t="n">
         <v>21</v>
       </c>
-      <c r="AA8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Feirense</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Felgueiras</t>
+          <t>Wisla Plock</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="G9" t="n">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="H9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I9" t="n">
         <v>3.35</v>
       </c>
-      <c r="I9" t="n">
-        <v>4.1</v>
-      </c>
       <c r="J9" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="P9" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="U9" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="X9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y9" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y9" t="n">
-        <v>970</v>
-      </c>
       <c r="Z9" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AA9" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="AF9" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AJ9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN9" t="n">
         <v>44</v>
       </c>
-      <c r="AK9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>42</v>
-      </c>
       <c r="AO9" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.5</v>
+        <v>8.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.65</v>
+        <v>8.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.4</v>
+        <v>17</v>
       </c>
       <c r="AS9" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.3</v>
+        <v>7.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.85</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.4</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Feirense</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>Felgueiras</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2</v>
+        <v>2.68</v>
       </c>
       <c r="H10" t="n">
         <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="N10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW10" t="n">
         <v>4.9</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="X10" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AX10" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="BB10" t="n">
-        <v>21</v>
+        <v>4.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>16.5</v>
+        <v>4.7</v>
       </c>
       <c r="BD10" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>19.5</v>
+        <v>5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,184 +2489,184 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.68</v>
+        <v>1.99</v>
       </c>
       <c r="G11" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="H11" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="I11" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="J11" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.6</v>
+        <v>1.59</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>5.3</v>
+        <v>2.48</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="U11" t="n">
-        <v>1.75</v>
+        <v>2.42</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.49</v>
+        <v>1.84</v>
       </c>
       <c r="X11" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="Y11" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="Z11" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AA11" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AD11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AF11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD11" t="n">
         <v>20</v>
       </c>
-      <c r="AG11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ11" t="n">
+      <c r="BE11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG11" t="n">
         <v>19.5</v>
       </c>
-      <c r="BA11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -2688,163 +2688,163 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.68</v>
       </c>
       <c r="G12" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="J12" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
       <c r="O12" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="P12" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="R12" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="X12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC12" t="n">
         <v>8</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AD12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV12" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS12" t="n">
+      <c r="AW12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA12" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BB12" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BC12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BD12" t="n">
         <v>5.3</v>
@@ -2856,18 +2856,18 @@
         <v>5.1</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.25</v>
+        <v>2.22</v>
       </c>
       <c r="G13" t="n">
-        <v>3.35</v>
+        <v>2.42</v>
       </c>
       <c r="H13" t="n">
-        <v>2.46</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>2.48</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="K13" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="M13" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>1.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="S13" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="V13" t="n">
-        <v>1.67</v>
+        <v>1.26</v>
       </c>
       <c r="W13" t="n">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="X13" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="AA13" t="n">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="AB13" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AC13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS13" t="n">
         <v>7.4</v>
       </c>
-      <c r="AD13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>30</v>
-      </c>
       <c r="AT13" t="n">
-        <v>11</v>
+        <v>3.55</v>
       </c>
       <c r="AU13" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="AW13" t="n">
-        <v>25</v>
+        <v>3.7</v>
       </c>
       <c r="AX13" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AY13" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16.5</v>
+        <v>6.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>38</v>
+        <v>3.75</v>
       </c>
       <c r="BB13" t="n">
-        <v>50</v>
+        <v>6.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>34</v>
+        <v>6.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>46</v>
+        <v>7.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>38</v>
+        <v>3.55</v>
       </c>
       <c r="BF13" t="n">
-        <v>34</v>
+        <v>6.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Amiens</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ESTAC Troyes</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="G14" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="H14" t="n">
-        <v>1.91</v>
+        <v>2.46</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N14" t="n">
         <v>3.6</v>
       </c>
-      <c r="K14" t="n">
+      <c r="O14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S14" t="n">
         <v>3.9</v>
       </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.55</v>
-      </c>
       <c r="T14" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="W14" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AA14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO14" t="n">
         <v>24</v>
       </c>
-      <c r="AB14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>970</v>
-      </c>
       <c r="AP14" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.14</v>
+        <v>20</v>
       </c>
       <c r="AY14" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.7</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.16</v>
+        <v>38</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.22</v>
+        <v>50</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.2</v>
+        <v>34</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.2</v>
+        <v>46</v>
       </c>
       <c r="BE14" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BG14" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Amiens</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>ESTAC Troyes</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.81</v>
+        <v>4.2</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="H15" t="n">
-        <v>5.2</v>
+        <v>1.91</v>
       </c>
       <c r="I15" t="n">
-        <v>5.8</v>
+        <v>2.04</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="M15" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="P15" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="T15" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="V15" t="n">
-        <v>1.21</v>
+        <v>1.96</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="X15" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Y15" t="n">
         <v>970</v>
       </c>
       <c r="Z15" t="n">
-        <v>48</v>
+        <v>970</v>
       </c>
       <c r="AA15" t="n">
-        <v>190</v>
+        <v>24</v>
       </c>
       <c r="AB15" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD15" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AE15" t="n">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="AF15" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AG15" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="AJ15" t="n">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="AK15" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="AL15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN15" t="n">
         <v>60</v>
       </c>
-      <c r="AM15" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>20</v>
-      </c>
       <c r="AO15" t="n">
-        <v>170</v>
+        <v>970</v>
       </c>
       <c r="AP15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF15" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>13</v>
-      </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.33</v>
+        <v>1.81</v>
       </c>
       <c r="G16" t="n">
-        <v>1.35</v>
+        <v>1.91</v>
       </c>
       <c r="H16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X16" t="n">
         <v>12.5</v>
       </c>
-      <c r="I16" t="n">
+      <c r="Y16" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF16" t="n">
         <v>13</v>
       </c>
-      <c r="J16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="X16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>720</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>270</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>230</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>440</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>95</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>34</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>6</v>
-      </c>
       <c r="BG16" t="n">
-        <v>85</v>
+        <v>5.3</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>6.8</v>
+        <v>1.35</v>
       </c>
       <c r="H17" t="n">
-        <v>1.63</v>
+        <v>12.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.64</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="U17" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="V17" t="n">
-        <v>2.52</v>
+        <v>1.08</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>3.9</v>
       </c>
       <c r="X17" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y17" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>720</v>
+      </c>
+      <c r="AB17" t="n">
         <v>7.4</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AC17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>230</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>440</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>34</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB17" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AA17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>210</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>170</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BC17" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="BE17" t="n">
-        <v>12.5</v>
+        <v>70</v>
       </c>
       <c r="BF17" t="n">
-        <v>12.5</v>
+        <v>5.9</v>
       </c>
       <c r="BG17" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="O18" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Lobos UPNFM</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="G19" t="n">
-        <v>2.42</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>2.78</v>
+        <v>1.02</v>
       </c>
       <c r="K19" t="n">
-        <v>3.15</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>2.32</v>
+        <v>1.08</v>
       </c>
       <c r="O19" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>1.41</v>
+        <v>1.08</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.96</v>
+        <v>1.27</v>
       </c>
       <c r="R19" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="S19" t="n">
-        <v>6.2</v>
+        <v>1.27</v>
       </c>
       <c r="T19" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV19" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY19" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,36 +4235,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -4273,19 +4273,19 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="O20" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="P20" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R20" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
         <v>1.01</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sportivo San Lorenzo</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N21" t="n">
-        <v>1.02</v>
+        <v>2.32</v>
       </c>
       <c r="O21" t="n">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="R21" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="S21" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,60 +4623,60 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>2.06</v>
+        <v>1.05</v>
       </c>
       <c r="I22" t="n">
-        <v>2.42</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>2.78</v>
+        <v>1.05</v>
       </c>
       <c r="K22" t="n">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="N22" t="n">
-        <v>1.42</v>
+        <v>1.08</v>
       </c>
       <c r="O22" t="n">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="P22" t="n">
-        <v>1.42</v>
+        <v>1.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.28</v>
+        <v>1.2</v>
       </c>
       <c r="R22" t="n">
         <v>1.08</v>
       </c>
       <c r="S22" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -4685,10 +4685,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4800,14 +4800,14 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Sportivo San Lorenzo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>2.74</v>
+        <v>1.02</v>
       </c>
       <c r="O23" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="P23" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="R23" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="S23" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="T23" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.99</v>
+        <v>3.55</v>
       </c>
       <c r="G24" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>4.9</v>
+        <v>2.06</v>
       </c>
       <c r="I24" t="n">
-        <v>5.5</v>
+        <v>2.42</v>
       </c>
       <c r="J24" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="K24" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>2.48</v>
+        <v>1.42</v>
       </c>
       <c r="O24" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="P24" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.72</v>
+        <v>2.28</v>
       </c>
       <c r="R24" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="S24" t="n">
-        <v>5.9</v>
+        <v>2.28</v>
       </c>
       <c r="T24" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.92</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,179 +5210,567 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="G25" t="n">
-        <v>8.6</v>
+        <v>3.6</v>
       </c>
       <c r="H25" t="n">
-        <v>1.61</v>
+        <v>2.38</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N25" t="n">
-        <v>1.72</v>
+        <v>2.74</v>
       </c>
       <c r="O25" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="P25" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="R25" t="n">
         <v>1.21</v>
       </c>
       <c r="S25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X25" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-01 02:55:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X26" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-01 02:55:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Independiente (Ecu)</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>6</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S27" t="n">
         <v>3.25</v>
       </c>
-      <c r="T25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V25" t="n">
+      <c r="T27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
         <v>2.24</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W27" t="n">
         <v>1.13</v>
       </c>
-      <c r="X25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH25" t="inlineStr">
-        <is>
-          <t>2026-03-01 00:35:27</t>
+      <c r="X27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -781,13 +781,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O2" t="n">
         <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q2" t="n">
         <v>1.2</v>
@@ -865,52 +865,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="G3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H3" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
         <v>4.7</v>
@@ -999,7 +999,7 @@
         <v>1.64</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
         <v>3.15</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>2.66</v>
       </c>
       <c r="G4" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="H4" t="n">
         <v>2.66</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J4" t="n">
         <v>2.9</v>
@@ -1196,7 +1196,7 @@
         <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
         <v>1.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
         <v>1.36</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -1602,13 +1602,13 @@
         <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>120</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AF6" t="n">
         <v>32</v>
@@ -1641,62 +1641,62 @@
         <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AR6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV6" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AW6" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.2</v>
+        <v>2.98</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="BG6" t="n">
         <v>9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -1775,10 +1775,10 @@
         <v>1.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X7" t="n">
         <v>11</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -2118,10 +2118,10 @@
         <v>2.58</v>
       </c>
       <c r="G9" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="H9" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>3.35</v>
@@ -2130,25 +2130,25 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N9" t="n">
         <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P9" t="n">
         <v>1.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R9" t="n">
         <v>1.23</v>
@@ -2157,7 +2157,7 @@
         <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
         <v>1.9</v>
@@ -2166,7 +2166,7 @@
         <v>1.43</v>
       </c>
       <c r="W9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X9" t="n">
         <v>11.5</v>
@@ -2232,7 +2232,7 @@
         <v>17</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT9" t="n">
         <v>7.8</v>
@@ -2244,7 +2244,7 @@
         <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX9" t="n">
         <v>14.5</v>
@@ -2253,32 +2253,32 @@
         <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD9" t="n">
         <v>7.6</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BE9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF9" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>7.6</v>
       </c>
       <c r="BG9" t="n">
         <v>7.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -2312,13 +2312,13 @@
         <v>2.3</v>
       </c>
       <c r="G10" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="n">
         <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J10" t="n">
         <v>2.84</v>
@@ -2327,28 +2327,28 @@
         <v>3.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M10" t="n">
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P10" t="n">
         <v>1.54</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R10" t="n">
         <v>1.19</v>
       </c>
       <c r="S10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T10" t="n">
         <v>1.92</v>
@@ -2357,7 +2357,7 @@
         <v>1.79</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W10" t="n">
         <v>1.6</v>
@@ -2375,7 +2375,7 @@
         <v>95</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC10" t="n">
         <v>8.199999999999999</v>
@@ -2420,7 +2420,7 @@
         <v>3.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AR10" t="n">
         <v>4.4</v>
@@ -2447,32 +2447,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BA10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB10" t="n">
         <v>4.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BD10" t="n">
         <v>4.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
         <v>2.2</v>
@@ -2512,13 +2512,13 @@
         <v>3.35</v>
       </c>
       <c r="I11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.9</v>
       </c>
-      <c r="J11" t="n">
-        <v>3.8</v>
-      </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.26</v>
@@ -2533,22 +2533,22 @@
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R11" t="n">
         <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="T11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U11" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V11" t="n">
         <v>1.35</v>
@@ -2575,7 +2575,7 @@
         <v>12</v>
       </c>
       <c r="AD11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE11" t="n">
         <v>44</v>
@@ -2602,16 +2602,16 @@
         <v>36</v>
       </c>
       <c r="AM11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN11" t="n">
         <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP11" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>15.5</v>
@@ -2620,10 +2620,10 @@
         <v>21</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU11" t="n">
         <v>8.4</v>
@@ -2632,10 +2632,10 @@
         <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AX11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY11" t="n">
         <v>9.6</v>
@@ -2644,13 +2644,13 @@
         <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BB11" t="n">
         <v>21</v>
       </c>
       <c r="BC11" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD11" t="n">
         <v>20</v>
@@ -2659,14 +2659,14 @@
         <v>4</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG11" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G13" t="n">
         <v>2.42</v>
@@ -2906,7 +2906,7 @@
         <v>2.84</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L13" t="n">
         <v>1.56</v>
@@ -2933,7 +2933,7 @@
         <v>6.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="U13" t="n">
         <v>1.61</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>2.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
         <v>3.45</v>
@@ -3133,7 +3133,7 @@
         <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W14" t="n">
         <v>1.42</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>4.2</v>
       </c>
       <c r="G15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I15" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>3.6</v>
@@ -3303,7 +3303,7 @@
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
         <v>1.34</v>
@@ -3327,7 +3327,7 @@
         <v>1.82</v>
       </c>
       <c r="V15" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="W15" t="n">
         <v>1.27</v>
@@ -3381,13 +3381,13 @@
         <v>140</v>
       </c>
       <c r="AN15" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AO15" t="n">
         <v>970</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AQ15" t="n">
         <v>4.5</v>
@@ -3396,53 +3396,53 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AW15" t="n">
         <v>17.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AY15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AZ15" t="n">
         <v>3.7</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BB15" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BE15" t="n">
         <v>2</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="BG15" t="n">
         <v>10.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -3476,10 +3476,10 @@
         <v>1.81</v>
       </c>
       <c r="G16" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
         <v>5.8</v>
@@ -3497,13 +3497,13 @@
         <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="O16" t="n">
         <v>1.38</v>
       </c>
       <c r="P16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q16" t="n">
         <v>2.14</v>
@@ -3518,7 +3518,7 @@
         <v>1.93</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V16" t="n">
         <v>1.21</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -3670,13 +3670,13 @@
         <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J17" t="n">
         <v>5.7</v>
@@ -3709,7 +3709,7 @@
         <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
         <v>1.67</v>
@@ -3718,7 +3718,7 @@
         <v>1.08</v>
       </c>
       <c r="W17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="X17" t="n">
         <v>16.5</v>
@@ -3730,7 +3730,7 @@
         <v>120</v>
       </c>
       <c r="AA17" t="n">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="AB17" t="n">
         <v>7.4</v>
@@ -3781,7 +3781,7 @@
         <v>30</v>
       </c>
       <c r="AR17" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="AS17" t="n">
         <v>55</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
         <v>6.8</v>
@@ -3891,13 +3891,13 @@
         <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q18" t="n">
         <v>2.06</v>
       </c>
       <c r="R18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S18" t="n">
         <v>3.8</v>
@@ -3906,7 +3906,7 @@
         <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="V18" t="n">
         <v>2.52</v>
@@ -3948,7 +3948,7 @@
         <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AJ18" t="n">
         <v>210</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="O19" t="n">
         <v>1.27</v>
@@ -4091,7 +4091,7 @@
         <v>1.27</v>
       </c>
       <c r="R19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S19" t="n">
         <v>1.27</v>
@@ -4163,52 +4163,52 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
         <v>1.01</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
@@ -4664,13 +4664,13 @@
         <v>1.08</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="P22" t="n">
         <v>1.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="R22" t="n">
         <v>1.08</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH27"/>
+  <dimension ref="A1:BH28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,22 +781,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="R2" t="n">
         <v>1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -966,16 +966,16 @@
         <v>4.7</v>
       </c>
       <c r="K3" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O3" t="n">
         <v>1.29</v>
@@ -993,13 +993,13 @@
         <v>3.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="V3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W3" t="n">
         <v>3.15</v>
@@ -1035,13 +1035,13 @@
         <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI3" t="n">
         <v>180</v>
       </c>
       <c r="AJ3" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AK3" t="n">
         <v>970</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX3" t="n">
         <v>6.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BA3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD3" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BE3" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF3" t="n">
         <v>5.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>2.66</v>
       </c>
       <c r="I4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
         <v>2.9</v>
@@ -1175,7 +1175,7 @@
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
         <v>2.1</v>
@@ -1190,7 +1190,7 @@
         <v>1.84</v>
       </c>
       <c r="U4" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="V4" t="n">
         <v>1.47</v>
@@ -1271,7 +1271,7 @@
         <v>3.15</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW4" t="n">
         <v>4.5</v>
@@ -1280,7 +1280,7 @@
         <v>4.1</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
         <v>4.1</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -1342,46 +1342,46 @@
         <v>2.02</v>
       </c>
       <c r="G5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H5" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J5" t="n">
         <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U5" t="n">
         <v>2.12</v>
@@ -1390,7 +1390,7 @@
         <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X5" t="n">
         <v>18.5</v>
@@ -1438,46 +1438,46 @@
         <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="n">
         <v>18.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP5" t="n">
         <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS5" t="n">
         <v>4.1</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU5" t="n">
         <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AW5" t="n">
         <v>4</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.6</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
         <v>4</v>
@@ -1486,10 +1486,10 @@
         <v>18.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.7</v>
+        <v>16</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BE5" t="n">
         <v>4.1</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>4.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1563,7 +1563,7 @@
         <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q6" t="n">
         <v>1.68</v>
@@ -1578,7 +1578,7 @@
         <v>1.55</v>
       </c>
       <c r="U6" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
         <v>1.78</v>
@@ -1602,7 +1602,7 @@
         <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>120</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
@@ -1677,7 +1677,7 @@
         <v>5.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BC6" t="n">
         <v>5.7</v>
@@ -1686,17 +1686,17 @@
         <v>5.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.55</v>
+        <v>5.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>9</v>
+        <v>4.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
         <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -1769,7 +1769,7 @@
         <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U7" t="n">
         <v>1.96</v>
@@ -1784,7 +1784,7 @@
         <v>11</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
         <v>11.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
         <v>8.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="I8" t="n">
         <v>1.61</v>
@@ -1951,7 +1951,7 @@
         <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
         <v>1.86</v>
@@ -1975,10 +1975,10 @@
         <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z8" t="n">
         <v>10.5</v>
@@ -2053,7 +2053,7 @@
         <v>14.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.8</v>
+        <v>50</v>
       </c>
       <c r="AY8" t="n">
         <v>21</v>
@@ -2062,16 +2062,16 @@
         <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC8" t="n">
         <v>5</v>
       </c>
-      <c r="BC8" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE8" t="n">
         <v>5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
         <v>2.88</v>
@@ -2127,7 +2127,7 @@
         <v>3.35</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K9" t="n">
         <v>3.35</v>
@@ -2163,10 +2163,10 @@
         <v>1.9</v>
       </c>
       <c r="V9" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X9" t="n">
         <v>11.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I10" t="n">
         <v>4.2</v>
@@ -2333,7 +2333,7 @@
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O10" t="n">
         <v>1.5</v>
@@ -2345,13 +2345,13 @@
         <v>2.36</v>
       </c>
       <c r="R10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
         <v>1.79</v>
@@ -2360,7 +2360,7 @@
         <v>1.32</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X10" t="n">
         <v>10.5</v>
@@ -2369,13 +2369,13 @@
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA10" t="n">
         <v>95</v>
       </c>
       <c r="AB10" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>8.199999999999999</v>
@@ -2399,7 +2399,7 @@
         <v>90</v>
       </c>
       <c r="AJ10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK10" t="n">
         <v>40</v>
@@ -2411,7 +2411,7 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO10" t="n">
         <v>90</v>
@@ -2423,7 +2423,7 @@
         <v>3.65</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS10" t="n">
         <v>5</v>
@@ -2444,35 +2444,35 @@
         <v>4</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB10" t="n">
         <v>4.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD10" t="n">
         <v>4.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -2506,10 +2506,10 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
         <v>3.8</v>
@@ -2527,7 +2527,7 @@
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>1.2</v>
@@ -2536,13 +2536,13 @@
         <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R11" t="n">
         <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="T11" t="n">
         <v>1.58</v>
@@ -2554,7 +2554,7 @@
         <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X11" t="n">
         <v>28</v>
@@ -2581,7 +2581,7 @@
         <v>44</v>
       </c>
       <c r="AF11" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG11" t="n">
         <v>13.5</v>
@@ -2632,7 +2632,7 @@
         <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AX11" t="n">
         <v>13.5</v>
@@ -2662,11 +2662,11 @@
         <v>8</v>
       </c>
       <c r="BG11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G12" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="H12" t="n">
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J12" t="n">
         <v>2.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2748,7 +2748,7 @@
         <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="X12" t="n">
         <v>8.6</v>
@@ -2775,10 +2775,10 @@
         <v>60</v>
       </c>
       <c r="AF12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH12" t="n">
         <v>27</v>
@@ -2814,7 +2814,7 @@
         <v>16.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT12" t="n">
         <v>7</v>
@@ -2826,7 +2826,7 @@
         <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX12" t="n">
         <v>14.5</v>
@@ -2838,29 +2838,29 @@
         <v>19.5</v>
       </c>
       <c r="BA12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG12" t="n">
         <v>5.3</v>
       </c>
-      <c r="BB12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>2.2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="H13" t="n">
         <v>4.2</v>
@@ -2906,10 +2906,10 @@
         <v>2.84</v>
       </c>
       <c r="K13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="M13" t="n">
         <v>1.14</v>
@@ -2918,7 +2918,7 @@
         <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="P13" t="n">
         <v>1.39</v>
@@ -2930,10 +2930,10 @@
         <v>1.13</v>
       </c>
       <c r="S13" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U13" t="n">
         <v>1.61</v>
@@ -2942,7 +2942,7 @@
         <v>1.26</v>
       </c>
       <c r="W13" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X13" t="n">
         <v>7.2</v>
@@ -2963,7 +2963,7 @@
         <v>970</v>
       </c>
       <c r="AD13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE13" t="n">
         <v>100</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Andorra CF</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.25</v>
+        <v>1.72</v>
       </c>
       <c r="G14" t="n">
-        <v>3.35</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>2.46</v>
+        <v>3.85</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>3.6</v>
+        <v>2.18</v>
       </c>
       <c r="O14" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="P14" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>3.9</v>
+        <v>2.38</v>
       </c>
       <c r="T14" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V14" t="n">
-        <v>1.67</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>46</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Amiens</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ESTAC Troyes</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="G15" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N15" t="n">
         <v>3.6</v>
       </c>
-      <c r="K15" t="n">
+      <c r="O15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S15" t="n">
         <v>3.9</v>
       </c>
-      <c r="L15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.65</v>
-      </c>
       <c r="T15" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="U15" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="W15" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="X15" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AB15" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AC15" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AE15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO15" t="n">
         <v>23</v>
       </c>
-      <c r="AF15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>970</v>
-      </c>
       <c r="AP15" t="n">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="AX15" t="n">
-        <v>2.12</v>
+        <v>20</v>
       </c>
       <c r="AY15" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.7</v>
+        <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.14</v>
+        <v>38</v>
       </c>
       <c r="BB15" t="n">
-        <v>2.2</v>
+        <v>50</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.18</v>
+        <v>34</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.18</v>
+        <v>46</v>
       </c>
       <c r="BE15" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="BF15" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BG15" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Amiens</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>ESTAC Troyes</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.81</v>
+        <v>4.3</v>
       </c>
       <c r="G16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H16" t="n">
         <v>1.9</v>
       </c>
-      <c r="H16" t="n">
-        <v>5.2</v>
-      </c>
       <c r="I16" t="n">
-        <v>5.8</v>
+        <v>1.99</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="T16" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="U16" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="V16" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="X16" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Y16" t="n">
         <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>48</v>
+        <v>970</v>
       </c>
       <c r="AA16" t="n">
-        <v>190</v>
+        <v>24</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD16" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="AF16" t="n">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="AJ16" t="n">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="AK16" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="AL16" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM16" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="AO16" t="n">
-        <v>170</v>
+        <v>970</v>
       </c>
       <c r="AP16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BC16" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD16" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.3</v>
+        <v>2.22</v>
       </c>
       <c r="BF16" t="n">
-        <v>13</v>
+        <v>1.97</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="G17" t="n">
-        <v>1.34</v>
+        <v>1.89</v>
       </c>
       <c r="H17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF17" t="n">
         <v>13</v>
       </c>
-      <c r="I17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="X17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>270</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>230</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>440</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>30</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>34</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BG17" t="n">
-        <v>55</v>
+        <v>5.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>1.33</v>
       </c>
       <c r="G18" t="n">
-        <v>6.8</v>
+        <v>1.35</v>
       </c>
       <c r="H18" t="n">
-        <v>1.63</v>
+        <v>13</v>
       </c>
       <c r="I18" t="n">
-        <v>1.64</v>
+        <v>13.5</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="P18" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="U18" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
-        <v>2.52</v>
+        <v>1.08</v>
       </c>
       <c r="W18" t="n">
-        <v>1.17</v>
+        <v>3.9</v>
       </c>
       <c r="X18" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="Z18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>430</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>34</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB18" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AA18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>210</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>170</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BC18" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="BE18" t="n">
-        <v>12.5</v>
+        <v>70</v>
       </c>
       <c r="BF18" t="n">
-        <v>12.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Genesis Huracan</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>1.65</v>
       </c>
       <c r="J19" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="O19" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="P19" t="n">
-        <v>1.08</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.27</v>
+        <v>2.04</v>
       </c>
       <c r="R19" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>1.27</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,36 +4235,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Lobos UPNFM</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -4273,22 +4273,22 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="O20" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="P20" t="n">
         <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,184 +4429,184 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>2.32</v>
+        <v>1.02</v>
       </c>
       <c r="O21" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="P21" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="R21" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="T21" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="H22" t="n">
-        <v>1.07</v>
+        <v>4.4</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J22" t="n">
-        <v>1.05</v>
+        <v>2.78</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>3.15</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="N22" t="n">
-        <v>1.08</v>
+        <v>2.32</v>
       </c>
       <c r="O22" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="P22" t="n">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.02</v>
+        <v>2.96</v>
       </c>
       <c r="R22" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="S22" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,57 +4817,57 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sportivo San Lorenzo</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="N23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1.02</v>
       </c>
-      <c r="O23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.01</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="S23" t="n">
         <v>1.01</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,36 +5011,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Sportivo San Lorenzo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5049,22 +5049,22 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="O24" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="P24" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -5073,10 +5073,10 @@
         <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,184 +5205,184 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="G25" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J25" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="K25" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>2.74</v>
+        <v>1.42</v>
       </c>
       <c r="O25" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="P25" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="R25" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="S25" t="n">
-        <v>4.9</v>
+        <v>2.28</v>
       </c>
       <c r="T25" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="X25" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -5404,373 +5404,567 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.99</v>
+        <v>3.35</v>
       </c>
       <c r="G26" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="H26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S26" t="n">
         <v>4.9</v>
       </c>
-      <c r="I26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S26" t="n">
-        <v>5.9</v>
-      </c>
       <c r="T26" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="U26" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="V26" t="n">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="W26" t="n">
-        <v>1.92</v>
+        <v>1.38</v>
       </c>
       <c r="X26" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="Y26" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="Z26" t="n">
-        <v>38</v>
+        <v>14.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>190</v>
+        <v>36</v>
       </c>
       <c r="AB26" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AD26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF26" t="n">
         <v>23</v>
       </c>
-      <c r="AE26" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>970</v>
-      </c>
       <c r="AG26" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI26" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AJ26" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="AK26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS26" t="n">
         <v>30</v>
       </c>
-      <c r="AL26" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>280</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>210</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS26" t="n">
+      <c r="AT26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>42</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE26" t="n">
         <v>12</v>
       </c>
-      <c r="AT26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BF26" t="n">
-        <v>9.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.72</v>
+        <v>24</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X27" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-01 07:36:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Ecuadorian Serie A</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>21:30:00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Manta FC</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Independiente (Ecu)</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F28" t="n">
         <v>6</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G28" t="n">
         <v>8.6</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H28" t="n">
         <v>1.6</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I28" t="n">
         <v>1.8</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J28" t="n">
         <v>3.6</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K28" t="n">
         <v>4.3</v>
       </c>
-      <c r="L27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N27" t="n">
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P28" t="n">
         <v>1.72</v>
       </c>
-      <c r="O27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R27" t="n">
+      <c r="Q28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R28" t="n">
         <v>1.21</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S28" t="n">
         <v>3.25</v>
       </c>
-      <c r="T27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V27" t="n">
+      <c r="T28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V28" t="n">
         <v>2.24</v>
       </c>
-      <c r="W27" t="n">
+      <c r="W28" t="n">
         <v>1.13</v>
       </c>
-      <c r="X27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH27" t="inlineStr">
-        <is>
-          <t>2026-03-01 05:15:02</t>
+      <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -781,13 +781,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="O2" t="n">
         <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q2" t="n">
         <v>1.22</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G3" t="n">
         <v>1.45</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>2.66</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="H4" t="n">
         <v>2.66</v>
@@ -1175,7 +1175,7 @@
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
         <v>2.1</v>
@@ -1187,7 +1187,7 @@
         <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
         <v>1.98</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>3.95</v>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
@@ -1372,13 +1372,13 @@
         <v>1.96</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R5" t="n">
         <v>1.37</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
         <v>1.74</v>
@@ -1459,13 +1459,13 @@
         <v>4.1</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU5" t="n">
         <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>11.5</v>
+        <v>3.55</v>
       </c>
       <c r="AW5" t="n">
         <v>4</v>
@@ -1474,22 +1474,22 @@
         <v>10</v>
       </c>
       <c r="AY5" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BA5" t="n">
         <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>18.5</v>
+        <v>3.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>16</v>
+        <v>3.75</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.95</v>
+        <v>25</v>
       </c>
       <c r="BE5" t="n">
         <v>4.1</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I6" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.68</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.55</v>
-      </c>
       <c r="U6" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="W6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
         <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
         <v>1.49</v>
@@ -1775,7 +1775,7 @@
         <v>1.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="W7" t="n">
         <v>1.27</v>
@@ -1826,7 +1826,7 @@
         <v>75</v>
       </c>
       <c r="AM7" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN7" t="n">
         <v>80</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>1.54</v>
       </c>
       <c r="I8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
         <v>4.1</v>
@@ -1969,7 +1969,7 @@
         <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="W8" t="n">
         <v>1.13</v>
@@ -1978,7 +1978,7 @@
         <v>17.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z8" t="n">
         <v>10.5</v>
@@ -2074,17 +2074,17 @@
         <v>5</v>
       </c>
       <c r="BE8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG8" t="n">
         <v>6.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G10" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H10" t="n">
         <v>3.4</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>2.84</v>
@@ -2339,28 +2339,28 @@
         <v>1.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="R10" t="n">
         <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
         <v>10.5</v>
@@ -2369,13 +2369,13 @@
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA10" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC10" t="n">
         <v>8.199999999999999</v>
@@ -2384,7 +2384,7 @@
         <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
         <v>970</v>
@@ -2399,7 +2399,7 @@
         <v>90</v>
       </c>
       <c r="AJ10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK10" t="n">
         <v>40</v>
@@ -2423,13 +2423,13 @@
         <v>3.65</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS10" t="n">
         <v>5</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AU10" t="n">
         <v>3.2</v>
@@ -2444,7 +2444,7 @@
         <v>4</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>3.85</v>
       </c>
       <c r="AZ10" t="n">
         <v>4.4</v>
@@ -2462,7 +2462,7 @@
         <v>4.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF10" t="n">
         <v>4.7</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="T11" t="n">
         <v>1.58</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="G12" t="n">
         <v>2.94</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I12" t="n">
         <v>3.4</v>
@@ -2712,19 +2712,19 @@
         <v>2.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.55</v>
+        <v>1.1</v>
       </c>
       <c r="P12" t="n">
         <v>1.51</v>
@@ -2733,10 +2733,10 @@
         <v>2.62</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="S12" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="T12" t="n">
         <v>2.08</v>
@@ -2754,16 +2754,16 @@
         <v>8.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA12" t="n">
         <v>65</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC12" t="n">
         <v>8</v>
@@ -2775,13 +2775,13 @@
         <v>60</v>
       </c>
       <c r="AF12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG12" t="n">
         <v>15.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
         <v>90</v>
@@ -2793,7 +2793,7 @@
         <v>50</v>
       </c>
       <c r="AL12" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM12" t="n">
         <v>220</v>
@@ -2814,7 +2814,7 @@
         <v>16.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AT12" t="n">
         <v>7</v>
@@ -2826,7 +2826,7 @@
         <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AX12" t="n">
         <v>14.5</v>
@@ -2838,29 +2838,29 @@
         <v>19.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -2906,10 +2906,10 @@
         <v>2.84</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M13" t="n">
         <v>1.14</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -3085,28 +3085,28 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="H14" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K14" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.3</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N14" t="n">
         <v>2.18</v>
@@ -3118,16 +3118,16 @@
         <v>2.16</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T14" t="n">
         <v>1.6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.58</v>
       </c>
       <c r="U14" t="n">
         <v>2.08</v>
@@ -3136,7 +3136,7 @@
         <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3193,52 +3193,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -3285,16 +3285,16 @@
         <v>3.35</v>
       </c>
       <c r="H15" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I15" t="n">
         <v>2.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L15" t="n">
         <v>1.46</v>
@@ -3330,7 +3330,7 @@
         <v>1.66</v>
       </c>
       <c r="W15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X15" t="n">
         <v>12.5</v>
@@ -3384,7 +3384,7 @@
         <v>40</v>
       </c>
       <c r="AO15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP15" t="n">
         <v>11.5</v>
@@ -3411,7 +3411,7 @@
         <v>25</v>
       </c>
       <c r="AX15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY15" t="n">
         <v>13</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -3488,10 +3488,10 @@
         <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
@@ -3518,7 +3518,7 @@
         <v>1.83</v>
       </c>
       <c r="U16" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="V16" t="n">
         <v>2</v>
@@ -3602,7 +3602,7 @@
         <v>5</v>
       </c>
       <c r="AW16" t="n">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="AX16" t="n">
         <v>7.4</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>1.8</v>
       </c>
       <c r="G17" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H17" t="n">
         <v>5.2</v>
@@ -3685,7 +3685,7 @@
         <v>3.75</v>
       </c>
       <c r="L17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
         <v>1.1</v>
@@ -3703,7 +3703,7 @@
         <v>2.44</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
         <v>4.4</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>1.33</v>
       </c>
       <c r="G18" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H18" t="n">
         <v>13</v>
@@ -3873,10 +3873,10 @@
         <v>13.5</v>
       </c>
       <c r="J18" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K18" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L18" t="n">
         <v>1.38</v>
@@ -3900,10 +3900,10 @@
         <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U18" t="n">
         <v>1.68</v>
@@ -3912,7 +3912,7 @@
         <v>1.08</v>
       </c>
       <c r="W18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="X18" t="n">
         <v>17</v>
@@ -3933,7 +3933,7 @@
         <v>12.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AE18" t="n">
         <v>260</v>
@@ -3948,28 +3948,28 @@
         <v>38</v>
       </c>
       <c r="AI18" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AJ18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AK18" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL18" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM18" t="n">
         <v>270</v>
       </c>
       <c r="AN18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO18" t="n">
         <v>430</v>
       </c>
       <c r="AP18" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>28</v>
@@ -3987,10 +3987,10 @@
         <v>11.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AW18" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AX18" t="n">
         <v>6.6</v>
@@ -4002,7 +4002,7 @@
         <v>34</v>
       </c>
       <c r="BA18" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BB18" t="n">
         <v>9.199999999999999</v>
@@ -4020,11 +4020,11 @@
         <v>5.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -4058,13 +4058,13 @@
         <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="I19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="J19" t="n">
         <v>4.2</v>
@@ -4079,31 +4079,31 @@
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q19" t="n">
         <v>2.04</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="T19" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U19" t="n">
         <v>1.85</v>
       </c>
       <c r="V19" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="W19" t="n">
         <v>1.17</v>
@@ -4112,13 +4112,13 @@
         <v>16</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z19" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AA19" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AB19" t="n">
         <v>20</v>
@@ -4136,16 +4136,16 @@
         <v>50</v>
       </c>
       <c r="AG19" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AH19" t="n">
         <v>25</v>
       </c>
       <c r="AI19" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AJ19" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AK19" t="n">
         <v>110</v>
@@ -4163,10 +4163,10 @@
         <v>12</v>
       </c>
       <c r="AP19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR19" t="n">
         <v>8.199999999999999</v>
@@ -4187,7 +4187,7 @@
         <v>16.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="AY19" t="n">
         <v>21</v>
@@ -4196,29 +4196,29 @@
         <v>21</v>
       </c>
       <c r="BA19" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="BB19" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BC19" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD19" t="n">
         <v>75</v>
       </c>
       <c r="BE19" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BF19" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BG19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
         <v>1.27</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -4640,28 +4640,28 @@
         <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H22" t="n">
         <v>4.4</v>
       </c>
       <c r="I22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
         <v>2.78</v>
       </c>
       <c r="K22" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N22" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O22" t="n">
         <v>1.65</v>
@@ -4670,7 +4670,7 @@
         <v>1.42</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="R22" t="n">
         <v>1.14</v>
@@ -4679,16 +4679,16 @@
         <v>6.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="U22" t="n">
         <v>1.64</v>
       </c>
       <c r="V22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W22" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="X22" t="n">
         <v>7.6</v>
@@ -4700,7 +4700,7 @@
         <v>32</v>
       </c>
       <c r="AA22" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB22" t="n">
         <v>6.6</v>
@@ -4742,7 +4742,7 @@
         <v>42</v>
       </c>
       <c r="AO22" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP22" t="n">
         <v>6.4</v>
@@ -4775,7 +4775,7 @@
         <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA22" t="n">
         <v>8</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -4837,13 +4837,13 @@
         <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
         <v>1.42</v>
       </c>
       <c r="O25" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="P25" t="n">
         <v>1.42</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -5416,13 +5416,13 @@
         <v>3.35</v>
       </c>
       <c r="G26" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H26" t="n">
         <v>2.38</v>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="J26" t="n">
         <v>3.25</v>
@@ -5443,7 +5443,7 @@
         <v>1.47</v>
       </c>
       <c r="P26" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q26" t="n">
         <v>2.42</v>
@@ -5461,7 +5461,7 @@
         <v>1.8</v>
       </c>
       <c r="V26" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="W26" t="n">
         <v>1.38</v>
@@ -5569,14 +5569,14 @@
         <v>12</v>
       </c>
       <c r="BF26" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="BG26" t="n">
         <v>24</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H27" t="n">
         <v>4.9</v>
@@ -5619,7 +5619,7 @@
         <v>5.5</v>
       </c>
       <c r="J27" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K27" t="n">
         <v>3.35</v>
@@ -5649,7 +5649,7 @@
         <v>5.9</v>
       </c>
       <c r="T27" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U27" t="n">
         <v>1.67</v>
@@ -5670,7 +5670,7 @@
         <v>38</v>
       </c>
       <c r="AA27" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB27" t="n">
         <v>970</v>
@@ -5712,7 +5712,7 @@
         <v>32</v>
       </c>
       <c r="AO27" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP27" t="n">
         <v>7.2</v>
@@ -5727,13 +5727,13 @@
         <v>12</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW27" t="n">
         <v>11.5</v>
@@ -5745,13 +5745,13 @@
         <v>6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BA27" t="n">
         <v>12</v>
       </c>
       <c r="BB27" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC27" t="n">
         <v>3.7</v>
@@ -5763,14 +5763,14 @@
         <v>1.73</v>
       </c>
       <c r="BF27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG27" t="n">
         <v>1.73</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G28" t="n">
         <v>8.6</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="J28" t="n">
         <v>3.6</v>
@@ -5825,7 +5825,7 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="O28" t="n">
         <v>1.37</v>
@@ -5834,7 +5834,7 @@
         <v>1.72</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R28" t="n">
         <v>1.21</v>
@@ -5849,7 +5849,7 @@
         <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="W28" t="n">
         <v>1.13</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH28"/>
+  <dimension ref="A1:BH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="J3" t="n">
         <v>4.7</v>
@@ -975,16 +975,16 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R3" t="n">
         <v>1.38</v>
@@ -1083,7 +1083,7 @@
         <v>5.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AY3" t="n">
         <v>3.85</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>3.65</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
         <v>3.5</v>
@@ -1357,7 +1357,7 @@
         <v>3.95</v>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
@@ -1369,16 +1369,16 @@
         <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
         <v>1.74</v>
@@ -1390,7 +1390,7 @@
         <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X5" t="n">
         <v>18.5</v>
@@ -1441,13 +1441,13 @@
         <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO5" t="n">
         <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>11</v>
+        <v>3.55</v>
       </c>
       <c r="AQ5" t="n">
         <v>11</v>
@@ -1459,10 +1459,10 @@
         <v>4.1</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV5" t="n">
         <v>3.55</v>
@@ -1477,22 +1477,22 @@
         <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BC5" t="n">
         <v>3.75</v>
       </c>
       <c r="BD5" t="n">
-        <v>25</v>
+        <v>3.95</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
         <v>11</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
         <v>2.12</v>
       </c>
       <c r="I6" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="J6" t="n">
         <v>3.55</v>
@@ -1557,19 +1557,19 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
         <v>2.74</v>
@@ -1578,125 +1578,125 @@
         <v>1.68</v>
       </c>
       <c r="U6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="W6" t="n">
         <v>1.36</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG6" t="n">
         <v>11</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -1754,10 +1754,10 @@
         <v>3.35</v>
       </c>
       <c r="O7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
         <v>2.22</v>
@@ -1769,16 +1769,16 @@
         <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V7" t="n">
         <v>1.94</v>
       </c>
       <c r="W7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X7" t="n">
         <v>11</v>
@@ -1802,7 +1802,7 @@
         <v>10.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF7" t="n">
         <v>32</v>
@@ -1811,7 +1811,7 @@
         <v>18</v>
       </c>
       <c r="AH7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
         <v>44</v>
@@ -1832,7 +1832,7 @@
         <v>80</v>
       </c>
       <c r="AO7" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP7" t="n">
         <v>10.5</v>
@@ -1871,26 +1871,26 @@
         <v>40</v>
       </c>
       <c r="BB7" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BC7" t="n">
         <v>50</v>
       </c>
       <c r="BD7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BE7" t="n">
         <v>42</v>
       </c>
       <c r="BF7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BG7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
         <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -2053,7 +2053,7 @@
         <v>14.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>50</v>
+        <v>4.9</v>
       </c>
       <c r="AY8" t="n">
         <v>21</v>
@@ -2068,7 +2068,7 @@
         <v>5.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BD8" t="n">
         <v>5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H9" t="n">
         <v>3</v>
@@ -2127,13 +2127,13 @@
         <v>3.35</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
         <v>3.35</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
         <v>1.11</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -2312,19 +2312,19 @@
         <v>2.32</v>
       </c>
       <c r="G10" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H10" t="n">
         <v>3.4</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J10" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L10" t="n">
         <v>1.48</v>
@@ -2342,7 +2342,7 @@
         <v>1.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="R10" t="n">
         <v>1.2</v>
@@ -2357,10 +2357,10 @@
         <v>1.81</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X10" t="n">
         <v>10.5</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>Al Batin</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="G11" t="n">
-        <v>2.22</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>1.02</v>
       </c>
       <c r="K11" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>1.24</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="P11" t="n">
-        <v>2.36</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.59</v>
+        <v>1.15</v>
       </c>
       <c r="R11" t="n">
-        <v>1.54</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>2.48</v>
+        <v>1.15</v>
       </c>
       <c r="T11" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
         <v>23</v>
       </c>
-      <c r="Z11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AQ11" t="n">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="AR11" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="AT11" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="AW11" t="n">
-        <v>3.85</v>
+        <v>50</v>
       </c>
       <c r="AX11" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="BA11" t="n">
-        <v>3.9</v>
+        <v>50</v>
       </c>
       <c r="BB11" t="n">
-        <v>21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC11" t="n">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BE11" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="BF11" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>Al-Arabi Al-Saudi</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Jeddah Club</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="G12" t="n">
-        <v>2.94</v>
+        <v>3.95</v>
       </c>
       <c r="H12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I12" t="n">
         <v>3.1</v>
       </c>
-      <c r="I12" t="n">
-        <v>3.4</v>
-      </c>
       <c r="J12" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K12" t="n">
-        <v>2.94</v>
+        <v>5.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="O12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="P12" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="R12" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5</v>
+        <v>1.87</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="W12" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="X12" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Al Jabalain</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Al-Zulfi SC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="G13" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="J13" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="K13" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>2.28</v>
+        <v>1.74</v>
       </c>
       <c r="O13" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="P13" t="n">
-        <v>1.39</v>
+        <v>1.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>6.6</v>
+        <v>1.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="X13" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,72 +3071,72 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Al-Adalh</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Andorra CF</t>
+          <t>Al Faisaly ( KSA )</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="G14" t="n">
-        <v>1.97</v>
+        <v>6.2</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>1.57</v>
       </c>
       <c r="I14" t="n">
-        <v>5.6</v>
+        <v>2.14</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="O14" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.21</v>
+        <v>1.87</v>
       </c>
       <c r="W14" t="n">
-        <v>2.02</v>
+        <v>1.19</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>3.35</v>
+        <v>2.22</v>
       </c>
       <c r="H15" t="n">
-        <v>2.46</v>
+        <v>3.3</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="K15" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="M15" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>1.59</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="S15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X15" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA15" t="n">
         <v>3.9</v>
       </c>
-      <c r="T15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="BB15" t="n">
         <v>21</v>
       </c>
-      <c r="AG15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH15" t="n">
+      <c r="BC15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG15" t="n">
         <v>18.5</v>
       </c>
-      <c r="AI15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>34</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>20</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Amiens</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ESTAC Troyes</t>
+          <t>Andorra CF</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.3</v>
+        <v>1.75</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.99</v>
+        <v>5.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>2.18</v>
       </c>
       <c r="O16" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>3.65</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="U16" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="V16" t="n">
-        <v>2</v>
+        <v>1.22</v>
       </c>
       <c r="W16" t="n">
-        <v>1.27</v>
+        <v>2.04</v>
       </c>
       <c r="X16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>1.88</v>
+        <v>2.34</v>
       </c>
       <c r="H17" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="I17" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="K17" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="N17" t="n">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
       <c r="O17" t="n">
-        <v>1.43</v>
+        <v>1.69</v>
       </c>
       <c r="P17" t="n">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="S17" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="U17" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="V17" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="W17" t="n">
-        <v>2.12</v>
+        <v>1.74</v>
       </c>
       <c r="X17" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="Y17" t="n">
         <v>970</v>
       </c>
       <c r="Z17" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AA17" t="n">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="AB17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD17" t="n">
         <v>7.6</v>
       </c>
-      <c r="AC17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BE17" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.33</v>
+        <v>2.68</v>
       </c>
       <c r="G18" t="n">
-        <v>1.34</v>
+        <v>3.15</v>
       </c>
       <c r="H18" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>13.5</v>
+        <v>3.65</v>
       </c>
       <c r="J18" t="n">
-        <v>5.7</v>
+        <v>2.82</v>
       </c>
       <c r="K18" t="n">
-        <v>5.8</v>
+        <v>2.94</v>
       </c>
       <c r="L18" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>2.34</v>
       </c>
       <c r="O18" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.87</v>
+        <v>2.58</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="V18" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>3.95</v>
+        <v>1.49</v>
       </c>
       <c r="X18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD18" t="n">
         <v>17</v>
       </c>
-      <c r="Y18" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="AE18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>7.6</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AR18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV18" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF18" t="n">
+      <c r="AW18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE18" t="n">
         <v>7</v>
       </c>
-      <c r="AG18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>230</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>430</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>34</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>70</v>
-      </c>
       <c r="BF18" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>65</v>
+        <v>6.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Amiens</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>ESTAC Troyes</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="G19" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="H19" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="I19" t="n">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P19" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
         <v>3.65</v>
       </c>
       <c r="T19" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="U19" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="V19" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="X19" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Y19" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX19" t="n">
         <v>7.6</v>
       </c>
-      <c r="Z19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>210</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>160</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>38</v>
-      </c>
       <c r="AY19" t="n">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="BA19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>9</v>
+        <v>2.22</v>
       </c>
       <c r="BC19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>75</v>
+        <v>3.35</v>
       </c>
       <c r="BE19" t="n">
-        <v>9</v>
+        <v>2.24</v>
       </c>
       <c r="BF19" t="n">
-        <v>9</v>
+        <v>1.99</v>
       </c>
       <c r="BG19" t="n">
-        <v>10</v>
+        <v>5.9</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Genesis Huracan</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>1.88</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1.02</v>
+        <v>3.4</v>
       </c>
       <c r="K20" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>2.88</v>
       </c>
       <c r="O20" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="P20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S20" t="n">
-        <v>1.27</v>
+        <v>4.4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>1.02</v>
+        <v>3.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="G22" t="n">
-        <v>2.38</v>
+        <v>1.34</v>
       </c>
       <c r="H22" t="n">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="J22" t="n">
-        <v>2.78</v>
+        <v>5.7</v>
       </c>
       <c r="K22" t="n">
-        <v>3.05</v>
+        <v>5.8</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M22" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>2.34</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="P22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.42</v>
       </c>
-      <c r="Q22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.14</v>
-      </c>
       <c r="S22" t="n">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
         <v>2.38</v>
       </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="V22" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="W22" t="n">
-        <v>1.74</v>
+        <v>3.9</v>
       </c>
       <c r="X22" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB22" t="n">
         <v>7.6</v>
       </c>
-      <c r="Y22" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>430</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX22" t="n">
         <v>6.6</v>
       </c>
-      <c r="AC22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN22" t="n">
+      <c r="AY22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>34</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD22" t="n">
         <v>42</v>
       </c>
-      <c r="AO22" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BE22" t="n">
-        <v>8.199999999999999</v>
+        <v>220</v>
       </c>
       <c r="BF22" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BG22" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="H23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M23" t="n">
         <v>1.07</v>
       </c>
-      <c r="I23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.2</v>
-      </c>
       <c r="N23" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="P23" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="R23" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,36 +5011,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sportivo San Lorenzo</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Lobos UPNFM</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5049,22 +5049,22 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="P24" t="n">
         <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="R24" t="n">
         <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,36 +5205,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5243,22 +5243,22 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.42</v>
+        <v>1.03</v>
       </c>
       <c r="O25" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="P25" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="R25" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -5267,10 +5267,10 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -5399,184 +5399,184 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.35</v>
+        <v>2.24</v>
       </c>
       <c r="G26" t="n">
-        <v>3.55</v>
+        <v>2.38</v>
       </c>
       <c r="H26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N26" t="n">
         <v>2.38</v>
       </c>
-      <c r="I26" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.74</v>
-      </c>
       <c r="O26" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="P26" t="n">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="R26" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="S26" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="U26" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="V26" t="n">
-        <v>1.68</v>
+        <v>1.26</v>
       </c>
       <c r="W26" t="n">
-        <v>1.38</v>
+        <v>1.73</v>
       </c>
       <c r="X26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Z26" t="n">
-        <v>14.5</v>
+        <v>50</v>
       </c>
       <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD26" t="n">
         <v>36</v>
       </c>
-      <c r="AB26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>42</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>11</v>
-      </c>
       <c r="BE26" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="BG26" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -5593,378 +5593,1154 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="G27" t="n">
-        <v>2.08</v>
+        <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>4.9</v>
+        <v>1.07</v>
       </c>
       <c r="I27" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="K27" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2.48</v>
+        <v>1.24</v>
       </c>
       <c r="O27" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="P27" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.72</v>
+        <v>1.02</v>
       </c>
       <c r="R27" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="S27" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="U27" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sportivo San Lorenzo</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-01 12:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Tigres FC Zipaquira</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Real Cartagena</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-01 12:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-01 12:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>48</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>25</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-01 12:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Ecuadorian Serie A</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>21:30:00</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Manta FC</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Independiente (Ecu)</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F32" t="n">
         <v>6.2</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G32" t="n">
         <v>8.6</v>
       </c>
-      <c r="H28" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="I28" t="n">
+      <c r="H32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I32" t="n">
         <v>1.74</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J32" t="n">
         <v>3.6</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K32" t="n">
         <v>4.3</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="O28" t="n">
+      <c r="L32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O32" t="n">
         <v>1.37</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P32" t="n">
         <v>1.72</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q32" t="n">
         <v>2.1</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R32" t="n">
         <v>1.21</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S32" t="n">
         <v>3.25</v>
       </c>
-      <c r="T28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V28" t="n">
+      <c r="T32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V32" t="n">
         <v>2.34</v>
       </c>
-      <c r="W28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH28" t="inlineStr">
-        <is>
-          <t>2026-03-01 09:55:59</t>
+      <c r="W32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -784,13 +784,13 @@
         <v>1.09</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P2" t="n">
         <v>1.09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="R2" t="n">
         <v>1.08</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G3" t="n">
         <v>1.42</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.45</v>
       </c>
       <c r="H3" t="n">
         <v>9.800000000000001</v>
@@ -981,7 +981,7 @@
         <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>1.86</v>
@@ -993,7 +993,7 @@
         <v>3.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
         <v>1.74</v>
@@ -1002,13 +1002,13 @@
         <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="Y3" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="Z3" t="n">
         <v>110</v>
@@ -1023,7 +1023,7 @@
         <v>13</v>
       </c>
       <c r="AD3" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
@@ -1035,16 +1035,16 @@
         <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AI3" t="n">
         <v>180</v>
       </c>
       <c r="AJ3" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AK3" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AL3" t="n">
         <v>55</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>2.66</v>
       </c>
       <c r="G4" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="H4" t="n">
         <v>2.66</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J4" t="n">
         <v>2.9</v>
@@ -1196,40 +1196,40 @@
         <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="AA4" t="n">
         <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AC4" t="n">
         <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AE4" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="AI4" t="n">
         <v>60</v>
@@ -1238,7 +1238,7 @@
         <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AL4" t="n">
         <v>60</v>
@@ -1247,10 +1247,10 @@
         <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AO4" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AP4" t="n">
         <v>3.65</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G5" t="n">
         <v>2.2</v>
@@ -1354,7 +1354,7 @@
         <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
         <v>1.32</v>
@@ -1381,7 +1381,7 @@
         <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U5" t="n">
         <v>2.12</v>
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="AA5" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB5" t="n">
         <v>12</v>
@@ -1468,7 +1468,7 @@
         <v>3.55</v>
       </c>
       <c r="AW5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX5" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
         <v>3.75</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE5" t="n">
         <v>4.2</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -1539,16 +1539,16 @@
         <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
         <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.31</v>
@@ -1563,7 +1563,7 @@
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
         <v>1.71</v>
@@ -1581,64 +1581,64 @@
         <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W6" t="n">
         <v>1.36</v>
       </c>
       <c r="X6" t="n">
-        <v>20</v>
+        <v>980</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="Z6" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AA6" t="n">
-        <v>29</v>
+        <v>980</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AE6" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AF6" t="n">
-        <v>27</v>
+        <v>980</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AH6" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AI6" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AJ6" t="n">
         <v>70</v>
       </c>
       <c r="AK6" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AL6" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AM6" t="n">
         <v>90</v>
       </c>
       <c r="AN6" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AO6" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AP6" t="n">
         <v>3.7</v>
@@ -1677,7 +1677,7 @@
         <v>1.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BC6" t="n">
         <v>1.69</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
         <v>2.02</v>
       </c>
-      <c r="I7" t="n">
-        <v>2.06</v>
-      </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
         <v>3.55</v>
@@ -1775,10 +1775,10 @@
         <v>1.97</v>
       </c>
       <c r="V7" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="W7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X7" t="n">
         <v>11</v>
@@ -1796,7 +1796,7 @@
         <v>14</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD7" t="n">
         <v>10.5</v>
@@ -1832,7 +1832,7 @@
         <v>80</v>
       </c>
       <c r="AO7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP7" t="n">
         <v>10.5</v>
@@ -1859,10 +1859,10 @@
         <v>21</v>
       </c>
       <c r="AX7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AY7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AZ7" t="n">
         <v>18.5</v>
@@ -1871,7 +1871,7 @@
         <v>40</v>
       </c>
       <c r="BB7" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="BC7" t="n">
         <v>50</v>
@@ -1883,14 +1883,14 @@
         <v>42</v>
       </c>
       <c r="BF7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BG7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -1921,25 +1921,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="G8" t="n">
         <v>8.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
         <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -1957,19 +1957,19 @@
         <v>1.86</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
         <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="W8" t="n">
         <v>1.13</v>
@@ -1999,7 +1999,7 @@
         <v>20</v>
       </c>
       <c r="AF8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AG8" t="n">
         <v>32</v>
@@ -2008,13 +2008,13 @@
         <v>29</v>
       </c>
       <c r="AI8" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AJ8" t="n">
         <v>280</v>
       </c>
       <c r="AK8" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AL8" t="n">
         <v>130</v>
@@ -2023,7 +2023,7 @@
         <v>180</v>
       </c>
       <c r="AN8" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AO8" t="n">
         <v>10.5</v>
@@ -2062,16 +2062,16 @@
         <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC8" t="n">
         <v>5.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE8" t="n">
         <v>5.1</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>3.35</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K9" t="n">
         <v>3.35</v>
@@ -2181,7 +2181,7 @@
         <v>60</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC9" t="n">
         <v>7.4</v>
@@ -2190,7 +2190,7 @@
         <v>14.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AF9" t="n">
         <v>17.5</v>
@@ -2205,7 +2205,7 @@
         <v>65</v>
       </c>
       <c r="AJ9" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AK9" t="n">
         <v>38</v>
@@ -2217,10 +2217,10 @@
         <v>160</v>
       </c>
       <c r="AN9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP9" t="n">
         <v>8.6</v>
@@ -2232,7 +2232,7 @@
         <v>17</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT9" t="n">
         <v>7.8</v>
@@ -2244,7 +2244,7 @@
         <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX9" t="n">
         <v>14.5</v>
@@ -2256,29 +2256,29 @@
         <v>17.5</v>
       </c>
       <c r="BA9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD9" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BE9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF9" t="n">
         <v>7.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -2312,13 +2312,13 @@
         <v>2.32</v>
       </c>
       <c r="G10" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
         <v>3.4</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J10" t="n">
         <v>2.94</v>
@@ -2342,7 +2342,7 @@
         <v>1.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="R10" t="n">
         <v>1.2</v>
@@ -2351,25 +2351,25 @@
         <v>4.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U10" t="n">
         <v>1.81</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X10" t="n">
         <v>10.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="Z10" t="n">
-        <v>28</v>
+        <v>980</v>
       </c>
       <c r="AA10" t="n">
         <v>90</v>
@@ -2381,28 +2381,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AE10" t="n">
         <v>65</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AH10" t="n">
-        <v>26</v>
+        <v>980</v>
       </c>
       <c r="AI10" t="n">
         <v>90</v>
       </c>
       <c r="AJ10" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AK10" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AL10" t="n">
         <v>70</v>
@@ -2411,7 +2411,7 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AO10" t="n">
         <v>90</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
@@ -2527,13 +2527,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
         <v>1.15</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
         <v>1.15</v>
@@ -2611,52 +2611,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="G12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF12" t="n">
         <v>3.95</v>
       </c>
-      <c r="H12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -2891,58 +2891,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="G13" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H13" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I13" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="J13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N13" t="n">
         <v>3.1</v>
       </c>
-      <c r="K13" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1.74</v>
-      </c>
       <c r="O13" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="P13" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="Q13" t="n">
         <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
         <v>1.8</v>
       </c>
-      <c r="T13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -3085,58 +3085,58 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="I14" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V14" t="n">
         <v>2.02</v>
       </c>
-      <c r="O14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.87</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
         <v>1.54</v>
       </c>
       <c r="S15" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="T15" t="n">
         <v>1.58</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -3473,43 +3473,43 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="H16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
         <v>4.2</v>
       </c>
-      <c r="I16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>2.18</v>
+        <v>4.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
         <v>2.56</v>
@@ -3518,55 +3518,55 @@
         <v>1.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="V16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W16" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL16" t="n">
         <v>1000</v>
@@ -3575,68 +3575,68 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="G17" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
         <v>2.84</v>
       </c>
       <c r="K17" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L17" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="M17" t="n">
         <v>1.14</v>
@@ -3715,52 +3715,52 @@
         <v>1.61</v>
       </c>
       <c r="V17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X17" t="n">
         <v>7.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="Z17" t="n">
-        <v>29</v>
+        <v>980</v>
       </c>
       <c r="AA17" t="n">
         <v>120</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AD17" t="n">
-        <v>24</v>
+        <v>980</v>
       </c>
       <c r="AE17" t="n">
         <v>100</v>
       </c>
       <c r="AF17" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AH17" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AI17" t="n">
         <v>180</v>
       </c>
       <c r="AJ17" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AK17" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AL17" t="n">
         <v>100</v>
@@ -3769,68 +3769,68 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AO17" t="n">
         <v>160</v>
       </c>
       <c r="AP17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS17" t="n">
         <v>3.85</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AT17" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="AU17" t="n">
         <v>6.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AX17" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AZ17" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="BB17" t="n">
         <v>6.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE17" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -3864,13 +3864,13 @@
         <v>2.68</v>
       </c>
       <c r="G18" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I18" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="J18" t="n">
         <v>2.82</v>
@@ -3879,16 +3879,16 @@
         <v>2.94</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M18" t="n">
         <v>1.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="O18" t="n">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="P18" t="n">
         <v>1.5</v>
@@ -3912,7 +3912,7 @@
         <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="X18" t="n">
         <v>8.6</v>
@@ -3930,13 +3930,13 @@
         <v>8.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF18" t="n">
         <v>19</v>
@@ -3954,7 +3954,7 @@
         <v>55</v>
       </c>
       <c r="AK18" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AL18" t="n">
         <v>75</v>
@@ -3978,7 +3978,7 @@
         <v>16.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
         <v>7</v>
@@ -3990,7 +3990,7 @@
         <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
         <v>14.5</v>
@@ -4002,29 +4002,29 @@
         <v>19.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BC18" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF18" t="n">
         <v>7</v>
       </c>
-      <c r="BF18" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG18" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -4103,46 +4103,46 @@
         <v>1.96</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W19" t="n">
         <v>1.27</v>
       </c>
       <c r="X19" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="Y19" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="Z19" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AA19" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AC19" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AD19" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AE19" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AF19" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AG19" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>980</v>
       </c>
       <c r="AI19" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AJ19" t="n">
         <v>90</v>
@@ -4160,7 +4160,7 @@
         <v>70</v>
       </c>
       <c r="AO19" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AP19" t="n">
         <v>5.8</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G20" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I20" t="n">
         <v>6.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K20" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L20" t="n">
         <v>1.44</v>
@@ -4291,7 +4291,7 @@
         <v>4.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="U20" t="n">
         <v>1.72</v>
@@ -4300,16 +4300,16 @@
         <v>1.21</v>
       </c>
       <c r="W20" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X20" t="n">
         <v>12</v>
       </c>
       <c r="Y20" t="n">
-        <v>17.5</v>
+        <v>980</v>
       </c>
       <c r="Z20" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AA20" t="n">
         <v>190</v>
@@ -4321,7 +4321,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>980</v>
       </c>
       <c r="AE20" t="n">
         <v>110</v>
@@ -4330,19 +4330,19 @@
         <v>11.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AH20" t="n">
-        <v>28</v>
+        <v>980</v>
       </c>
       <c r="AI20" t="n">
         <v>120</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24</v>
+        <v>980</v>
       </c>
       <c r="AK20" t="n">
-        <v>27</v>
+        <v>980</v>
       </c>
       <c r="AL20" t="n">
         <v>55</v>
@@ -4351,34 +4351,34 @@
         <v>200</v>
       </c>
       <c r="AN20" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AO20" t="n">
         <v>170</v>
       </c>
       <c r="AP20" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AQ20" t="n">
         <v>11.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT20" t="n">
         <v>5.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX20" t="n">
         <v>8.6</v>
@@ -4387,32 +4387,32 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB20" t="n">
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G21" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H21" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="J21" t="n">
         <v>3.4</v>
@@ -4473,10 +4473,10 @@
         <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R21" t="n">
         <v>1.32</v>
@@ -4491,16 +4491,16 @@
         <v>2.12</v>
       </c>
       <c r="V21" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W21" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X21" t="n">
         <v>12.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z21" t="n">
         <v>15</v>
@@ -4527,7 +4527,7 @@
         <v>14</v>
       </c>
       <c r="AH21" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
         <v>44</v>
@@ -4569,7 +4569,7 @@
         <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW21" t="n">
         <v>25</v>
@@ -4578,7 +4578,7 @@
         <v>19.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ21" t="n">
         <v>16.5</v>
@@ -4599,14 +4599,14 @@
         <v>38</v>
       </c>
       <c r="BF21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BG21" t="n">
         <v>20</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
         <v>1.29</v>
@@ -4670,10 +4670,10 @@
         <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
         <v>3.25</v>
@@ -4691,7 +4691,7 @@
         <v>3.9</v>
       </c>
       <c r="X22" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y22" t="n">
         <v>34</v>
@@ -4700,7 +4700,7 @@
         <v>120</v>
       </c>
       <c r="AA22" t="n">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="AB22" t="n">
         <v>7.6</v>
@@ -4727,7 +4727,7 @@
         <v>220</v>
       </c>
       <c r="AJ22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AK22" t="n">
         <v>15</v>
@@ -4742,10 +4742,10 @@
         <v>6</v>
       </c>
       <c r="AO22" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AP22" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>28</v>
@@ -4763,10 +4763,10 @@
         <v>11.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AW22" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX22" t="n">
         <v>6.6</v>
@@ -4781,10 +4781,10 @@
         <v>65</v>
       </c>
       <c r="BB22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD22" t="n">
         <v>42</v>
@@ -4796,11 +4796,11 @@
         <v>5.8</v>
       </c>
       <c r="BG22" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -4855,19 +4855,19 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O23" t="n">
         <v>1.36</v>
       </c>
       <c r="P23" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
         <v>3.75</v>
@@ -4885,55 +4885,55 @@
         <v>1.18</v>
       </c>
       <c r="X23" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC23" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AA23" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AD23" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF23" t="n">
         <v>50</v>
       </c>
       <c r="AG23" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AH23" t="n">
         <v>25</v>
       </c>
       <c r="AI23" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AJ23" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AK23" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AL23" t="n">
         <v>120</v>
       </c>
       <c r="AM23" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AN23" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AO23" t="n">
         <v>11.5</v>
@@ -4942,59 +4942,59 @@
         <v>12</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR23" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AS23" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW23" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX23" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BB23" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BD23" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="BG23" t="n">
         <v>10</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -5049,13 +5049,13 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O24" t="n">
         <v>1.27</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q24" t="n">
         <v>1.27</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
         <v>6.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U26" t="n">
         <v>1.65</v>
@@ -5467,13 +5467,13 @@
         <v>1.73</v>
       </c>
       <c r="X26" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Y26" t="n">
         <v>11</v>
       </c>
       <c r="Z26" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
@@ -5485,19 +5485,19 @@
         <v>7</v>
       </c>
       <c r="AD26" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE26" t="n">
         <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG26" t="n">
         <v>13.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
@@ -5515,7 +5515,7 @@
         <v>320</v>
       </c>
       <c r="AN26" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
@@ -5527,13 +5527,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR26" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS26" t="n">
         <v>40</v>
       </c>
       <c r="AT26" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU26" t="n">
         <v>6.2</v>
@@ -5542,7 +5542,7 @@
         <v>18</v>
       </c>
       <c r="AW26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX26" t="n">
         <v>10.5</v>
@@ -5557,13 +5557,13 @@
         <v>44</v>
       </c>
       <c r="BB26" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC26" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BD26" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BE26" t="n">
         <v>12.5</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -5607,40 +5607,40 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H27" t="n">
-        <v>1.07</v>
+        <v>3.2</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
-        <v>1.03</v>
+        <v>2.6</v>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="N27" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="O27" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.02</v>
+        <v>3.8</v>
       </c>
       <c r="R27" t="n">
         <v>1.1</v>
@@ -5649,49 +5649,49 @@
         <v>10</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
@@ -5715,62 +5715,62 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -5825,10 +5825,10 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="O28" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P28" t="n">
         <v>1.24</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
         <v>3.35</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M30" t="n">
         <v>1.13</v>
@@ -6225,10 +6225,10 @@
         <v>2.74</v>
       </c>
       <c r="R30" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S30" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="T30" t="n">
         <v>2.28</v>
@@ -6249,7 +6249,7 @@
         <v>14.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA30" t="n">
         <v>150</v>
@@ -6291,25 +6291,25 @@
         <v>280</v>
       </c>
       <c r="AN30" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ30" t="n">
         <v>10</v>
       </c>
       <c r="AR30" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AS30" t="n">
         <v>40</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU30" t="n">
         <v>6.6</v>
@@ -6318,7 +6318,7 @@
         <v>17</v>
       </c>
       <c r="AW30" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AX30" t="n">
         <v>8.6</v>
@@ -6339,7 +6339,7 @@
         <v>23</v>
       </c>
       <c r="BD30" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BE30" t="n">
         <v>48</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -6386,19 +6386,19 @@
         <v>3.3</v>
       </c>
       <c r="G31" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H31" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I31" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="J31" t="n">
         <v>3.3</v>
       </c>
       <c r="K31" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L31" t="n">
         <v>1.53</v>
@@ -6407,13 +6407,13 @@
         <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O31" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P31" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q31" t="n">
         <v>2.44</v>
@@ -6449,7 +6449,7 @@
         <v>36</v>
       </c>
       <c r="AB31" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC31" t="n">
         <v>7.6</v>
@@ -6506,7 +6506,7 @@
         <v>9</v>
       </c>
       <c r="AU31" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV31" t="n">
         <v>11</v>
@@ -6521,32 +6521,32 @@
         <v>13.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA31" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BB31" t="n">
         <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BD31" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BE31" t="n">
         <v>46</v>
       </c>
       <c r="BF31" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BG31" t="n">
         <v>25</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -6580,10 +6580,10 @@
         <v>6.2</v>
       </c>
       <c r="G32" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="H32" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I32" t="n">
         <v>1.74</v>
@@ -6595,34 +6595,34 @@
         <v>4.3</v>
       </c>
       <c r="L32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O32" t="n">
         <v>1.38</v>
       </c>
-      <c r="M32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>1.73</v>
       </c>
-      <c r="O32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.72</v>
-      </c>
       <c r="Q32" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R32" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="S32" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V32" t="n">
         <v>2.34</v>
@@ -6631,116 +6631,116 @@
         <v>1.15</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN32" t="n">
         <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -757,61 +757,61 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.02</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
         <v>1.09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="R2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S2" t="n">
         <v>1.22</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y2" t="n">
         <v>1000</v>
@@ -868,59 +868,59 @@
         <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="J3" t="n">
         <v>4.7</v>
@@ -999,7 +999,7 @@
         <v>1.74</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
         <v>3.35</v>
@@ -1044,77 +1044,77 @@
         <v>980</v>
       </c>
       <c r="AK3" t="n">
-        <v>980</v>
+        <v>18.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT3" t="n">
         <v>6.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX3" t="n">
         <v>6.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF3" t="n">
         <v>5.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.66</v>
+        <v>2.28</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="H4" t="n">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="I4" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K4" t="n">
         <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1175,7 +1175,7 @@
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
         <v>2.1</v>
@@ -1184,34 +1184,34 @@
         <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U4" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V4" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="X4" t="n">
         <v>980</v>
       </c>
       <c r="Y4" t="n">
-        <v>980</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>980</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
         <v>8.6</v>
@@ -1220,73 +1220,73 @@
         <v>980</v>
       </c>
       <c r="AE4" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
         <v>980</v>
       </c>
       <c r="AG4" t="n">
-        <v>980</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
         <v>980</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL4" t="n">
         <v>55</v>
       </c>
-      <c r="AK4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>60</v>
-      </c>
       <c r="AM4" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN4" t="n">
         <v>980</v>
       </c>
       <c r="AO4" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB4" t="n">
         <v>4.6</v>
@@ -1295,20 +1295,20 @@
         <v>4.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF4" t="n">
         <v>4.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>2.2</v>
       </c>
       <c r="H5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
         <v>4.2</v>
@@ -1366,13 +1366,13 @@
         <v>3.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="P5" t="n">
         <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R5" t="n">
         <v>1.38</v>
@@ -1384,7 +1384,7 @@
         <v>1.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
         <v>1.31</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
         <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R6" t="n">
         <v>1.44</v>
@@ -1641,7 +1641,7 @@
         <v>980</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="AQ6" t="n">
         <v>5.2</v>
@@ -1650,22 +1650,22 @@
         <v>5.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="AT6" t="n">
         <v>5.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AV6" t="n">
         <v>5.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.46</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
         <v>6</v>
@@ -1674,16 +1674,16 @@
         <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.69</v>
+        <v>2.04</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.05</v>
+        <v>7.8</v>
       </c>
       <c r="BE6" t="n">
         <v>8.6</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G7" t="n">
         <v>4.7</v>
@@ -1745,109 +1745,109 @@
         <v>3.55</v>
       </c>
       <c r="L7" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="T7" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="V7" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="W7" t="n">
         <v>1.27</v>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA7" t="n">
         <v>24</v>
       </c>
       <c r="AB7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
         <v>10.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF7" t="n">
         <v>32</v>
       </c>
       <c r="AG7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AJ7" t="n">
         <v>110</v>
       </c>
       <c r="AK7" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL7" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AM7" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AN7" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AO7" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AP7" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
         <v>21</v>
       </c>
       <c r="AT7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU7" t="n">
         <v>7.2</v>
@@ -1856,41 +1856,41 @@
         <v>10</v>
       </c>
       <c r="AW7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>21</v>
       </c>
-      <c r="AX7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BA7" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB7" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="BC7" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BD7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="BE7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BF7" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="BG7" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -1927,58 +1927,58 @@
         <v>8.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="I8" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.32</v>
       </c>
-      <c r="M8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.37</v>
-      </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="V8" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="W8" t="n">
         <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z8" t="n">
         <v>10.5</v>
@@ -1987,7 +1987,7 @@
         <v>17</v>
       </c>
       <c r="AB8" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AC8" t="n">
         <v>10.5</v>
@@ -1999,16 +1999,16 @@
         <v>20</v>
       </c>
       <c r="AF8" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG8" t="n">
         <v>32</v>
       </c>
       <c r="AH8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI8" t="n">
-        <v>980</v>
+        <v>50</v>
       </c>
       <c r="AJ8" t="n">
         <v>280</v>
@@ -2023,68 +2023,68 @@
         <v>180</v>
       </c>
       <c r="AN8" t="n">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="AO8" t="n">
         <v>10.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS8" t="n">
         <v>12</v>
       </c>
       <c r="AT8" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AU8" t="n">
         <v>8.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW8" t="n">
         <v>14.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ8" t="n">
         <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G9" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="H9" t="n">
         <v>3</v>
@@ -2139,7 +2139,7 @@
         <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O9" t="n">
         <v>1.46</v>
@@ -2148,13 +2148,13 @@
         <v>1.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R9" t="n">
         <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T9" t="n">
         <v>1.94</v>
@@ -2166,10 +2166,10 @@
         <v>1.45</v>
       </c>
       <c r="W9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y9" t="n">
         <v>10.5</v>
@@ -2181,7 +2181,7 @@
         <v>60</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC9" t="n">
         <v>7.4</v>
@@ -2193,7 +2193,7 @@
         <v>980</v>
       </c>
       <c r="AF9" t="n">
-        <v>17.5</v>
+        <v>980</v>
       </c>
       <c r="AG9" t="n">
         <v>13</v>
@@ -2232,7 +2232,7 @@
         <v>17</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.8</v>
+        <v>46</v>
       </c>
       <c r="AT9" t="n">
         <v>7.8</v>
@@ -2244,7 +2244,7 @@
         <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="AX9" t="n">
         <v>14.5</v>
@@ -2256,29 +2256,29 @@
         <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BC9" t="n">
         <v>30</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG9" t="n">
         <v>36</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -2312,19 +2312,19 @@
         <v>2.32</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J10" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L10" t="n">
         <v>1.48</v>
@@ -2333,7 +2333,7 @@
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O10" t="n">
         <v>1.5</v>
@@ -2351,13 +2351,13 @@
         <v>4.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
         <v>1.81</v>
       </c>
       <c r="V10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
         <v>1.63</v>
@@ -2366,7 +2366,7 @@
         <v>10.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>980</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
         <v>980</v>
@@ -2417,10 +2417,10 @@
         <v>90</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AR10" t="n">
         <v>4.4</v>
@@ -2429,22 +2429,22 @@
         <v>5</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="AW10" t="n">
         <v>4.9</v>
       </c>
       <c r="AX10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AZ10" t="n">
         <v>4.4</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -2503,58 +2503,58 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>12</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>950</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M11" t="n">
         <v>1.02</v>
       </c>
-      <c r="G11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N11" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="O11" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.66</v>
       </c>
       <c r="S11" t="n">
-        <v>1.15</v>
+        <v>2.08</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -2697,55 +2697,55 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="G12" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="H12" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="I12" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="J12" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V12" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="W12" t="n">
         <v>1.36</v>
@@ -2808,59 +2808,59 @@
         <v>3.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AT12" t="n">
         <v>3.3</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AW12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA12" t="n">
         <v>3.9</v>
       </c>
-      <c r="AX12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA12" t="n">
+      <c r="BB12" t="n">
         <v>4</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BC12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE12" t="n">
         <v>4.1</v>
       </c>
-      <c r="BC12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -2891,58 +2891,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G13" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I13" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="J13" t="n">
-        <v>2.74</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="Q13" t="n">
         <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U13" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W13" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3002,7 +3002,7 @@
         <v>3.45</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.55</v>
+        <v>15</v>
       </c>
       <c r="AR13" t="n">
         <v>3.9</v>
@@ -3014,7 +3014,7 @@
         <v>3.05</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AV13" t="n">
         <v>3.6</v>
@@ -3026,19 +3026,19 @@
         <v>3.25</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AZ13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB13" t="n">
         <v>3.65</v>
       </c>
-      <c r="BA13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BC13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BD13" t="n">
         <v>3.9</v>
@@ -3047,14 +3047,14 @@
         <v>4.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BG13" t="n">
         <v>4.1</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="G14" t="n">
         <v>5.4</v>
@@ -3094,46 +3094,46 @@
         <v>1.77</v>
       </c>
       <c r="I14" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="K14" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M14" t="n">
         <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
         <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R14" t="n">
         <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="T14" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U14" t="n">
         <v>2.2</v>
       </c>
       <c r="V14" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="W14" t="n">
         <v>1.22</v>
@@ -3154,7 +3154,7 @@
         <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3190,25 +3190,25 @@
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AP14" t="n">
         <v>4.1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AS14" t="n">
         <v>4.1</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="AV14" t="n">
         <v>3.5</v>
@@ -3226,29 +3226,29 @@
         <v>4</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE14" t="n">
         <v>4.7</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.45</v>
+        <v>7.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G15" t="n">
         <v>2.22</v>
@@ -3288,7 +3288,7 @@
         <v>3.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J15" t="n">
         <v>3.9</v>
@@ -3300,7 +3300,7 @@
         <v>1.26</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
         <v>5</v>
@@ -3309,16 +3309,16 @@
         <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
         <v>1.59</v>
       </c>
       <c r="R15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S15" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="T15" t="n">
         <v>1.58</v>
@@ -3327,7 +3327,7 @@
         <v>2.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
         <v>1.83</v>
@@ -3336,7 +3336,7 @@
         <v>28</v>
       </c>
       <c r="Y15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z15" t="n">
         <v>36</v>
@@ -3354,19 +3354,19 @@
         <v>18.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF15" t="n">
         <v>19.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ15" t="n">
         <v>32</v>
@@ -3375,16 +3375,16 @@
         <v>24</v>
       </c>
       <c r="AL15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM15" t="n">
         <v>75</v>
       </c>
       <c r="AN15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP15" t="n">
         <v>19.5</v>
@@ -3396,7 +3396,7 @@
         <v>20</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AT15" t="n">
         <v>11.5</v>
@@ -3408,7 +3408,7 @@
         <v>13</v>
       </c>
       <c r="AW15" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="AX15" t="n">
         <v>13.5</v>
@@ -3420,10 +3420,10 @@
         <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC15" t="n">
         <v>17</v>
@@ -3432,7 +3432,7 @@
         <v>21</v>
       </c>
       <c r="BE15" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BF15" t="n">
         <v>8</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -3473,85 +3473,85 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="G16" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J16" t="n">
         <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
         <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q16" t="n">
         <v>1.68</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="U16" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W16" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y16" t="n">
         <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB16" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
         <v>13</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>16.5</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
@@ -3563,13 +3563,13 @@
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
@@ -3581,16 +3581,16 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.35</v>
+        <v>17.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>17</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.35</v>
+        <v>7.6</v>
       </c>
       <c r="AT16" t="n">
         <v>9.6</v>
@@ -3602,7 +3602,7 @@
         <v>15.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="AX16" t="n">
         <v>10.5</v>
@@ -3614,10 +3614,10 @@
         <v>14.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="BB16" t="n">
-        <v>2.98</v>
+        <v>17</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
@@ -3626,17 +3626,17 @@
         <v>22</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="BF16" t="n">
         <v>7.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="J17" t="n">
         <v>2.84</v>
@@ -3775,16 +3775,16 @@
         <v>160</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AR17" t="n">
         <v>6.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AT17" t="n">
         <v>5.4</v>
@@ -3793,13 +3793,13 @@
         <v>6.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.85</v>
+        <v>8</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AY17" t="n">
         <v>5.3</v>
@@ -3808,7 +3808,7 @@
         <v>7</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BB17" t="n">
         <v>6.8</v>
@@ -3820,7 +3820,7 @@
         <v>8</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="BF17" t="n">
         <v>7.4</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G18" t="n">
         <v>2.94</v>
@@ -3870,7 +3870,7 @@
         <v>3.1</v>
       </c>
       <c r="I18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J18" t="n">
         <v>2.82</v>
@@ -3879,7 +3879,7 @@
         <v>2.94</v>
       </c>
       <c r="L18" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M18" t="n">
         <v>1.13</v>
@@ -3888,13 +3888,13 @@
         <v>2.56</v>
       </c>
       <c r="O18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P18" t="n">
         <v>1.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R18" t="n">
         <v>1.18</v>
@@ -3903,16 +3903,16 @@
         <v>5.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U18" t="n">
         <v>1.75</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W18" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X18" t="n">
         <v>8.6</v>
@@ -3942,7 +3942,7 @@
         <v>19</v>
       </c>
       <c r="AG18" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH18" t="n">
         <v>25</v>
@@ -3978,7 +3978,7 @@
         <v>16.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT18" t="n">
         <v>7</v>
@@ -3990,7 +3990,7 @@
         <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="AX18" t="n">
         <v>14.5</v>
@@ -4002,29 +4002,29 @@
         <v>19.5</v>
       </c>
       <c r="BA18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG18" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G19" t="n">
         <v>4.9</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="I19" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="J19" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.35</v>
@@ -4103,7 +4103,7 @@
         <v>1.96</v>
       </c>
       <c r="V19" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="W19" t="n">
         <v>1.27</v>
@@ -4199,7 +4199,7 @@
         <v>7.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.22</v>
+        <v>8.6</v>
       </c>
       <c r="BC19" t="n">
         <v>8.4</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="G20" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="H20" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I20" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="J20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L20" t="n">
         <v>1.44</v>
@@ -4291,16 +4291,16 @@
         <v>4.4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="U20" t="n">
         <v>1.72</v>
       </c>
       <c r="V20" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X20" t="n">
         <v>12</v>
@@ -4357,28 +4357,28 @@
         <v>170</v>
       </c>
       <c r="AP20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ20" t="n">
         <v>11.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT20" t="n">
         <v>5.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV20" t="n">
         <v>5.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX20" t="n">
         <v>8.6</v>
@@ -4387,32 +4387,32 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB20" t="n">
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BD20" t="n">
         <v>6.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG20" t="n">
         <v>6.6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -4449,67 +4449,67 @@
         <v>3.3</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="I21" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N21" t="n">
         <v>3.45</v>
       </c>
-      <c r="L21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.6</v>
-      </c>
       <c r="O21" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P21" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U21" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V21" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W21" t="n">
         <v>1.44</v>
       </c>
       <c r="X21" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y21" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z21" t="n">
         <v>15</v>
       </c>
       <c r="AA21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC21" t="n">
         <v>7.4</v>
@@ -4518,19 +4518,19 @@
         <v>11.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF21" t="n">
         <v>21</v>
       </c>
       <c r="AG21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ21" t="n">
         <v>60</v>
@@ -4542,28 +4542,28 @@
         <v>55</v>
       </c>
       <c r="AM21" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN21" t="n">
         <v>40</v>
       </c>
       <c r="AO21" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AP21" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR21" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS21" t="n">
         <v>30</v>
       </c>
       <c r="AT21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU21" t="n">
         <v>7</v>
@@ -4578,10 +4578,10 @@
         <v>19.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
         <v>38</v>
@@ -4599,14 +4599,14 @@
         <v>38</v>
       </c>
       <c r="BF21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG21" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -4637,64 +4637,64 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" t="n">
         <v>12.5</v>
       </c>
-      <c r="I22" t="n">
-        <v>13</v>
-      </c>
       <c r="J22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K22" t="n">
         <v>5.7</v>
       </c>
-      <c r="K22" t="n">
-        <v>5.8</v>
-      </c>
       <c r="L22" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="O22" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
         <v>1.08</v>
       </c>
       <c r="W22" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="X22" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y22" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Z22" t="n">
         <v>120</v>
@@ -4703,104 +4703,104 @@
         <v>690</v>
       </c>
       <c r="AB22" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD22" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AE22" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="AF22" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AG22" t="n">
         <v>10.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AI22" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="AJ22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>510</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV22" t="n">
         <v>46</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>420</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>40</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>42</v>
       </c>
       <c r="AW22" t="n">
         <v>65</v>
       </c>
       <c r="AX22" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BA22" t="n">
         <v>65</v>
       </c>
       <c r="BB22" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BC22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD22" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BE22" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="G23" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H23" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I23" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="J23" t="n">
         <v>4.3</v>
@@ -4855,22 +4855,22 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O23" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P23" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R23" t="n">
         <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T23" t="n">
         <v>2.1</v>
@@ -4882,13 +4882,13 @@
         <v>2.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y23" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z23" t="n">
         <v>9</v>
@@ -4897,16 +4897,16 @@
         <v>16.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC23" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF23" t="n">
         <v>50</v>
@@ -4927,7 +4927,7 @@
         <v>110</v>
       </c>
       <c r="AL23" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM23" t="n">
         <v>170</v>
@@ -4942,7 +4942,7 @@
         <v>12</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR23" t="n">
         <v>8.199999999999999</v>
@@ -4951,7 +4951,7 @@
         <v>14.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU23" t="n">
         <v>8.4</v>
@@ -4963,7 +4963,7 @@
         <v>17</v>
       </c>
       <c r="AX23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AY23" t="n">
         <v>22</v>
@@ -4975,26 +4975,26 @@
         <v>36</v>
       </c>
       <c r="BB23" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BC23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE23" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG23" t="n">
         <v>10</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="O24" t="n">
         <v>1.27</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -5243,10 +5243,10 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="O25" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P25" t="n">
         <v>1.24</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>2.24</v>
       </c>
       <c r="G26" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H26" t="n">
         <v>4.4</v>
@@ -5428,7 +5428,7 @@
         <v>2.82</v>
       </c>
       <c r="K26" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
         <v>1.65</v>
@@ -5437,13 +5437,13 @@
         <v>1.16</v>
       </c>
       <c r="N26" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="O26" t="n">
         <v>1.65</v>
       </c>
       <c r="P26" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q26" t="n">
         <v>3.05</v>
@@ -5455,10 +5455,10 @@
         <v>6.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U26" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V26" t="n">
         <v>1.26</v>
@@ -5476,7 +5476,7 @@
         <v>48</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB26" t="n">
         <v>6.6</v>
@@ -5500,13 +5500,13 @@
         <v>48</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ26" t="n">
         <v>32</v>
       </c>
       <c r="AK26" t="n">
-        <v>75</v>
+        <v>980</v>
       </c>
       <c r="AL26" t="n">
         <v>1000</v>
@@ -5515,10 +5515,10 @@
         <v>320</v>
       </c>
       <c r="AN26" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP26" t="n">
         <v>6.4</v>
@@ -5551,10 +5551,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BA26" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB26" t="n">
         <v>19</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="G27" t="n">
         <v>3.15</v>
@@ -5622,7 +5622,7 @@
         <v>2.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -5631,10 +5631,10 @@
         <v>1.22</v>
       </c>
       <c r="N27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O27" t="n">
         <v>1.94</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.9</v>
       </c>
       <c r="P27" t="n">
         <v>1.28</v>
@@ -5670,13 +5670,13 @@
         <v>26</v>
       </c>
       <c r="AA27" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB27" t="n">
         <v>7.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD27" t="n">
         <v>30</v>
@@ -5691,13 +5691,13 @@
         <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AK27" t="n">
         <v>1000</v>
@@ -5721,7 +5721,7 @@
         <v>6.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS27" t="n">
         <v>25</v>
@@ -5736,7 +5736,7 @@
         <v>16.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AX27" t="n">
         <v>12.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5825,7 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="O28" t="n">
         <v>1.38</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -5995,170 +5995,170 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H29" t="n">
         <v>2.06</v>
       </c>
       <c r="I29" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="J29" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ29" t="n">
         <v>4.3</v>
       </c>
-      <c r="L29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
         <v>4.9</v>
       </c>
       <c r="I30" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J30" t="n">
         <v>3.15</v>
@@ -6213,7 +6213,7 @@
         <v>1.13</v>
       </c>
       <c r="N30" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="O30" t="n">
         <v>1.58</v>
@@ -6231,16 +6231,16 @@
         <v>5.8</v>
       </c>
       <c r="T30" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U30" t="n">
         <v>1.69</v>
       </c>
       <c r="V30" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W30" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="X30" t="n">
         <v>9.199999999999999</v>
@@ -6249,7 +6249,7 @@
         <v>14.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AA30" t="n">
         <v>150</v>
@@ -6261,13 +6261,13 @@
         <v>8</v>
       </c>
       <c r="AD30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG30" t="n">
         <v>14</v>
@@ -6279,10 +6279,10 @@
         <v>150</v>
       </c>
       <c r="AJ30" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AK30" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AL30" t="n">
         <v>1000</v>
@@ -6303,7 +6303,7 @@
         <v>10</v>
       </c>
       <c r="AR30" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS30" t="n">
         <v>40</v>
@@ -6330,7 +6330,7 @@
         <v>18.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB30" t="n">
         <v>16.5</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -6386,10 +6386,10 @@
         <v>3.3</v>
       </c>
       <c r="G31" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H31" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I31" t="n">
         <v>2.48</v>
@@ -6413,10 +6413,10 @@
         <v>1.49</v>
       </c>
       <c r="P31" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R31" t="n">
         <v>1.21</v>
@@ -6431,7 +6431,7 @@
         <v>1.83</v>
       </c>
       <c r="V31" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W31" t="n">
         <v>1.4</v>
@@ -6446,7 +6446,7 @@
         <v>13.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB31" t="n">
         <v>10</v>
@@ -6527,10 +6527,10 @@
         <v>32</v>
       </c>
       <c r="BB31" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BC31" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BD31" t="n">
         <v>48</v>
@@ -6539,14 +6539,14 @@
         <v>46</v>
       </c>
       <c r="BF31" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BG31" t="n">
         <v>25</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -6580,10 +6580,10 @@
         <v>6.2</v>
       </c>
       <c r="G32" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="H32" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="I32" t="n">
         <v>1.74</v>
@@ -6595,7 +6595,7 @@
         <v>4.3</v>
       </c>
       <c r="L32" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M32" t="n">
         <v>1.08</v>
@@ -6607,28 +6607,28 @@
         <v>1.38</v>
       </c>
       <c r="P32" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R32" t="n">
         <v>1.27</v>
       </c>
       <c r="S32" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="T32" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U32" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V32" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="W32" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X32" t="n">
         <v>15</v>
@@ -6640,7 +6640,7 @@
         <v>9.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB32" t="n">
         <v>23</v>
@@ -6664,7 +6664,7 @@
         <v>32</v>
       </c>
       <c r="AI32" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ32" t="n">
         <v>270</v>
@@ -6676,7 +6676,7 @@
         <v>140</v>
       </c>
       <c r="AM32" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN32" t="n">
         <v>1000</v>
@@ -6709,7 +6709,7 @@
         <v>17</v>
       </c>
       <c r="AX32" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY32" t="n">
         <v>21</v>
@@ -6718,29 +6718,29 @@
         <v>21</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC32" t="n">
         <v>5.5</v>
       </c>
-      <c r="BC32" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BD32" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF32" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG32" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H2" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>1.05</v>
+        <v>2.18</v>
       </c>
       <c r="K2" t="n">
         <v>11</v>
@@ -805,7 +805,7 @@
         <v>1.05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
         <v>1.04</v>
@@ -868,66 +868,66 @@
         <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FK Kudrivka</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.39</v>
+        <v>3.15</v>
       </c>
       <c r="G3" t="n">
-        <v>1.42</v>
+        <v>5.1</v>
       </c>
       <c r="H3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.86</v>
       </c>
       <c r="I3" t="n">
-        <v>12.5</v>
+        <v>2.4</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>1.05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.74</v>
+        <v>1.05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.09</v>
+        <v>1.71</v>
       </c>
       <c r="W3" t="n">
-        <v>3.35</v>
+        <v>1.24</v>
       </c>
       <c r="X3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1136,85 +1136,85 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FK IMT Novi Beograd</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.28</v>
+        <v>1.38</v>
       </c>
       <c r="G4" t="n">
-        <v>2.76</v>
+        <v>1.42</v>
       </c>
       <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S4" t="n">
         <v>3.25</v>
       </c>
-      <c r="I4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="T4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.09</v>
       </c>
-      <c r="N4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.37</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.61</v>
+        <v>3.35</v>
       </c>
       <c r="X4" t="n">
         <v>980</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>980</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AD4" t="n">
         <v>980</v>
@@ -1223,99 +1223,99 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>980</v>
+        <v>9</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
         <v>980</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="AJ4" t="n">
-        <v>980</v>
+        <v>12</v>
       </c>
       <c r="AK4" t="n">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AM4" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>980</v>
+        <v>7.4</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="AR4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY4" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AZ4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC4" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD4" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Omonia</t>
+          <t>FK IMT Novi Beograd</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Apollon Limassol</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.5</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S5" t="n">
         <v>3.9</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T5" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="U5" t="n">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="X5" t="n">
-        <v>18.5</v>
+        <v>980</v>
       </c>
       <c r="Y5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>19.5</v>
+        <v>980</v>
       </c>
       <c r="AE5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>16.5</v>
+        <v>980</v>
       </c>
       <c r="AG5" t="n">
         <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ5" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AK5" t="n">
-        <v>27</v>
+        <v>980</v>
       </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="AO5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AR5" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.4</v>
+        <v>3.45</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>4.3</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>4.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>11</v>
+        <v>4.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Manisa FK</t>
+          <t>Omonia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Corum Belediyespor</t>
+          <t>Apollon Limassol</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="G6" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.14</v>
+        <v>3.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE6" t="n">
         <v>4.2</v>
       </c>
-      <c r="O6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X6" t="n">
-        <v>980</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>980</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>980</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>980</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>980</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>980</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>980</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>980</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>980</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BF6" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BG6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Wieczysta Krakow</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.6</v>
+        <v>1.88</v>
       </c>
       <c r="G7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X7" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV7" t="n">
         <v>4.7</v>
       </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>10</v>
-      </c>
       <c r="AW7" t="n">
-        <v>22</v>
+        <v>1.44</v>
       </c>
       <c r="AX7" t="n">
-        <v>29</v>
+        <v>2.78</v>
       </c>
       <c r="AY7" t="n">
-        <v>17.5</v>
+        <v>5.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="BA7" t="n">
-        <v>44</v>
+        <v>1.76</v>
       </c>
       <c r="BB7" t="n">
-        <v>95</v>
+        <v>2.68</v>
       </c>
       <c r="BC7" t="n">
-        <v>65</v>
+        <v>2.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>80</v>
+        <v>2.38</v>
       </c>
       <c r="BE7" t="n">
-        <v>44</v>
+        <v>1.37</v>
       </c>
       <c r="BF7" t="n">
-        <v>85</v>
+        <v>6.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Manisa FK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>Corum Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="G8" t="n">
-        <v>8.4</v>
+        <v>3.75</v>
       </c>
       <c r="H8" t="n">
-        <v>1.53</v>
+        <v>2.14</v>
       </c>
       <c r="I8" t="n">
-        <v>1.61</v>
+        <v>2.32</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.98</v>
+        <v>1.69</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>3.65</v>
+        <v>2.74</v>
       </c>
       <c r="T8" t="n">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="U8" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="V8" t="n">
-        <v>2.62</v>
+        <v>1.76</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="X8" t="n">
-        <v>17</v>
+        <v>980</v>
       </c>
       <c r="Y8" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>980</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>980</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE8" t="n">
         <v>8.6</v>
       </c>
-      <c r="Z8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>280</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>140</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>240</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BF8" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wisla Plock</t>
+          <t>Rapid Bucharest</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.62</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>2.82</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1.47</v>
       </c>
       <c r="I9" t="n">
-        <v>3.35</v>
+        <v>1.51</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="T9" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>2.96</v>
       </c>
       <c r="W9" t="n">
-        <v>1.55</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC9" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AD9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>350</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>180</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>170</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>230</v>
+      </c>
+      <c r="AO9" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="AP9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG9" t="n">
         <v>7.4</v>
       </c>
-      <c r="AD9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>36</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>36</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Feirense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Felgueiras</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.32</v>
+        <v>4.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.58</v>
+        <v>4.6</v>
       </c>
       <c r="H10" t="n">
-        <v>3.45</v>
+        <v>2.02</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9</v>
+        <v>2.04</v>
       </c>
       <c r="J10" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="M10" t="n">
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.66</v>
+        <v>2.98</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P10" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="U10" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.96</v>
       </c>
       <c r="W10" t="n">
-        <v>1.63</v>
+        <v>1.28</v>
       </c>
       <c r="X10" t="n">
         <v>10.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Z10" t="n">
-        <v>980</v>
+        <v>10.5</v>
       </c>
       <c r="AA10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL10" t="n">
         <v>90</v>
       </c>
-      <c r="AB10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE10" t="n">
+      <c r="AM10" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BC10" t="n">
         <v>65</v>
       </c>
-      <c r="AF10" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>980</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BD10" t="n">
-        <v>4.9</v>
+        <v>80</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.1</v>
+        <v>60</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.7</v>
+        <v>110</v>
       </c>
       <c r="BG10" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Zaglebie Lubin</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Batin</t>
+          <t>Wisla Plock</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.31</v>
+        <v>2.62</v>
       </c>
       <c r="G11" t="n">
-        <v>1.32</v>
+        <v>2.84</v>
       </c>
       <c r="H11" t="n">
-        <v>7.6</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>3.35</v>
       </c>
       <c r="J11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX11" t="n">
         <v>6.4</v>
       </c>
-      <c r="K11" t="n">
-        <v>950</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ11" t="n">
+      <c r="AY11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC11" t="n">
         <v>30</v>
       </c>
-      <c r="AR11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="BE11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.62</v>
+        <v>8.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.88</v>
+        <v>36</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,184 +2683,184 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Al-Arabi Al-Saudi</t>
+          <t>Feirense</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jeddah Club</t>
+          <t>Felgueiras</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.94</v>
+        <v>2.36</v>
       </c>
       <c r="G12" t="n">
-        <v>3.9</v>
+        <v>2.58</v>
       </c>
       <c r="H12" t="n">
-        <v>2.34</v>
+        <v>3.45</v>
       </c>
       <c r="I12" t="n">
-        <v>2.72</v>
+        <v>3.85</v>
       </c>
       <c r="J12" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="V12" t="n">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU12" t="n">
         <v>3.4</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.94</v>
-      </c>
       <c r="AV12" t="n">
-        <v>3.3</v>
+        <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.65</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB12" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -2882,67 +2882,67 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al Jabalain</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al-Zulfi SC</t>
+          <t>Al Batin</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.72</v>
+        <v>1.31</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="H13" t="n">
-        <v>3.95</v>
+        <v>7.6</v>
       </c>
       <c r="I13" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
-        <v>4.9</v>
+        <v>500</v>
       </c>
       <c r="L13" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="P13" t="n">
-        <v>1.92</v>
+        <v>2.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="T13" t="n">
         <v>1.78</v>
       </c>
       <c r="U13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>1.91</v>
+        <v>3.3</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AR13" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="AU13" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Al-Adalh</t>
+          <t>Al-Arabi Al-Saudi</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Faisaly ( KSA )</t>
+          <t>Jeddah Club</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.2</v>
+        <v>2.96</v>
       </c>
       <c r="G14" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="H14" t="n">
-        <v>1.77</v>
+        <v>2.18</v>
       </c>
       <c r="I14" t="n">
-        <v>1.92</v>
+        <v>2.76</v>
       </c>
       <c r="J14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS14" t="n">
         <v>3.9</v>
       </c>
-      <c r="K14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AP14" t="n">
+      <c r="AT14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE14" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BF14" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Jabalain</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>Al-Zulfi SC</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U15" t="n">
         <v>2.02</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="H15" t="n">
+      <c r="V15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF15" t="n">
         <v>3.3</v>
       </c>
-      <c r="I15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="X15" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>8</v>
-      </c>
       <c r="BG15" t="n">
-        <v>18.5</v>
+        <v>4.1</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Al-Adalh</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Andorra CF</t>
+          <t>Al Faisaly ( KSA )</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.81</v>
+        <v>4.2</v>
       </c>
       <c r="G16" t="n">
-        <v>1.86</v>
+        <v>5.4</v>
       </c>
       <c r="H16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC16" t="n">
         <v>4.5</v>
       </c>
-      <c r="I16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="X16" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>15</v>
-      </c>
       <c r="BD16" t="n">
-        <v>22</v>
+        <v>4.5</v>
       </c>
       <c r="BE16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG16" t="n">
         <v>7.4</v>
       </c>
-      <c r="BF16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>7</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Sporting Gijon</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="G17" t="n">
-        <v>2.26</v>
+        <v>990</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="I17" t="n">
-        <v>5.8</v>
+        <v>990</v>
       </c>
       <c r="J17" t="n">
-        <v>2.84</v>
+        <v>1.02</v>
       </c>
       <c r="K17" t="n">
-        <v>3.05</v>
+        <v>980</v>
       </c>
       <c r="L17" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.28</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="P17" t="n">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>1.37</v>
       </c>
       <c r="R17" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="S17" t="n">
-        <v>6.6</v>
+        <v>1.37</v>
       </c>
       <c r="T17" t="n">
-        <v>2.36</v>
+        <v>1.05</v>
       </c>
       <c r="U17" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="V17" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.72</v>
+        <v>2.18</v>
       </c>
       <c r="G18" t="n">
-        <v>2.94</v>
+        <v>2.32</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I18" t="n">
         <v>3.4</v>
       </c>
       <c r="J18" t="n">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2.94</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
+        <v>5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P18" t="n">
         <v>2.56</v>
       </c>
-      <c r="O18" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Q18" t="n">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="S18" t="n">
-        <v>5.3</v>
+        <v>2.36</v>
       </c>
       <c r="T18" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="U18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.75</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.52</v>
-      </c>
       <c r="X18" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AA18" t="n">
         <v>65</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AD18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH18" t="n">
         <v>16</v>
       </c>
-      <c r="AE18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG18" t="n">
+      <c r="AI18" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>14.5</v>
       </c>
-      <c r="AH18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AR18" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT18" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AU18" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW18" t="n">
-        <v>40</v>
+        <v>5.9</v>
       </c>
       <c r="AX18" t="n">
         <v>14.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="BC18" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="BE18" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="BF18" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Amiens</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ESTAC Troyes</t>
+          <t>Andorra CF</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.4</v>
+        <v>1.81</v>
       </c>
       <c r="G19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I19" t="n">
         <v>4.9</v>
       </c>
-      <c r="H19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.95</v>
-      </c>
       <c r="J19" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="O19" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>3.65</v>
+        <v>2.68</v>
       </c>
       <c r="T19" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="U19" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="V19" t="n">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>1.27</v>
+        <v>2.16</v>
       </c>
       <c r="X19" t="n">
-        <v>980</v>
+        <v>24</v>
       </c>
       <c r="Y19" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="Z19" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>980</v>
+        <v>120</v>
       </c>
       <c r="AB19" t="n">
-        <v>980</v>
+        <v>11.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>980</v>
+        <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>980</v>
+        <v>19.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>980</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
-        <v>980</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>980</v>
+        <v>18.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="AK19" t="n">
-        <v>70</v>
+        <v>18.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AM19" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>70</v>
+        <v>9.6</v>
       </c>
       <c r="AO19" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.8</v>
+        <v>17.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.6</v>
+        <v>17</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.1</v>
+        <v>15.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA19" t="n">
         <v>7.6</v>
       </c>
-      <c r="AY19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA19" t="n">
+      <c r="BB19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF19" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.99</v>
-      </c>
       <c r="BG19" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,75 +4235,75 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.84</v>
+        <v>2.18</v>
       </c>
       <c r="G20" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="H20" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I20" t="n">
         <v>5.4</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="K20" t="n">
-        <v>3.7</v>
+        <v>2.92</v>
       </c>
       <c r="L20" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="N20" t="n">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="O20" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="P20" t="n">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="U20" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="V20" t="n">
         <v>1.23</v>
       </c>
       <c r="W20" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="X20" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Y20" t="n">
         <v>980</v>
@@ -4312,22 +4312,22 @@
         <v>980</v>
       </c>
       <c r="AA20" t="n">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="AB20" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AD20" t="n">
         <v>980</v>
       </c>
       <c r="AE20" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="AF20" t="n">
-        <v>11.5</v>
+        <v>980</v>
       </c>
       <c r="AG20" t="n">
         <v>980</v>
@@ -4336,7 +4336,7 @@
         <v>980</v>
       </c>
       <c r="AI20" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AJ20" t="n">
         <v>980</v>
@@ -4345,81 +4345,81 @@
         <v>980</v>
       </c>
       <c r="AL20" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AM20" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
         <v>980</v>
       </c>
       <c r="AO20" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.5</v>
+        <v>4.9</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AW20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC20" t="n">
         <v>7.2</v>
       </c>
-      <c r="AX20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BD20" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.6</v>
+        <v>3.55</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="G21" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="H21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N21" t="n">
         <v>2.56</v>
       </c>
-      <c r="I21" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O21" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="U21" t="n">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="V21" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="X21" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AA21" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AB21" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AC21" t="n">
         <v>7.4</v>
       </c>
       <c r="AD21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY21" t="n">
         <v>11.5</v>
       </c>
-      <c r="AE21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX21" t="n">
+      <c r="AZ21" t="n">
         <v>19.5</v>
       </c>
-      <c r="AY21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>17</v>
-      </c>
       <c r="BA21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF21" t="n">
         <v>38</v>
       </c>
-      <c r="BB21" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>34</v>
-      </c>
       <c r="BG21" t="n">
-        <v>23</v>
+        <v>7.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Amiens</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>ESTAC Troyes</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.34</v>
+        <v>4.4</v>
       </c>
       <c r="G22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L22" t="n">
         <v>1.35</v>
       </c>
-      <c r="H22" t="n">
-        <v>12</v>
-      </c>
-      <c r="I22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.4</v>
-      </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="O22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
         <v>2.02</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
         <v>3.65</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="U22" t="n">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="V22" t="n">
-        <v>1.08</v>
+        <v>2.04</v>
       </c>
       <c r="W22" t="n">
-        <v>3.8</v>
+        <v>1.27</v>
       </c>
       <c r="X22" t="n">
-        <v>16</v>
+        <v>980</v>
       </c>
       <c r="Y22" t="n">
-        <v>29</v>
+        <v>980</v>
       </c>
       <c r="Z22" t="n">
-        <v>120</v>
+        <v>980</v>
       </c>
       <c r="AA22" t="n">
-        <v>690</v>
+        <v>980</v>
       </c>
       <c r="AB22" t="n">
-        <v>6.6</v>
+        <v>980</v>
       </c>
       <c r="AC22" t="n">
-        <v>12</v>
+        <v>980</v>
       </c>
       <c r="AD22" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AE22" t="n">
-        <v>300</v>
+        <v>980</v>
       </c>
       <c r="AF22" t="n">
-        <v>6.6</v>
+        <v>980</v>
       </c>
       <c r="AG22" t="n">
-        <v>10.5</v>
+        <v>980</v>
       </c>
       <c r="AH22" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AI22" t="n">
-        <v>260</v>
+        <v>980</v>
       </c>
       <c r="AJ22" t="n">
-        <v>10.5</v>
+        <v>90</v>
       </c>
       <c r="AK22" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="AL22" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AM22" t="n">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="AN22" t="n">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="AO22" t="n">
-        <v>510</v>
+        <v>980</v>
       </c>
       <c r="AP22" t="n">
-        <v>14.5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>26</v>
+        <v>4.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>60</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS22" t="n">
-        <v>75</v>
+        <v>6.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU22" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>46</v>
+        <v>5.1</v>
       </c>
       <c r="AW22" t="n">
-        <v>65</v>
+        <v>6.8</v>
       </c>
       <c r="AX22" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="BA22" t="n">
-        <v>65</v>
+        <v>7.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BC22" t="n">
-        <v>16</v>
+        <v>8.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>48</v>
+        <v>3.35</v>
       </c>
       <c r="BE22" t="n">
-        <v>260</v>
+        <v>2.24</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.6</v>
+        <v>1.99</v>
       </c>
       <c r="BG22" t="n">
-        <v>75</v>
+        <v>5.9</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.9</v>
+        <v>1.88</v>
       </c>
       <c r="G23" t="n">
-        <v>6.2</v>
+        <v>1.94</v>
       </c>
       <c r="H23" t="n">
-        <v>1.65</v>
+        <v>4.8</v>
       </c>
       <c r="I23" t="n">
-        <v>1.67</v>
+        <v>5.4</v>
       </c>
       <c r="J23" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="L23" t="n">
         <v>1.44</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="P23" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="S23" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U23" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="V23" t="n">
-        <v>2.5</v>
+        <v>1.23</v>
       </c>
       <c r="W23" t="n">
-        <v>1.19</v>
+        <v>2.06</v>
       </c>
       <c r="X23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Y23" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU23" t="n">
         <v>7.2</v>
       </c>
-      <c r="Z23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>200</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>150</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ23" t="n">
+      <c r="AV23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>6.8</v>
       </c>
-      <c r="AR23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU23" t="n">
+      <c r="BA23" t="n">
         <v>8.4</v>
       </c>
-      <c r="AV23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW23" t="n">
+      <c r="BB23" t="n">
         <v>17</v>
       </c>
-      <c r="AX23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>16</v>
-      </c>
       <c r="BC23" t="n">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="BD23" t="n">
-        <v>15</v>
+        <v>7.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>15.5</v>
+        <v>8.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Genesis Huracan</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="J24" t="n">
-        <v>1.02</v>
+        <v>3.25</v>
       </c>
       <c r="K24" t="n">
-        <v>950</v>
+        <v>3.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.27</v>
+        <v>2.22</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>1.27</v>
+        <v>4.2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,72 +5205,72 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Zeljeznicar</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M25" t="n">
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.02</v>
+        <v>1.98</v>
       </c>
       <c r="O25" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="R25" t="n">
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.24</v>
+        <v>1.36</v>
       </c>
       <c r="G26" t="n">
-        <v>2.36</v>
+        <v>1.37</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="I26" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="J26" t="n">
-        <v>2.82</v>
+        <v>5.3</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="M26" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>2.44</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="P26" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="R26" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="S26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X26" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>620</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF26" t="n">
         <v>6.6</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="X26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Y26" t="n">
+      <c r="AG26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>460</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU26" t="n">
         <v>11</v>
       </c>
-      <c r="Z26" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="AV26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>36</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>260</v>
+      </c>
+      <c r="BF26" t="n">
         <v>6.6</v>
       </c>
-      <c r="AC26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>48</v>
-      </c>
-      <c r="AI26" t="n">
+      <c r="BG26" t="n">
         <v>130</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>60</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>44</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.98</v>
+        <v>6.2</v>
       </c>
       <c r="G27" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2</v>
+        <v>1.66</v>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>1.67</v>
       </c>
       <c r="J27" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="K27" t="n">
-        <v>2.74</v>
+        <v>4.3</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M27" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>1.98</v>
+        <v>3.5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.94</v>
+        <v>1.37</v>
       </c>
       <c r="P27" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.8</v>
+        <v>2.06</v>
       </c>
       <c r="R27" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X27" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD27" t="n">
         <v>10</v>
       </c>
-      <c r="T27" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X27" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>30</v>
-      </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF27" t="n">
-        <v>19.5</v>
+        <v>50</v>
       </c>
       <c r="AG27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AH27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK27" t="n">
         <v>110</v>
       </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>400</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1000</v>
-      </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BF27" t="n">
         <v>15</v>
       </c>
-      <c r="AS27" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>29</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>36</v>
-      </c>
       <c r="BG27" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sportivo San Lorenzo</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.02</v>
+        <v>2.5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S28" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AI28" t="n">
         <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,72 +5981,72 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Lobos UPNFM</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="I29" t="n">
-        <v>2.18</v>
+        <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>1.02</v>
       </c>
       <c r="K29" t="n">
-        <v>3.45</v>
+        <v>950</v>
       </c>
       <c r="L29" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>2.56</v>
+        <v>1.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.51</v>
+        <v>1.27</v>
       </c>
       <c r="P29" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.38</v>
+        <v>1.26</v>
       </c>
       <c r="R29" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>4.8</v>
+        <v>1.26</v>
       </c>
       <c r="T29" t="n">
-        <v>2.12</v>
+        <v>1.05</v>
       </c>
       <c r="U29" t="n">
-        <v>1.72</v>
+        <v>1.05</v>
       </c>
       <c r="V29" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6103,69 +6103,69 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,184 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.99</v>
+        <v>1.21</v>
       </c>
       <c r="G30" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="H30" t="n">
-        <v>4.9</v>
+        <v>3.65</v>
       </c>
       <c r="I30" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J30" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K30" t="n">
-        <v>3.35</v>
+        <v>110</v>
       </c>
       <c r="L30" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.54</v>
+        <v>1.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="P30" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.74</v>
+        <v>2.16</v>
       </c>
       <c r="R30" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S30" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="T30" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V30" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W30" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="X30" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
         <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -6369,378 +6369,1736 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="G31" t="n">
-        <v>3.5</v>
+        <v>2.36</v>
       </c>
       <c r="H31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N31" t="n">
         <v>2.42</v>
       </c>
-      <c r="I31" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="J31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.78</v>
-      </c>
       <c r="O31" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="P31" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.46</v>
+        <v>2.98</v>
       </c>
       <c r="R31" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="S31" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="T31" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="U31" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="V31" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="W31" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="X31" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="Z31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG31" t="n">
         <v>13.5</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AH31" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN31" t="n">
         <v>38</v>
       </c>
-      <c r="AB31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF31" t="n">
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC31" t="n">
         <v>22</v>
       </c>
-      <c r="AG31" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI31" t="n">
+      <c r="BD31" t="n">
         <v>60</v>
       </c>
-      <c r="AJ31" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY31" t="n">
+      <c r="BE31" t="n">
         <v>13.5</v>
       </c>
-      <c r="AZ31" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB31" t="n">
+      <c r="BF31" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG31" t="n">
         <v>44</v>
       </c>
-      <c r="BC31" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>48</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>25</v>
-      </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>19:15:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>CA Platense</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>110</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>48</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Juventud De Las Piedras</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Curico Unido</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sportivo San Lorenzo</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Tigres FC Zipaquira</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Real Cartagena</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I37" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="X37" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>42</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>50</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>25</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Ecuadorian Serie A</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>21:30:00</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Manta FC</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Independiente (Ecu)</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="F39" t="n">
         <v>6.2</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G39" t="n">
         <v>8.6</v>
       </c>
-      <c r="H32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I32" t="n">
+      <c r="H39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I39" t="n">
         <v>1.74</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J39" t="n">
         <v>3.6</v>
       </c>
-      <c r="K32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="K39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L39" t="n">
         <v>1.38</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M39" t="n">
         <v>1.08</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N39" t="n">
         <v>3.1</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O39" t="n">
         <v>1.38</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P39" t="n">
         <v>1.72</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q39" t="n">
         <v>2.1</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R39" t="n">
         <v>1.27</v>
       </c>
-      <c r="S32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T32" t="n">
+      <c r="S39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T39" t="n">
         <v>2.06</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U39" t="n">
         <v>1.77</v>
       </c>
-      <c r="V32" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X32" t="n">
+      <c r="V39" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X39" t="n">
         <v>15</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="Y39" t="n">
         <v>7.4</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="Z39" t="n">
         <v>9.6</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AA39" t="n">
         <v>20</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AB39" t="n">
         <v>23</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AC39" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AD39" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AE39" t="n">
         <v>21</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AF39" t="n">
         <v>70</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AG39" t="n">
         <v>28</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AH39" t="n">
         <v>32</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AI39" t="n">
         <v>55</v>
       </c>
-      <c r="AJ32" t="n">
+      <c r="AJ39" t="n">
         <v>270</v>
       </c>
-      <c r="AK32" t="n">
+      <c r="AK39" t="n">
         <v>150</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AL39" t="n">
         <v>140</v>
       </c>
-      <c r="AM32" t="n">
+      <c r="AM39" t="n">
         <v>210</v>
       </c>
-      <c r="AN32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO32" t="n">
+      <c r="AN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO39" t="n">
         <v>15.5</v>
       </c>
-      <c r="AP32" t="n">
+      <c r="AP39" t="n">
         <v>10</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AQ39" t="n">
         <v>6</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AR39" t="n">
         <v>7.8</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AS39" t="n">
         <v>14</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="AT39" t="n">
         <v>15.5</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AU39" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AV39" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AW32" t="n">
+      <c r="AW39" t="n">
         <v>17</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="AX39" t="n">
         <v>5.3</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="AY39" t="n">
         <v>21</v>
       </c>
-      <c r="AZ32" t="n">
+      <c r="AZ39" t="n">
         <v>21</v>
       </c>
-      <c r="BA32" t="n">
+      <c r="BA39" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BB39" t="n">
         <v>5.6</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BC39" t="n">
         <v>5.5</v>
       </c>
-      <c r="BD32" t="n">
+      <c r="BD39" t="n">
         <v>5.5</v>
       </c>
-      <c r="BE32" t="n">
+      <c r="BE39" t="n">
         <v>5.6</v>
       </c>
-      <c r="BF32" t="n">
+      <c r="BF39" t="n">
         <v>5.6</v>
       </c>
-      <c r="BG32" t="n">
+      <c r="BG39" t="n">
         <v>10.5</v>
       </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:36:43</t>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="G2" t="n">
         <v>24</v>
       </c>
       <c r="H2" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="J2" t="n">
-        <v>2.18</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
         <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
@@ -787,13 +787,13 @@
         <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>1.09</v>
+        <v>1.47</v>
       </c>
       <c r="Q2" t="n">
         <v>1.22</v>
       </c>
       <c r="R2" t="n">
-        <v>1.09</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
         <v>1.22</v>
@@ -805,13 +805,13 @@
         <v>1.05</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>2.78</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Y2" t="n">
         <v>1000</v>
@@ -862,65 +862,65 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.06</v>
+        <v>4.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.06</v>
+        <v>4.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.06</v>
+        <v>4.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.06</v>
+        <v>4.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.06</v>
+        <v>4.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.06</v>
+        <v>4.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.06</v>
+        <v>4.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.06</v>
+        <v>1.78</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S3" t="n">
         <v>3.15</v>
       </c>
-      <c r="G3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.48</v>
-      </c>
       <c r="T3" t="n">
-        <v>1.05</v>
+        <v>1.8</v>
       </c>
       <c r="U3" t="n">
-        <v>1.05</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="W3" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
         <v>4.8</v>
@@ -1175,10 +1175,10 @@
         <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
         <v>1.38</v>
@@ -1199,7 +1199,7 @@
         <v>3.35</v>
       </c>
       <c r="X4" t="n">
-        <v>980</v>
+        <v>19.5</v>
       </c>
       <c r="Y4" t="n">
         <v>980</v>
@@ -1220,31 +1220,31 @@
         <v>980</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF4" t="n">
         <v>9</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>980</v>
+        <v>80</v>
       </c>
       <c r="AI4" t="n">
-        <v>180</v>
+        <v>520</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="AK4" t="n">
         <v>19</v>
       </c>
       <c r="AL4" t="n">
-        <v>980</v>
+        <v>170</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN4" t="n">
         <v>7.4</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.4</v>
+        <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT4" t="n">
         <v>6.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AZ4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5.4</v>
       </c>
-      <c r="BA4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD4" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -1393,52 +1393,52 @@
         <v>1.62</v>
       </c>
       <c r="X5" t="n">
-        <v>980</v>
+        <v>24</v>
       </c>
       <c r="Y5" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="n">
         <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>980</v>
+        <v>30</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AH5" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="AJ5" t="n">
-        <v>980</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
         <v>980</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AM5" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
         <v>980</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="AS5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT5" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT5" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AU5" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>3.7</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
         <v>3.5</v>
@@ -1563,7 +1563,7 @@
         <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
         <v>1.89</v>
@@ -1581,7 +1581,7 @@
         <v>2.14</v>
       </c>
       <c r="V6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W6" t="n">
         <v>1.84</v>
@@ -1596,13 +1596,13 @@
         <v>36</v>
       </c>
       <c r="AA6" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD6" t="n">
         <v>19.5</v>
@@ -1611,10 +1611,10 @@
         <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
         <v>22</v>
@@ -1632,7 +1632,7 @@
         <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>330</v>
       </c>
       <c r="AN6" t="n">
         <v>18</v>
@@ -1641,7 +1641,7 @@
         <v>55</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="AQ6" t="n">
         <v>11</v>
@@ -1650,7 +1650,7 @@
         <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT6" t="n">
         <v>8.800000000000001</v>
@@ -1659,10 +1659,10 @@
         <v>7.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.55</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.1</v>
+        <v>32</v>
       </c>
       <c r="AX6" t="n">
         <v>10</v>
@@ -1671,32 +1671,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.1</v>
+        <v>36</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.85</v>
+        <v>11.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.75</v>
+        <v>10.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BF6" t="n">
         <v>11</v>
       </c>
       <c r="BG6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N7" t="n">
         <v>4.5</v>
@@ -1757,13 +1757,13 @@
         <v>1.19</v>
       </c>
       <c r="P7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
         <v>1.58</v>
       </c>
       <c r="R7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S7" t="n">
         <v>2.42</v>
@@ -1778,10 +1778,10 @@
         <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X7" t="n">
-        <v>980</v>
+        <v>75</v>
       </c>
       <c r="Y7" t="n">
         <v>980</v>
@@ -1796,7 +1796,7 @@
         <v>980</v>
       </c>
       <c r="AC7" t="n">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="AD7" t="n">
         <v>980</v>
@@ -1811,7 +1811,7 @@
         <v>980</v>
       </c>
       <c r="AH7" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AI7" t="n">
         <v>980</v>
@@ -1826,71 +1826,71 @@
         <v>980</v>
       </c>
       <c r="AM7" t="n">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AO7" t="n">
         <v>980</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.64</v>
+        <v>7.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.55</v>
+        <v>3.75</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.32</v>
+        <v>28</v>
       </c>
       <c r="AT7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.44</v>
+        <v>3.15</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.78</v>
+        <v>7.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.76</v>
+        <v>9</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.68</v>
+        <v>7.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.38</v>
+        <v>8</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.37</v>
+        <v>3.25</v>
       </c>
       <c r="BF7" t="n">
         <v>6.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G8" t="n">
         <v>3.75</v>
@@ -1936,7 +1936,7 @@
         <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.31</v>
@@ -1975,7 +1975,7 @@
         <v>1.37</v>
       </c>
       <c r="X8" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="Y8" t="n">
         <v>980</v>
@@ -1990,10 +1990,10 @@
         <v>980</v>
       </c>
       <c r="AC8" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AD8" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AE8" t="n">
         <v>980</v>
@@ -2002,16 +2002,16 @@
         <v>980</v>
       </c>
       <c r="AG8" t="n">
-        <v>980</v>
+        <v>30</v>
       </c>
       <c r="AH8" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AI8" t="n">
         <v>980</v>
       </c>
       <c r="AJ8" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
         <v>980</v>
@@ -2020,71 +2020,71 @@
         <v>980</v>
       </c>
       <c r="AM8" t="n">
-        <v>85</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
         <v>980</v>
       </c>
       <c r="AO8" t="n">
-        <v>980</v>
+        <v>85</v>
       </c>
       <c r="AP8" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="AX8" t="n">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="AY8" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.04</v>
+        <v>2.56</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="BG8" t="n">
         <v>11</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="H9" t="n">
         <v>1.47</v>
@@ -2130,7 +2130,7 @@
         <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.4</v>
@@ -2148,7 +2148,7 @@
         <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R9" t="n">
         <v>1.34</v>
@@ -2160,10 +2160,10 @@
         <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V9" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="W9" t="n">
         <v>1.12</v>
@@ -2172,16 +2172,16 @@
         <v>17</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z9" t="n">
         <v>9.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AB9" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AC9" t="n">
         <v>10.5</v>
@@ -2211,13 +2211,13 @@
         <v>180</v>
       </c>
       <c r="AL9" t="n">
-        <v>170</v>
+        <v>520</v>
       </c>
       <c r="AM9" t="n">
-        <v>230</v>
+        <v>430</v>
       </c>
       <c r="AN9" t="n">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="AO9" t="n">
         <v>10.5</v>
@@ -2235,7 +2235,7 @@
         <v>11.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU9" t="n">
         <v>8.6</v>
@@ -2247,7 +2247,7 @@
         <v>14.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.4</v>
+        <v>50</v>
       </c>
       <c r="AY9" t="n">
         <v>22</v>
@@ -2256,29 +2256,29 @@
         <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.3</v>
+        <v>19.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG9" t="n">
         <v>7.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
         <v>2.02</v>
       </c>
-      <c r="I10" t="n">
-        <v>2.04</v>
-      </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
         <v>1.54</v>
@@ -2333,58 +2333,58 @@
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="V10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X10" t="n">
         <v>10.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z10" t="n">
         <v>10.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD10" t="n">
         <v>10.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF10" t="n">
         <v>32</v>
@@ -2393,34 +2393,34 @@
         <v>18.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN10" t="n">
         <v>120</v>
       </c>
-      <c r="AK10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>140</v>
-      </c>
       <c r="AO10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP10" t="n">
         <v>9.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR10" t="n">
         <v>10</v>
@@ -2429,25 +2429,25 @@
         <v>21</v>
       </c>
       <c r="AT10" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX10" t="n">
         <v>29</v>
       </c>
       <c r="AY10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA10" t="n">
         <v>44</v>
@@ -2459,20 +2459,20 @@
         <v>65</v>
       </c>
       <c r="BD10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BE10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BF10" t="n">
         <v>110</v>
       </c>
       <c r="BG10" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -2524,19 +2524,19 @@
         <v>1.45</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="O11" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R11" t="n">
         <v>1.23</v>
@@ -2548,10 +2548,10 @@
         <v>1.94</v>
       </c>
       <c r="U11" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
         <v>1.54</v>
@@ -2563,34 +2563,34 @@
         <v>10.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AA11" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AB11" t="n">
         <v>9</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AE11" t="n">
-        <v>980</v>
+        <v>190</v>
       </c>
       <c r="AF11" t="n">
-        <v>980</v>
+        <v>30</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="AI11" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AJ11" t="n">
         <v>980</v>
@@ -2599,19 +2599,19 @@
         <v>38</v>
       </c>
       <c r="AL11" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AM11" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
         <v>42</v>
       </c>
       <c r="AO11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ11" t="n">
         <v>8.6</v>
@@ -2623,7 +2623,7 @@
         <v>46</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
         <v>6.2</v>
@@ -2635,16 +2635,16 @@
         <v>36</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="AY11" t="n">
         <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BB11" t="n">
         <v>36</v>
@@ -2653,20 +2653,20 @@
         <v>30</v>
       </c>
       <c r="BD11" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="BE11" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG11" t="n">
         <v>36</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G12" t="n">
         <v>2.58</v>
@@ -2712,7 +2712,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L12" t="n">
         <v>1.48</v>
@@ -2721,7 +2721,7 @@
         <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O12" t="n">
         <v>1.5</v>
@@ -2751,28 +2751,28 @@
         <v>1.64</v>
       </c>
       <c r="X12" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>950</v>
       </c>
       <c r="Z12" t="n">
         <v>980</v>
       </c>
       <c r="AA12" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AD12" t="n">
         <v>980</v>
       </c>
       <c r="AE12" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AF12" t="n">
         <v>980</v>
@@ -2784,7 +2784,7 @@
         <v>980</v>
       </c>
       <c r="AI12" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="AJ12" t="n">
         <v>980</v>
@@ -2793,7 +2793,7 @@
         <v>980</v>
       </c>
       <c r="AL12" t="n">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>90</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AV12" t="n">
         <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="G13" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="H13" t="n">
         <v>7.6</v>
@@ -2903,10 +2903,10 @@
         <v>12</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="K13" t="n">
-        <v>500</v>
+        <v>13</v>
       </c>
       <c r="L13" t="n">
         <v>1.23</v>
@@ -2939,10 +2939,10 @@
         <v>2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2960,7 +2960,7 @@
         <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD13" t="n">
         <v>1000</v>
@@ -2993,68 +2993,68 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="AQ13" t="n">
         <v>30</v>
       </c>
       <c r="AR13" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.95</v>
+        <v>2.82</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AW13" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.4</v>
+        <v>2.04</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.95</v>
+        <v>2.62</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>2.06</v>
       </c>
       <c r="BE13" t="n">
-        <v>5</v>
+        <v>2.08</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.88</v>
+        <v>7.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -3088,16 +3088,16 @@
         <v>2.96</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="H14" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="I14" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="J14" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="K14" t="n">
         <v>4.3</v>
@@ -3127,19 +3127,19 @@
         <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U14" t="n">
         <v>2.06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y14" t="n">
         <v>1000</v>
@@ -3154,7 +3154,7 @@
         <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3169,7 +3169,7 @@
         <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.94</v>
+        <v>4.9</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.1</v>
+        <v>2.44</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I15" t="n">
         <v>6.2</v>
@@ -3303,37 +3303,37 @@
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P15" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
         <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="T15" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V15" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W15" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y15" t="n">
         <v>1000</v>
@@ -3345,10 +3345,10 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD15" t="n">
         <v>1000</v>
@@ -3357,22 +3357,22 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI15" t="n">
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL15" t="n">
         <v>1000</v>
@@ -3381,68 +3381,68 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="AQ15" t="n">
         <v>15</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AS15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV15" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AW15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC15" t="n">
         <v>4</v>
       </c>
-      <c r="AX15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BD15" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="H16" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="I16" t="n">
         <v>1.92</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.31</v>
@@ -3503,7 +3503,7 @@
         <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
         <v>1.61</v>
@@ -3524,31 +3524,31 @@
         <v>2.08</v>
       </c>
       <c r="W16" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AC16" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF16" t="n">
         <v>1000</v>
@@ -3557,7 +3557,7 @@
         <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
@@ -3572,71 +3572,71 @@
         <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
         <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="AT16" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AU16" t="n">
         <v>7.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="G17" t="n">
-        <v>990</v>
+        <v>2.64</v>
       </c>
       <c r="H17" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="I17" t="n">
-        <v>990</v>
+        <v>110</v>
       </c>
       <c r="J17" t="n">
-        <v>1.02</v>
+        <v>2.8</v>
       </c>
       <c r="K17" t="n">
-        <v>980</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.44</v>
@@ -3694,19 +3694,19 @@
         <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P17" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Q17" t="n">
         <v>1.37</v>
       </c>
       <c r="R17" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="S17" t="n">
-        <v>1.37</v>
+        <v>1.05</v>
       </c>
       <c r="T17" t="n">
         <v>1.05</v>
@@ -3715,58 +3715,58 @@
         <v>1.71</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AC17" t="n">
         <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
         <v>1000</v>
@@ -3775,62 +3775,62 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>2.18</v>
       </c>
       <c r="G18" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H18" t="n">
         <v>3.05</v>
@@ -3876,7 +3876,7 @@
         <v>3.8</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.26</v>
@@ -3894,10 +3894,10 @@
         <v>2.56</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S18" t="n">
         <v>2.36</v>
@@ -3909,10 +3909,10 @@
         <v>2.48</v>
       </c>
       <c r="V18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X18" t="n">
         <v>28</v>
@@ -3945,10 +3945,10 @@
         <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>980</v>
+        <v>85</v>
       </c>
       <c r="AJ18" t="n">
         <v>36</v>
@@ -3960,7 +3960,7 @@
         <v>36</v>
       </c>
       <c r="AM18" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
         <v>15</v>
@@ -3990,7 +3990,7 @@
         <v>12</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.9</v>
+        <v>23</v>
       </c>
       <c r="AX18" t="n">
         <v>14.5</v>
@@ -4002,7 +4002,7 @@
         <v>13</v>
       </c>
       <c r="BA18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB18" t="n">
         <v>25</v>
@@ -4014,7 +4014,7 @@
         <v>21</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.7</v>
+        <v>30</v>
       </c>
       <c r="BF18" t="n">
         <v>9</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -4058,19 +4058,19 @@
         <v>1.81</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H19" t="n">
         <v>4.6</v>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
         <v>1.33</v>
@@ -4082,10 +4082,10 @@
         <v>4.6</v>
       </c>
       <c r="O19" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P19" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q19" t="n">
         <v>1.7</v>
@@ -4094,10 +4094,10 @@
         <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="T19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U19" t="n">
         <v>2.26</v>
@@ -4106,16 +4106,16 @@
         <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X19" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="n">
         <v>21</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA19" t="n">
         <v>120</v>
@@ -4130,7 +4130,7 @@
         <v>19.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF19" t="n">
         <v>13</v>
@@ -4142,7 +4142,7 @@
         <v>18.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ19" t="n">
         <v>21</v>
@@ -4151,16 +4151,16 @@
         <v>18.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN19" t="n">
         <v>9.6</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AP19" t="n">
         <v>17.5</v>
@@ -4169,10 +4169,10 @@
         <v>17</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
@@ -4184,7 +4184,7 @@
         <v>15.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.6</v>
+        <v>44</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
@@ -4196,29 +4196,29 @@
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.6</v>
+        <v>44</v>
       </c>
       <c r="BB19" t="n">
-        <v>17</v>
+        <v>7.4</v>
       </c>
       <c r="BC19" t="n">
         <v>15</v>
       </c>
       <c r="BD19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BE19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BF19" t="n">
         <v>7.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -4264,10 +4264,10 @@
         <v>2.7</v>
       </c>
       <c r="K20" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
         <v>1.14</v>
@@ -4276,22 +4276,22 @@
         <v>2.24</v>
       </c>
       <c r="O20" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="P20" t="n">
         <v>1.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
         <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U20" t="n">
         <v>1.61</v>
@@ -4306,13 +4306,13 @@
         <v>7</v>
       </c>
       <c r="Y20" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="Z20" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AA20" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AB20" t="n">
         <v>6.2</v>
@@ -4321,98 +4321,98 @@
         <v>7.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AE20" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AF20" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AG20" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AH20" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AI20" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AJ20" t="n">
         <v>980</v>
       </c>
       <c r="AK20" t="n">
-        <v>980</v>
+        <v>140</v>
       </c>
       <c r="AL20" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN20" t="n">
         <v>980</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP20" t="n">
         <v>4.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AU20" t="n">
         <v>6.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AY20" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BC20" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF20" t="n">
         <v>8</v>
       </c>
-      <c r="BE20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BG20" t="n">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G21" t="n">
         <v>2.92</v>
@@ -4452,7 +4452,7 @@
         <v>3.15</v>
       </c>
       <c r="I21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J21" t="n">
         <v>2.82</v>
@@ -4476,7 +4476,7 @@
         <v>1.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="R21" t="n">
         <v>1.18</v>
@@ -4488,10 +4488,10 @@
         <v>2.12</v>
       </c>
       <c r="U21" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W21" t="n">
         <v>1.52</v>
@@ -4506,7 +4506,7 @@
         <v>21</v>
       </c>
       <c r="AA21" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AB21" t="n">
         <v>8.6</v>
@@ -4515,7 +4515,7 @@
         <v>7.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE21" t="n">
         <v>55</v>
@@ -4527,13 +4527,13 @@
         <v>14.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>85</v>
+        <v>460</v>
       </c>
       <c r="AJ21" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK21" t="n">
         <v>44</v>
@@ -4548,7 +4548,7 @@
         <v>50</v>
       </c>
       <c r="AO21" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP21" t="n">
         <v>7.2</v>
@@ -4560,7 +4560,7 @@
         <v>16.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="AT21" t="n">
         <v>7</v>
@@ -4572,7 +4572,7 @@
         <v>12.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AX21" t="n">
         <v>14.5</v>
@@ -4584,29 +4584,29 @@
         <v>19.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="BC21" t="n">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF21" t="n">
         <v>38</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G22" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H22" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="I22" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="J22" t="n">
         <v>3.8</v>
@@ -4661,28 +4661,28 @@
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.35</v>
       </c>
-      <c r="P22" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.31</v>
-      </c>
       <c r="S22" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="T22" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="U22" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="V22" t="n">
         <v>2.04</v>
@@ -4691,116 +4691,116 @@
         <v>1.27</v>
       </c>
       <c r="X22" t="n">
-        <v>980</v>
+        <v>26</v>
       </c>
       <c r="Y22" t="n">
-        <v>980</v>
+        <v>9.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>980</v>
+        <v>22</v>
       </c>
       <c r="AA22" t="n">
-        <v>980</v>
+        <v>75</v>
       </c>
       <c r="AB22" t="n">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="AC22" t="n">
-        <v>980</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>980</v>
+        <v>10.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AF22" t="n">
         <v>980</v>
       </c>
       <c r="AG22" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AH22" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AI22" t="n">
-        <v>980</v>
+        <v>100</v>
       </c>
       <c r="AJ22" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AK22" t="n">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="AL22" t="n">
-        <v>75</v>
+        <v>330</v>
       </c>
       <c r="AM22" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>70</v>
+        <v>270</v>
       </c>
       <c r="AO22" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR22" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3</v>
+        <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB22" t="n">
         <v>8.6</v>
       </c>
       <c r="BC22" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.35</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.99</v>
+        <v>8.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G23" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H23" t="n">
         <v>4.8</v>
       </c>
       <c r="I23" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K23" t="n">
         <v>3.6</v>
@@ -4855,82 +4855,82 @@
         <v>1.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="O23" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="P23" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="R23" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S23" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U23" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="V23" t="n">
         <v>1.23</v>
       </c>
       <c r="W23" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X23" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z23" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA23" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB23" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD23" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="AE23" t="n">
-        <v>90</v>
+        <v>230</v>
       </c>
       <c r="AF23" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG23" t="n">
         <v>11</v>
       </c>
       <c r="AH23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI23" t="n">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AJ23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL23" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AM23" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN23" t="n">
         <v>21</v>
@@ -4939,62 +4939,62 @@
         <v>140</v>
       </c>
       <c r="AP23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AT23" t="n">
         <v>6.2</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV23" t="n">
         <v>18</v>
       </c>
       <c r="AW23" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AX23" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="AY23" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ23" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BD23" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="BF23" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G24" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="H24" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="I24" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
         <v>3.25</v>
@@ -5055,28 +5055,28 @@
         <v>1.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q24" t="n">
         <v>2.22</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T24" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U24" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V24" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W24" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="X24" t="n">
         <v>11.5</v>
@@ -5088,10 +5088,10 @@
         <v>15</v>
       </c>
       <c r="AA24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC24" t="n">
         <v>7.2</v>
@@ -5100,25 +5100,25 @@
         <v>11.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG24" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH24" t="n">
         <v>18.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ24" t="n">
         <v>60</v>
       </c>
       <c r="AK24" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL24" t="n">
         <v>55</v>
@@ -5127,10 +5127,10 @@
         <v>110</v>
       </c>
       <c r="AN24" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AO24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP24" t="n">
         <v>10.5</v>
@@ -5139,56 +5139,56 @@
         <v>9</v>
       </c>
       <c r="AR24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AT24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU24" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV24" t="n">
         <v>11</v>
       </c>
       <c r="AW24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX24" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY24" t="n">
         <v>13</v>
       </c>
       <c r="AZ24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA24" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB24" t="n">
         <v>50</v>
       </c>
       <c r="BC24" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD24" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BE24" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF24" t="n">
         <v>40</v>
       </c>
-      <c r="BF24" t="n">
-        <v>36</v>
-      </c>
       <c r="BG24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -5219,170 +5219,170 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="G25" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="H25" t="n">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="I25" t="n">
-        <v>3.2</v>
+        <v>2.28</v>
       </c>
       <c r="J25" t="n">
-        <v>2.44</v>
+        <v>2.92</v>
       </c>
       <c r="K25" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="L25" t="n">
         <v>1.51</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N25" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="O25" t="n">
-        <v>1.31</v>
+        <v>1.59</v>
       </c>
       <c r="P25" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="R25" t="n">
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="T25" t="n">
-        <v>1.05</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.05</v>
+        <v>1.69</v>
       </c>
       <c r="V25" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="W25" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
         <v>5.3</v>
       </c>
       <c r="K26" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L26" t="n">
         <v>1.41</v>
@@ -5437,13 +5437,13 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O26" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q26" t="n">
         <v>2.02</v>
@@ -5455,7 +5455,7 @@
         <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="U26" t="n">
         <v>1.64</v>
@@ -5476,19 +5476,19 @@
         <v>120</v>
       </c>
       <c r="AA26" t="n">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="AB26" t="n">
         <v>6.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD26" t="n">
         <v>55</v>
       </c>
       <c r="AE26" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AF26" t="n">
         <v>6.6</v>
@@ -5500,31 +5500,31 @@
         <v>40</v>
       </c>
       <c r="AI26" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AJ26" t="n">
         <v>10.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM26" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AN26" t="n">
         <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="AP26" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR26" t="n">
         <v>60</v>
@@ -5551,13 +5551,13 @@
         <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BA26" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BB26" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC26" t="n">
         <v>16</v>
@@ -5569,14 +5569,14 @@
         <v>260</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG26" t="n">
         <v>130</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -5613,13 +5613,13 @@
         <v>6.6</v>
       </c>
       <c r="H27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I27" t="n">
         <v>1.66</v>
       </c>
-      <c r="I27" t="n">
-        <v>1.67</v>
-      </c>
       <c r="J27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K27" t="n">
         <v>4.3</v>
@@ -5628,58 +5628,58 @@
         <v>1.44</v>
       </c>
       <c r="M27" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O27" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P27" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q27" t="n">
         <v>2.06</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="T27" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="V27" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y27" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="Z27" t="n">
         <v>9</v>
       </c>
       <c r="AA27" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC27" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE27" t="n">
         <v>19</v>
@@ -5691,10 +5691,10 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ27" t="n">
         <v>200</v>
@@ -5706,40 +5706,40 @@
         <v>110</v>
       </c>
       <c r="AM27" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN27" t="n">
         <v>150</v>
       </c>
       <c r="AO27" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS27" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT27" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV27" t="n">
         <v>9.4</v>
       </c>
       <c r="AW27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX27" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AY27" t="n">
         <v>22</v>
@@ -5748,29 +5748,29 @@
         <v>22</v>
       </c>
       <c r="BA27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB27" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF27" t="n">
         <v>15.5</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>15</v>
       </c>
       <c r="BG27" t="n">
         <v>10</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -5810,34 +5810,34 @@
         <v>3.15</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J28" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="K28" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="L28" t="n">
         <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O28" t="n">
         <v>1.49</v>
       </c>
       <c r="P28" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
         <v>4.5</v>
@@ -5846,16 +5846,16 @@
         <v>1.87</v>
       </c>
       <c r="U28" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="V28" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W28" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="X28" t="n">
-        <v>980</v>
+        <v>90</v>
       </c>
       <c r="Y28" t="n">
         <v>980</v>
@@ -5864,7 +5864,7 @@
         <v>980</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB28" t="n">
         <v>980</v>
@@ -5876,7 +5876,7 @@
         <v>980</v>
       </c>
       <c r="AE28" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AF28" t="n">
         <v>980</v>
@@ -5888,7 +5888,7 @@
         <v>980</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AJ28" t="n">
         <v>980</v>
@@ -5897,7 +5897,7 @@
         <v>980</v>
       </c>
       <c r="AL28" t="n">
-        <v>70</v>
+        <v>230</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
@@ -5909,62 +5909,62 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="AR28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BB28" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BC28" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>5</v>
+        <v>2.84</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.7</v>
+        <v>2.22</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K29" t="n">
         <v>950</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.21</v>
+        <v>2.06</v>
       </c>
       <c r="G30" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="H30" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="I30" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J30" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="K30" t="n">
-        <v>110</v>
+        <v>3.9</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -6213,31 +6213,31 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.5</v>
+        <v>2.08</v>
       </c>
       <c r="O30" t="n">
         <v>1.44</v>
       </c>
       <c r="P30" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q30" t="n">
         <v>2.16</v>
       </c>
       <c r="R30" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S30" t="n">
         <v>3.9</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="U30" t="n">
         <v>1.71</v>
       </c>
       <c r="V30" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="W30" t="n">
         <v>1.8</v>
@@ -6297,62 +6297,62 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
         <v>2.82</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="L31" t="n">
         <v>1.65</v>
@@ -6407,16 +6407,16 @@
         <v>1.16</v>
       </c>
       <c r="N31" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="O31" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="P31" t="n">
         <v>1.44</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="R31" t="n">
         <v>1.15</v>
@@ -6425,10 +6425,10 @@
         <v>6.6</v>
       </c>
       <c r="T31" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="U31" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="V31" t="n">
         <v>1.27</v>
@@ -6437,16 +6437,16 @@
         <v>1.73</v>
       </c>
       <c r="X31" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="Y31" t="n">
         <v>10.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB31" t="n">
         <v>6.6</v>
@@ -6455,10 +6455,10 @@
         <v>7</v>
       </c>
       <c r="AD31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF31" t="n">
         <v>12.5</v>
@@ -6470,43 +6470,43 @@
         <v>48</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ31" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AK31" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM31" t="n">
         <v>320</v>
       </c>
       <c r="AN31" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP31" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AQ31" t="n">
         <v>9.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AT31" t="n">
         <v>6</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV31" t="n">
         <v>18</v>
@@ -6515,38 +6515,38 @@
         <v>36</v>
       </c>
       <c r="AX31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY31" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BA31" t="n">
         <v>42</v>
       </c>
       <c r="BB31" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="BC31" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BD31" t="n">
         <v>60</v>
       </c>
       <c r="BE31" t="n">
-        <v>13.5</v>
+        <v>65</v>
       </c>
       <c r="BF31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG31" t="n">
         <v>44</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -6583,16 +6583,16 @@
         <v>3.15</v>
       </c>
       <c r="H32" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I32" t="n">
         <v>3.35</v>
       </c>
       <c r="J32" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="K32" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -6607,10 +6607,10 @@
         <v>1.97</v>
       </c>
       <c r="P32" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="R32" t="n">
         <v>1.09</v>
@@ -6622,7 +6622,7 @@
         <v>2.96</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="V32" t="n">
         <v>1.42</v>
@@ -6631,22 +6631,22 @@
         <v>1.47</v>
       </c>
       <c r="X32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y32" t="n">
         <v>7.6</v>
       </c>
       <c r="Z32" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA32" t="n">
         <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD32" t="n">
         <v>34</v>
@@ -6655,25 +6655,25 @@
         <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG32" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AH32" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AJ32" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
         <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AM32" t="n">
         <v>1000</v>
@@ -6685,19 +6685,19 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR32" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AT32" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU32" t="n">
         <v>6.4</v>
@@ -6730,17 +6730,17 @@
         <v>46</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.7</v>
+        <v>70</v>
       </c>
       <c r="BF32" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BG32" t="n">
         <v>36</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -6771,170 +6771,170 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="G33" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="H33" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="I33" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="J33" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K33" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="L33" t="n">
         <v>1.41</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N33" t="n">
-        <v>1.52</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="P33" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="R33" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S33" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V33" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W33" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP33" t="n">
         <v>9</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AR33" t="n">
-        <v>21</v>
+        <v>4.8</v>
       </c>
       <c r="AS33" t="n">
-        <v>50</v>
+        <v>5.3</v>
       </c>
       <c r="AT33" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU33" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>46</v>
+        <v>5.2</v>
       </c>
       <c r="AX33" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AY33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ33" t="n">
-        <v>18.5</v>
+        <v>4.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>50</v>
+        <v>5.2</v>
       </c>
       <c r="BB33" t="n">
-        <v>18.5</v>
+        <v>4.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>19</v>
+        <v>4.6</v>
       </c>
       <c r="BD33" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="BE33" t="n">
-        <v>50</v>
+        <v>5.3</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -6968,22 +6968,22 @@
         <v>2.18</v>
       </c>
       <c r="G34" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H34" t="n">
         <v>3.4</v>
       </c>
       <c r="I34" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J34" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="K34" t="n">
         <v>4.1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M34" t="n">
         <v>1.01</v>
@@ -7013,55 +7013,55 @@
         <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W34" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF34" t="n">
         <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AH34" t="n">
         <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM34" t="n">
         <v>1000</v>
@@ -7073,62 +7073,62 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="AQ34" t="n">
-        <v>8.199999999999999</v>
+        <v>1.28</v>
       </c>
       <c r="AR34" t="n">
-        <v>16.5</v>
+        <v>1.29</v>
       </c>
       <c r="AS34" t="n">
-        <v>40</v>
+        <v>1.3</v>
       </c>
       <c r="AT34" t="n">
-        <v>6.6</v>
+        <v>1.27</v>
       </c>
       <c r="AU34" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>11</v>
+        <v>1.28</v>
       </c>
       <c r="AW34" t="n">
-        <v>34</v>
+        <v>1.3</v>
       </c>
       <c r="AX34" t="n">
-        <v>9.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AY34" t="n">
-        <v>9.4</v>
+        <v>1.27</v>
       </c>
       <c r="AZ34" t="n">
-        <v>18</v>
+        <v>1.3</v>
       </c>
       <c r="BA34" t="n">
-        <v>46</v>
+        <v>1.3</v>
       </c>
       <c r="BB34" t="n">
-        <v>25</v>
+        <v>1.29</v>
       </c>
       <c r="BC34" t="n">
-        <v>24</v>
+        <v>1.29</v>
       </c>
       <c r="BD34" t="n">
-        <v>40</v>
+        <v>1.29</v>
       </c>
       <c r="BE34" t="n">
-        <v>50</v>
+        <v>1.3</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -7159,22 +7159,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7183,34 +7183,34 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.02</v>
+        <v>1.6</v>
       </c>
       <c r="O35" t="n">
         <v>1.38</v>
       </c>
       <c r="P35" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R35" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S35" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
         <v>2.18</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K36" t="n">
         <v>3.45</v>
@@ -7509,14 +7509,14 @@
         <v>5.2</v>
       </c>
       <c r="BF36" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG36" t="n">
         <v>4.5</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
         <v>1.13</v>
       </c>
       <c r="N37" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="O37" t="n">
         <v>1.58</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -7849,7 +7849,7 @@
         <v>34</v>
       </c>
       <c r="AP38" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ38" t="n">
         <v>7.4</v>
@@ -7870,7 +7870,7 @@
         <v>11.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX38" t="n">
         <v>19.5</v>
@@ -7897,14 +7897,14 @@
         <v>46</v>
       </c>
       <c r="BF38" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BG38" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -7938,13 +7938,13 @@
         <v>6.2</v>
       </c>
       <c r="G39" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="H39" t="n">
         <v>1.61</v>
       </c>
       <c r="I39" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="J39" t="n">
         <v>3.6</v>
@@ -7974,7 +7974,7 @@
         <v>1.27</v>
       </c>
       <c r="S39" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T39" t="n">
         <v>2.06</v>
@@ -7983,10 +7983,10 @@
         <v>1.77</v>
       </c>
       <c r="V39" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="W39" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X39" t="n">
         <v>15</v>
@@ -8067,25 +8067,25 @@
         <v>17</v>
       </c>
       <c r="AX39" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY39" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ39" t="n">
         <v>21</v>
       </c>
       <c r="BA39" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB39" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC39" t="n">
         <v>5.6</v>
       </c>
-      <c r="BC39" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BD39" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE39" t="n">
         <v>5.6</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH39"/>
+  <dimension ref="A1:BH38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="G2" t="n">
         <v>24</v>
@@ -766,7 +766,7 @@
         <v>1.22</v>
       </c>
       <c r="I2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
         <v>4.2</v>
@@ -796,7 +796,7 @@
         <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="T2" t="n">
         <v>1.05</v>
@@ -805,7 +805,7 @@
         <v>1.05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.78</v>
+        <v>2.48</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
@@ -865,28 +865,28 @@
         <v>29</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AT2" t="n">
         <v>4.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AX2" t="n">
         <v>4.2</v>
@@ -895,10 +895,10 @@
         <v>4.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="BB2" t="n">
         <v>4.2</v>
@@ -910,7 +910,7 @@
         <v>4.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="BF2" t="n">
         <v>4.2</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>4.1</v>
       </c>
       <c r="H3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I3" t="n">
         <v>2.2</v>
@@ -966,10 +966,10 @@
         <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -984,16 +984,16 @@
         <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
         <v>2.12</v>
@@ -1041,7 +1041,7 @@
         <v>95</v>
       </c>
       <c r="AJ3" t="n">
-        <v>900</v>
+        <v>260</v>
       </c>
       <c r="AK3" t="n">
         <v>260</v>
@@ -1071,7 +1071,7 @@
         <v>21</v>
       </c>
       <c r="AT3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
         <v>7.2</v>
@@ -1083,7 +1083,7 @@
         <v>18.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="AY3" t="n">
         <v>13.5</v>
@@ -1104,7 +1104,7 @@
         <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BF3" t="n">
         <v>36</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -1151,10 +1151,10 @@
         <v>1.42</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J4" t="n">
         <v>4.8</v>
@@ -1169,7 +1169,7 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O4" t="n">
         <v>1.29</v>
@@ -1178,7 +1178,7 @@
         <v>1.99</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R4" t="n">
         <v>1.38</v>
@@ -1199,22 +1199,22 @@
         <v>3.35</v>
       </c>
       <c r="X4" t="n">
-        <v>19.5</v>
+        <v>90</v>
       </c>
       <c r="Y4" t="n">
         <v>980</v>
       </c>
       <c r="Z4" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AC4" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AD4" t="n">
         <v>980</v>
@@ -1223,13 +1223,13 @@
         <v>230</v>
       </c>
       <c r="AF4" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="AG4" t="n">
         <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>80</v>
+        <v>980</v>
       </c>
       <c r="AI4" t="n">
         <v>520</v>
@@ -1238,77 +1238,77 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="AL4" t="n">
-        <v>170</v>
+        <v>980</v>
       </c>
       <c r="AM4" t="n">
         <v>240</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
         <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>30</v>
+        <v>4.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT4" t="n">
         <v>6.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX4" t="n">
         <v>6.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G5" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="H5" t="n">
         <v>3.4</v>
@@ -1351,28 +1351,28 @@
         <v>3.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P5" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.27</v>
@@ -1381,7 +1381,7 @@
         <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U5" t="n">
         <v>1.96</v>
@@ -1390,7 +1390,7 @@
         <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="X5" t="n">
         <v>24</v>
@@ -1408,7 +1408,7 @@
         <v>16.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
         <v>30</v>
@@ -1420,13 +1420,13 @@
         <v>38</v>
       </c>
       <c r="AG5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH5" t="n">
         <v>60</v>
       </c>
       <c r="AI5" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
         <v>900</v>
@@ -1435,7 +1435,7 @@
         <v>980</v>
       </c>
       <c r="AL5" t="n">
-        <v>290</v>
+        <v>980</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
@@ -1447,16 +1447,16 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
         <v>5.1</v>
@@ -1465,44 +1465,44 @@
         <v>4.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AX5" t="n">
         <v>7.6</v>
       </c>
       <c r="AY5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF5" t="n">
         <v>7</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG5" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
         <v>1.32</v>
@@ -1566,94 +1566,94 @@
         <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="n">
         <v>2.14</v>
       </c>
       <c r="V6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="X6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG6" t="n">
         <v>11</v>
       </c>
-      <c r="AC6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG6" t="n">
+      <c r="AH6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>980</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>330</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>11</v>
-      </c>
       <c r="AR6" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU6" t="n">
         <v>7.4</v>
@@ -1662,19 +1662,19 @@
         <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
         <v>9</v>
       </c>
       <c r="BA6" t="n">
-        <v>36</v>
+        <v>9.6</v>
       </c>
       <c r="BB6" t="n">
         <v>11.5</v>
@@ -1686,17 +1686,17 @@
         <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BF6" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BG6" t="n">
         <v>9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
         <v>4.3</v>
@@ -1760,7 +1760,7 @@
         <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="R7" t="n">
         <v>1.6</v>
@@ -1769,7 +1769,7 @@
         <v>2.42</v>
       </c>
       <c r="T7" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="U7" t="n">
         <v>2.48</v>
@@ -1778,10 +1778,10 @@
         <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="X7" t="n">
-        <v>75</v>
+        <v>980</v>
       </c>
       <c r="Y7" t="n">
         <v>980</v>
@@ -1790,19 +1790,19 @@
         <v>980</v>
       </c>
       <c r="AA7" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AB7" t="n">
         <v>980</v>
       </c>
       <c r="AC7" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="AD7" t="n">
         <v>980</v>
       </c>
       <c r="AE7" t="n">
-        <v>980</v>
+        <v>170</v>
       </c>
       <c r="AF7" t="n">
         <v>980</v>
@@ -1832,65 +1832,65 @@
         <v>55</v>
       </c>
       <c r="AO7" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.199999999999999</v>
+        <v>2.28</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.4</v>
+        <v>2.68</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>28</v>
+        <v>2.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>3.7</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.15</v>
+        <v>2.18</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.6</v>
+        <v>3.55</v>
       </c>
       <c r="AY7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8.4</v>
+        <v>2.92</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>2.14</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.6</v>
+        <v>2.56</v>
       </c>
       <c r="BC7" t="n">
-        <v>7</v>
+        <v>3.65</v>
       </c>
       <c r="BD7" t="n">
-        <v>8</v>
+        <v>2.72</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.25</v>
+        <v>2.18</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.1</v>
+        <v>2.12</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>3.25</v>
       </c>
       <c r="G8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H8" t="n">
         <v>2.14</v>
@@ -1933,10 +1933,10 @@
         <v>2.32</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
         <v>1.31</v>
@@ -1954,7 +1954,7 @@
         <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
         <v>1.45</v>
@@ -2002,7 +2002,7 @@
         <v>980</v>
       </c>
       <c r="AG8" t="n">
-        <v>30</v>
+        <v>980</v>
       </c>
       <c r="AH8" t="n">
         <v>60</v>
@@ -2032,59 +2032,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AR8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BE8" t="n">
         <v>3</v>
       </c>
-      <c r="AT8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BC8" t="n">
+      <c r="BF8" t="n">
         <v>2.56</v>
       </c>
-      <c r="BD8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5</v>
-      </c>
       <c r="BG8" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="H9" t="n">
         <v>1.47</v>
@@ -2127,10 +2127,10 @@
         <v>1.51</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.4</v>
@@ -2139,13 +2139,13 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O9" t="n">
         <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
         <v>1.94</v>
@@ -2157,7 +2157,7 @@
         <v>3.45</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
         <v>1.76</v>
@@ -2166,43 +2166,43 @@
         <v>2.94</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y9" t="n">
         <v>7.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AB9" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AC9" t="n">
         <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>85</v>
+        <v>420</v>
       </c>
       <c r="AG9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AH9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI9" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AJ9" t="n">
         <v>350</v>
@@ -2220,34 +2220,34 @@
         <v>290</v>
       </c>
       <c r="AO9" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>6.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
         <v>21</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>50</v>
+        <v>10.5</v>
       </c>
       <c r="AY9" t="n">
         <v>22</v>
@@ -2256,29 +2256,29 @@
         <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BD9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -2318,22 +2318,22 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J10" t="n">
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M10" t="n">
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
         <v>1.45</v>
@@ -2342,7 +2342,7 @@
         <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
@@ -2354,10 +2354,10 @@
         <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V10" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="W10" t="n">
         <v>1.27</v>
@@ -2417,10 +2417,10 @@
         <v>21</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR10" t="n">
         <v>10</v>
@@ -2444,19 +2444,19 @@
         <v>29</v>
       </c>
       <c r="AY10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB10" t="n">
         <v>100</v>
       </c>
       <c r="BC10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BD10" t="n">
         <v>75</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>2.62</v>
       </c>
       <c r="G11" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>3.05</v>
@@ -2527,7 +2527,7 @@
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O11" t="n">
         <v>1.44</v>
@@ -2536,16 +2536,16 @@
         <v>1.64</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R11" t="n">
         <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T11" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U11" t="n">
         <v>1.94</v>
@@ -2554,7 +2554,7 @@
         <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X11" t="n">
         <v>10.5</v>
@@ -2566,16 +2566,16 @@
         <v>38</v>
       </c>
       <c r="AA11" t="n">
-        <v>150</v>
+        <v>340</v>
       </c>
       <c r="AB11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC11" t="n">
         <v>7.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
         <v>190</v>
@@ -2590,13 +2590,13 @@
         <v>50</v>
       </c>
       <c r="AI11" t="n">
-        <v>160</v>
+        <v>380</v>
       </c>
       <c r="AJ11" t="n">
-        <v>980</v>
+        <v>280</v>
       </c>
       <c r="AK11" t="n">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="AL11" t="n">
         <v>150</v>
@@ -2605,22 +2605,22 @@
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>9</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="AT11" t="n">
         <v>8</v>
@@ -2629,44 +2629,44 @@
         <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AX11" t="n">
         <v>14</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="BA11" t="n">
         <v>28</v>
       </c>
       <c r="BB11" t="n">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="BC11" t="n">
         <v>30</v>
       </c>
       <c r="BD11" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="BE11" t="n">
-        <v>28</v>
+        <v>12.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG11" t="n">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G12" t="n">
         <v>2.58</v>
@@ -2739,10 +2739,10 @@
         <v>4.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.04</v>
+        <v>1.05</v>
       </c>
       <c r="U12" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V12" t="n">
         <v>1.37</v>
@@ -2772,7 +2772,7 @@
         <v>980</v>
       </c>
       <c r="AE12" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AF12" t="n">
         <v>980</v>
@@ -2784,7 +2784,7 @@
         <v>980</v>
       </c>
       <c r="AI12" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AJ12" t="n">
         <v>980</v>
@@ -2793,16 +2793,16 @@
         <v>980</v>
       </c>
       <c r="AL12" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN12" t="n">
         <v>980</v>
       </c>
       <c r="AO12" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AP12" t="n">
         <v>4.5</v>
@@ -2814,10 +2814,10 @@
         <v>6.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AU12" t="n">
         <v>4.2</v>
@@ -2838,7 +2838,7 @@
         <v>6.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
@@ -2847,7 +2847,7 @@
         <v>6.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE12" t="n">
         <v>8</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="G13" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="H13" t="n">
         <v>7.6</v>
@@ -2906,7 +2906,7 @@
         <v>5.2</v>
       </c>
       <c r="K13" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.23</v>
@@ -2921,7 +2921,7 @@
         <v>1.16</v>
       </c>
       <c r="P13" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
         <v>1.43</v>
@@ -2933,7 +2933,7 @@
         <v>2.08</v>
       </c>
       <c r="T13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U13" t="n">
         <v>2</v>
@@ -2942,7 +2942,7 @@
         <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2999,7 +2999,7 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AQ13" t="n">
         <v>30</v>
@@ -3011,10 +3011,10 @@
         <v>4.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.8</v>
+        <v>2.26</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.82</v>
+        <v>1.99</v>
       </c>
       <c r="AV13" t="n">
         <v>4.2</v>
@@ -3023,38 +3023,38 @@
         <v>4.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>4</v>
+        <v>2.24</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="BA13" t="n">
         <v>4.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.85</v>
+        <v>2.08</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.08</v>
+        <v>1.79</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="G14" t="n">
         <v>3.6</v>
@@ -3094,13 +3094,13 @@
         <v>2.32</v>
       </c>
       <c r="I14" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="L14" t="n">
         <v>1.35</v>
@@ -3109,16 +3109,16 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R14" t="n">
         <v>1.32</v>
@@ -3127,19 +3127,19 @@
         <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.74</v>
+        <v>1.05</v>
       </c>
       <c r="U14" t="n">
-        <v>2.06</v>
+        <v>1.05</v>
       </c>
       <c r="V14" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="Y14" t="n">
         <v>1000</v>
@@ -3148,7 +3148,7 @@
         <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
         <v>1000</v>
@@ -3175,7 +3175,7 @@
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
         <v>1000</v>
@@ -3202,7 +3202,7 @@
         <v>7.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT14" t="n">
         <v>6.2</v>
@@ -3214,41 +3214,41 @@
         <v>7.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AY14" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="BE14" t="n">
         <v>2.44</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BG14" t="n">
         <v>6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G15" t="n">
         <v>2.06</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="I15" t="n">
         <v>6.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
         <v>4.9</v>
@@ -3306,34 +3306,34 @@
         <v>3.35</v>
       </c>
       <c r="O15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T15" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U15" t="n">
         <v>2.04</v>
       </c>
       <c r="V15" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="X15" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
         <v>1000</v>
@@ -3357,7 +3357,7 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AG15" t="n">
         <v>40</v>
@@ -3393,10 +3393,10 @@
         <v>15</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.6</v>
+        <v>2.78</v>
       </c>
       <c r="AT15" t="n">
         <v>5.1</v>
@@ -3405,10 +3405,10 @@
         <v>5.1</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.1</v>
+        <v>2.74</v>
       </c>
       <c r="AX15" t="n">
         <v>5.8</v>
@@ -3417,32 +3417,32 @@
         <v>7</v>
       </c>
       <c r="AZ15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE15" t="n">
         <v>4.1</v>
       </c>
-      <c r="BA15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BF15" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.55</v>
+        <v>2.34</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -3482,13 +3482,13 @@
         <v>1.78</v>
       </c>
       <c r="I16" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="J16" t="n">
         <v>3.95</v>
       </c>
       <c r="K16" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="L16" t="n">
         <v>1.31</v>
@@ -3503,10 +3503,10 @@
         <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="R16" t="n">
         <v>1.47</v>
@@ -3521,7 +3521,7 @@
         <v>2.2</v>
       </c>
       <c r="V16" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="W16" t="n">
         <v>1.27</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="G17" t="n">
         <v>2.64</v>
       </c>
       <c r="H17" t="n">
-        <v>2.48</v>
+        <v>2.86</v>
       </c>
       <c r="I17" t="n">
-        <v>110</v>
+        <v>11.5</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="K17" t="n">
         <v>4.2</v>
@@ -3775,10 +3775,10 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AR17" t="n">
         <v>1.13</v>
@@ -3787,7 +3787,7 @@
         <v>1.14</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AU17" t="n">
         <v>1.14</v>
@@ -3799,7 +3799,7 @@
         <v>1.14</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AY17" t="n">
         <v>1.12</v>
@@ -3811,16 +3811,16 @@
         <v>1.14</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BF17" t="n">
         <v>1.55</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>2.18</v>
       </c>
       <c r="G18" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H18" t="n">
         <v>3.05</v>
@@ -3885,7 +3885,7 @@
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O18" t="n">
         <v>1.2</v>
@@ -3897,52 +3897,52 @@
         <v>1.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S18" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="T18" t="n">
         <v>1.57</v>
       </c>
       <c r="U18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
         <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X18" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Y18" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Z18" t="n">
         <v>26</v>
       </c>
       <c r="AA18" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB18" t="n">
         <v>14</v>
       </c>
       <c r="AC18" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>14.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AF18" t="n">
         <v>17.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH18" t="n">
         <v>15.5</v>
@@ -3951,19 +3951,19 @@
         <v>85</v>
       </c>
       <c r="AJ18" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AK18" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL18" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AM18" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AO18" t="n">
         <v>27</v>
@@ -3972,13 +3972,13 @@
         <v>19.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="AT18" t="n">
         <v>12</v>
@@ -4002,13 +4002,13 @@
         <v>13</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BB18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD18" t="n">
         <v>21</v>
@@ -4017,14 +4017,14 @@
         <v>30</v>
       </c>
       <c r="BF18" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="G19" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
@@ -4106,19 +4106,19 @@
         <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X19" t="n">
         <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z19" t="n">
         <v>40</v>
       </c>
       <c r="AA19" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AB19" t="n">
         <v>11.5</v>
@@ -4127,10 +4127,10 @@
         <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE19" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF19" t="n">
         <v>13</v>
@@ -4142,7 +4142,7 @@
         <v>18.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ19" t="n">
         <v>21</v>
@@ -4157,22 +4157,22 @@
         <v>200</v>
       </c>
       <c r="AN19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO19" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ19" t="n">
         <v>17</v>
       </c>
       <c r="AR19" t="n">
-        <v>30</v>
+        <v>7.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
@@ -4181,7 +4181,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW19" t="n">
         <v>44</v>
@@ -4199,7 +4199,7 @@
         <v>44</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.4</v>
+        <v>17</v>
       </c>
       <c r="BC19" t="n">
         <v>15</v>
@@ -4208,17 +4208,17 @@
         <v>25</v>
       </c>
       <c r="BE19" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BF19" t="n">
         <v>7.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -4252,16 +4252,16 @@
         <v>2.18</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H20" t="n">
         <v>4.8</v>
       </c>
       <c r="I20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K20" t="n">
         <v>2.9</v>
@@ -4300,16 +4300,16 @@
         <v>1.23</v>
       </c>
       <c r="W20" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X20" t="n">
         <v>7</v>
       </c>
       <c r="Y20" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z20" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="AA20" t="n">
         <v>700</v>
@@ -4318,10 +4318,10 @@
         <v>6.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AE20" t="n">
         <v>700</v>
@@ -4357,62 +4357,62 @@
         <v>700</v>
       </c>
       <c r="AP20" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AR20" t="n">
         <v>8.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT20" t="n">
         <v>5.3</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="AW20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX20" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>5.8</v>
       </c>
       <c r="AY20" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC20" t="n">
         <v>7.4</v>
       </c>
-      <c r="BA20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BD20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BF20" t="n">
         <v>8</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -4443,19 +4443,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G21" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="H21" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I21" t="n">
         <v>3.35</v>
       </c>
       <c r="J21" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K21" t="n">
         <v>2.94</v>
@@ -4476,13 +4476,13 @@
         <v>1.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S21" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T21" t="n">
         <v>2.12</v>
@@ -4494,13 +4494,13 @@
         <v>1.42</v>
       </c>
       <c r="W21" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X21" t="n">
         <v>8.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z21" t="n">
         <v>21</v>
@@ -4536,16 +4536,16 @@
         <v>48</v>
       </c>
       <c r="AK21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL21" t="n">
         <v>75</v>
       </c>
       <c r="AM21" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AO21" t="n">
         <v>65</v>
@@ -4557,10 +4557,10 @@
         <v>7.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
-        <v>20</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT21" t="n">
         <v>7</v>
@@ -4572,7 +4572,7 @@
         <v>12.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX21" t="n">
         <v>14.5</v>
@@ -4581,13 +4581,13 @@
         <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB21" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="BC21" t="n">
         <v>18</v>
@@ -4596,24 +4596,24 @@
         <v>9</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="BG21" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Amiens</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ESTAC Troyes</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.3</v>
+        <v>1.89</v>
       </c>
       <c r="G22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H22" t="n">
         <v>4.7</v>
       </c>
-      <c r="H22" t="n">
-        <v>1.91</v>
-      </c>
       <c r="I22" t="n">
-        <v>1.95</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="O22" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.89</v>
+        <v>2.46</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="T22" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="V22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W22" t="n">
         <v>2.04</v>
       </c>
-      <c r="W22" t="n">
-        <v>1.27</v>
-      </c>
       <c r="X22" t="n">
-        <v>26</v>
+        <v>10.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="Z22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>230</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>22</v>
       </c>
-      <c r="AA22" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>110</v>
-      </c>
       <c r="AK22" t="n">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="AL22" t="n">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="AM22" t="n">
-        <v>580</v>
+        <v>250</v>
       </c>
       <c r="AN22" t="n">
-        <v>270</v>
+        <v>25</v>
       </c>
       <c r="AO22" t="n">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="AP22" t="n">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AR22" t="n">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="AS22" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU22" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE22" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BF22" t="n">
         <v>8.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.9</v>
+        <v>3.35</v>
       </c>
       <c r="G23" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="H23" t="n">
-        <v>4.8</v>
+        <v>2.48</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="K23" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="U23" t="n">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="V23" t="n">
-        <v>1.23</v>
+        <v>1.66</v>
       </c>
       <c r="W23" t="n">
-        <v>2.04</v>
+        <v>1.41</v>
       </c>
       <c r="X23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP23" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AQ23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR23" t="n">
         <v>14</v>
       </c>
-      <c r="Z23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>230</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG23" t="n">
+      <c r="AS23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT23" t="n">
         <v>11</v>
       </c>
-      <c r="AH23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AU23" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AW23" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="AX23" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9.6</v>
+        <v>17</v>
       </c>
       <c r="BA23" t="n">
-        <v>12.5</v>
+        <v>38</v>
       </c>
       <c r="BB23" t="n">
-        <v>19.5</v>
+        <v>55</v>
       </c>
       <c r="BC23" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BD23" t="n">
-        <v>11.5</v>
+        <v>50</v>
       </c>
       <c r="BE23" t="n">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="BF23" t="n">
-        <v>17.5</v>
+        <v>40</v>
       </c>
       <c r="BG23" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Zeljeznicar</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="G24" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="H24" t="n">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="J24" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="K24" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L24" t="n">
         <v>1.48</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="O24" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="P24" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="V24" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA24" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AB24" t="n">
         <v>12</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH24" t="n">
         <v>28</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AI24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>230</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>22</v>
       </c>
-      <c r="AG24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ24" t="n">
+      <c r="BA24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD24" t="n">
         <v>9</v>
       </c>
-      <c r="AR24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>38</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>50</v>
-      </c>
       <c r="BE24" t="n">
-        <v>60</v>
+        <v>9.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>40</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG24" t="n">
-        <v>23</v>
+        <v>7.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bosnian Premier League</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Zeljeznicar</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H25" t="n">
+        <v>12</v>
+      </c>
+      <c r="I25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N25" t="n">
         <v>3.9</v>
       </c>
-      <c r="G25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="O25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q25" t="n">
         <v>2.02</v>
       </c>
-      <c r="I25" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.58</v>
-      </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="S25" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="U25" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="V25" t="n">
-        <v>1.78</v>
+        <v>1.08</v>
       </c>
       <c r="W25" t="n">
-        <v>1.24</v>
+        <v>3.75</v>
       </c>
       <c r="X25" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="Y25" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>620</v>
+      </c>
+      <c r="AB25" t="n">
         <v>6.8</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AC25" t="n">
         <v>12</v>
       </c>
-      <c r="AA25" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AD25" t="n">
-        <v>12.5</v>
+        <v>55</v>
       </c>
       <c r="AE25" t="n">
-        <v>34</v>
+        <v>280</v>
       </c>
       <c r="AF25" t="n">
-        <v>34</v>
+        <v>6.6</v>
       </c>
       <c r="AG25" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AI25" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AJ25" t="n">
-        <v>900</v>
+        <v>10.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>230</v>
+        <v>16.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>290</v>
+        <v>50</v>
       </c>
       <c r="AM25" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="AN25" t="n">
-        <v>180</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="n">
+        <v>470</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>90</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>130</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>36</v>
       </c>
-      <c r="AP25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BA25" t="n">
-        <v>8.6</v>
+        <v>55</v>
       </c>
       <c r="BB25" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BC25" t="n">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="BD25" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.4</v>
+        <v>270</v>
       </c>
       <c r="BF25" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>7.6</v>
+        <v>130</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.36</v>
+        <v>6.4</v>
       </c>
       <c r="G26" t="n">
-        <v>1.37</v>
+        <v>6.8</v>
       </c>
       <c r="H26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X26" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP26" t="n">
         <v>12.5</v>
       </c>
-      <c r="I26" t="n">
-        <v>13</v>
-      </c>
-      <c r="J26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X26" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y26" t="n">
+      <c r="AQ26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD26" t="n">
         <v>29</v>
       </c>
-      <c r="Z26" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>640</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>280</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK26" t="n">
+      <c r="BE26" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF26" t="n">
         <v>16.5</v>
       </c>
-      <c r="AL26" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>290</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>470</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>130</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>65</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>34</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>260</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG26" t="n">
-        <v>130</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>6.2</v>
+        <v>2.52</v>
       </c>
       <c r="G27" t="n">
-        <v>6.6</v>
+        <v>2.82</v>
       </c>
       <c r="H27" t="n">
-        <v>1.64</v>
+        <v>3.1</v>
       </c>
       <c r="I27" t="n">
-        <v>1.66</v>
+        <v>3.75</v>
       </c>
       <c r="J27" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="K27" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L27" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M27" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="N27" t="n">
-        <v>3.65</v>
+        <v>2.54</v>
       </c>
       <c r="O27" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="P27" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="Q27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X27" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AY27" t="n">
         <v>2.06</v>
       </c>
-      <c r="R27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T27" t="n">
+      <c r="AZ27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BC27" t="n">
         <v>2.06</v>
       </c>
-      <c r="U27" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X27" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>200</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>150</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>40</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>28</v>
-      </c>
       <c r="BD27" t="n">
-        <v>29</v>
+        <v>1.98</v>
       </c>
       <c r="BE27" t="n">
-        <v>42</v>
+        <v>2.08</v>
       </c>
       <c r="BF27" t="n">
-        <v>15.5</v>
+        <v>1.88</v>
       </c>
       <c r="BG27" t="n">
-        <v>10</v>
+        <v>1.86</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,186 +5792,186 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Lobos UPNFM</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="G28" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="K28" t="n">
-        <v>3.25</v>
+        <v>950</v>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>2.54</v>
+        <v>1.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="P28" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.44</v>
+        <v>1.26</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>4.5</v>
+        <v>1.26</v>
       </c>
       <c r="T28" t="n">
-        <v>1.87</v>
+        <v>1.05</v>
       </c>
       <c r="U28" t="n">
-        <v>1.77</v>
+        <v>1.05</v>
       </c>
       <c r="V28" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,72 +5981,72 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Genesis Huracan</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>2.26</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="J29" t="n">
-        <v>1.03</v>
+        <v>2.72</v>
       </c>
       <c r="K29" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>1.1</v>
+        <v>2.12</v>
       </c>
       <c r="O29" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="P29" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.26</v>
+        <v>2.18</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S29" t="n">
-        <v>1.26</v>
+        <v>3.9</v>
       </c>
       <c r="T29" t="n">
         <v>1.05</v>
       </c>
       <c r="U29" t="n">
-        <v>1.05</v>
+        <v>1.74</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6064,7 +6064,7 @@
         <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD29" t="n">
         <v>1000</v>
@@ -6094,7 +6094,7 @@
         <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN29" t="n">
         <v>1000</v>
@@ -6103,69 +6103,69 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,184 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="G30" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="H30" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="J30" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="K30" t="n">
-        <v>3.9</v>
+        <v>2.96</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N30" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="O30" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="P30" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.16</v>
+        <v>3.05</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="S30" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="T30" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="U30" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="V30" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W30" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.15</v>
+        <v>6.2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.22</v>
+        <v>20</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.23</v>
+        <v>40</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.21</v>
+        <v>5.9</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.23</v>
+        <v>6.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.22</v>
+        <v>15</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.23</v>
+        <v>36</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.21</v>
+        <v>10.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.2</v>
+        <v>11.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.21</v>
+        <v>23</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.23</v>
+        <v>42</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.22</v>
+        <v>19</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.21</v>
+        <v>27</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.23</v>
+        <v>36</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.23</v>
+        <v>65</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.23</v>
+        <v>30</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.55</v>
+        <v>44</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -6374,186 +6374,186 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="G31" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="H31" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="I31" t="n">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="J31" t="n">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="K31" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="L31" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="N31" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="O31" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="P31" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="Q31" t="n">
         <v>3.05</v>
       </c>
       <c r="R31" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="S31" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="T31" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="V31" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="W31" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="X31" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AA31" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AC31" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AD31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>150</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>310</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>270</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS31" t="n">
         <v>29</v>
       </c>
-      <c r="AE31" t="n">
-        <v>200</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>48</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>180</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>55</v>
-      </c>
       <c r="AT31" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU31" t="n">
         <v>6.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AW31" t="n">
         <v>36</v>
       </c>
       <c r="AX31" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA31" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BB31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC31" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BD31" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="BE31" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="BF31" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="BG31" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,191 +6563,191 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.96</v>
+        <v>1.9</v>
       </c>
       <c r="G32" t="n">
-        <v>3.15</v>
+        <v>2.02</v>
       </c>
       <c r="H32" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="I32" t="n">
-        <v>3.35</v>
+        <v>5.4</v>
       </c>
       <c r="J32" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="K32" t="n">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R32" t="n">
         <v>1.23</v>
       </c>
-      <c r="N32" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.09</v>
-      </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="T32" t="n">
-        <v>2.96</v>
+        <v>2.06</v>
       </c>
       <c r="U32" t="n">
-        <v>1.41</v>
+        <v>1.82</v>
       </c>
       <c r="V32" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="W32" t="n">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="X32" t="n">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="Z32" t="n">
-        <v>27</v>
+        <v>980</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB32" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC32" t="n">
         <v>7.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AF32" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AG32" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="AH32" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AI32" t="n">
-        <v>310</v>
+        <v>380</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL32" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AP32" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="AQ32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT32" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR32" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AU32" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV32" t="n">
-        <v>16.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW32" t="n">
-        <v>48</v>
+        <v>5.2</v>
       </c>
       <c r="AX32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE32" t="n">
         <v>12.5</v>
       </c>
-      <c r="AY32" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>30</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>48</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>70</v>
-      </c>
       <c r="BF32" t="n">
-        <v>34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG32" t="n">
-        <v>36</v>
+        <v>3.7</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Curico Unido</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G33" t="n">
-        <v>2.04</v>
+        <v>2.92</v>
       </c>
       <c r="H33" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="I33" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="K33" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="L33" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="O33" t="n">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="P33" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="R33" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="S33" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T33" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="U33" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="V33" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="W33" t="n">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="X33" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AA33" t="n">
-        <v>900</v>
+        <v>230</v>
       </c>
       <c r="AB33" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC33" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>480</v>
+        <v>150</v>
       </c>
       <c r="AF33" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AG33" t="n">
         <v>12.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AI33" t="n">
-        <v>380</v>
+        <v>310</v>
       </c>
       <c r="AJ33" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AK33" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AL33" t="n">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="AM33" t="n">
-        <v>580</v>
+        <v>180</v>
       </c>
       <c r="AN33" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AO33" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AP33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ33" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="AT33" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU33" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="AX33" t="n">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="AY33" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="BB33" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="BC33" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BG33" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6956,186 +6956,186 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Sportivo San Lorenzo</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Curico Unido</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.18</v>
+        <v>3.05</v>
       </c>
       <c r="G34" t="n">
-        <v>2.98</v>
+        <v>5</v>
       </c>
       <c r="H34" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>5.4</v>
+        <v>990</v>
       </c>
       <c r="J34" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="K34" t="n">
-        <v>4.1</v>
+        <v>980</v>
       </c>
       <c r="L34" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
         <v>1.01</v>
       </c>
-      <c r="N34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="O34" t="n">
+      <c r="AQ34" t="n">
         <v>1.01</v>
       </c>
-      <c r="P34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T34" t="n">
+      <c r="AR34" t="n">
         <v>1.01</v>
       </c>
-      <c r="U34" t="n">
+      <c r="AS34" t="n">
         <v>1.01</v>
       </c>
-      <c r="V34" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X34" t="n">
-        <v>980</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>190</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>980</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>190</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>230</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>310</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>160</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>200</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AT34" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,73 +7145,73 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sportivo San Lorenzo</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="G35" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="H35" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>110</v>
+        <v>3.45</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N35" t="n">
-        <v>1.6</v>
+        <v>2.56</v>
       </c>
       <c r="O35" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="P35" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="R35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W35" t="n">
         <v>1.22</v>
       </c>
-      <c r="S35" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X35" t="n">
         <v>1000</v>
       </c>
@@ -7267,69 +7267,69 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,184 +7339,184 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4.1</v>
+        <v>1.98</v>
       </c>
       <c r="G36" t="n">
-        <v>5.6</v>
+        <v>2.08</v>
       </c>
       <c r="H36" t="n">
-        <v>2.06</v>
+        <v>4.8</v>
       </c>
       <c r="I36" t="n">
-        <v>2.18</v>
+        <v>5.4</v>
       </c>
       <c r="J36" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K36" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L36" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="M36" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N36" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P36" t="n">
         <v>1.51</v>
       </c>
-      <c r="P36" t="n">
-        <v>1.52</v>
-      </c>
       <c r="Q36" t="n">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="R36" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S36" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="T36" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="U36" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="V36" t="n">
-        <v>1.86</v>
+        <v>1.23</v>
       </c>
       <c r="W36" t="n">
-        <v>1.25</v>
+        <v>1.93</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE36" t="n">
         <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL36" t="n">
         <v>1000</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP36" t="n">
-        <v>3.45</v>
+        <v>7.4</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3.15</v>
+        <v>10</v>
       </c>
       <c r="AR36" t="n">
-        <v>3.8</v>
+        <v>22</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.5</v>
+        <v>40</v>
       </c>
       <c r="AT36" t="n">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.25</v>
+        <v>6.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>3.75</v>
+        <v>17</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.6</v>
+        <v>50</v>
       </c>
       <c r="AX36" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="AY36" t="n">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>4.9</v>
+        <v>42</v>
       </c>
       <c r="BB36" t="n">
-        <v>5.1</v>
+        <v>16.5</v>
       </c>
       <c r="BC36" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="BD36" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="BE36" t="n">
-        <v>5.2</v>
+        <v>48</v>
       </c>
       <c r="BF36" t="n">
-        <v>5.1</v>
+        <v>16.5</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.5</v>
+        <v>42</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -7538,186 +7538,186 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.97</v>
+        <v>3.35</v>
       </c>
       <c r="G37" t="n">
-        <v>2.08</v>
+        <v>3.6</v>
       </c>
       <c r="H37" t="n">
-        <v>4.9</v>
+        <v>2.46</v>
       </c>
       <c r="I37" t="n">
-        <v>5.4</v>
+        <v>2.52</v>
       </c>
       <c r="J37" t="n">
         <v>3.15</v>
       </c>
       <c r="K37" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L37" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="M37" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N37" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="O37" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="P37" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.74</v>
+        <v>2.46</v>
       </c>
       <c r="R37" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="S37" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="T37" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="U37" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="V37" t="n">
-        <v>1.23</v>
+        <v>1.65</v>
       </c>
       <c r="W37" t="n">
-        <v>1.93</v>
+        <v>1.39</v>
       </c>
       <c r="X37" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="Y37" t="n">
-        <v>14.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z37" t="n">
-        <v>980</v>
+        <v>14</v>
       </c>
       <c r="AA37" t="n">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="AB37" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC37" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AD37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE37" t="n">
         <v>32</v>
       </c>
-      <c r="AE37" t="n">
-        <v>1000</v>
-      </c>
       <c r="AF37" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="AG37" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="AI37" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AJ37" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO37" t="n">
         <v>34</v>
       </c>
-      <c r="AK37" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>280</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP37" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ37" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ37" t="n">
-        <v>10</v>
-      </c>
       <c r="AR37" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AT37" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="AU37" t="n">
         <v>6.6</v>
       </c>
       <c r="AV37" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AW37" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="AX37" t="n">
-        <v>8.6</v>
+        <v>19.5</v>
       </c>
       <c r="AY37" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA37" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="BB37" t="n">
-        <v>16.5</v>
+        <v>32</v>
       </c>
       <c r="BC37" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BD37" t="n">
         <v>48</v>
       </c>
       <c r="BE37" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF37" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="BG37" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7732,373 +7732,179 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="G38" t="n">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="H38" t="n">
-        <v>2.42</v>
+        <v>1.61</v>
       </c>
       <c r="I38" t="n">
-        <v>2.48</v>
+        <v>1.74</v>
       </c>
       <c r="J38" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="K38" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L38" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="M38" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N38" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="O38" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="P38" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="R38" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="S38" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="T38" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U38" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="V38" t="n">
-        <v>1.67</v>
+        <v>2.34</v>
       </c>
       <c r="W38" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="X38" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>270</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP38" t="n">
         <v>10</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AQ38" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR38" t="n">
         <v>7.8</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AS38" t="n">
         <v>14</v>
       </c>
-      <c r="AA38" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF38" t="n">
+      <c r="AT38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY38" t="n">
         <v>22</v>
       </c>
-      <c r="AG38" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AZ38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA38" t="n">
-        <v>32</v>
+        <v>5.5</v>
       </c>
       <c r="BB38" t="n">
-        <v>30</v>
+        <v>5.8</v>
       </c>
       <c r="BC38" t="n">
-        <v>42</v>
+        <v>5.7</v>
       </c>
       <c r="BD38" t="n">
-        <v>48</v>
+        <v>5.7</v>
       </c>
       <c r="BE38" t="n">
-        <v>46</v>
+        <v>5.8</v>
       </c>
       <c r="BF38" t="n">
-        <v>30</v>
+        <v>5.8</v>
       </c>
       <c r="BG38" t="n">
-        <v>27</v>
+        <v>10.5</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Ecuadorian Serie A</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Independiente (Ecu)</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G39" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J39" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K39" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V39" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X39" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>70</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>270</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>150</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH39" t="inlineStr">
-        <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH38"/>
+  <dimension ref="A1:BH39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="H2" t="n">
         <v>1.22</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="J2" t="n">
         <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.23</v>
@@ -787,16 +787,16 @@
         <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.22</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T2" t="n">
         <v>1.05</v>
@@ -805,7 +805,7 @@
         <v>1.05</v>
       </c>
       <c r="V2" t="n">
-        <v>2.48</v>
+        <v>3.25</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -951,76 +951,76 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G3" t="n">
         <v>4.1</v>
       </c>
       <c r="H3" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
         <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O3" t="n">
         <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
         <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="W3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y3" t="n">
         <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA3" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="AB3" t="n">
         <v>16</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
         <v>11.5</v>
@@ -1029,7 +1029,7 @@
         <v>23</v>
       </c>
       <c r="AF3" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AG3" t="n">
         <v>17</v>
@@ -1044,22 +1044,22 @@
         <v>260</v>
       </c>
       <c r="AK3" t="n">
-        <v>260</v>
+        <v>120</v>
       </c>
       <c r="AL3" t="n">
         <v>130</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>600</v>
+        <v>980</v>
       </c>
       <c r="AO3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>8.800000000000001</v>
@@ -1074,7 +1074,7 @@
         <v>13</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
         <v>9.199999999999999</v>
@@ -1083,7 +1083,7 @@
         <v>18.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY3" t="n">
         <v>13.5</v>
@@ -1092,16 +1092,16 @@
         <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="BB3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE3" t="n">
         <v>38</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="G4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H4" t="n">
         <v>10.5</v>
       </c>
       <c r="I4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J4" t="n">
         <v>4.8</v>
@@ -1163,25 +1163,25 @@
         <v>5.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
         <v>3.25</v>
@@ -1196,7 +1196,7 @@
         <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="X4" t="n">
         <v>90</v>
@@ -1238,16 +1238,16 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL4" t="n">
         <v>980</v>
       </c>
       <c r="AM4" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AN4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1259,10 +1259,10 @@
         <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AT4" t="n">
         <v>6.6</v>
@@ -1271,10 +1271,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="AX4" t="n">
         <v>6.8</v>
@@ -1283,32 +1283,32 @@
         <v>6.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BB4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BC4" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BF4" t="n">
         <v>6.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -1339,67 +1339,67 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="G5" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
         <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="U5" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y5" t="n">
         <v>23</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
@@ -1417,7 +1417,7 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AG5" t="n">
         <v>22</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BA5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB5" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB5" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BC5" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BF5" t="n">
         <v>8</v>
       </c>
-      <c r="BE5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7</v>
-      </c>
       <c r="BG5" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G6" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="I6" t="n">
         <v>3.9</v>
@@ -1548,34 +1548,34 @@
         <v>3.45</v>
       </c>
       <c r="K6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.85</v>
       </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
         <v>1.32</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.34</v>
       </c>
       <c r="P6" t="n">
         <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
         <v>1.37</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="U6" t="n">
         <v>2.14</v>
@@ -1584,10 +1584,10 @@
         <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
         <v>14.5</v>
@@ -1599,10 +1599,10 @@
         <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
         <v>28</v>
@@ -1611,7 +1611,7 @@
         <v>980</v>
       </c>
       <c r="AF6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
@@ -1620,7 +1620,7 @@
         <v>25</v>
       </c>
       <c r="AI6" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="AJ6" t="n">
         <v>90</v>
@@ -1638,7 +1638,7 @@
         <v>34</v>
       </c>
       <c r="AO6" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
         <v>13</v>
@@ -1650,7 +1650,7 @@
         <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
         <v>8.6</v>
@@ -1662,7 +1662,7 @@
         <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AX6" t="n">
         <v>11.5</v>
@@ -1674,7 +1674,7 @@
         <v>9</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB6" t="n">
         <v>11.5</v>
@@ -1686,17 +1686,17 @@
         <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF6" t="n">
         <v>13.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="G7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.19</v>
@@ -1760,13 +1760,13 @@
         <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="R7" t="n">
         <v>1.6</v>
       </c>
       <c r="S7" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
         <v>1.5</v>
@@ -1778,7 +1778,7 @@
         <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
         <v>980</v>
@@ -1814,7 +1814,7 @@
         <v>60</v>
       </c>
       <c r="AI7" t="n">
-        <v>980</v>
+        <v>160</v>
       </c>
       <c r="AJ7" t="n">
         <v>980</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.28</v>
+        <v>5.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AS7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BD7" t="n">
         <v>2.2</v>
       </c>
-      <c r="AT7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>2.72</v>
-      </c>
       <c r="BE7" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G8" t="n">
         <v>3.7</v>
@@ -1930,46 +1930,46 @@
         <v>2.14</v>
       </c>
       <c r="I8" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
         <v>1.76</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="T8" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V8" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W8" t="n">
         <v>1.37</v>
@@ -2032,59 +2032,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="AR8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AT8" t="n">
         <v>5</v>
       </c>
-      <c r="AS8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.95</v>
+        <v>2.84</v>
       </c>
       <c r="AY8" t="n">
         <v>4.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.45</v>
+        <v>2.64</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.4</v>
+        <v>2.76</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="BD8" t="n">
         <v>2.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="BF8" t="n">
         <v>2.56</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -2118,55 +2118,55 @@
         <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="I9" t="n">
         <v>1.51</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
         <v>4.7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="R9" t="n">
         <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
         <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V9" t="n">
         <v>2.94</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
         <v>15.5</v>
@@ -2181,7 +2181,7 @@
         <v>13</v>
       </c>
       <c r="AB9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC9" t="n">
         <v>10.5</v>
@@ -2196,19 +2196,19 @@
         <v>420</v>
       </c>
       <c r="AG9" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="AH9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
         <v>120</v>
       </c>
       <c r="AJ9" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AK9" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AL9" t="n">
         <v>520</v>
@@ -2217,7 +2217,7 @@
         <v>430</v>
       </c>
       <c r="AN9" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AO9" t="n">
         <v>9</v>
@@ -2247,38 +2247,38 @@
         <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="AY9" t="n">
         <v>22</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BB9" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BC9" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG9" t="n">
         <v>7.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -2321,43 +2321,43 @@
         <v>2.04</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
         <v>3.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M10" t="n">
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="W10" t="n">
         <v>1.27</v>
@@ -2366,7 +2366,7 @@
         <v>10.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="Z10" t="n">
         <v>10.5</v>
@@ -2375,7 +2375,7 @@
         <v>23</v>
       </c>
       <c r="AB10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC10" t="n">
         <v>7.4</v>
@@ -2390,7 +2390,7 @@
         <v>32</v>
       </c>
       <c r="AG10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH10" t="n">
         <v>22</v>
@@ -2405,19 +2405,19 @@
         <v>70</v>
       </c>
       <c r="AL10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM10" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN10" t="n">
         <v>120</v>
       </c>
       <c r="AO10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
         <v>7</v>
@@ -2453,26 +2453,26 @@
         <v>42</v>
       </c>
       <c r="BB10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BC10" t="n">
         <v>60</v>
       </c>
       <c r="BD10" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BE10" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BF10" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="BG10" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -2506,55 +2506,55 @@
         <v>2.62</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="H11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I11" t="n">
         <v>3.3</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
         <v>3.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P11" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V11" t="n">
         <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
         <v>10.5</v>
@@ -2563,7 +2563,7 @@
         <v>10.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AA11" t="n">
         <v>340</v>
@@ -2578,7 +2578,7 @@
         <v>14</v>
       </c>
       <c r="AE11" t="n">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="AF11" t="n">
         <v>30</v>
@@ -2593,13 +2593,13 @@
         <v>380</v>
       </c>
       <c r="AJ11" t="n">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="AK11" t="n">
         <v>110</v>
       </c>
       <c r="AL11" t="n">
-        <v>150</v>
+        <v>290</v>
       </c>
       <c r="AM11" t="n">
         <v>580</v>
@@ -2635,7 +2635,7 @@
         <v>29</v>
       </c>
       <c r="AX11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY11" t="n">
         <v>10.5</v>
@@ -2647,26 +2647,26 @@
         <v>28</v>
       </c>
       <c r="BB11" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="BD11" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="BE11" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BF11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -2700,46 +2700,46 @@
         <v>2.4</v>
       </c>
       <c r="G12" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="H12" t="n">
         <v>3.45</v>
       </c>
       <c r="I12" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
         <v>3.25</v>
       </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="M12" t="n">
         <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="O12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="R12" t="n">
         <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.05</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
         <v>1.79</v>
@@ -2748,7 +2748,7 @@
         <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X12" t="n">
         <v>18.5</v>
@@ -2808,13 +2808,13 @@
         <v>4.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AR12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT12" t="n">
         <v>4.4</v>
@@ -2826,41 +2826,41 @@
         <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD12" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BE12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G13" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="H13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I13" t="n">
         <v>12</v>
@@ -2915,34 +2915,34 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
         <v>1.16</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="Q13" t="n">
         <v>1.43</v>
       </c>
       <c r="R13" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="S13" t="n">
         <v>2.08</v>
       </c>
       <c r="T13" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V13" t="n">
         <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2981,7 +2981,7 @@
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
         <v>1000</v>
@@ -2999,7 +2999,7 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AQ13" t="n">
         <v>30</v>
@@ -3011,10 +3011,10 @@
         <v>4.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.26</v>
+        <v>1.75</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.99</v>
+        <v>1.62</v>
       </c>
       <c r="AV13" t="n">
         <v>4.2</v>
@@ -3023,38 +3023,38 @@
         <v>4.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>2.24</v>
+        <v>1.73</v>
       </c>
       <c r="AY13" t="n">
-        <v>5</v>
+        <v>1.61</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="BA13" t="n">
         <v>4.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -3088,43 +3088,43 @@
         <v>3.05</v>
       </c>
       <c r="G14" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
         <v>3.75</v>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="T14" t="n">
         <v>1.05</v>
@@ -3133,10 +3133,10 @@
         <v>1.05</v>
       </c>
       <c r="V14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X14" t="n">
         <v>90</v>
@@ -3199,10 +3199,10 @@
         <v>5.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="AT14" t="n">
         <v>6.2</v>
@@ -3211,34 +3211,34 @@
         <v>4.9</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="AW14" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AX14" t="n">
         <v>6.8</v>
       </c>
-      <c r="AX14" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AY14" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.55</v>
+        <v>2.26</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.4</v>
+        <v>2.26</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.88</v>
+        <v>2.18</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.44</v>
+        <v>1.8</v>
       </c>
       <c r="BF14" t="n">
         <v>7.4</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="G15" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L15" t="n">
         <v>1.39</v>
@@ -3303,22 +3303,22 @@
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
         <v>1.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
         <v>1.79</v>
@@ -3327,13 +3327,13 @@
         <v>2.04</v>
       </c>
       <c r="V15" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="W15" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y15" t="n">
         <v>1000</v>
@@ -3345,7 +3345,7 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AC15" t="n">
         <v>14</v>
@@ -3387,16 +3387,16 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AQ15" t="n">
         <v>15</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.4</v>
+        <v>2.48</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.78</v>
+        <v>1.93</v>
       </c>
       <c r="AT15" t="n">
         <v>5.1</v>
@@ -3405,10 +3405,10 @@
         <v>5.1</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.74</v>
+        <v>1.93</v>
       </c>
       <c r="AX15" t="n">
         <v>5.8</v>
@@ -3417,32 +3417,32 @@
         <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.4</v>
+        <v>2.48</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.1</v>
+        <v>1.96</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H16" t="n">
         <v>1.78</v>
       </c>
       <c r="I16" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="J16" t="n">
         <v>3.95</v>
@@ -3491,37 +3491,37 @@
         <v>4.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U16" t="n">
         <v>2.2</v>
       </c>
       <c r="V16" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W16" t="n">
         <v>1.27</v>
@@ -3533,10 +3533,10 @@
         <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AA16" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
         <v>44</v>
@@ -3581,7 +3581,7 @@
         <v>55</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ16" t="n">
         <v>6.2</v>
@@ -3590,7 +3590,7 @@
         <v>6.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
         <v>10.5</v>
@@ -3602,10 +3602,10 @@
         <v>6.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY16" t="n">
         <v>10.5</v>
@@ -3614,29 +3614,29 @@
         <v>10.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC16" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC16" t="n">
-        <v>7</v>
-      </c>
       <c r="BD16" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG16" t="n">
         <v>7.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -3670,13 +3670,13 @@
         <v>1.8</v>
       </c>
       <c r="G17" t="n">
-        <v>2.64</v>
+        <v>6.2</v>
       </c>
       <c r="H17" t="n">
         <v>2.86</v>
       </c>
       <c r="I17" t="n">
-        <v>11.5</v>
+        <v>27</v>
       </c>
       <c r="J17" t="n">
         <v>3.05</v>
@@ -3697,13 +3697,13 @@
         <v>1.02</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Q17" t="n">
         <v>1.37</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="S17" t="n">
         <v>1.05</v>
@@ -3715,10 +3715,10 @@
         <v>1.71</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.68</v>
+        <v>1.19</v>
       </c>
       <c r="X17" t="n">
         <v>950</v>
@@ -3727,16 +3727,16 @@
         <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB17" t="n">
         <v>980</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD17" t="n">
         <v>950</v>
@@ -3745,7 +3745,7 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AG17" t="n">
         <v>950</v>
@@ -3757,13 +3757,13 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AK17" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AL17" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
         <v>580</v>
@@ -3775,52 +3775,52 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BF17" t="n">
         <v>1.55</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -3861,31 +3861,31 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="H18" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O18" t="n">
         <v>1.2</v>
@@ -3894,25 +3894,25 @@
         <v>2.56</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R18" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="S18" t="n">
-        <v>2.28</v>
+        <v>2.58</v>
       </c>
       <c r="T18" t="n">
         <v>1.57</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W18" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="X18" t="n">
         <v>24</v>
@@ -3924,16 +3924,16 @@
         <v>26</v>
       </c>
       <c r="AA18" t="n">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="AB18" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC18" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE18" t="n">
         <v>80</v>
@@ -3942,7 +3942,7 @@
         <v>17.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH18" t="n">
         <v>15.5</v>
@@ -3954,7 +3954,7 @@
         <v>29</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="n">
         <v>29</v>
@@ -3966,19 +3966,19 @@
         <v>12</v>
       </c>
       <c r="AO18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP18" t="n">
         <v>19.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR18" t="n">
         <v>22</v>
       </c>
       <c r="AS18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT18" t="n">
         <v>12</v>
@@ -4005,7 +4005,7 @@
         <v>30</v>
       </c>
       <c r="BB18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC18" t="n">
         <v>18.5</v>
@@ -4017,14 +4017,14 @@
         <v>30</v>
       </c>
       <c r="BF18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -4055,49 +4055,49 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="G19" t="n">
         <v>1.83</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K19" t="n">
         <v>4</v>
       </c>
-      <c r="K19" t="n">
-        <v>4.3</v>
-      </c>
       <c r="L19" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
         <v>1.24</v>
       </c>
       <c r="P19" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S19" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U19" t="n">
         <v>2.26</v>
@@ -4112,7 +4112,7 @@
         <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z19" t="n">
         <v>40</v>
@@ -4163,16 +4163,16 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>17</v>
+        <v>7.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
@@ -4208,7 +4208,7 @@
         <v>25</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF19" t="n">
         <v>7.8</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -4249,61 +4249,61 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="G20" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
         <v>2.72</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="M20" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="N20" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="O20" t="n">
         <v>1.72</v>
       </c>
       <c r="P20" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
         <v>1.13</v>
       </c>
       <c r="S20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U20" t="n">
         <v>1.61</v>
       </c>
       <c r="V20" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="X20" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Y20" t="n">
         <v>24</v>
@@ -4318,7 +4318,7 @@
         <v>6.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD20" t="n">
         <v>70</v>
@@ -4333,7 +4333,7 @@
         <v>34</v>
       </c>
       <c r="AH20" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="AI20" t="n">
         <v>700</v>
@@ -4363,56 +4363,56 @@
         <v>8</v>
       </c>
       <c r="AR20" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="AY20" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BC20" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF20" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -4443,46 +4443,46 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G21" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H21" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I21" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J21" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K21" t="n">
         <v>2.94</v>
       </c>
       <c r="L21" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="M21" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N21" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O21" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T21" t="n">
         <v>2.12</v>
@@ -4491,10 +4491,10 @@
         <v>1.76</v>
       </c>
       <c r="V21" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X21" t="n">
         <v>8.6</v>
@@ -4572,7 +4572,7 @@
         <v>12.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX21" t="n">
         <v>14.5</v>
@@ -4584,7 +4584,7 @@
         <v>20</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BB21" t="n">
         <v>36</v>
@@ -4596,7 +4596,7 @@
         <v>9</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF21" t="n">
         <v>9</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Amiens</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>ESTAC Troyes</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.89</v>
+        <v>4.3</v>
       </c>
       <c r="G22" t="n">
-        <v>1.96</v>
+        <v>4.5</v>
       </c>
       <c r="H22" t="n">
-        <v>4.7</v>
+        <v>1.92</v>
       </c>
       <c r="I22" t="n">
-        <v>5.3</v>
+        <v>1.97</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="K22" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="M22" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="O22" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="P22" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="R22" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="U22" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="V22" t="n">
-        <v>1.23</v>
+        <v>2.02</v>
       </c>
       <c r="W22" t="n">
-        <v>2.04</v>
+        <v>1.28</v>
       </c>
       <c r="X22" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD22" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z22" t="n">
+      <c r="AE22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG22" t="n">
         <v>36</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AH22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI22" t="n">
         <v>150</v>
       </c>
-      <c r="AB22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>230</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>140</v>
-      </c>
       <c r="AJ22" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AK22" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL22" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AM22" t="n">
-        <v>250</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AO22" t="n">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="AP22" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ22" t="n">
         <v>8</v>
       </c>
       <c r="AR22" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AS22" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="AW22" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC22" t="n">
-        <v>22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD22" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>14.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.35</v>
+        <v>1.9</v>
       </c>
       <c r="G23" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="H23" t="n">
-        <v>2.48</v>
+        <v>4.9</v>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="M23" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="T23" t="n">
-        <v>1.87</v>
+        <v>2.18</v>
       </c>
       <c r="U23" t="n">
-        <v>2.08</v>
+        <v>1.76</v>
       </c>
       <c r="V23" t="n">
-        <v>1.66</v>
+        <v>1.23</v>
       </c>
       <c r="W23" t="n">
-        <v>1.41</v>
+        <v>2.06</v>
       </c>
       <c r="X23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>480</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV23" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AW23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB23" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Z23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF23" t="n">
+      <c r="BC23" t="n">
         <v>22</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="BD23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BE23" t="n">
         <v>14.5</v>
       </c>
-      <c r="AH23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>55</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>38</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>90</v>
-      </c>
       <c r="BF23" t="n">
-        <v>40</v>
+        <v>17.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>23</v>
+        <v>5.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bosnian Premier League</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Zeljeznicar</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="G24" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="H24" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="I24" t="n">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="J24" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="K24" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L24" t="n">
         <v>1.48</v>
       </c>
       <c r="M24" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>2.42</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.58</v>
+        <v>2.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="U24" t="n">
-        <v>1.69</v>
+        <v>2.08</v>
       </c>
       <c r="V24" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="X24" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z24" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AA24" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AB24" t="n">
         <v>12</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD24" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AF24" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AG24" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>28</v>
+        <v>17.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>200</v>
+        <v>44</v>
       </c>
       <c r="AJ24" t="n">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="AK24" t="n">
-        <v>230</v>
+        <v>40</v>
       </c>
       <c r="AL24" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM24" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AN24" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AO24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC24" t="n">
         <v>36</v>
       </c>
-      <c r="AP24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BD24" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.4</v>
+        <v>60</v>
       </c>
       <c r="BF24" t="n">
-        <v>9.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BG24" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Zeljeznicar</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.35</v>
+        <v>4.7</v>
       </c>
       <c r="G25" t="n">
-        <v>1.36</v>
+        <v>5.4</v>
       </c>
       <c r="H25" t="n">
-        <v>12</v>
+        <v>1.97</v>
       </c>
       <c r="I25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB25" t="n">
         <v>12.5</v>
       </c>
-      <c r="J25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="AC25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>230</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>5.6</v>
       </c>
-      <c r="L25" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X25" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>30</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>620</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="AR25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX25" t="n">
         <v>6.8</v>
       </c>
-      <c r="AC25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>280</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>470</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>27</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>90</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>130</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>44</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>65</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AY25" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>36</v>
+        <v>7.4</v>
       </c>
       <c r="BA25" t="n">
-        <v>55</v>
+        <v>7.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BC25" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="BD25" t="n">
-        <v>46</v>
+        <v>7.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>270</v>
+        <v>8</v>
       </c>
       <c r="BF25" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BG25" t="n">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>13</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X26" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>620</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>230</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>290</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>470</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>90</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT26" t="n">
         <v>6.4</v>
       </c>
-      <c r="G26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V26" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X26" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA26" t="n">
+      <c r="AU26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>230</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>36</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC26" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>200</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>100</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN26" t="n">
+      <c r="BD26" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG26" t="n">
         <v>130</v>
       </c>
-      <c r="AO26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>42</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.52</v>
+        <v>6.8</v>
       </c>
       <c r="G27" t="n">
-        <v>2.82</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="I27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S27" t="n">
         <v>3.75</v>
       </c>
-      <c r="J27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4.5</v>
-      </c>
       <c r="T27" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V27" t="n">
-        <v>1.37</v>
+        <v>2.62</v>
       </c>
       <c r="W27" t="n">
-        <v>1.55</v>
+        <v>1.16</v>
       </c>
       <c r="X27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>210</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC27" t="n">
         <v>90</v>
       </c>
-      <c r="Y27" t="n">
-        <v>980</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>980</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>980</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>980</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.06</v>
-      </c>
       <c r="BD27" t="n">
-        <v>1.98</v>
+        <v>36</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.08</v>
+        <v>36</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.88</v>
+        <v>19.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.86</v>
+        <v>9.4</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,55 +5792,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Genesis Huracan</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="H28" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="I28" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J28" t="n">
-        <v>1.03</v>
+        <v>2.76</v>
       </c>
       <c r="K28" t="n">
-        <v>950</v>
+        <v>3.05</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N28" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="P28" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.26</v>
+        <v>2.54</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
-        <v>1.26</v>
+        <v>4.8</v>
       </c>
       <c r="T28" t="n">
         <v>1.05</v>
@@ -5849,129 +5849,129 @@
         <v>1.05</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,72 +5981,72 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Lobos UPNFM</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>2.26</v>
+        <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="I29" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>2.72</v>
+        <v>1.03</v>
       </c>
       <c r="K29" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L29" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>2.12</v>
+        <v>1.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="P29" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.18</v>
+        <v>1.26</v>
       </c>
       <c r="R29" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>3.9</v>
+        <v>1.26</v>
       </c>
       <c r="T29" t="n">
         <v>1.05</v>
       </c>
       <c r="U29" t="n">
-        <v>1.74</v>
+        <v>1.05</v>
       </c>
       <c r="V29" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6064,7 +6064,7 @@
         <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
         <v>1000</v>
@@ -6094,7 +6094,7 @@
         <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
         <v>1000</v>
@@ -6103,69 +6103,69 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,184 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="F30" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G30" t="n">
         <v>2.24</v>
       </c>
-      <c r="G30" t="n">
-        <v>2.3</v>
-      </c>
       <c r="H30" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S30" t="n">
         <v>4.7</v>
       </c>
-      <c r="J30" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S30" t="n">
-        <v>6.6</v>
-      </c>
       <c r="T30" t="n">
-        <v>2.4</v>
+        <v>1.05</v>
       </c>
       <c r="U30" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="V30" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W30" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="X30" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>6.6</v>
+        <v>500</v>
       </c>
       <c r="AC30" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="AD30" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN30" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>6.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ30" t="n">
-        <v>9.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="AR30" t="n">
-        <v>20</v>
+        <v>1.41</v>
       </c>
       <c r="AS30" t="n">
-        <v>40</v>
+        <v>1.41</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.9</v>
+        <v>1.35</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.4</v>
+        <v>1.29</v>
       </c>
       <c r="AV30" t="n">
-        <v>15</v>
+        <v>1.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>36</v>
+        <v>1.41</v>
       </c>
       <c r="AX30" t="n">
-        <v>10.5</v>
+        <v>1.39</v>
       </c>
       <c r="AY30" t="n">
-        <v>11.5</v>
+        <v>1.37</v>
       </c>
       <c r="AZ30" t="n">
-        <v>23</v>
+        <v>1.38</v>
       </c>
       <c r="BA30" t="n">
-        <v>42</v>
+        <v>1.41</v>
       </c>
       <c r="BB30" t="n">
-        <v>19</v>
+        <v>1.41</v>
       </c>
       <c r="BC30" t="n">
-        <v>27</v>
+        <v>1.39</v>
       </c>
       <c r="BD30" t="n">
-        <v>36</v>
+        <v>1.41</v>
       </c>
       <c r="BE30" t="n">
-        <v>65</v>
+        <v>1.41</v>
       </c>
       <c r="BF30" t="n">
-        <v>30</v>
+        <v>1.39</v>
       </c>
       <c r="BG30" t="n">
-        <v>44</v>
+        <v>1.55</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -6374,186 +6374,186 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.96</v>
+        <v>2.28</v>
       </c>
       <c r="G31" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q31" t="n">
         <v>3.15</v>
       </c>
-      <c r="H31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I31" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V31" t="n">
         <v>1.27</v>
       </c>
-      <c r="Q31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.42</v>
-      </c>
       <c r="W31" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="X31" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC31" t="n">
         <v>7</v>
       </c>
-      <c r="AC31" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AD31" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>180</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR31" t="n">
         <v>20</v>
       </c>
-      <c r="AG31" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>150</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>310</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>270</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AS31" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU31" t="n">
         <v>6.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW31" t="n">
         <v>36</v>
       </c>
       <c r="AX31" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AY31" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BA31" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BB31" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BD31" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="BE31" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="BF31" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BG31" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,191 +6563,191 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L32" t="n">
         <v>1.9</v>
       </c>
-      <c r="G32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="H32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.45</v>
-      </c>
       <c r="M32" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="N32" t="n">
-        <v>2.88</v>
+        <v>1.94</v>
       </c>
       <c r="O32" t="n">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.32</v>
+        <v>4.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="S32" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="T32" t="n">
-        <v>2.06</v>
+        <v>2.96</v>
       </c>
       <c r="U32" t="n">
-        <v>1.82</v>
+        <v>1.41</v>
       </c>
       <c r="V32" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="W32" t="n">
-        <v>1.98</v>
+        <v>1.47</v>
       </c>
       <c r="X32" t="n">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>980</v>
+        <v>27</v>
       </c>
       <c r="AA32" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB32" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC32" t="n">
         <v>7.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AE32" t="n">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AG32" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AH32" t="n">
+        <v>140</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>210</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>380</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>490</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>29</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>48</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE32" t="n">
         <v>70</v>
       </c>
-      <c r="AI32" t="n">
-        <v>380</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>290</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>300</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BF32" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BG32" t="n">
-        <v>3.7</v>
+        <v>36</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Curico Unido</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="G33" t="n">
-        <v>2.92</v>
+        <v>1.94</v>
       </c>
       <c r="H33" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="I33" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S33" t="n">
         <v>4.7</v>
       </c>
-      <c r="J33" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="K33" t="n">
+      <c r="T33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB33" t="n">
         <v>7</v>
       </c>
-      <c r="L33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X33" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z33" t="n">
+      <c r="AC33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD33" t="n">
         <v>29</v>
       </c>
-      <c r="AA33" t="n">
-        <v>230</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="AE33" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>70</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS33" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>310</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AT33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU33" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU33" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AV33" t="n">
-        <v>12.5</v>
+        <v>6.6</v>
       </c>
       <c r="AW33" t="n">
         <v>8</v>
       </c>
       <c r="AX33" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY33" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="AZ33" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE33" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB33" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF33" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="BG33" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6956,186 +6956,186 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sportivo San Lorenzo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Curico Unido</t>
         </is>
       </c>
       <c r="F34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K34" t="n">
         <v>3.05</v>
       </c>
-      <c r="G34" t="n">
-        <v>5</v>
-      </c>
-      <c r="H34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" t="n">
-        <v>990</v>
-      </c>
-      <c r="J34" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K34" t="n">
-        <v>980</v>
-      </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M34" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="N34" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="O34" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="P34" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.96</v>
+        <v>2.56</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S34" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="T34" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="U34" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="V34" t="n">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="W34" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,72 +7145,72 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Sportivo San Lorenzo</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="G35" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="H35" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I35" t="n">
         <v>2.2</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="K35" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="L35" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="M35" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N35" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="O35" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="P35" t="n">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="S35" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="T35" t="n">
-        <v>2.12</v>
+        <v>1.05</v>
       </c>
       <c r="U35" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="V35" t="n">
         <v>1.83</v>
       </c>
       <c r="W35" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7267,69 +7267,69 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,184 +7339,184 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.98</v>
+        <v>4.2</v>
       </c>
       <c r="G36" t="n">
-        <v>2.08</v>
+        <v>5</v>
       </c>
       <c r="H36" t="n">
-        <v>4.8</v>
+        <v>2.06</v>
       </c>
       <c r="I36" t="n">
-        <v>5.4</v>
+        <v>2.16</v>
       </c>
       <c r="J36" t="n">
         <v>3.15</v>
       </c>
       <c r="K36" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L36" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="M36" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N36" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="O36" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="P36" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="R36" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AS36" t="n">
         <v>1.17</v>
       </c>
-      <c r="S36" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="X36" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>980</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>290</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>40</v>
-      </c>
       <c r="AT36" t="n">
-        <v>5.7</v>
+        <v>1.21</v>
       </c>
       <c r="AU36" t="n">
-        <v>6.8</v>
+        <v>1.21</v>
       </c>
       <c r="AV36" t="n">
-        <v>17</v>
+        <v>1.21</v>
       </c>
       <c r="AW36" t="n">
-        <v>50</v>
+        <v>1.17</v>
       </c>
       <c r="AX36" t="n">
-        <v>8.6</v>
+        <v>1.17</v>
       </c>
       <c r="AY36" t="n">
-        <v>10.5</v>
+        <v>1.15</v>
       </c>
       <c r="AZ36" t="n">
-        <v>18.5</v>
+        <v>1.16</v>
       </c>
       <c r="BA36" t="n">
-        <v>42</v>
+        <v>1.21</v>
       </c>
       <c r="BB36" t="n">
-        <v>16.5</v>
+        <v>1.21</v>
       </c>
       <c r="BC36" t="n">
-        <v>23</v>
+        <v>1.21</v>
       </c>
       <c r="BD36" t="n">
-        <v>48</v>
+        <v>1.21</v>
       </c>
       <c r="BE36" t="n">
-        <v>48</v>
+        <v>1.21</v>
       </c>
       <c r="BF36" t="n">
-        <v>16.5</v>
+        <v>1.21</v>
       </c>
       <c r="BG36" t="n">
-        <v>42</v>
+        <v>1.21</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -7538,186 +7538,186 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.35</v>
+        <v>1.99</v>
       </c>
       <c r="G37" t="n">
-        <v>3.6</v>
+        <v>2.06</v>
       </c>
       <c r="H37" t="n">
-        <v>2.46</v>
+        <v>4.8</v>
       </c>
       <c r="I37" t="n">
-        <v>2.52</v>
+        <v>5.2</v>
       </c>
       <c r="J37" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K37" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="L37" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="M37" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N37" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="O37" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="P37" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.46</v>
+        <v>2.82</v>
       </c>
       <c r="R37" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T37" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="U37" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="V37" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="W37" t="n">
-        <v>1.39</v>
+        <v>1.94</v>
       </c>
       <c r="X37" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="Z37" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG37" t="n">
         <v>14</v>
       </c>
-      <c r="AA37" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB37" t="n">
+      <c r="AH37" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ37" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC37" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK37" t="n">
+      <c r="AR37" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD37" t="n">
         <v>55</v>
       </c>
-      <c r="AL37" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD37" t="n">
+      <c r="BE37" t="n">
         <v>48</v>
       </c>
-      <c r="BE37" t="n">
-        <v>46</v>
-      </c>
       <c r="BF37" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7732,179 +7732,373 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>6.2</v>
+        <v>3.35</v>
       </c>
       <c r="G38" t="n">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="H38" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P38" t="n">
         <v>1.61</v>
       </c>
-      <c r="I38" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="J38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.73</v>
-      </c>
       <c r="Q38" t="n">
-        <v>2.12</v>
+        <v>2.54</v>
       </c>
       <c r="R38" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S38" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="T38" t="n">
         <v>2.06</v>
       </c>
       <c r="U38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-03-02 01:18:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Independiente (Ecu)</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U39" t="n">
         <v>1.77</v>
       </c>
-      <c r="V38" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X38" t="n">
+      <c r="V39" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X39" t="n">
         <v>15</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="Y39" t="n">
         <v>7.4</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="Z39" t="n">
         <v>9.6</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AA39" t="n">
         <v>20</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AB39" t="n">
         <v>22</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AC39" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AD39" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE38" t="n">
+      <c r="AE39" t="n">
         <v>21</v>
       </c>
-      <c r="AF38" t="n">
+      <c r="AF39" t="n">
         <v>70</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AG39" t="n">
         <v>28</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AH39" t="n">
         <v>30</v>
       </c>
-      <c r="AI38" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ38" t="n">
+      <c r="AI39" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>270</v>
       </c>
-      <c r="AK38" t="n">
+      <c r="AK39" t="n">
         <v>150</v>
       </c>
-      <c r="AL38" t="n">
+      <c r="AL39" t="n">
         <v>140</v>
       </c>
-      <c r="AM38" t="n">
+      <c r="AM39" t="n">
         <v>210</v>
       </c>
-      <c r="AN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO38" t="n">
+      <c r="AN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT39" t="n">
         <v>15.5</v>
       </c>
-      <c r="AP38" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ38" t="n">
+      <c r="AU39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC39" t="n">
         <v>6</v>
       </c>
-      <c r="AR38" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG38" t="n">
+      <c r="BD39" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG39" t="n">
         <v>10.5</v>
       </c>
-      <c r="BH38" t="inlineStr">
-        <is>
-          <t>2026-03-01 23:07:57</t>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -766,7 +766,7 @@
         <v>1.22</v>
       </c>
       <c r="I2" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="J2" t="n">
         <v>4.2</v>
@@ -790,7 +790,7 @@
         <v>1.46</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
         <v>1.46</v>
@@ -805,7 +805,7 @@
         <v>1.05</v>
       </c>
       <c r="V2" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>3.75</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I3" t="n">
         <v>2.16</v>
@@ -966,7 +966,7 @@
         <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>1.39</v>
@@ -975,19 +975,19 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
         <v>1.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
         <v>3.3</v>
@@ -996,13 +996,13 @@
         <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="V3" t="n">
         <v>1.86</v>
       </c>
       <c r="W3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X3" t="n">
         <v>16</v>
@@ -1017,7 +1017,7 @@
         <v>46</v>
       </c>
       <c r="AB3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC3" t="n">
         <v>8.6</v>
@@ -1032,7 +1032,7 @@
         <v>46</v>
       </c>
       <c r="AG3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH3" t="n">
         <v>18.5</v>
@@ -1059,7 +1059,7 @@
         <v>15</v>
       </c>
       <c r="AP3" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="AQ3" t="n">
         <v>8.800000000000001</v>
@@ -1095,7 +1095,7 @@
         <v>16</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC3" t="n">
         <v>20</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -1145,58 +1145,58 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G4" t="n">
         <v>1.4</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.41</v>
-      </c>
       <c r="H4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
         <v>13</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.38</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="X4" t="n">
         <v>90</v>
@@ -1205,110 +1205,110 @@
         <v>980</v>
       </c>
       <c r="Z4" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC4" t="n">
         <v>23</v>
       </c>
       <c r="AD4" t="n">
-        <v>980</v>
+        <v>180</v>
       </c>
       <c r="AE4" t="n">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AF4" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AG4" t="n">
         <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>980</v>
+        <v>950</v>
       </c>
       <c r="AI4" t="n">
         <v>520</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AK4" t="n">
         <v>65</v>
       </c>
       <c r="AL4" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AN4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR4" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
         <v>4.2</v>
       </c>
       <c r="AT4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX4" t="n">
         <v>6.6</v>
       </c>
-      <c r="AU4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV4" t="n">
+      <c r="AY4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA4" t="n">
         <v>12</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>13.5</v>
       </c>
       <c r="BB4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BC4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG4" t="n">
         <v>12.5</v>
       </c>
-      <c r="BD4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>14</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -1339,64 +1339,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G5" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="H5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I5" t="n">
         <v>3.7</v>
       </c>
       <c r="J5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.1</v>
       </c>
-      <c r="K5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P5" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U5" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V5" t="n">
         <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="X5" t="n">
         <v>22</v>
       </c>
       <c r="Y5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
         <v>48</v>
@@ -1435,7 +1435,7 @@
         <v>980</v>
       </c>
       <c r="AL5" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
@@ -1453,22 +1453,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.7</v>
+        <v>9.6</v>
       </c>
       <c r="AT5" t="n">
         <v>5.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="AX5" t="n">
         <v>12</v>
@@ -1477,32 +1477,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC5" t="n">
         <v>14.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -1575,19 +1575,19 @@
         <v>3.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U6" t="n">
         <v>2.14</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
         <v>1.81</v>
       </c>
       <c r="X6" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y6" t="n">
         <v>14.5</v>
@@ -1599,7 +1599,7 @@
         <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC6" t="n">
         <v>8.199999999999999</v>
@@ -1626,7 +1626,7 @@
         <v>90</v>
       </c>
       <c r="AK6" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AL6" t="n">
         <v>130</v>
@@ -1650,7 +1650,7 @@
         <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
         <v>8.6</v>
@@ -1659,10 +1659,10 @@
         <v>7.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX6" t="n">
         <v>11.5</v>
@@ -1674,7 +1674,7 @@
         <v>9</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB6" t="n">
         <v>11.5</v>
@@ -1686,17 +1686,17 @@
         <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
         <v>3.95</v>
@@ -1751,19 +1751,19 @@
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.19</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q7" t="n">
         <v>1.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S7" t="n">
         <v>2.5</v>
@@ -1775,7 +1775,7 @@
         <v>2.48</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
         <v>2</v>
@@ -1802,19 +1802,19 @@
         <v>980</v>
       </c>
       <c r="AE7" t="n">
-        <v>170</v>
+        <v>980</v>
       </c>
       <c r="AF7" t="n">
         <v>980</v>
       </c>
       <c r="AG7" t="n">
-        <v>980</v>
+        <v>950</v>
       </c>
       <c r="AH7" t="n">
         <v>60</v>
       </c>
       <c r="AI7" t="n">
-        <v>160</v>
+        <v>980</v>
       </c>
       <c r="AJ7" t="n">
         <v>980</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="AQ7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="AT7" t="n">
         <v>9.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AV7" t="n">
         <v>7.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.22</v>
+        <v>3.15</v>
       </c>
       <c r="AX7" t="n">
         <v>7.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="BA7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG7" t="n">
         <v>2.22</v>
       </c>
-      <c r="BB7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.04</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -1924,58 +1924,58 @@
         <v>3.3</v>
       </c>
       <c r="G8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P8" t="n">
         <v>2.16</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.76</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.78</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X8" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="Y8" t="n">
         <v>980</v>
@@ -2032,59 +2032,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="AT8" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.35</v>
+        <v>7.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="BB8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BG8" t="n">
         <v>2.76</v>
       </c>
-      <c r="BC8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>3</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>9</v>
@@ -2124,13 +2124,13 @@
         <v>1.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.42</v>
@@ -2139,40 +2139,40 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
         <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V9" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="W9" t="n">
         <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z9" t="n">
         <v>8.199999999999999</v>
@@ -2184,7 +2184,7 @@
         <v>25</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="n">
         <v>10.5</v>
@@ -2199,7 +2199,7 @@
         <v>95</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI9" t="n">
         <v>120</v>
@@ -2217,16 +2217,16 @@
         <v>430</v>
       </c>
       <c r="AN9" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AO9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR9" t="n">
         <v>7</v>
@@ -2247,7 +2247,7 @@
         <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="AY9" t="n">
         <v>22</v>
@@ -2256,29 +2256,29 @@
         <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="BB9" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC9" t="n">
         <v>13</v>
       </c>
-      <c r="BC9" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BD9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG9" t="n">
         <v>7.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J10" t="n">
         <v>3.45</v>
@@ -2327,100 +2327,100 @@
         <v>3.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="W10" t="n">
         <v>1.27</v>
       </c>
       <c r="X10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="n">
         <v>7.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA10" t="n">
         <v>23</v>
       </c>
       <c r="AB10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD10" t="n">
         <v>10.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF10" t="n">
         <v>32</v>
       </c>
       <c r="AG10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH10" t="n">
         <v>22</v>
       </c>
       <c r="AI10" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ10" t="n">
         <v>110</v>
       </c>
       <c r="AK10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM10" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AO10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR10" t="n">
         <v>10</v>
@@ -2429,22 +2429,22 @@
         <v>21</v>
       </c>
       <c r="AT10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY10" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>20</v>
@@ -2453,10 +2453,10 @@
         <v>42</v>
       </c>
       <c r="BB10" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BC10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BD10" t="n">
         <v>65</v>
@@ -2465,14 +2465,14 @@
         <v>90</v>
       </c>
       <c r="BF10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BG10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G11" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I11" t="n">
         <v>3.3</v>
@@ -2518,37 +2518,37 @@
         <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P11" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V11" t="n">
         <v>1.43</v>
@@ -2557,31 +2557,31 @@
         <v>1.58</v>
       </c>
       <c r="X11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="n">
         <v>10.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AA11" t="n">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC11" t="n">
         <v>7.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AE11" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AF11" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AG11" t="n">
         <v>12.5</v>
@@ -2593,25 +2593,25 @@
         <v>380</v>
       </c>
       <c r="AJ11" t="n">
-        <v>230</v>
+        <v>980</v>
       </c>
       <c r="AK11" t="n">
         <v>110</v>
       </c>
       <c r="AL11" t="n">
-        <v>290</v>
+        <v>150</v>
       </c>
       <c r="AM11" t="n">
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ11" t="n">
         <v>9</v>
@@ -2620,7 +2620,7 @@
         <v>17.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT11" t="n">
         <v>8</v>
@@ -2632,19 +2632,19 @@
         <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX11" t="n">
         <v>13.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB11" t="n">
         <v>18</v>
@@ -2653,20 +2653,20 @@
         <v>16</v>
       </c>
       <c r="BD11" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE11" t="n">
-        <v>28</v>
+        <v>9.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="H12" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I12" t="n">
         <v>3.65</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
         <v>3.25</v>
@@ -2739,22 +2739,22 @@
         <v>5.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W12" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X12" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="Z12" t="n">
         <v>980</v>
@@ -2802,65 +2802,65 @@
         <v>980</v>
       </c>
       <c r="AO12" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AR12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF12" t="n">
         <v>6.6</v>
       </c>
-      <c r="AS12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BG12" t="n">
-        <v>4.2</v>
+        <v>2.86</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="G13" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="H13" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J13" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
         <v>9.6</v>
@@ -2912,7 +2912,7 @@
         <v>1.23</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
         <v>3.45</v>
@@ -2921,28 +2921,28 @@
         <v>1.16</v>
       </c>
       <c r="P13" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="R13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="S13" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="T13" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="U13" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="W13" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2993,13 +2993,13 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AQ13" t="n">
         <v>30</v>
@@ -3011,10 +3011,10 @@
         <v>4.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AV13" t="n">
         <v>4.2</v>
@@ -3023,38 +3023,38 @@
         <v>4.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="BA13" t="n">
         <v>4.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="BD13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.7</v>
       </c>
-      <c r="BE13" t="n">
-        <v>1.71</v>
-      </c>
       <c r="BF13" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="BG13" t="n">
         <v>4.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
         <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
         <v>1.43</v>
@@ -3109,28 +3109,28 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
         <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T14" t="n">
-        <v>1.05</v>
+        <v>1.72</v>
       </c>
       <c r="U14" t="n">
-        <v>1.05</v>
+        <v>2.08</v>
       </c>
       <c r="V14" t="n">
         <v>1.61</v>
@@ -3199,10 +3199,10 @@
         <v>5.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AT14" t="n">
         <v>6.2</v>
@@ -3211,31 +3211,31 @@
         <v>4.9</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="AX14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY14" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="BE14" t="n">
         <v>1.8</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -3279,55 +3279,55 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="G15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="V15" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W15" t="n">
         <v>2</v>
@@ -3387,13 +3387,13 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AQ15" t="n">
         <v>15</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="AS15" t="n">
         <v>1.93</v>
@@ -3405,7 +3405,7 @@
         <v>5.1</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AW15" t="n">
         <v>1.93</v>
@@ -3417,32 +3417,32 @@
         <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG15" t="n">
         <v>1.93</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="I16" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="J16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L16" t="n">
         <v>1.33</v>
@@ -3497,34 +3497,34 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="R16" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="S16" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="U16" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="V16" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
         <v>90</v>
@@ -3533,13 +3533,13 @@
         <v>21</v>
       </c>
       <c r="Z16" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AA16" t="n">
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
         <v>14</v>
@@ -3578,34 +3578,34 @@
         <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>55</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR16" t="n">
         <v>6.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT16" t="n">
         <v>10.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="AV16" t="n">
         <v>6.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY16" t="n">
         <v>10.5</v>
@@ -3614,29 +3614,29 @@
         <v>10.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF16" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>7.2</v>
       </c>
       <c r="BG16" t="n">
         <v>7.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -3691,22 +3691,22 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="O17" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="P17" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Q17" t="n">
         <v>1.37</v>
       </c>
       <c r="R17" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="S17" t="n">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="T17" t="n">
         <v>1.05</v>
@@ -3715,7 +3715,7 @@
         <v>1.71</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="W17" t="n">
         <v>1.19</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="H18" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I18" t="n">
         <v>3.3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K18" t="n">
         <v>4.3</v>
@@ -3894,31 +3894,31 @@
         <v>2.56</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="S18" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U18" t="n">
         <v>2.58</v>
       </c>
-      <c r="T18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.52</v>
-      </c>
       <c r="V18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="X18" t="n">
         <v>24</v>
       </c>
       <c r="Y18" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z18" t="n">
         <v>26</v>
@@ -3939,13 +3939,13 @@
         <v>80</v>
       </c>
       <c r="AF18" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG18" t="n">
         <v>11.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI18" t="n">
         <v>85</v>
@@ -3957,7 +3957,7 @@
         <v>21</v>
       </c>
       <c r="AL18" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="AM18" t="n">
         <v>580</v>
@@ -3966,7 +3966,7 @@
         <v>12</v>
       </c>
       <c r="AO18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP18" t="n">
         <v>19.5</v>
@@ -3975,13 +3975,13 @@
         <v>15.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS18" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AT18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU18" t="n">
         <v>8.4</v>
@@ -3990,7 +3990,7 @@
         <v>12</v>
       </c>
       <c r="AW18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX18" t="n">
         <v>14.5</v>
@@ -4002,7 +4002,7 @@
         <v>13</v>
       </c>
       <c r="BA18" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BB18" t="n">
         <v>25</v>
@@ -4020,11 +4020,11 @@
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>4.9</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
         <v>3.95</v>
@@ -4103,7 +4103,7 @@
         <v>2.26</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W19" t="n">
         <v>2.2</v>
@@ -4142,7 +4142,7 @@
         <v>18.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ19" t="n">
         <v>21</v>
@@ -4154,7 +4154,7 @@
         <v>32</v>
       </c>
       <c r="AM19" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AN19" t="n">
         <v>9.800000000000001</v>
@@ -4163,16 +4163,16 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.800000000000001</v>
+        <v>75</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G20" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
         <v>5.2</v>
@@ -4264,7 +4264,7 @@
         <v>2.72</v>
       </c>
       <c r="K20" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="L20" t="n">
         <v>1.71</v>
@@ -4300,7 +4300,7 @@
         <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X20" t="n">
         <v>6.8</v>
@@ -4318,7 +4318,7 @@
         <v>6.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD20" t="n">
         <v>70</v>
@@ -4330,7 +4330,7 @@
         <v>34</v>
       </c>
       <c r="AG20" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AH20" t="n">
         <v>980</v>
@@ -4360,7 +4360,7 @@
         <v>5.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="AR20" t="n">
         <v>11.5</v>
@@ -4369,7 +4369,7 @@
         <v>10</v>
       </c>
       <c r="AT20" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AU20" t="n">
         <v>6.2</v>
@@ -4381,13 +4381,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AX20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY20" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA20" t="n">
         <v>9.800000000000001</v>
@@ -4396,7 +4396,7 @@
         <v>8.6</v>
       </c>
       <c r="BC20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BD20" t="n">
         <v>9.4</v>
@@ -4408,11 +4408,11 @@
         <v>8.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G21" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H21" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>2.88</v>
@@ -4467,16 +4467,16 @@
         <v>1.14</v>
       </c>
       <c r="N21" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O21" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="P21" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R21" t="n">
         <v>1.18</v>
@@ -4491,10 +4491,10 @@
         <v>1.76</v>
       </c>
       <c r="V21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X21" t="n">
         <v>8.6</v>
@@ -4509,7 +4509,7 @@
         <v>150</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC21" t="n">
         <v>7.4</v>
@@ -4560,7 +4560,7 @@
         <v>17</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT21" t="n">
         <v>7</v>
@@ -4572,7 +4572,7 @@
         <v>12.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX21" t="n">
         <v>14.5</v>
@@ -4584,7 +4584,7 @@
         <v>20</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB21" t="n">
         <v>36</v>
@@ -4596,7 +4596,7 @@
         <v>9</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF21" t="n">
         <v>9</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G22" t="n">
         <v>4.5</v>
       </c>
       <c r="H22" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I22" t="n">
         <v>1.97</v>
@@ -4661,28 +4661,28 @@
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O22" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" t="n">
-        <v>1.98</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T22" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U22" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>2.02</v>
@@ -4694,7 +4694,7 @@
         <v>26</v>
       </c>
       <c r="Y22" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z22" t="n">
         <v>22</v>
@@ -4706,7 +4706,7 @@
         <v>28</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD22" t="n">
         <v>10.5</v>
@@ -4739,7 +4739,7 @@
         <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>500</v>
+        <v>270</v>
       </c>
       <c r="AO22" t="n">
         <v>32</v>
@@ -4748,7 +4748,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ22" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="AR22" t="n">
         <v>10</v>
@@ -4769,7 +4769,7 @@
         <v>10.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY22" t="n">
         <v>14.5</v>
@@ -4778,29 +4778,29 @@
         <v>12.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB22" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BC22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BD22" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF22" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>9.6</v>
       </c>
       <c r="BG22" t="n">
         <v>11</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G23" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H23" t="n">
         <v>4.9</v>
@@ -4843,7 +4843,7 @@
         <v>5.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K23" t="n">
         <v>3.6</v>
@@ -4852,7 +4852,7 @@
         <v>1.52</v>
       </c>
       <c r="M23" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N23" t="n">
         <v>3</v>
@@ -4861,13 +4861,13 @@
         <v>1.48</v>
       </c>
       <c r="P23" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R23" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S23" t="n">
         <v>4.9</v>
@@ -4882,22 +4882,22 @@
         <v>1.23</v>
       </c>
       <c r="W23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X23" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y23" t="n">
         <v>14</v>
       </c>
       <c r="Z23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA23" t="n">
         <v>150</v>
       </c>
       <c r="AB23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC23" t="n">
         <v>8</v>
@@ -4933,34 +4933,34 @@
         <v>190</v>
       </c>
       <c r="AN23" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AO23" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR23" t="n">
         <v>16</v>
       </c>
       <c r="AS23" t="n">
-        <v>13.5</v>
+        <v>7.2</v>
       </c>
       <c r="AT23" t="n">
         <v>6.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AV23" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="AX23" t="n">
         <v>7.8</v>
@@ -4969,32 +4969,32 @@
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD23" t="n">
         <v>13</v>
       </c>
-      <c r="BB23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BE23" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
         <v>3.4</v>
       </c>
       <c r="H24" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I24" t="n">
         <v>2.52</v>
@@ -5043,7 +5043,7 @@
         <v>3.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M24" t="n">
         <v>1.09</v>
@@ -5055,22 +5055,22 @@
         <v>1.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
         <v>4.1</v>
       </c>
       <c r="T24" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U24" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V24" t="n">
         <v>1.65</v>
@@ -5082,7 +5082,7 @@
         <v>11.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z24" t="n">
         <v>15</v>
@@ -5109,7 +5109,7 @@
         <v>14.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI24" t="n">
         <v>44</v>
@@ -5121,22 +5121,22 @@
         <v>40</v>
       </c>
       <c r="AL24" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
       </c>
       <c r="AN24" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP24" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR24" t="n">
         <v>14</v>
@@ -5175,20 +5175,20 @@
         <v>36</v>
       </c>
       <c r="BD24" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BE24" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="BF24" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BG24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G25" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="H25" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="J25" t="n">
         <v>3.1</v>
       </c>
       <c r="K25" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L25" t="n">
         <v>1.6</v>
@@ -5243,16 +5243,16 @@
         <v>1.12</v>
       </c>
       <c r="N25" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O25" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P25" t="n">
         <v>1.52</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R25" t="n">
         <v>1.19</v>
@@ -5264,28 +5264,28 @@
         <v>2.22</v>
       </c>
       <c r="U25" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="V25" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="W25" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Y25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB25" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC25" t="n">
         <v>7.8</v>
@@ -5294,25 +5294,25 @@
         <v>11.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF25" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH25" t="n">
-        <v>980</v>
+        <v>27</v>
       </c>
       <c r="AI25" t="n">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="AJ25" t="n">
         <v>900</v>
       </c>
       <c r="AK25" t="n">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AL25" t="n">
         <v>500</v>
@@ -5324,7 +5324,7 @@
         <v>500</v>
       </c>
       <c r="AO25" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AP25" t="n">
         <v>7.4</v>
@@ -5336,53 +5336,53 @@
         <v>9.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT25" t="n">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV25" t="n">
         <v>10</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX25" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="AY25" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BF25" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BG25" t="n">
         <v>21</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G26" t="n">
         <v>1.36</v>
       </c>
-      <c r="G26" t="n">
-        <v>1.37</v>
-      </c>
       <c r="H26" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="I26" t="n">
         <v>13</v>
@@ -5431,7 +5431,7 @@
         <v>5.5</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
@@ -5449,13 +5449,13 @@
         <v>2.02</v>
       </c>
       <c r="R26" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T26" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="U26" t="n">
         <v>1.63</v>
@@ -5470,7 +5470,7 @@
         <v>16</v>
       </c>
       <c r="Y26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z26" t="n">
         <v>110</v>
@@ -5485,7 +5485,7 @@
         <v>12</v>
       </c>
       <c r="AD26" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AE26" t="n">
         <v>270</v>
@@ -5512,7 +5512,7 @@
         <v>50</v>
       </c>
       <c r="AM26" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AN26" t="n">
         <v>6.8</v>
@@ -5521,16 +5521,16 @@
         <v>470</v>
       </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>27</v>
       </c>
       <c r="AR26" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AS26" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AT26" t="n">
         <v>6.4</v>
@@ -5554,7 +5554,7 @@
         <v>36</v>
       </c>
       <c r="BA26" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="BB26" t="n">
         <v>10</v>
@@ -5566,7 +5566,7 @@
         <v>46</v>
       </c>
       <c r="BE26" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="BF26" t="n">
         <v>6.4</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -5607,85 +5607,85 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="I27" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="J27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O27" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P27" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T27" t="n">
         <v>2.04</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.06</v>
       </c>
       <c r="U27" t="n">
         <v>1.89</v>
       </c>
       <c r="V27" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="W27" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X27" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y27" t="n">
         <v>7.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AE27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AG27" t="n">
         <v>27</v>
@@ -5697,46 +5697,46 @@
         <v>40</v>
       </c>
       <c r="AJ27" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AK27" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AL27" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AM27" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN27" t="n">
         <v>160</v>
       </c>
-      <c r="AN27" t="n">
-        <v>140</v>
-      </c>
       <c r="AO27" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR27" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AS27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT27" t="n">
         <v>18.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV27" t="n">
         <v>9.4</v>
       </c>
       <c r="AW27" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX27" t="n">
         <v>48</v>
@@ -5751,26 +5751,26 @@
         <v>36</v>
       </c>
       <c r="BB27" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BC27" t="n">
         <v>90</v>
       </c>
       <c r="BD27" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="BE27" t="n">
         <v>36</v>
       </c>
       <c r="BF27" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BG27" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -5801,19 +5801,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G28" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="H28" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I28" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J28" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="K28" t="n">
         <v>3.05</v>
@@ -5825,34 +5825,34 @@
         <v>1.13</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O28" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="P28" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R28" t="n">
         <v>1.21</v>
       </c>
       <c r="S28" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.05</v>
+        <v>1.97</v>
       </c>
       <c r="U28" t="n">
-        <v>1.05</v>
+        <v>1.85</v>
       </c>
       <c r="V28" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W28" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X28" t="n">
         <v>90</v>
@@ -5876,7 +5876,7 @@
         <v>980</v>
       </c>
       <c r="AE28" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="AF28" t="n">
         <v>980</v>
@@ -5909,69 +5909,69 @@
         <v>500</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="AR28" t="n">
-        <v>3.15</v>
+        <v>1.87</v>
       </c>
       <c r="AS28" t="n">
-        <v>3.3</v>
+        <v>1.93</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.46</v>
+        <v>4.7</v>
       </c>
       <c r="AU28" t="n">
-        <v>2.28</v>
+        <v>4.1</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.92</v>
+        <v>2.44</v>
       </c>
       <c r="AW28" t="n">
-        <v>3.15</v>
+        <v>1.93</v>
       </c>
       <c r="AX28" t="n">
-        <v>2.84</v>
+        <v>1.84</v>
       </c>
       <c r="AY28" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="BA28" t="n">
-        <v>3.35</v>
+        <v>1.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>3.3</v>
+        <v>1.93</v>
       </c>
       <c r="BC28" t="n">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.3</v>
+        <v>1.89</v>
       </c>
       <c r="BE28" t="n">
-        <v>3.35</v>
+        <v>1.93</v>
       </c>
       <c r="BF28" t="n">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Genesis Huracan</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J29" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="K29" t="n">
-        <v>950</v>
+        <v>3.35</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N29" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="P29" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.26</v>
+        <v>2.48</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S29" t="n">
-        <v>1.26</v>
+        <v>4.7</v>
       </c>
       <c r="T29" t="n">
-        <v>1.05</v>
+        <v>2.02</v>
       </c>
       <c r="U29" t="n">
-        <v>1.05</v>
+        <v>1.85</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6180,67 +6180,67 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Lobos UPNFM</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="G30" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="I30" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="K30" t="n">
-        <v>3.35</v>
+        <v>950</v>
       </c>
       <c r="L30" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="O30" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="P30" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.48</v>
+        <v>1.26</v>
       </c>
       <c r="R30" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>4.7</v>
+        <v>1.26</v>
       </c>
       <c r="T30" t="n">
         <v>1.05</v>
       </c>
       <c r="U30" t="n">
-        <v>1.75</v>
+        <v>1.05</v>
       </c>
       <c r="V30" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6255,10 +6255,10 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
         <v>1000</v>
@@ -6288,7 +6288,7 @@
         <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
         <v>1000</v>
@@ -6297,62 +6297,62 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -6383,25 +6383,25 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G31" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="H31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I31" t="n">
         <v>4.5</v>
       </c>
-      <c r="I31" t="n">
-        <v>4.7</v>
-      </c>
       <c r="J31" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K31" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="L31" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="M31" t="n">
         <v>1.17</v>
@@ -6410,7 +6410,7 @@
         <v>2.42</v>
       </c>
       <c r="O31" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="P31" t="n">
         <v>1.44</v>
@@ -6425,16 +6425,16 @@
         <v>6.8</v>
       </c>
       <c r="T31" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="U31" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V31" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W31" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="X31" t="n">
         <v>6.8</v>
@@ -6443,25 +6443,25 @@
         <v>10.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AA31" t="n">
         <v>700</v>
       </c>
       <c r="AB31" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC31" t="n">
         <v>7</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AF31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG31" t="n">
         <v>13.5</v>
@@ -6473,13 +6473,13 @@
         <v>700</v>
       </c>
       <c r="AJ31" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AK31" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL31" t="n">
-        <v>180</v>
+        <v>460</v>
       </c>
       <c r="AM31" t="n">
         <v>500</v>
@@ -6497,22 +6497,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR31" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AS31" t="n">
         <v>40</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV31" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AX31" t="n">
         <v>11</v>
@@ -6527,13 +6527,13 @@
         <v>42</v>
       </c>
       <c r="BB31" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="BC31" t="n">
         <v>30</v>
       </c>
       <c r="BD31" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BE31" t="n">
         <v>65</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -6577,58 +6577,58 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="G32" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H32" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I32" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J32" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="K32" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="L32" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="M32" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="N32" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O32" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="P32" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="R32" t="n">
         <v>1.09</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="U32" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W32" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X32" t="n">
         <v>5.2</v>
@@ -6646,7 +6646,7 @@
         <v>7</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD32" t="n">
         <v>34</v>
@@ -6655,19 +6655,19 @@
         <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG32" t="n">
         <v>30</v>
       </c>
       <c r="AH32" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AI32" t="n">
         <v>500</v>
       </c>
       <c r="AJ32" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AK32" t="n">
         <v>210</v>
@@ -6676,7 +6676,7 @@
         <v>500</v>
       </c>
       <c r="AM32" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
         <v>380</v>
@@ -6685,7 +6685,7 @@
         <v>490</v>
       </c>
       <c r="AP32" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AQ32" t="n">
         <v>6.2</v>
@@ -6697,25 +6697,25 @@
         <v>29</v>
       </c>
       <c r="AT32" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU32" t="n">
         <v>6.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AX32" t="n">
         <v>12.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BA32" t="n">
         <v>46</v>
@@ -6733,14 +6733,14 @@
         <v>70</v>
       </c>
       <c r="BF32" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BG32" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G33" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H33" t="n">
         <v>4.8</v>
       </c>
       <c r="I33" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J33" t="n">
         <v>3.35</v>
       </c>
       <c r="K33" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L33" t="n">
         <v>1.52</v>
@@ -6795,7 +6795,7 @@
         <v>1.1</v>
       </c>
       <c r="N33" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O33" t="n">
         <v>1.46</v>
@@ -6807,13 +6807,13 @@
         <v>2.4</v>
       </c>
       <c r="R33" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S33" t="n">
         <v>4.7</v>
       </c>
       <c r="T33" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U33" t="n">
         <v>1.8</v>
@@ -6822,13 +6822,13 @@
         <v>1.22</v>
       </c>
       <c r="W33" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X33" t="n">
         <v>10.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>980</v>
+        <v>30</v>
       </c>
       <c r="Z33" t="n">
         <v>980</v>
@@ -6843,10 +6843,10 @@
         <v>7.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>29</v>
+        <v>980</v>
       </c>
       <c r="AE33" t="n">
-        <v>700</v>
+        <v>480</v>
       </c>
       <c r="AF33" t="n">
         <v>23</v>
@@ -6864,7 +6864,7 @@
         <v>900</v>
       </c>
       <c r="AK33" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AL33" t="n">
         <v>290</v>
@@ -6879,16 +6879,16 @@
         <v>700</v>
       </c>
       <c r="AP33" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AQ33" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR33" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>8.199999999999999</v>
+        <v>2.86</v>
       </c>
       <c r="AT33" t="n">
         <v>6.2</v>
@@ -6897,44 +6897,44 @@
         <v>6.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW33" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="AX33" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY33" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AZ33" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA33" t="n">
-        <v>7.6</v>
+        <v>2.9</v>
       </c>
       <c r="BB33" t="n">
-        <v>14.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC33" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="BD33" t="n">
-        <v>7.4</v>
+        <v>3.2</v>
       </c>
       <c r="BE33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF33" t="n">
         <v>8.4</v>
       </c>
-      <c r="BF33" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BG33" t="n">
-        <v>7.8</v>
+        <v>2.86</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -6965,31 +6965,31 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G34" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="H34" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I34" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="K34" t="n">
         <v>3.05</v>
       </c>
       <c r="L34" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M34" t="n">
         <v>1.13</v>
       </c>
       <c r="N34" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O34" t="n">
         <v>1.48</v>
@@ -6998,7 +6998,7 @@
         <v>1.57</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R34" t="n">
         <v>1.21</v>
@@ -7007,34 +7007,34 @@
         <v>4.8</v>
       </c>
       <c r="T34" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="U34" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V34" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W34" t="n">
         <v>1.58</v>
       </c>
       <c r="X34" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Y34" t="n">
         <v>11.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA34" t="n">
         <v>230</v>
       </c>
       <c r="AB34" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC34" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AD34" t="n">
         <v>16.5</v>
@@ -7043,22 +7043,22 @@
         <v>150</v>
       </c>
       <c r="AF34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG34" t="n">
         <v>12.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI34" t="n">
         <v>310</v>
       </c>
       <c r="AJ34" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK34" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL34" t="n">
         <v>60</v>
@@ -7070,31 +7070,31 @@
         <v>38</v>
       </c>
       <c r="AO34" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AP34" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ34" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR34" t="n">
         <v>20</v>
       </c>
       <c r="AS34" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT34" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU34" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV34" t="n">
         <v>12.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX34" t="n">
         <v>11</v>
@@ -7106,29 +7106,29 @@
         <v>15.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB34" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC34" t="n">
-        <v>24</v>
+        <v>8.4</v>
       </c>
       <c r="BD34" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BE34" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BG34" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -7159,52 +7159,52 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="G35" t="n">
         <v>4.3</v>
       </c>
       <c r="H35" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J35" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K35" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="L35" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M35" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N35" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O35" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="P35" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="R35" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S35" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="T35" t="n">
-        <v>1.05</v>
+        <v>1.94</v>
       </c>
       <c r="U35" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="V35" t="n">
         <v>1.83</v>
@@ -7213,25 +7213,25 @@
         <v>1.31</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA35" t="n">
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE35" t="n">
         <v>1000</v>
@@ -7249,7 +7249,7 @@
         <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK35" t="n">
         <v>1000</v>
@@ -7258,7 +7258,7 @@
         <v>1000</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN35" t="n">
         <v>1000</v>
@@ -7267,62 +7267,62 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G36" t="n">
         <v>5</v>
@@ -7362,7 +7362,7 @@
         <v>2.06</v>
       </c>
       <c r="I36" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J36" t="n">
         <v>3.15</v>
@@ -7371,7 +7371,7 @@
         <v>3.45</v>
       </c>
       <c r="L36" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M36" t="n">
         <v>1.12</v>
@@ -7392,16 +7392,16 @@
         <v>1.19</v>
       </c>
       <c r="S36" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U36" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V36" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="W36" t="n">
         <v>1.27</v>
@@ -7410,7 +7410,7 @@
         <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Z36" t="n">
         <v>1000</v>
@@ -7461,62 +7461,62 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.21</v>
+        <v>4</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.21</v>
+        <v>3.55</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.21</v>
+        <v>4.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.17</v>
+        <v>4.7</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.21</v>
+        <v>4.4</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.21</v>
+        <v>3.65</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.21</v>
+        <v>4.3</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.17</v>
+        <v>5.1</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.17</v>
+        <v>5.4</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.15</v>
+        <v>4.8</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.16</v>
+        <v>5</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.21</v>
+        <v>3.75</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.21</v>
+        <v>3</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.21</v>
+        <v>2.96</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.21</v>
+        <v>3.85</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.21</v>
+        <v>3.9</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.21</v>
+        <v>3</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.21</v>
+        <v>5.4</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -7538,179 +7538,179 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.99</v>
+        <v>3.3</v>
       </c>
       <c r="G37" t="n">
-        <v>2.06</v>
+        <v>3.4</v>
       </c>
       <c r="H37" t="n">
-        <v>4.8</v>
+        <v>2.54</v>
       </c>
       <c r="I37" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="J37" t="n">
         <v>3.2</v>
       </c>
       <c r="K37" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P37" t="n">
         <v>1.61</v>
       </c>
-      <c r="M37" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.51</v>
-      </c>
       <c r="Q37" t="n">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="R37" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="T37" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="U37" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="V37" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="W37" t="n">
-        <v>1.94</v>
+        <v>1.41</v>
       </c>
       <c r="X37" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z37" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AA37" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN37" t="n">
         <v>65</v>
       </c>
-      <c r="AA37" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC37" t="n">
+      <c r="AO37" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ37" t="n">
         <v>7.6</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AR37" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>42</v>
+      </c>
+      <c r="BD37" t="n">
         <v>32</v>
       </c>
-      <c r="AE37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>48</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>280</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>55</v>
-      </c>
       <c r="BE37" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BF37" t="n">
-        <v>16.5</v>
+        <v>29</v>
       </c>
       <c r="BG37" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -7732,179 +7732,179 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.35</v>
+        <v>2</v>
       </c>
       <c r="G38" t="n">
-        <v>3.5</v>
+        <v>2.06</v>
       </c>
       <c r="H38" t="n">
-        <v>2.46</v>
+        <v>4.8</v>
       </c>
       <c r="I38" t="n">
-        <v>2.52</v>
+        <v>5</v>
       </c>
       <c r="J38" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K38" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="L38" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="M38" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N38" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="O38" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="P38" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.54</v>
+        <v>2.84</v>
       </c>
       <c r="R38" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="T38" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="U38" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="V38" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
-        <v>1.4</v>
+        <v>1.94</v>
       </c>
       <c r="X38" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y38" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="Z38" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG38" t="n">
         <v>14</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AH38" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW38" t="n">
         <v>36</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AX38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY38" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC38" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK38" t="n">
+      <c r="AZ38" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD38" t="n">
         <v>55</v>
       </c>
-      <c r="AL38" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>48</v>
-      </c>
       <c r="BE38" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BF38" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="BG38" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -7941,10 +7941,10 @@
         <v>7.6</v>
       </c>
       <c r="H39" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="I39" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="J39" t="n">
         <v>3.7</v>
@@ -7953,28 +7953,28 @@
         <v>4.2</v>
       </c>
       <c r="L39" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M39" t="n">
         <v>1.08</v>
       </c>
       <c r="N39" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O39" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P39" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R39" t="n">
         <v>1.28</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T39" t="n">
         <v>2.06</v>
@@ -7983,7 +7983,7 @@
         <v>1.77</v>
       </c>
       <c r="V39" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="W39" t="n">
         <v>1.17</v>
@@ -7992,13 +7992,13 @@
         <v>15</v>
       </c>
       <c r="Y39" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AA39" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AB39" t="n">
         <v>22</v>
@@ -8040,7 +8040,7 @@
         <v>1000</v>
       </c>
       <c r="AO39" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP39" t="n">
         <v>10</v>
@@ -8067,7 +8067,7 @@
         <v>17</v>
       </c>
       <c r="AX39" t="n">
-        <v>5.8</v>
+        <v>44</v>
       </c>
       <c r="AY39" t="n">
         <v>22</v>
@@ -8076,29 +8076,29 @@
         <v>21</v>
       </c>
       <c r="BA39" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB39" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC39" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BD39" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE39" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF39" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG39" t="n">
         <v>10.5</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH39"/>
+  <dimension ref="A1:BH38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,43 +760,43 @@
         <v>5.1</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="H2" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="I2" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>16.5</v>
+        <v>7.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.23</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
         <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="S2" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="T2" t="n">
         <v>1.05</v>
@@ -811,7 +811,7 @@
         <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Y2" t="n">
         <v>1000</v>
@@ -820,7 +820,7 @@
         <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB2" t="n">
         <v>1000</v>
@@ -865,28 +865,28 @@
         <v>29</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AT2" t="n">
         <v>4.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AX2" t="n">
         <v>4.2</v>
@@ -895,10 +895,10 @@
         <v>4.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="BB2" t="n">
         <v>4.2</v>
@@ -910,7 +910,7 @@
         <v>4.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="BF2" t="n">
         <v>4.2</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -951,88 +951,88 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="G3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K3" t="n">
         <v>4</v>
       </c>
-      <c r="H3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.85</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
         <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V3" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
         <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="AB3" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AF3" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AG3" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH3" t="n">
         <v>18.5</v>
@@ -1041,61 +1041,61 @@
         <v>95</v>
       </c>
       <c r="AJ3" t="n">
-        <v>260</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
         <v>120</v>
       </c>
       <c r="AL3" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
         <v>980</v>
       </c>
       <c r="AO3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AP3" t="n">
         <v>15</v>
       </c>
-      <c r="AP3" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AQ3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY3" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.199999999999999</v>
+        <v>75</v>
       </c>
       <c r="BC3" t="n">
         <v>20</v>
@@ -1110,11 +1110,11 @@
         <v>36</v>
       </c>
       <c r="BG3" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="G4" t="n">
         <v>1.4</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1175,121 +1175,121 @@
         <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R4" t="n">
         <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U4" t="n">
         <v>1.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W4" t="n">
         <v>3.5</v>
       </c>
       <c r="X4" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="Y4" t="n">
-        <v>980</v>
+        <v>75</v>
       </c>
       <c r="Z4" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AD4" t="n">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="AE4" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="AF4" t="n">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
         <v>520</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AK4" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AM4" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AN4" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AV4" t="n">
         <v>18</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC4" t="n">
         <v>8.4</v>
@@ -1298,17 +1298,17 @@
         <v>19.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BF4" t="n">
         <v>6</v>
       </c>
       <c r="BG4" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.42</v>
+        <v>2.82</v>
       </c>
       <c r="G5" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>3.05</v>
@@ -1357,16 +1357,16 @@
         <v>3.35</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
         <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
         <v>1.7</v>
@@ -1378,64 +1378,64 @@
         <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U5" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="Y5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG5" t="n">
         <v>21</v>
       </c>
-      <c r="Z5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>22</v>
-      </c>
       <c r="AH5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI5" t="n">
         <v>60</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AJ5" t="n">
         <v>500</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>900</v>
       </c>
       <c r="AK5" t="n">
         <v>980</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
@@ -1444,46 +1444,46 @@
         <v>980</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY5" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AR5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC5" t="n">
         <v>14.5</v>
@@ -1492,17 +1492,17 @@
         <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.14</v>
       </c>
       <c r="G6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H6" t="n">
         <v>3.65</v>
@@ -1548,7 +1548,7 @@
         <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
         <v>1.41</v>
@@ -1581,7 +1581,7 @@
         <v>2.14</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
         <v>1.81</v>
@@ -1638,7 +1638,7 @@
         <v>34</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
         <v>13</v>
@@ -1656,7 +1656,7 @@
         <v>8.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
         <v>13.5</v>
@@ -1677,7 +1677,7 @@
         <v>11.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC6" t="n">
         <v>10.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L7" t="n">
         <v>1.3</v>
@@ -1751,34 +1751,34 @@
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O7" t="n">
         <v>1.19</v>
       </c>
       <c r="P7" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="Q7" t="n">
         <v>1.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T7" t="n">
         <v>1.5</v>
       </c>
       <c r="U7" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X7" t="n">
         <v>980</v>
@@ -1808,7 +1808,7 @@
         <v>980</v>
       </c>
       <c r="AG7" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="AH7" t="n">
         <v>60</v>
@@ -1835,16 +1835,16 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.56</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AT7" t="n">
         <v>9.6</v>
@@ -1856,41 +1856,41 @@
         <v>7.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.15</v>
+        <v>10.5</v>
       </c>
       <c r="AX7" t="n">
         <v>7.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD7" t="n">
         <v>9.6</v>
       </c>
-      <c r="BC7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BE7" t="n">
-        <v>2.66</v>
+        <v>2.26</v>
       </c>
       <c r="BF7" t="n">
         <v>5.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -1921,61 +1921,61 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="G8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H8" t="n">
         <v>2.16</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T8" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="W8" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X8" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="Y8" t="n">
         <v>980</v>
@@ -1993,7 +1993,7 @@
         <v>42</v>
       </c>
       <c r="AD8" t="n">
-        <v>40</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
         <v>980</v>
@@ -2026,22 +2026,22 @@
         <v>980</v>
       </c>
       <c r="AO8" t="n">
-        <v>85</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.52</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
         <v>7.6</v>
@@ -2050,41 +2050,41 @@
         <v>6.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.15</v>
+        <v>9.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.44</v>
+        <v>10.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.52</v>
+        <v>3.7</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.46</v>
+        <v>5.9</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.76</v>
+        <v>3.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
         <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="I9" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
         <v>1.42</v>
@@ -2139,13 +2139,13 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O9" t="n">
         <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
         <v>2</v>
@@ -2157,13 +2157,13 @@
         <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="V9" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="W9" t="n">
         <v>1.13</v>
@@ -2172,19 +2172,19 @@
         <v>16</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AA9" t="n">
         <v>13</v>
       </c>
       <c r="AB9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
         <v>10.5</v>
@@ -2196,19 +2196,19 @@
         <v>420</v>
       </c>
       <c r="AG9" t="n">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="AH9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AJ9" t="n">
         <v>330</v>
       </c>
       <c r="AK9" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AL9" t="n">
         <v>520</v>
@@ -2217,16 +2217,16 @@
         <v>430</v>
       </c>
       <c r="AN9" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AO9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
         <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR9" t="n">
         <v>7</v>
@@ -2235,19 +2235,19 @@
         <v>11</v>
       </c>
       <c r="AT9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW9" t="n">
         <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AY9" t="n">
         <v>22</v>
@@ -2256,16 +2256,16 @@
         <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>42</v>
+        <v>13.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BE9" t="n">
         <v>13</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -2309,46 +2309,46 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I10" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
-        <v>2.02</v>
-      </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R10" t="n">
         <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
@@ -2357,19 +2357,19 @@
         <v>1.95</v>
       </c>
       <c r="V10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA10" t="n">
         <v>23</v>
@@ -2384,19 +2384,19 @@
         <v>10.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF10" t="n">
         <v>32</v>
       </c>
       <c r="AG10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH10" t="n">
         <v>22</v>
       </c>
       <c r="AI10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ10" t="n">
         <v>110</v>
@@ -2411,10 +2411,10 @@
         <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP10" t="n">
         <v>10.5</v>
@@ -2432,7 +2432,7 @@
         <v>13</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV10" t="n">
         <v>10</v>
@@ -2441,19 +2441,19 @@
         <v>21</v>
       </c>
       <c r="AX10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AY10" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB10" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BC10" t="n">
         <v>55</v>
@@ -2462,17 +2462,17 @@
         <v>65</v>
       </c>
       <c r="BE10" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="BF10" t="n">
         <v>70</v>
       </c>
       <c r="BG10" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="G11" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="H11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.15</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>3.3</v>
       </c>
-      <c r="J11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.25</v>
-      </c>
       <c r="L11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P11" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.95</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.94</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
         <v>500</v>
       </c>
       <c r="AB11" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC11" t="n">
         <v>7.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>980</v>
+        <v>190</v>
       </c>
       <c r="AF11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AI11" t="n">
-        <v>380</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>980</v>
+        <v>110</v>
       </c>
       <c r="AK11" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AL11" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AR11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>17.5</v>
       </c>
-      <c r="AS11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX11" t="n">
+      <c r="BA11" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG11" t="n">
         <v>13.5</v>
       </c>
-      <c r="AY11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G12" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H12" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="I12" t="n">
         <v>3.65</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
         <v>3.25</v>
@@ -2727,10 +2727,10 @@
         <v>1.52</v>
       </c>
       <c r="P12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R12" t="n">
         <v>1.2</v>
@@ -2745,10 +2745,10 @@
         <v>1.8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X12" t="n">
         <v>17</v>
@@ -2793,7 +2793,7 @@
         <v>980</v>
       </c>
       <c r="AL12" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AM12" t="n">
         <v>500</v>
@@ -2805,62 +2805,62 @@
         <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.92</v>
+        <v>7.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AU12" t="n">
         <v>4.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY12" t="n">
         <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC12" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC12" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BD12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Al-Arabi Al-Saudi</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Batin</t>
+          <t>Jeddah Club</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.26</v>
+        <v>2.94</v>
       </c>
       <c r="G13" t="n">
-        <v>1.31</v>
+        <v>3.35</v>
       </c>
       <c r="H13" t="n">
-        <v>8.6</v>
+        <v>2.34</v>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>2.54</v>
       </c>
       <c r="J13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X13" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>210</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG13" t="n">
         <v>6</v>
       </c>
-      <c r="K13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -3076,73 +3076,73 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Al-Arabi Al-Saudi</t>
+          <t>Al Jabalain</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jeddah Club</t>
+          <t>Al-Zulfi SC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="H14" t="n">
-        <v>2.38</v>
+        <v>3.6</v>
       </c>
       <c r="I14" t="n">
-        <v>2.64</v>
+        <v>3.95</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.33</v>
       </c>
-      <c r="P14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.61</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="X14" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3151,10 +3151,10 @@
         <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3163,13 +3163,13 @@
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH14" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -3178,7 +3178,7 @@
         <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL14" t="n">
         <v>1000</v>
@@ -3187,68 +3187,68 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.6</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.4</v>
+        <v>19.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.38</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.9</v>
+        <v>8.4</v>
       </c>
       <c r="AX14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY14" t="n">
         <v>7</v>
       </c>
-      <c r="AY14" t="n">
-        <v>6</v>
-      </c>
       <c r="AZ14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.24</v>
+        <v>4.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.85</v>
+        <v>7.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.3</v>
+        <v>7.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.24</v>
+        <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.8</v>
+        <v>9.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Al Jabalain</t>
+          <t>Al-Adalh</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al-Zulfi SC</t>
+          <t>Al Faisaly ( KSA )</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.85</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>1.84</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>1.95</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="T15" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="U15" t="n">
-        <v>2.14</v>
+        <v>2.46</v>
       </c>
       <c r="V15" t="n">
-        <v>1.26</v>
+        <v>2.06</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="X15" t="n">
+        <v>500</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH15" t="n">
         <v>34</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>60</v>
-      </c>
       <c r="AI15" t="n">
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL15" t="n">
         <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO15" t="n">
         <v>55</v>
       </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU15" t="n">
         <v>6.4</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AV15" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.93</v>
+        <v>11</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.93</v>
+        <v>16.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC15" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.92</v>
+        <v>9.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.93</v>
+        <v>4.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,117 +3459,117 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Al-Adalh</t>
+          <t>Sporting Gijon</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Faisaly ( KSA )</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K16" t="n">
         <v>3.95</v>
       </c>
-      <c r="G16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="R16" t="n">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.61</v>
+        <v>1.88</v>
       </c>
       <c r="U16" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="V16" t="n">
-        <v>2.04</v>
+        <v>1.24</v>
       </c>
       <c r="W16" t="n">
-        <v>1.28</v>
+        <v>1.98</v>
       </c>
       <c r="X16" t="n">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="Z16" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AA16" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AC16" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="AE16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AH16" t="n">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
         <v>580</v>
@@ -3578,72 +3578,72 @@
         <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV16" t="n">
         <v>9</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AW16" t="n">
-        <v>6.4</v>
+        <v>1.84</v>
       </c>
       <c r="AX16" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.4</v>
+        <v>1.84</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.6</v>
+        <v>1.82</v>
       </c>
       <c r="BC16" t="n">
-        <v>8</v>
+        <v>1.81</v>
       </c>
       <c r="BD16" t="n">
-        <v>8</v>
+        <v>1.83</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.6</v>
+        <v>1.83</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.6</v>
+        <v>1.83</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sporting Gijon</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="H17" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="I17" t="n">
-        <v>27</v>
+        <v>3.3</v>
       </c>
       <c r="J17" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="K17" t="n">
         <v>4.2</v>
       </c>
       <c r="L17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.44</v>
       </c>
-      <c r="M17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.12</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.19</v>
+        <v>1.76</v>
       </c>
       <c r="X17" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="Y17" t="n">
-        <v>950</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AA17" t="n">
         <v>500</v>
       </c>
       <c r="AB17" t="n">
-        <v>980</v>
+        <v>14.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>500</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF17" t="n">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ17" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AK17" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AM17" t="n">
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.17</v>
+        <v>19.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.17</v>
+        <v>15.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.17</v>
+        <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.18</v>
+        <v>11</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.16</v>
+        <v>12.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.15</v>
+        <v>8.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.17</v>
+        <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.18</v>
+        <v>24</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.16</v>
+        <v>14.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.16</v>
+        <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.16</v>
+        <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.18</v>
+        <v>26</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.17</v>
+        <v>14</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.17</v>
+        <v>18.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.18</v>
+        <v>21</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.17</v>
+        <v>30</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.55</v>
+        <v>10</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.55</v>
+        <v>17.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,184 +3847,184 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>Ghazl El Mahallah</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q18" t="n">
         <v>3.3</v>
       </c>
-      <c r="J18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="R18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT18" t="n">
         <v>5.5</v>
       </c>
-      <c r="O18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="X18" t="n">
+      <c r="AU18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>24</v>
       </c>
-      <c r="Y18" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG18" t="n">
+      <c r="BA18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE18" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>30</v>
-      </c>
       <c r="BF18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BG18" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -4079,31 +4079,31 @@
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q19" t="n">
         <v>1.73</v>
       </c>
       <c r="R19" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S19" t="n">
         <v>2.84</v>
       </c>
       <c r="T19" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U19" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
         <v>2.2</v>
@@ -4115,7 +4115,7 @@
         <v>21</v>
       </c>
       <c r="Z19" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AA19" t="n">
         <v>700</v>
@@ -4124,7 +4124,7 @@
         <v>11.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
         <v>20</v>
@@ -4133,40 +4133,40 @@
         <v>65</v>
       </c>
       <c r="AF19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG19" t="n">
         <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ19" t="n">
         <v>21</v>
       </c>
       <c r="AK19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>18.5</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>18</v>
       </c>
       <c r="AR19" t="n">
         <v>32</v>
@@ -4175,13 +4175,13 @@
         <v>75</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW19" t="n">
         <v>44</v>
@@ -4199,7 +4199,7 @@
         <v>44</v>
       </c>
       <c r="BB19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC19" t="n">
         <v>15</v>
@@ -4208,7 +4208,7 @@
         <v>25</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.6</v>
+        <v>60</v>
       </c>
       <c r="BF19" t="n">
         <v>7.8</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ghazl El Mahallah</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
-        <v>2.34</v>
+        <v>2.92</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="K20" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="L20" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="M20" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="N20" t="n">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="O20" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="P20" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="R20" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC20" t="n">
         <v>7.4</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="X20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="AD20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH20" t="n">
         <v>24</v>
       </c>
-      <c r="Z20" t="n">
-        <v>980</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>980</v>
-      </c>
       <c r="AI20" t="n">
-        <v>700</v>
+        <v>460</v>
       </c>
       <c r="AJ20" t="n">
-        <v>980</v>
+        <v>48</v>
       </c>
       <c r="AK20" t="n">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="AL20" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AM20" t="n">
         <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>980</v>
+        <v>150</v>
       </c>
       <c r="AO20" t="n">
-        <v>700</v>
+        <v>65</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="AR20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY20" t="n">
         <v>11.5</v>
       </c>
-      <c r="AS20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="BC20" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD20" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BE20" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BG20" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>Amiens</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>ESTAC Troyes</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="G21" t="n">
-        <v>2.92</v>
+        <v>4.5</v>
       </c>
       <c r="H21" t="n">
-        <v>3.15</v>
+        <v>1.91</v>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>1.96</v>
       </c>
       <c r="J21" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="K21" t="n">
-        <v>2.94</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="M21" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>2.64</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="P21" t="n">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.78</v>
+        <v>1.98</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>5.7</v>
+        <v>3.55</v>
       </c>
       <c r="T21" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>2.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="X21" t="n">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA21" t="n">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AD21" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AF21" t="n">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="AG21" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AH21" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AI21" t="n">
-        <v>460</v>
+        <v>36</v>
       </c>
       <c r="AJ21" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AK21" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AL21" t="n">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="AM21" t="n">
         <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="AO21" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AP21" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AQ21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU21" t="n">
         <v>7.6</v>
       </c>
-      <c r="AR21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>6</v>
-      </c>
       <c r="AV21" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AW21" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AX21" t="n">
         <v>14.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AZ21" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="BA21" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC21" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BB21" t="n">
-        <v>36</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>18</v>
-      </c>
       <c r="BD21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Amiens</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ESTAC Troyes</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.4</v>
+        <v>1.87</v>
       </c>
       <c r="G22" t="n">
-        <v>4.5</v>
+        <v>1.91</v>
       </c>
       <c r="H22" t="n">
-        <v>1.93</v>
+        <v>5.1</v>
       </c>
       <c r="I22" t="n">
-        <v>1.97</v>
+        <v>5.4</v>
       </c>
       <c r="J22" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="L22" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="T22" t="n">
-        <v>1.81</v>
+        <v>2.16</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="V22" t="n">
-        <v>2.02</v>
+        <v>1.23</v>
       </c>
       <c r="W22" t="n">
-        <v>1.28</v>
+        <v>2.08</v>
       </c>
       <c r="X22" t="n">
-        <v>26</v>
+        <v>10.5</v>
       </c>
       <c r="Y22" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP22" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Z22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>270</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AQ22" t="n">
-        <v>5.3</v>
+        <v>13</v>
       </c>
       <c r="AR22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY22" t="n">
         <v>10</v>
       </c>
-      <c r="AS22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AZ22" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="BA22" t="n">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BB22" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="BC22" t="n">
-        <v>9.6</v>
+        <v>21</v>
       </c>
       <c r="BD22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BE22" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BF22" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="BG22" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T23" t="n">
         <v>1.89</v>
       </c>
-      <c r="G23" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="H23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.18</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="V23" t="n">
-        <v>1.23</v>
+        <v>1.64</v>
       </c>
       <c r="W23" t="n">
-        <v>2.08</v>
+        <v>1.41</v>
       </c>
       <c r="X23" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG23" t="n">
         <v>14</v>
       </c>
-      <c r="Z23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AH23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ23" t="n">
         <v>9</v>
       </c>
-      <c r="AC23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>480</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG23" t="n">
+      <c r="AR23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT23" t="n">
         <v>11</v>
       </c>
-      <c r="AH23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>290</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ23" t="n">
+      <c r="AU23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV23" t="n">
         <v>11</v>
       </c>
-      <c r="AR23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AW23" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="AX23" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="AY23" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA23" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="BB23" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="BC23" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="BD23" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="BE23" t="n">
-        <v>15.5</v>
+        <v>95</v>
       </c>
       <c r="BF23" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Zeljeznicar</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
         <v>3.35</v>
       </c>
-      <c r="G24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.3</v>
-      </c>
       <c r="L24" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="P24" t="n">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.22</v>
+        <v>2.76</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="T24" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="V24" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="W24" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="X24" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA24" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AB24" t="n">
         <v>12</v>
       </c>
       <c r="AC24" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AD24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>700</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE24" t="n">
         <v>11.5</v>
       </c>
-      <c r="AE24" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT24" t="n">
+      <c r="BF24" t="n">
         <v>11</v>
       </c>
-      <c r="AU24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>55</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>95</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>42</v>
-      </c>
       <c r="BG24" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bosnian Premier League</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Zeljeznicar</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.8</v>
+        <v>1.37</v>
       </c>
       <c r="G25" t="n">
-        <v>5.6</v>
+        <v>1.38</v>
       </c>
       <c r="H25" t="n">
-        <v>1.92</v>
+        <v>12</v>
       </c>
       <c r="I25" t="n">
-        <v>2.06</v>
+        <v>12.5</v>
       </c>
       <c r="J25" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="K25" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="M25" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>2.56</v>
+        <v>3.85</v>
       </c>
       <c r="O25" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="P25" t="n">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.72</v>
+        <v>2.02</v>
       </c>
       <c r="R25" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>5.5</v>
+        <v>3.65</v>
       </c>
       <c r="T25" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="U25" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="V25" t="n">
-        <v>1.96</v>
+        <v>1.08</v>
       </c>
       <c r="W25" t="n">
-        <v>1.22</v>
+        <v>3.65</v>
       </c>
       <c r="X25" t="n">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="Y25" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>570</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>290</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>470</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>90</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AT25" t="n">
         <v>6.4</v>
       </c>
-      <c r="Z25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>700</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AU25" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="AV25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>210</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY25" t="n">
         <v>10</v>
       </c>
-      <c r="AW25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AZ25" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="BA25" t="n">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="BB25" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BC25" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BD25" t="n">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="BE25" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="BF25" t="n">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.35</v>
+        <v>6.8</v>
       </c>
       <c r="G26" t="n">
-        <v>1.36</v>
+        <v>7.2</v>
       </c>
       <c r="H26" t="n">
-        <v>12</v>
+        <v>1.6</v>
       </c>
       <c r="I26" t="n">
-        <v>13</v>
+        <v>1.61</v>
       </c>
       <c r="J26" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="K26" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M26" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
         <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.48</v>
+        <v>2.02</v>
       </c>
       <c r="U26" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="V26" t="n">
-        <v>1.08</v>
+        <v>2.62</v>
       </c>
       <c r="W26" t="n">
-        <v>3.75</v>
+        <v>1.16</v>
       </c>
       <c r="X26" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW26" t="n">
         <v>16</v>
       </c>
-      <c r="Y26" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>620</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD26" t="n">
+      <c r="AX26" t="n">
         <v>48</v>
       </c>
-      <c r="AE26" t="n">
-        <v>270</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>230</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>470</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>27</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>95</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>120</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>230</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AY26" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AZ26" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="BA26" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="BB26" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="BC26" t="n">
-        <v>15.5</v>
+        <v>90</v>
       </c>
       <c r="BD26" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="BE26" t="n">
-        <v>150</v>
+        <v>42</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BG26" t="n">
-        <v>130</v>
+        <v>9.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>2.62</v>
       </c>
       <c r="G27" t="n">
-        <v>7.4</v>
+        <v>2.84</v>
       </c>
       <c r="H27" t="n">
-        <v>1.56</v>
+        <v>3.25</v>
       </c>
       <c r="I27" t="n">
-        <v>1.57</v>
+        <v>3.55</v>
       </c>
       <c r="J27" t="n">
-        <v>4.4</v>
+        <v>2.86</v>
       </c>
       <c r="K27" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="M27" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="N27" t="n">
-        <v>3.9</v>
+        <v>2.84</v>
       </c>
       <c r="O27" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.99</v>
+        <v>2.54</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="S27" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="U27" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="V27" t="n">
-        <v>2.74</v>
+        <v>1.39</v>
       </c>
       <c r="W27" t="n">
-        <v>1.15</v>
+        <v>1.55</v>
       </c>
       <c r="X27" t="n">
-        <v>15.5</v>
+        <v>90</v>
       </c>
       <c r="Y27" t="n">
-        <v>7.6</v>
+        <v>980</v>
       </c>
       <c r="Z27" t="n">
-        <v>8.4</v>
+        <v>980</v>
       </c>
       <c r="AA27" t="n">
-        <v>13.5</v>
+        <v>900</v>
       </c>
       <c r="AB27" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>9.6</v>
+        <v>980</v>
       </c>
       <c r="AE27" t="n">
-        <v>16.5</v>
+        <v>980</v>
       </c>
       <c r="AF27" t="n">
-        <v>60</v>
+        <v>980</v>
       </c>
       <c r="AG27" t="n">
-        <v>27</v>
+        <v>980</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="AI27" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AJ27" t="n">
-        <v>240</v>
+        <v>900</v>
       </c>
       <c r="AK27" t="n">
-        <v>120</v>
+        <v>980</v>
       </c>
       <c r="AL27" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AM27" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>160</v>
+        <v>980</v>
       </c>
       <c r="AO27" t="n">
-        <v>9.199999999999999</v>
+        <v>500</v>
       </c>
       <c r="AP27" t="n">
-        <v>13.5</v>
+        <v>5.2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>8.199999999999999</v>
+        <v>1.72</v>
       </c>
       <c r="AS27" t="n">
-        <v>13</v>
+        <v>1.77</v>
       </c>
       <c r="AT27" t="n">
-        <v>18.5</v>
+        <v>4.9</v>
       </c>
       <c r="AU27" t="n">
-        <v>9.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="AV27" t="n">
-        <v>9.4</v>
+        <v>2.16</v>
       </c>
       <c r="AW27" t="n">
-        <v>16</v>
+        <v>1.77</v>
       </c>
       <c r="AX27" t="n">
-        <v>48</v>
+        <v>1.7</v>
       </c>
       <c r="AY27" t="n">
-        <v>24</v>
+        <v>2.14</v>
       </c>
       <c r="AZ27" t="n">
-        <v>22</v>
+        <v>1.71</v>
       </c>
       <c r="BA27" t="n">
-        <v>36</v>
+        <v>1.78</v>
       </c>
       <c r="BB27" t="n">
-        <v>24</v>
+        <v>1.77</v>
       </c>
       <c r="BC27" t="n">
-        <v>90</v>
+        <v>1.76</v>
       </c>
       <c r="BD27" t="n">
-        <v>85</v>
+        <v>1.77</v>
       </c>
       <c r="BE27" t="n">
-        <v>36</v>
+        <v>1.77</v>
       </c>
       <c r="BF27" t="n">
-        <v>23</v>
+        <v>1.75</v>
       </c>
       <c r="BG27" t="n">
-        <v>8.6</v>
+        <v>1.78</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.62</v>
+        <v>2.14</v>
       </c>
       <c r="G28" t="n">
-        <v>2.84</v>
+        <v>2.24</v>
       </c>
       <c r="H28" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="I28" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="K28" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M28" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N28" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="P28" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="T28" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="U28" t="n">
         <v>1.85</v>
       </c>
       <c r="V28" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="W28" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="X28" t="n">
-        <v>90</v>
+        <v>10.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>980</v>
+        <v>12.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AA28" t="n">
         <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>980</v>
+        <v>7.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AE28" t="n">
-        <v>980</v>
+        <v>270</v>
       </c>
       <c r="AF28" t="n">
-        <v>980</v>
+        <v>12.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>980</v>
+        <v>11.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AI28" t="n">
-        <v>500</v>
+        <v>360</v>
       </c>
       <c r="AJ28" t="n">
-        <v>900</v>
+        <v>65</v>
       </c>
       <c r="AK28" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AL28" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AO28" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.87</v>
+        <v>19</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.93</v>
+        <v>10.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.44</v>
+        <v>15.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.93</v>
+        <v>10</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.84</v>
+        <v>10.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>2.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.9</v>
+        <v>10.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.93</v>
+        <v>8.4</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.91</v>
+        <v>22</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.89</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.93</v>
+        <v>11</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.79</v>
+        <v>17.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.82</v>
+        <v>10.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5986,186 +5986,186 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Lobos UPNFM</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.14</v>
+        <v>1.71</v>
       </c>
       <c r="G29" t="n">
-        <v>2.24</v>
+        <v>3.6</v>
       </c>
       <c r="H29" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="I29" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="J29" t="n">
-        <v>3.15</v>
+        <v>1.68</v>
       </c>
       <c r="K29" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="M29" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="P29" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="R29" t="n">
         <v>1.23</v>
       </c>
       <c r="S29" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="T29" t="n">
-        <v>2.02</v>
+        <v>1.05</v>
       </c>
       <c r="U29" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="V29" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="W29" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="X29" t="n">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="Y29" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR29" t="n">
-        <v>8.800000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AS29" t="n">
-        <v>10.5</v>
+        <v>1.05</v>
       </c>
       <c r="AT29" t="n">
-        <v>6.6</v>
+        <v>1.05</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.6</v>
+        <v>1.05</v>
       </c>
       <c r="AV29" t="n">
-        <v>15.5</v>
+        <v>1.05</v>
       </c>
       <c r="AW29" t="n">
-        <v>10</v>
+        <v>1.05</v>
       </c>
       <c r="AX29" t="n">
-        <v>10.5</v>
+        <v>1.05</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.800000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AZ29" t="n">
-        <v>7.8</v>
+        <v>1.05</v>
       </c>
       <c r="BA29" t="n">
-        <v>10.5</v>
+        <v>1.05</v>
       </c>
       <c r="BB29" t="n">
-        <v>8.4</v>
+        <v>1.05</v>
       </c>
       <c r="BC29" t="n">
-        <v>22</v>
+        <v>1.05</v>
       </c>
       <c r="BD29" t="n">
-        <v>9.800000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="BE29" t="n">
-        <v>11</v>
+        <v>1.05</v>
       </c>
       <c r="BF29" t="n">
-        <v>17.5</v>
+        <v>1.05</v>
       </c>
       <c r="BG29" t="n">
-        <v>10.5</v>
+        <v>1.55</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,184 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Genesis Huracan</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J30" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="K30" t="n">
-        <v>950</v>
+        <v>2.9</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="N30" t="n">
-        <v>1.1</v>
+        <v>2.46</v>
       </c>
       <c r="O30" t="n">
-        <v>1.27</v>
+        <v>1.66</v>
       </c>
       <c r="P30" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.26</v>
+        <v>3.1</v>
       </c>
       <c r="R30" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="S30" t="n">
-        <v>1.26</v>
+        <v>6.8</v>
       </c>
       <c r="T30" t="n">
-        <v>1.05</v>
+        <v>2.34</v>
       </c>
       <c r="U30" t="n">
-        <v>1.05</v>
+        <v>1.68</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>110</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -6374,186 +6374,186 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="G31" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="H31" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="I31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q31" t="n">
         <v>4.5</v>
       </c>
-      <c r="J31" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.15</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="S31" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="U31" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="W31" t="n">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="X31" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="AA31" t="n">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AB31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC31" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>80</v>
+      </c>
+      <c r="AI31" t="n">
         <v>500</v>
       </c>
-      <c r="AF31" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>44</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>700</v>
-      </c>
       <c r="AJ31" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="AK31" t="n">
-        <v>40</v>
+        <v>210</v>
       </c>
       <c r="AL31" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AM31" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>40</v>
+        <v>380</v>
       </c>
       <c r="AO31" t="n">
-        <v>700</v>
+        <v>490</v>
       </c>
       <c r="AP31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ31" t="n">
         <v>6.2</v>
       </c>
-      <c r="AQ31" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AR31" t="n">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AT31" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV31" t="n">
         <v>17.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AX31" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BA31" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BB31" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="BC31" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="BD31" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BE31" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="BF31" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG31" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,191 +6563,191 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N32" t="n">
         <v>2.96</v>
       </c>
-      <c r="G32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1.91</v>
-      </c>
       <c r="O32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W32" t="n">
         <v>2.04</v>
       </c>
-      <c r="P32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="S32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.48</v>
-      </c>
       <c r="X32" t="n">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="Z32" t="n">
-        <v>27</v>
+        <v>980</v>
       </c>
       <c r="AA32" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB32" t="n">
         <v>7</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AF32" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AG32" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="AH32" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AI32" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AJ32" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN32" t="n">
         <v>85</v>
       </c>
-      <c r="AK32" t="n">
-        <v>210</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>380</v>
-      </c>
       <c r="AO32" t="n">
-        <v>490</v>
+        <v>700</v>
       </c>
       <c r="AP32" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT32" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR32" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AU32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY32" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV32" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AZ32" t="n">
-        <v>32</v>
+        <v>9.4</v>
       </c>
       <c r="BA32" t="n">
-        <v>46</v>
+        <v>2.9</v>
       </c>
       <c r="BB32" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="BC32" t="n">
-        <v>48</v>
+        <v>9.4</v>
       </c>
       <c r="BD32" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="BE32" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="BF32" t="n">
-        <v>32</v>
+        <v>8.6</v>
       </c>
       <c r="BG32" t="n">
-        <v>38</v>
+        <v>2.88</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Curico Unido</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.87</v>
+        <v>2.52</v>
       </c>
       <c r="G33" t="n">
-        <v>1.95</v>
+        <v>2.68</v>
       </c>
       <c r="H33" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="I33" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
-        <v>3.35</v>
+        <v>2.82</v>
       </c>
       <c r="K33" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="N33" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="O33" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P33" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T33" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="U33" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="V33" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="W33" t="n">
-        <v>2.04</v>
+        <v>1.59</v>
       </c>
       <c r="X33" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Y33" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="Z33" t="n">
-        <v>980</v>
+        <v>27</v>
       </c>
       <c r="AA33" t="n">
-        <v>900</v>
+        <v>230</v>
       </c>
       <c r="AB33" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>980</v>
+        <v>16.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>480</v>
+        <v>150</v>
       </c>
       <c r="AF33" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AG33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>310</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE33" t="n">
         <v>11</v>
       </c>
-      <c r="AH33" t="n">
-        <v>70</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>290</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV33" t="n">
+      <c r="BF33" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AW33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BG33" t="n">
-        <v>2.86</v>
+        <v>10</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6956,186 +6956,186 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Sportivo San Lorenzo</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Curico Unido</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="G34" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="H34" t="n">
-        <v>3.55</v>
+        <v>2.12</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="K34" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="L34" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="M34" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="O34" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="P34" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="R34" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="S34" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="T34" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U34" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V34" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="W34" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="X34" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="Y34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS34" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z34" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>230</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF34" t="n">
+      <c r="AT34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG34" t="n">
         <v>16</v>
       </c>
-      <c r="AG34" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>310</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,93 +7145,93 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sportivo San Lorenzo</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="G35" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="H35" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T35" t="n">
         <v>2.12</v>
       </c>
-      <c r="I35" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="J35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K35" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.94</v>
-      </c>
       <c r="U35" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="V35" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="W35" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="X35" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AA35" t="n">
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD35" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE35" t="n">
         <v>1000</v>
@@ -7249,7 +7249,7 @@
         <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
         <v>1000</v>
@@ -7258,7 +7258,7 @@
         <v>1000</v>
       </c>
       <c r="AM35" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
         <v>1000</v>
@@ -7267,69 +7267,69 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ35" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="AR35" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT35" t="n">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="AU35" t="n">
-        <v>6.6</v>
+        <v>3.95</v>
       </c>
       <c r="AV35" t="n">
-        <v>9.4</v>
+        <v>4.8</v>
       </c>
       <c r="AW35" t="n">
         <v>4.9</v>
       </c>
       <c r="AX35" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ35" t="n">
         <v>5</v>
       </c>
-      <c r="AY35" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BA35" t="n">
-        <v>5.3</v>
+        <v>2.04</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.6</v>
+        <v>1.79</v>
       </c>
       <c r="BC35" t="n">
-        <v>5.4</v>
+        <v>1.77</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.6</v>
+        <v>2.06</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.7</v>
+        <v>2.08</v>
       </c>
       <c r="BF35" t="n">
-        <v>5.5</v>
+        <v>2.06</v>
       </c>
       <c r="BG35" t="n">
-        <v>16</v>
+        <v>5.9</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,184 +7339,184 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="H36" t="n">
-        <v>2.06</v>
+        <v>2.54</v>
       </c>
       <c r="I36" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="J36" t="n">
         <v>3.15</v>
       </c>
       <c r="K36" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="L36" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="M36" t="n">
         <v>1.12</v>
       </c>
       <c r="N36" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="O36" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="P36" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="R36" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S36" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="T36" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="U36" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="V36" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="W36" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP36" t="n">
-        <v>4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="AR36" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.7</v>
+        <v>30</v>
       </c>
       <c r="AT36" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.65</v>
+        <v>6.6</v>
       </c>
       <c r="AV36" t="n">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="AW36" t="n">
-        <v>5.1</v>
+        <v>28</v>
       </c>
       <c r="AX36" t="n">
-        <v>5.4</v>
+        <v>19</v>
       </c>
       <c r="AY36" t="n">
-        <v>4.8</v>
+        <v>13.5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>5</v>
+        <v>19.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>3.75</v>
+        <v>30</v>
       </c>
       <c r="BB36" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.96</v>
+        <v>42</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.85</v>
+        <v>32</v>
       </c>
       <c r="BE36" t="n">
-        <v>3.9</v>
+        <v>44</v>
       </c>
       <c r="BF36" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="BG36" t="n">
-        <v>5.4</v>
+        <v>28</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -7538,186 +7538,186 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.3</v>
+        <v>1.99</v>
       </c>
       <c r="G37" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I37" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K37" t="n">
         <v>3.4</v>
       </c>
-      <c r="H37" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="I37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K37" t="n">
-        <v>3.25</v>
-      </c>
       <c r="L37" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="M37" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="O37" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="P37" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="R37" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="T37" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="U37" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="V37" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="W37" t="n">
-        <v>1.41</v>
+        <v>1.96</v>
       </c>
       <c r="X37" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="Z37" t="n">
-        <v>14.5</v>
+        <v>980</v>
       </c>
       <c r="AA37" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN37" t="n">
         <v>38</v>
       </c>
-      <c r="AB37" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK37" t="n">
+      <c r="AO37" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>75</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD37" t="n">
         <v>55</v>
       </c>
-      <c r="AL37" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB37" t="n">
+      <c r="BE37" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG37" t="n">
         <v>44</v>
       </c>
-      <c r="BC37" t="n">
-        <v>42</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>29</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>28</v>
-      </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7732,373 +7732,179 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>6.2</v>
       </c>
       <c r="G38" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T38" t="n">
         <v>2.06</v>
       </c>
-      <c r="H38" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I38" t="n">
-        <v>5</v>
-      </c>
-      <c r="J38" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S38" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.36</v>
-      </c>
       <c r="U38" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="V38" t="n">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="W38" t="n">
-        <v>1.94</v>
+        <v>1.17</v>
       </c>
       <c r="X38" t="n">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="Y38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>270</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
         <v>14</v>
       </c>
-      <c r="Z38" t="n">
-        <v>980</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF38" t="n">
+      <c r="AP38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>44</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG38" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG38" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>50</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>280</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>55</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>44</v>
-      </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Ecuadorian Serie A</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Independiente (Ecu)</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G39" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="J39" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K39" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S39" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X39" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>70</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>270</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>150</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>44</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH39" t="inlineStr">
-        <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -763,13 +763,13 @@
         <v>24</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="I2" t="n">
         <v>1.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
         <v>7.8</v>
@@ -778,28 +778,28 @@
         <v>1.23</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1</v>
+        <v>2.02</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="R2" t="n">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>1.57</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="U2" t="n">
         <v>1.05</v>
@@ -826,7 +826,7 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -865,16 +865,16 @@
         <v>29</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AT2" t="n">
         <v>4.2</v>
@@ -883,10 +883,10 @@
         <v>1.3</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.27</v>
+        <v>7.2</v>
       </c>
       <c r="AX2" t="n">
         <v>4.2</v>
@@ -895,10 +895,10 @@
         <v>4.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BB2" t="n">
         <v>4.2</v>
@@ -907,10 +907,10 @@
         <v>4.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.3</v>
+        <v>110</v>
       </c>
       <c r="BF2" t="n">
         <v>4.2</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="I3" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
         <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V3" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="X3" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AB3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG3" t="n">
         <v>19</v>
       </c>
-      <c r="AC3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="AJ3" t="n">
         <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AL3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>980</v>
+        <v>80</v>
       </c>
       <c r="AO3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AP3" t="n">
         <v>15</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS3" t="n">
         <v>17.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW3" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="AY3" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="BC3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.6</v>
+        <v>48</v>
       </c>
       <c r="BE3" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BF3" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.37</v>
@@ -1169,76 +1169,76 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="X4" t="n">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="Z4" t="n">
         <v>110</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>640</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC4" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AE4" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AI4" t="n">
-        <v>520</v>
+        <v>200</v>
       </c>
       <c r="AJ4" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>30</v>
+        <v>15.5</v>
       </c>
       <c r="AL4" t="n">
         <v>46</v>
@@ -1247,68 +1247,68 @@
         <v>230</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR4" t="n">
         <v>14</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>12</v>
-      </c>
       <c r="AS4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AW4" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC4" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BF4" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BG4" t="n">
         <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="G5" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="H5" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
         <v>3.35</v>
       </c>
       <c r="L5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
@@ -1366,73 +1366,73 @@
         <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R5" t="n">
         <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U5" t="n">
         <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W5" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Y5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AA5" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="AB5" t="n">
-        <v>17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5" t="n">
         <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>980</v>
       </c>
       <c r="AE5" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AF5" t="n">
         <v>30</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
         <v>34</v>
       </c>
       <c r="AI5" t="n">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="AJ5" t="n">
         <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>980</v>
+        <v>80</v>
       </c>
       <c r="AL5" t="n">
         <v>55</v>
@@ -1444,65 +1444,65 @@
         <v>980</v>
       </c>
       <c r="AO5" t="n">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW5" t="n">
         <v>9.6</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>21</v>
-      </c>
       <c r="AX5" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BB5" t="n">
         <v>16.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
         <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -1533,136 +1533,136 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2.14</v>
       </c>
-      <c r="G6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="R6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S6" t="n">
         <v>3.9</v>
       </c>
-      <c r="J6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="X6" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
         <v>85</v>
       </c>
       <c r="AA6" t="n">
-        <v>500</v>
+        <v>270</v>
       </c>
       <c r="AB6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
-        <v>980</v>
+        <v>200</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
         <v>250</v>
       </c>
       <c r="AJ6" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AK6" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AL6" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="AP6" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR6" t="n">
         <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
         <v>13.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="AX6" t="n">
         <v>11.5</v>
@@ -1671,16 +1671,16 @@
         <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BB6" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="BC6" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD6" t="n">
         <v>30</v>
@@ -1689,14 +1689,14 @@
         <v>12.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="BG6" t="n">
         <v>11</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G7" t="n">
         <v>1.98</v>
@@ -1751,7 +1751,7 @@
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="O7" t="n">
         <v>1.19</v>
@@ -1760,10 +1760,10 @@
         <v>2.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S7" t="n">
         <v>2.48</v>
@@ -1772,7 +1772,7 @@
         <v>1.5</v>
       </c>
       <c r="U7" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V7" t="n">
         <v>1.31</v>
@@ -1781,73 +1781,73 @@
         <v>2.02</v>
       </c>
       <c r="X7" t="n">
-        <v>980</v>
+        <v>90</v>
       </c>
       <c r="Y7" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="Z7" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI7" t="n">
         <v>500</v>
       </c>
-      <c r="AB7" t="n">
-        <v>980</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>980</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>980</v>
+        <v>90</v>
       </c>
       <c r="AK7" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AL7" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS7" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AT7" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AU7" t="n">
         <v>6.8</v>
@@ -1856,19 +1856,19 @@
         <v>7.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX7" t="n">
         <v>7.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AZ7" t="n">
         <v>7.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BB7" t="n">
         <v>11</v>
@@ -1880,17 +1880,17 @@
         <v>9.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.26</v>
+        <v>2.82</v>
       </c>
       <c r="BF7" t="n">
         <v>5.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.14</v>
+        <v>2.46</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -1924,55 +1924,55 @@
         <v>3.55</v>
       </c>
       <c r="G8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H8" t="n">
         <v>2.16</v>
       </c>
       <c r="I8" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
         <v>3.95</v>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
         <v>1.66</v>
       </c>
       <c r="U8" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="W8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X8" t="n">
         <v>36</v>
@@ -2038,53 +2038,53 @@
         <v>7.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AV8" t="n">
         <v>6.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
         <v>6.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.7</v>
+        <v>2.98</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.24</v>
+        <v>2.82</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H9" t="n">
         <v>1.49</v>
@@ -2127,34 +2127,34 @@
         <v>1.51</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R9" t="n">
         <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T9" t="n">
         <v>2.16</v>
@@ -2166,16 +2166,16 @@
         <v>2.96</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AA9" t="n">
         <v>13</v>
@@ -2187,98 +2187,98 @@
         <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
-        <v>420</v>
+        <v>75</v>
       </c>
       <c r="AG9" t="n">
         <v>34</v>
       </c>
       <c r="AH9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI9" t="n">
         <v>44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AK9" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AL9" t="n">
         <v>520</v>
       </c>
       <c r="AM9" t="n">
-        <v>430</v>
+        <v>190</v>
       </c>
       <c r="AN9" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AO9" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS9" t="n">
         <v>11</v>
       </c>
       <c r="AT9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW9" t="n">
         <v>15</v>
       </c>
       <c r="AX9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>25</v>
       </c>
-      <c r="AY9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>21</v>
-      </c>
       <c r="BA9" t="n">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="BB9" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="BD9" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="BE9" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -2309,37 +2309,37 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="G10" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H10" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="J10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.5</v>
       </c>
-      <c r="K10" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M10" t="n">
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
         <v>1.41</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q10" t="n">
         <v>2.26</v>
@@ -2354,22 +2354,22 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="W10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="n">
         <v>7.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA10" t="n">
         <v>23</v>
@@ -2378,25 +2378,25 @@
         <v>14</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD10" t="n">
         <v>10.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG10" t="n">
         <v>18</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ10" t="n">
         <v>110</v>
@@ -2405,7 +2405,7 @@
         <v>65</v>
       </c>
       <c r="AL10" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM10" t="n">
         <v>140</v>
@@ -2414,13 +2414,13 @@
         <v>110</v>
       </c>
       <c r="AO10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AP10" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR10" t="n">
         <v>10</v>
@@ -2432,7 +2432,7 @@
         <v>13</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
         <v>10</v>
@@ -2441,22 +2441,22 @@
         <v>21</v>
       </c>
       <c r="AX10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AY10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AZ10" t="n">
         <v>19.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB10" t="n">
         <v>95</v>
       </c>
       <c r="BC10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BD10" t="n">
         <v>65</v>
@@ -2465,14 +2465,14 @@
         <v>120</v>
       </c>
       <c r="BF10" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BG10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -2509,164 +2509,164 @@
         <v>2.62</v>
       </c>
       <c r="H11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I11" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
         <v>1.61</v>
       </c>
       <c r="X11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
         <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD11" t="n">
         <v>14.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="AF11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>38</v>
+        <v>19.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ11" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="AK11" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AO11" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
         <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY11" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA11" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BB11" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
         <v>16.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BE11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BF11" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="G12" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="H12" t="n">
         <v>3.55</v>
       </c>
       <c r="I12" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="J12" t="n">
         <v>3.1</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.57</v>
@@ -2724,70 +2724,70 @@
         <v>2.78</v>
       </c>
       <c r="O12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P12" t="n">
         <v>1.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="R12" t="n">
         <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X12" t="n">
         <v>17</v>
       </c>
       <c r="Y12" t="n">
-        <v>980</v>
+        <v>22</v>
       </c>
       <c r="Z12" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>250</v>
       </c>
       <c r="AB12" t="n">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="AC12" t="n">
         <v>13.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AE12" t="n">
         <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="AG12" t="n">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="AH12" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AI12" t="n">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AJ12" t="n">
-        <v>980</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
         <v>980</v>
@@ -2796,71 +2796,71 @@
         <v>170</v>
       </c>
       <c r="AM12" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>980</v>
+        <v>600</v>
       </c>
       <c r="AO12" t="n">
         <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AT12" t="n">
         <v>6.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY12" t="n">
         <v>7</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AZ12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC12" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AX12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY12" t="n">
+      <c r="BD12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG12" t="n">
         <v>10</v>
       </c>
-      <c r="AZ12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>3</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="G13" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="I13" t="n">
-        <v>2.54</v>
+        <v>2.84</v>
       </c>
       <c r="J13" t="n">
         <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
         <v>1.38</v>
@@ -2915,7 +2915,7 @@
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O13" t="n">
         <v>1.28</v>
@@ -2930,37 +2930,37 @@
         <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U13" t="n">
         <v>2.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="W13" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="X13" t="n">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="Y13" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="Z13" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD13" t="n">
         <v>1000</v>
@@ -2969,19 +2969,19 @@
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG13" t="n">
         <v>500</v>
       </c>
       <c r="AH13" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI13" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="AK13" t="n">
         <v>1000</v>
@@ -2990,16 +2990,16 @@
         <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
         <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>5.6</v>
@@ -3008,53 +3008,53 @@
         <v>7.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT13" t="n">
         <v>6.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE13" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="BF13" t="n">
         <v>7.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -3085,64 +3085,64 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I14" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
         <v>1.29</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R14" t="n">
         <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W14" t="n">
         <v>1.83</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y14" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3166,10 +3166,10 @@
         <v>40</v>
       </c>
       <c r="AG14" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AH14" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -3193,13 +3193,13 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ14" t="n">
         <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS14" t="n">
         <v>9.199999999999999</v>
@@ -3208,13 +3208,13 @@
         <v>5.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX14" t="n">
         <v>6</v>
@@ -3223,32 +3223,32 @@
         <v>7</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BD14" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF14" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -3279,76 +3279,76 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G15" t="n">
         <v>4</v>
       </c>
-      <c r="G15" t="n">
-        <v>4.7</v>
-      </c>
       <c r="H15" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="I15" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M15" t="n">
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P15" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="S15" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="T15" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="U15" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="V15" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="W15" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
+        <v>46</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA15" t="n">
         <v>500</v>
       </c>
-      <c r="Y15" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>22</v>
-      </c>
       <c r="AB15" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AC15" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
         <v>20</v>
@@ -3357,92 +3357,92 @@
         <v>65</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI15" t="n">
         <v>500</v>
       </c>
-      <c r="AH15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK15" t="n">
         <v>500</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM15" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AO15" t="n">
-        <v>55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP15" t="n">
         <v>21</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS15" t="n">
         <v>10.5</v>
       </c>
       <c r="AT15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW15" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>11</v>
       </c>
       <c r="AX15" t="n">
         <v>14.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BA15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="G16" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
         <v>3.35</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L16" t="n">
         <v>1.45</v>
@@ -3497,7 +3497,7 @@
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
         <v>1.37</v>
@@ -3506,10 +3506,10 @@
         <v>1.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
         <v>3.6</v>
@@ -3518,19 +3518,19 @@
         <v>1.88</v>
       </c>
       <c r="U16" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="X16" t="n">
         <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="Z16" t="n">
         <v>500</v>
@@ -3545,16 +3545,16 @@
         <v>42</v>
       </c>
       <c r="AD16" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AH16" t="n">
         <v>160</v>
@@ -3566,7 +3566,7 @@
         <v>500</v>
       </c>
       <c r="AK16" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AL16" t="n">
         <v>500</v>
@@ -3581,16 +3581,16 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ16" t="n">
         <v>7</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.81</v>
+        <v>12.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AT16" t="n">
         <v>4.4</v>
@@ -3602,7 +3602,7 @@
         <v>9</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AX16" t="n">
         <v>6.2</v>
@@ -3614,29 +3614,29 @@
         <v>11.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.82</v>
+        <v>11.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.81</v>
+        <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.83</v>
+        <v>17.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="BF16" t="n">
         <v>4.9</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.83</v>
+        <v>5.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G17" t="n">
         <v>2.3</v>
@@ -3676,13 +3676,13 @@
         <v>3.1</v>
       </c>
       <c r="I17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.3</v>
@@ -3691,28 +3691,28 @@
         <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O17" t="n">
         <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S17" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U17" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="V17" t="n">
         <v>1.44</v>
@@ -3739,10 +3739,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="AF17" t="n">
         <v>17.5</v>
@@ -3754,7 +3754,7 @@
         <v>15</v>
       </c>
       <c r="AI17" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AJ17" t="n">
         <v>29</v>
@@ -3766,13 +3766,13 @@
         <v>85</v>
       </c>
       <c r="AM17" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AP17" t="n">
         <v>19.5</v>
@@ -3781,10 +3781,10 @@
         <v>15.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS17" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AT17" t="n">
         <v>12.5</v>
@@ -3793,7 +3793,7 @@
         <v>8.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW17" t="n">
         <v>24</v>
@@ -3811,16 +3811,16 @@
         <v>26</v>
       </c>
       <c r="BB17" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BC17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD17" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="BF17" t="n">
         <v>10</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -3864,16 +3864,16 @@
         <v>2.26</v>
       </c>
       <c r="G18" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H18" t="n">
         <v>4.6</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="K18" t="n">
         <v>2.86</v>
@@ -3888,13 +3888,13 @@
         <v>2.32</v>
       </c>
       <c r="O18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="P18" t="n">
         <v>1.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R18" t="n">
         <v>1.14</v>
@@ -3912,7 +3912,7 @@
         <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X18" t="n">
         <v>6.8</v>
@@ -3930,7 +3930,7 @@
         <v>6.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD18" t="n">
         <v>70</v>
@@ -3942,10 +3942,10 @@
         <v>23</v>
       </c>
       <c r="AG18" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AI18" t="n">
         <v>700</v>
@@ -3972,16 +3972,16 @@
         <v>5.9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR18" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU18" t="n">
         <v>6.2</v>
@@ -3990,31 +3990,31 @@
         <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AY18" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC18" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="BE18" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF18" t="n">
         <v>9</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -4061,46 +4061,46 @@
         <v>1.83</v>
       </c>
       <c r="H19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="T19" t="n">
         <v>1.72</v>
       </c>
       <c r="U19" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V19" t="n">
         <v>1.25</v>
@@ -4109,70 +4109,70 @@
         <v>2.2</v>
       </c>
       <c r="X19" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y19" t="n">
         <v>21</v>
       </c>
       <c r="Z19" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AA19" t="n">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AB19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI19" t="n">
         <v>55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM19" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN19" t="n">
         <v>9.6</v>
       </c>
       <c r="AO19" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AP19" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS19" t="n">
-        <v>75</v>
+        <v>17.5</v>
       </c>
       <c r="AT19" t="n">
         <v>9.800000000000001</v>
@@ -4181,44 +4181,44 @@
         <v>8.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW19" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AX19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY19" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB19" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE19" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG19" t="n">
         <v>42</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G20" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="H20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J20" t="n">
         <v>2.9</v>
@@ -4273,34 +4273,34 @@
         <v>1.14</v>
       </c>
       <c r="N20" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="O20" t="n">
         <v>1.57</v>
       </c>
       <c r="P20" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
         <v>2.14</v>
       </c>
       <c r="U20" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="V20" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X20" t="n">
         <v>8.6</v>
@@ -4351,7 +4351,7 @@
         <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AO20" t="n">
         <v>65</v>
@@ -4366,7 +4366,7 @@
         <v>17</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT20" t="n">
         <v>7</v>
@@ -4378,7 +4378,7 @@
         <v>12.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="AX20" t="n">
         <v>14.5</v>
@@ -4396,23 +4396,23 @@
         <v>36</v>
       </c>
       <c r="BC20" t="n">
-        <v>8.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="BD20" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF20" t="n">
         <v>9</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="H21" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="I21" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="J21" t="n">
         <v>3.9</v>
@@ -4467,67 +4467,67 @@
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T21" t="n">
         <v>1.8</v>
       </c>
       <c r="U21" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V21" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="W21" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X21" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AB21" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AC21" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD21" t="n">
         <v>11</v>
       </c>
       <c r="AE21" t="n">
-        <v>40</v>
+        <v>19.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AG21" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AH21" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AI21" t="n">
         <v>36</v>
@@ -4536,77 +4536,77 @@
         <v>500</v>
       </c>
       <c r="AK21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL21" t="n">
         <v>65</v>
       </c>
-      <c r="AL21" t="n">
-        <v>190</v>
-      </c>
       <c r="AM21" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AN21" t="n">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="AO21" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="AP21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW21" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AY21" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="BB21" t="n">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BD21" t="n">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="BF21" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BG21" t="n">
         <v>11</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G22" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H22" t="n">
         <v>5.1</v>
@@ -4649,55 +4649,55 @@
         <v>5.4</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K22" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M22" t="n">
         <v>1.1</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P22" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="R22" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U22" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V22" t="n">
         <v>1.23</v>
       </c>
       <c r="W22" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="AA22" t="n">
         <v>150</v>
@@ -4712,95 +4712,95 @@
         <v>21</v>
       </c>
       <c r="AE22" t="n">
-        <v>90</v>
+        <v>230</v>
       </c>
       <c r="AF22" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AG22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AI22" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AJ22" t="n">
         <v>21</v>
       </c>
       <c r="AK22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM22" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>55</v>
+        <v>18.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AP22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ22" t="n">
         <v>13</v>
       </c>
       <c r="AR22" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AS22" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AT22" t="n">
         <v>6.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>16.5</v>
+        <v>40</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ22" t="n">
         <v>23</v>
       </c>
       <c r="BA22" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="BB22" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC22" t="n">
         <v>21</v>
       </c>
       <c r="BD22" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="BE22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BF22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BG22" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
         <v>3.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M23" t="n">
         <v>1.09</v>
@@ -4864,7 +4864,7 @@
         <v>1.79</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R23" t="n">
         <v>1.3</v>
@@ -4882,16 +4882,16 @@
         <v>1.64</v>
       </c>
       <c r="W23" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X23" t="n">
         <v>11.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA23" t="n">
         <v>34</v>
@@ -4915,7 +4915,7 @@
         <v>14</v>
       </c>
       <c r="AH23" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI23" t="n">
         <v>44</v>
@@ -4984,17 +4984,17 @@
         <v>50</v>
       </c>
       <c r="BE23" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BF23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BG23" t="n">
         <v>24</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -5025,91 +5025,91 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="H24" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K24" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M24" t="n">
         <v>1.13</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O24" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="P24" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S24" t="n">
         <v>5.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U24" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V24" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="W24" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AB24" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AC24" t="n">
         <v>7.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF24" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AG24" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AH24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI24" t="n">
         <v>65</v>
@@ -5130,65 +5130,65 @@
         <v>600</v>
       </c>
       <c r="AO24" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AP24" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AR24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT24" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV24" t="n">
         <v>10</v>
       </c>
       <c r="AW24" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="AY24" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="BB24" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BD24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE24" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -5219,91 +5219,91 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="G25" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="H25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I25" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="J25" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="K25" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L25" t="n">
         <v>1.42</v>
       </c>
       <c r="M25" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O25" t="n">
         <v>1.34</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T25" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="U25" t="n">
         <v>1.65</v>
       </c>
       <c r="V25" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W25" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="X25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y25" t="n">
         <v>28</v>
       </c>
       <c r="Z25" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AA25" t="n">
-        <v>570</v>
+        <v>530</v>
       </c>
       <c r="AB25" t="n">
         <v>6.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD25" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AE25" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AF25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AG25" t="n">
         <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI25" t="n">
         <v>220</v>
@@ -5315,37 +5315,37 @@
         <v>16.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM25" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AO25" t="n">
-        <v>470</v>
+        <v>410</v>
       </c>
       <c r="AP25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR25" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AS25" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV25" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AW25" t="n">
         <v>210</v>
@@ -5354,13 +5354,13 @@
         <v>6.4</v>
       </c>
       <c r="AY25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BA25" t="n">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="BB25" t="n">
         <v>10</v>
@@ -5369,20 +5369,20 @@
         <v>16</v>
       </c>
       <c r="BD25" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BE25" t="n">
         <v>70</v>
       </c>
       <c r="BF25" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG25" t="n">
-        <v>130</v>
+        <v>380</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
         <v>7.2</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="I26" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="J26" t="n">
         <v>4.3</v>
@@ -5431,67 +5431,67 @@
         <v>4.4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M26" t="n">
         <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O26" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P26" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.02</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V26" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="W26" t="n">
         <v>1.16</v>
       </c>
       <c r="X26" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD26" t="n">
         <v>9</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>9.4</v>
       </c>
       <c r="AE26" t="n">
         <v>17.5</v>
       </c>
       <c r="AF26" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AG26" t="n">
         <v>26</v>
@@ -5500,7 +5500,7 @@
         <v>24</v>
       </c>
       <c r="AI26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ26" t="n">
         <v>220</v>
@@ -5512,7 +5512,7 @@
         <v>110</v>
       </c>
       <c r="AM26" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN26" t="n">
         <v>140</v>
@@ -5521,62 +5521,62 @@
         <v>10</v>
       </c>
       <c r="AP26" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AQ26" t="n">
         <v>6.8</v>
       </c>
       <c r="AR26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS26" t="n">
         <v>13.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU26" t="n">
         <v>9</v>
       </c>
       <c r="AV26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW26" t="n">
         <v>16</v>
       </c>
       <c r="AX26" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AY26" t="n">
         <v>23</v>
       </c>
       <c r="AZ26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA26" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BB26" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="BC26" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BD26" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="BE26" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="BF26" t="n">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -5607,19 +5607,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G27" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H27" t="n">
         <v>3.25</v>
       </c>
       <c r="I27" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J27" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="K27" t="n">
         <v>3.1</v>
@@ -5631,7 +5631,7 @@
         <v>1.13</v>
       </c>
       <c r="N27" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O27" t="n">
         <v>1.48</v>
@@ -5640,19 +5640,19 @@
         <v>1.59</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R27" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S27" t="n">
         <v>4.8</v>
       </c>
       <c r="T27" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U27" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="V27" t="n">
         <v>1.39</v>
@@ -5661,10 +5661,10 @@
         <v>1.55</v>
       </c>
       <c r="X27" t="n">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="Y27" t="n">
-        <v>980</v>
+        <v>22</v>
       </c>
       <c r="Z27" t="n">
         <v>980</v>
@@ -5673,7 +5673,7 @@
         <v>900</v>
       </c>
       <c r="AB27" t="n">
-        <v>980</v>
+        <v>26</v>
       </c>
       <c r="AC27" t="n">
         <v>14.5</v>
@@ -5697,10 +5697,10 @@
         <v>500</v>
       </c>
       <c r="AJ27" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AK27" t="n">
-        <v>980</v>
+        <v>230</v>
       </c>
       <c r="AL27" t="n">
         <v>500</v>
@@ -5712,65 +5712,65 @@
         <v>980</v>
       </c>
       <c r="AO27" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AQ27" t="n">
         <v>5.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.72</v>
+        <v>7</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.77</v>
+        <v>2.68</v>
       </c>
       <c r="AT27" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AU27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX27" t="n">
         <v>4.3</v>
       </c>
-      <c r="AV27" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AY27" t="n">
-        <v>2.14</v>
+        <v>5.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.71</v>
+        <v>7</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.78</v>
+        <v>2.68</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.77</v>
+        <v>2.98</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.76</v>
+        <v>2.56</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.77</v>
+        <v>2.62</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.77</v>
+        <v>3.1</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.78</v>
+        <v>3.85</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G28" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="H28" t="n">
         <v>4.1</v>
       </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J28" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K28" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L28" t="n">
         <v>1.54</v>
@@ -5825,13 +5825,13 @@
         <v>1.11</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="O28" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P28" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q28" t="n">
         <v>2.46</v>
@@ -5840,31 +5840,31 @@
         <v>1.23</v>
       </c>
       <c r="S28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U28" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V28" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W28" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="X28" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z28" t="n">
-        <v>32</v>
+        <v>170</v>
       </c>
       <c r="AA28" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
         <v>7.6</v>
@@ -5876,7 +5876,7 @@
         <v>34</v>
       </c>
       <c r="AE28" t="n">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AF28" t="n">
         <v>12.5</v>
@@ -5888,37 +5888,37 @@
         <v>60</v>
       </c>
       <c r="AI28" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AK28" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AL28" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="AM28" t="n">
         <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>65</v>
+        <v>600</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AQ28" t="n">
         <v>10.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS28" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT28" t="n">
         <v>6.6</v>
@@ -5930,7 +5930,7 @@
         <v>15.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="AX28" t="n">
         <v>10.5</v>
@@ -5939,32 +5939,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BA28" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB28" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="BC28" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE28" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF28" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BG28" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -5995,170 +5995,170 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="G29" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="H29" t="n">
-        <v>2.1</v>
+        <v>3.65</v>
       </c>
       <c r="I29" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="J29" t="n">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="K29" t="n">
         <v>4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="M29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>1.1</v>
+        <v>3.55</v>
       </c>
       <c r="O29" t="n">
         <v>1.27</v>
       </c>
       <c r="P29" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="R29" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>2.96</v>
       </c>
       <c r="T29" t="n">
-        <v>1.05</v>
+        <v>1.69</v>
       </c>
       <c r="U29" t="n">
-        <v>1.05</v>
+        <v>2.06</v>
       </c>
       <c r="V29" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="W29" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="X29" t="n">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.05</v>
+        <v>5</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.05</v>
+        <v>5.8</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.05</v>
+        <v>6.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.05</v>
+        <v>4.3</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.05</v>
+        <v>5.1</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.05</v>
+        <v>6</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.05</v>
+        <v>4.7</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.05</v>
+        <v>4.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.05</v>
+        <v>5.1</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.05</v>
+        <v>5.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.05</v>
+        <v>5.3</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.05</v>
+        <v>5.9</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.05</v>
+        <v>6.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.05</v>
+        <v>4.7</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -6189,19 +6189,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G30" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H30" t="n">
         <v>4.2</v>
       </c>
       <c r="I30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J30" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K30" t="n">
         <v>2.9</v>
@@ -6231,16 +6231,16 @@
         <v>6.8</v>
       </c>
       <c r="T30" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U30" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V30" t="n">
         <v>1.29</v>
       </c>
       <c r="W30" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X30" t="n">
         <v>7</v>
@@ -6249,7 +6249,7 @@
         <v>10.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA30" t="n">
         <v>110</v>
@@ -6261,10 +6261,10 @@
         <v>7</v>
       </c>
       <c r="AD30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE30" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AF30" t="n">
         <v>12.5</v>
@@ -6273,7 +6273,7 @@
         <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI30" t="n">
         <v>420</v>
@@ -6288,25 +6288,25 @@
         <v>80</v>
       </c>
       <c r="AM30" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN30" t="n">
         <v>40</v>
       </c>
       <c r="AO30" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AP30" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AR30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS30" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AT30" t="n">
         <v>6.2</v>
@@ -6339,10 +6339,10 @@
         <v>32</v>
       </c>
       <c r="BD30" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BE30" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="BF30" t="n">
         <v>34</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G31" t="n">
         <v>3.1</v>
@@ -6392,7 +6392,7 @@
         <v>3.4</v>
       </c>
       <c r="I31" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J31" t="n">
         <v>2.58</v>
@@ -6401,19 +6401,19 @@
         <v>2.66</v>
       </c>
       <c r="L31" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="M31" t="n">
         <v>1.25</v>
       </c>
       <c r="N31" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="O31" t="n">
         <v>2.04</v>
       </c>
       <c r="P31" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Q31" t="n">
         <v>4.5</v>
@@ -6425,13 +6425,13 @@
         <v>11.5</v>
       </c>
       <c r="T31" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V31" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W31" t="n">
         <v>1.48</v>
@@ -6443,40 +6443,40 @@
         <v>7.6</v>
       </c>
       <c r="Z31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>220</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG31" t="n">
         <v>27</v>
       </c>
-      <c r="AA31" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>30</v>
-      </c>
       <c r="AH31" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AI31" t="n">
         <v>500</v>
       </c>
       <c r="AJ31" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AK31" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AL31" t="n">
         <v>500</v>
@@ -6485,40 +6485,40 @@
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="AO31" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ31" t="n">
         <v>6.2</v>
       </c>
       <c r="AR31" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AS31" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU31" t="n">
         <v>6.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AX31" t="n">
         <v>12.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ31" t="n">
         <v>32</v>
@@ -6527,26 +6527,26 @@
         <v>46</v>
       </c>
       <c r="BB31" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BC31" t="n">
         <v>48</v>
       </c>
       <c r="BD31" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BE31" t="n">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="BF31" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BG31" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="G32" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H32" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I32" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J32" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L32" t="n">
         <v>1.52</v>
@@ -6601,7 +6601,7 @@
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
         <v>1.46</v>
@@ -6610,25 +6610,25 @@
         <v>1.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R32" t="n">
         <v>1.23</v>
       </c>
       <c r="S32" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T32" t="n">
         <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V32" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W32" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X32" t="n">
         <v>10.5</v>
@@ -6637,7 +6637,7 @@
         <v>30</v>
       </c>
       <c r="Z32" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AA32" t="n">
         <v>900</v>
@@ -6646,19 +6646,19 @@
         <v>7</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>980</v>
+        <v>50</v>
       </c>
       <c r="AE32" t="n">
-        <v>480</v>
+        <v>700</v>
       </c>
       <c r="AF32" t="n">
         <v>23</v>
       </c>
       <c r="AG32" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AH32" t="n">
         <v>70</v>
@@ -6667,7 +6667,7 @@
         <v>700</v>
       </c>
       <c r="AJ32" t="n">
-        <v>900</v>
+        <v>90</v>
       </c>
       <c r="AK32" t="n">
         <v>65</v>
@@ -6685,49 +6685,49 @@
         <v>700</v>
       </c>
       <c r="AP32" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ32" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="AR32" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.88</v>
+        <v>14</v>
       </c>
       <c r="AT32" t="n">
         <v>6.2</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV32" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BB32" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AW32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>9</v>
-      </c>
       <c r="BC32" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BD32" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="BE32" t="n">
         <v>14</v>
@@ -6736,11 +6736,11 @@
         <v>8.6</v>
       </c>
       <c r="BG32" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -6771,19 +6771,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G33" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H33" t="n">
         <v>3.5</v>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J33" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K33" t="n">
         <v>3</v>
@@ -6795,7 +6795,7 @@
         <v>1.13</v>
       </c>
       <c r="N33" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O33" t="n">
         <v>1.49</v>
@@ -6804,13 +6804,13 @@
         <v>1.58</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R33" t="n">
         <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T33" t="n">
         <v>1.97</v>
@@ -6819,7 +6819,7 @@
         <v>1.86</v>
       </c>
       <c r="V33" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W33" t="n">
         <v>1.59</v>
@@ -6846,7 +6846,7 @@
         <v>16.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AF33" t="n">
         <v>16</v>
@@ -6879,7 +6879,7 @@
         <v>500</v>
       </c>
       <c r="AP33" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ33" t="n">
         <v>9</v>
@@ -6900,7 +6900,7 @@
         <v>12.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX33" t="n">
         <v>13</v>
@@ -6909,32 +6909,32 @@
         <v>10</v>
       </c>
       <c r="AZ33" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BA33" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="BB33" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC33" t="n">
         <v>9</v>
       </c>
-      <c r="BC33" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BD33" t="n">
-        <v>9.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="BE33" t="n">
         <v>11</v>
       </c>
       <c r="BF33" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG33" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
         <v>2.2</v>
       </c>
       <c r="J34" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K34" t="n">
         <v>3.5</v>
@@ -7025,13 +7025,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z34" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AA34" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB34" t="n">
-        <v>24</v>
+        <v>13.5</v>
       </c>
       <c r="AC34" t="n">
         <v>8</v>
@@ -7043,10 +7043,10 @@
         <v>65</v>
       </c>
       <c r="AF34" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AG34" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AH34" t="n">
         <v>50</v>
@@ -7073,7 +7073,7 @@
         <v>55</v>
       </c>
       <c r="AP34" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AQ34" t="n">
         <v>7</v>
@@ -7082,53 +7082,53 @@
         <v>10.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AT34" t="n">
         <v>10.5</v>
       </c>
       <c r="AU34" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV34" t="n">
         <v>9.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AX34" t="n">
         <v>13</v>
       </c>
       <c r="AY34" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="BB34" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC34" t="n">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BD34" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE34" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF34" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG34" t="n">
         <v>16</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -7162,22 +7162,22 @@
         <v>4.3</v>
       </c>
       <c r="G35" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H35" t="n">
         <v>2.06</v>
       </c>
       <c r="I35" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K35" t="n">
         <v>3.45</v>
       </c>
       <c r="L35" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M35" t="n">
         <v>1.12</v>
@@ -7207,7 +7207,7 @@
         <v>1.72</v>
       </c>
       <c r="V35" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="W35" t="n">
         <v>1.27</v>
@@ -7270,13 +7270,13 @@
         <v>4.2</v>
       </c>
       <c r="AQ35" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AR35" t="n">
         <v>5</v>
       </c>
       <c r="AS35" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AT35" t="n">
         <v>4.8</v>
@@ -7288,41 +7288,41 @@
         <v>4.8</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AX35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ35" t="n">
         <v>5.9</v>
       </c>
-      <c r="AY35" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>5</v>
-      </c>
       <c r="BA35" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="BD35" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="BF35" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="BG35" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
         <v>2.6</v>
       </c>
       <c r="J36" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K36" t="n">
         <v>3.25</v>
@@ -7377,13 +7377,13 @@
         <v>1.12</v>
       </c>
       <c r="N36" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O36" t="n">
         <v>1.51</v>
       </c>
       <c r="P36" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q36" t="n">
         <v>2.56</v>
@@ -7404,16 +7404,16 @@
         <v>1.62</v>
       </c>
       <c r="W36" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X36" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y36" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Z36" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA36" t="n">
         <v>38</v>
@@ -7455,13 +7455,13 @@
         <v>170</v>
       </c>
       <c r="AN36" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO36" t="n">
         <v>40</v>
       </c>
       <c r="AP36" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ36" t="n">
         <v>7.6</v>
@@ -7491,19 +7491,19 @@
         <v>13.5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA36" t="n">
         <v>30</v>
       </c>
       <c r="BB36" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BC36" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BD36" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BE36" t="n">
         <v>44</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -7547,16 +7547,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
         <v>2.04</v>
       </c>
       <c r="H37" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I37" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J37" t="n">
         <v>3.25</v>
@@ -7568,19 +7568,19 @@
         <v>1.61</v>
       </c>
       <c r="M37" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N37" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O37" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="P37" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
@@ -7592,10 +7592,10 @@
         <v>2.36</v>
       </c>
       <c r="U37" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V37" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W37" t="n">
         <v>1.96</v>
@@ -7610,7 +7610,7 @@
         <v>980</v>
       </c>
       <c r="AA37" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB37" t="n">
         <v>6.4</v>
@@ -7646,13 +7646,13 @@
         <v>1000</v>
       </c>
       <c r="AM37" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AN37" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AO37" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AP37" t="n">
         <v>7.4</v>
@@ -7673,13 +7673,13 @@
         <v>6.8</v>
       </c>
       <c r="AV37" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AX37" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AY37" t="n">
         <v>10.5</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -7747,13 +7747,13 @@
         <v>7.6</v>
       </c>
       <c r="H38" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="I38" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="J38" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K38" t="n">
         <v>4.1</v>
@@ -7771,7 +7771,7 @@
         <v>1.39</v>
       </c>
       <c r="P38" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q38" t="n">
         <v>2.2</v>
@@ -7789,7 +7789,7 @@
         <v>1.77</v>
       </c>
       <c r="V38" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="W38" t="n">
         <v>1.17</v>
@@ -7822,7 +7822,7 @@
         <v>70</v>
       </c>
       <c r="AG38" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH38" t="n">
         <v>30</v>
@@ -7834,7 +7834,7 @@
         <v>270</v>
       </c>
       <c r="AK38" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AL38" t="n">
         <v>140</v>
@@ -7873,7 +7873,7 @@
         <v>17</v>
       </c>
       <c r="AX38" t="n">
-        <v>44</v>
+        <v>6.4</v>
       </c>
       <c r="AY38" t="n">
         <v>22</v>
@@ -7882,10 +7882,10 @@
         <v>21</v>
       </c>
       <c r="BA38" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB38" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC38" t="n">
         <v>6.6</v>
@@ -7894,17 +7894,17 @@
         <v>6.6</v>
       </c>
       <c r="BE38" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF38" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG38" t="n">
         <v>10.5</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-02.xlsx
@@ -757,91 +757,91 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>980</v>
       </c>
       <c r="H2" t="n">
         <v>1.34</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="K2" t="n">
-        <v>7.8</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>1.23</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.02</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>1.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="R2" t="n">
-        <v>1.53</v>
+        <v>1.07</v>
       </c>
       <c r="S2" t="n">
         <v>1.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.07</v>
+        <v>1.93</v>
       </c>
       <c r="U2" t="n">
-        <v>1.05</v>
+        <v>1.74</v>
       </c>
       <c r="V2" t="n">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Y2" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA2" t="n">
         <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>500</v>
       </c>
       <c r="AB2" t="n">
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -850,7 +850,7 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -862,65 +862,65 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>29</v>
+        <v>980</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.29</v>
+        <v>1.93</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.3</v>
+        <v>1.97</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.32</v>
+        <v>1.92</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.2</v>
+        <v>1.24</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.2</v>
+        <v>1.38</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.2</v>
+        <v>1.24</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.2</v>
+        <v>1.22</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.2</v>
+        <v>1.24</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.2</v>
+        <v>1.22</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>1.24</v>
       </c>
       <c r="BE2" t="n">
-        <v>110</v>
+        <v>1.24</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.2</v>
+        <v>1.61</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1</v>
+        <v>290</v>
       </c>
       <c r="H3" t="n">
-        <v>1.78</v>
+        <v>2.32</v>
       </c>
       <c r="I3" t="n">
-        <v>1.82</v>
+        <v>2.54</v>
       </c>
       <c r="J3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>850</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>3.95</v>
       </c>
-      <c r="K3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X3" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AR3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BF3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>46</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>50</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>50</v>
-      </c>
       <c r="BG3" t="n">
-        <v>9.6</v>
+        <v>2.48</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -1148,91 +1148,91 @@
         <v>1.34</v>
       </c>
       <c r="G4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="H4" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.37</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R4" t="n">
         <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U4" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="V4" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z4" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AA4" t="n">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="AB4" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD4" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AE4" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AF4" t="n">
         <v>7.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
         <v>36</v>
       </c>
       <c r="AI4" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AJ4" t="n">
         <v>10.5</v>
@@ -1244,71 +1244,71 @@
         <v>46</v>
       </c>
       <c r="AM4" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AN4" t="n">
         <v>6.4</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AP4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AR4" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="AS4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT4" t="n">
         <v>7</v>
       </c>
       <c r="AU4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AW4" t="n">
         <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BA4" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC4" t="n">
         <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BE4" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG4" t="n">
         <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -1339,61 +1339,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G5" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I5" t="n">
         <v>3.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="O5" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S5" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="V5" t="n">
         <v>1.42</v>
       </c>
       <c r="W5" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="X5" t="n">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="Y5" t="n">
         <v>11</v>
@@ -1405,19 +1405,19 @@
         <v>500</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>980</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
         <v>12.5</v>
@@ -1432,10 +1432,10 @@
         <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
@@ -1444,31 +1444,31 @@
         <v>980</v>
       </c>
       <c r="AO5" t="n">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AU5" t="n">
         <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW5" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
         <v>12</v>
@@ -1477,13 +1477,13 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA5" t="n">
         <v>36</v>
       </c>
       <c r="BB5" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC5" t="n">
         <v>22</v>
@@ -1492,17 +1492,17 @@
         <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -1533,73 +1533,73 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.7</v>
       </c>
-      <c r="I6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.5</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="Z6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA6" t="n">
-        <v>270</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
         <v>7.8</v>
@@ -1611,7 +1611,7 @@
         <v>200</v>
       </c>
       <c r="AF6" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG6" t="n">
         <v>11.5</v>
@@ -1629,31 +1629,31 @@
         <v>42</v>
       </c>
       <c r="AL6" t="n">
-        <v>100</v>
+        <v>980</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO6" t="n">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="AP6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
         <v>11.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AS6" t="n">
-        <v>28</v>
+        <v>11.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU6" t="n">
         <v>6.8</v>
@@ -1662,7 +1662,7 @@
         <v>13.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AX6" t="n">
         <v>11.5</v>
@@ -1671,32 +1671,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="BB6" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BC6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="BG6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J7" t="n">
         <v>3.9</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
       </c>
       <c r="K7" t="n">
         <v>4.3</v>
@@ -1754,31 +1754,31 @@
         <v>5.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q7" t="n">
         <v>1.59</v>
       </c>
       <c r="R7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S7" t="n">
         <v>2.48</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="U7" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
         <v>90</v>
@@ -1802,7 +1802,7 @@
         <v>30</v>
       </c>
       <c r="AE7" t="n">
-        <v>170</v>
+        <v>980</v>
       </c>
       <c r="AF7" t="n">
         <v>32</v>
@@ -1844,28 +1844,28 @@
         <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU7" t="n">
         <v>8</v>
       </c>
-      <c r="AU7" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AV7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
         <v>11</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA7" t="n">
         <v>11</v>
@@ -1874,7 +1874,7 @@
         <v>11</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BD7" t="n">
         <v>9.6</v>
@@ -1883,14 +1883,14 @@
         <v>2.82</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="G8" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="I8" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="J8" t="n">
         <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
         <v>1.39</v>
@@ -1945,58 +1945,58 @@
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R8" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U8" t="n">
         <v>2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="W8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X8" t="n">
         <v>36</v>
       </c>
       <c r="Y8" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="Z8" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
-        <v>980</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AC8" t="n">
-        <v>42</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
         <v>980</v>
@@ -2005,13 +2005,13 @@
         <v>980</v>
       </c>
       <c r="AH8" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AI8" t="n">
         <v>980</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AK8" t="n">
         <v>980</v>
@@ -2020,71 +2020,71 @@
         <v>980</v>
       </c>
       <c r="AM8" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN8" t="n">
         <v>980</v>
       </c>
       <c r="AO8" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AP8" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AT8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV8" t="n">
         <v>7</v>
       </c>
-      <c r="AU8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AW8" t="n">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="AX8" t="n">
         <v>12</v>
       </c>
       <c r="AY8" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BA8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.98</v>
+        <v>12</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.05</v>
+        <v>7.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.88</v>
+        <v>5.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="G9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="I9" t="n">
         <v>1.51</v>
       </c>
       <c r="J9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K9" t="n">
         <v>4.9</v>
@@ -2139,7 +2139,7 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O9" t="n">
         <v>1.32</v>
@@ -2148,16 +2148,16 @@
         <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U9" t="n">
         <v>1.76</v>
@@ -2166,22 +2166,22 @@
         <v>2.96</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AA9" t="n">
         <v>13</v>
       </c>
       <c r="AB9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AC9" t="n">
         <v>10.5</v>
@@ -2196,7 +2196,7 @@
         <v>75</v>
       </c>
       <c r="AG9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AH9" t="n">
         <v>29</v>
@@ -2217,7 +2217,7 @@
         <v>190</v>
       </c>
       <c r="AN9" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AO9" t="n">
         <v>8.6</v>
@@ -2229,56 +2229,56 @@
         <v>6.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT9" t="n">
         <v>21</v>
       </c>
       <c r="AU9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV9" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AV9" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AW9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AY9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AZ9" t="n">
         <v>25</v>
       </c>
       <c r="BA9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB9" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="BE9" t="n">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="BF9" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H10" t="n">
         <v>2.02</v>
@@ -2321,40 +2321,40 @@
         <v>2.04</v>
       </c>
       <c r="J10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.45</v>
       </c>
-      <c r="K10" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.41</v>
       </c>
       <c r="P10" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R10" t="n">
         <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V10" t="n">
         <v>1.96</v>
@@ -2387,19 +2387,19 @@
         <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
         <v>44</v>
       </c>
       <c r="AJ10" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK10" t="n">
         <v>65</v>
@@ -2414,7 +2414,7 @@
         <v>110</v>
       </c>
       <c r="AO10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AP10" t="n">
         <v>10.5</v>
@@ -2423,13 +2423,13 @@
         <v>7.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS10" t="n">
         <v>21</v>
       </c>
       <c r="AT10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU10" t="n">
         <v>7.2</v>
@@ -2441,16 +2441,16 @@
         <v>21</v>
       </c>
       <c r="AX10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY10" t="n">
         <v>17</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB10" t="n">
         <v>95</v>
@@ -2465,14 +2465,14 @@
         <v>120</v>
       </c>
       <c r="BF10" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BG10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -2503,40 +2503,40 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I11" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J11" t="n">
         <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P11" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R11" t="n">
         <v>1.26</v>
@@ -2545,19 +2545,19 @@
         <v>4.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U11" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y11" t="n">
         <v>11</v>
@@ -2569,19 +2569,19 @@
         <v>60</v>
       </c>
       <c r="AB11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG11" t="n">
         <v>12.5</v>
@@ -2596,22 +2596,22 @@
         <v>40</v>
       </c>
       <c r="AK11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AN11" t="n">
         <v>32</v>
       </c>
       <c r="AO11" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ11" t="n">
         <v>9.4</v>
@@ -2620,53 +2620,53 @@
         <v>18.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="AT11" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="AX11" t="n">
         <v>14</v>
       </c>
       <c r="AY11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
         <v>17</v>
       </c>
       <c r="BA11" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC11" t="n">
         <v>28</v>
       </c>
-      <c r="BB11" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BD11" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="BE11" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.6</v>
+        <v>27</v>
       </c>
       <c r="BG11" t="n">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G12" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H12" t="n">
         <v>3.55</v>
       </c>
       <c r="I12" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="J12" t="n">
         <v>3.1</v>
@@ -2715,28 +2715,28 @@
         <v>3.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M12" t="n">
         <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="R12" t="n">
         <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T12" t="n">
         <v>2.08</v>
@@ -2745,10 +2745,10 @@
         <v>1.81</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X12" t="n">
         <v>17</v>
@@ -2757,16 +2757,16 @@
         <v>22</v>
       </c>
       <c r="Z12" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AA12" t="n">
-        <v>250</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
         <v>7.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AD12" t="n">
         <v>500</v>
@@ -2775,7 +2775,7 @@
         <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AG12" t="n">
         <v>25</v>
@@ -2793,19 +2793,19 @@
         <v>980</v>
       </c>
       <c r="AL12" t="n">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>600</v>
+        <v>980</v>
       </c>
       <c r="AO12" t="n">
         <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
         <v>8.800000000000001</v>
@@ -2814,25 +2814,25 @@
         <v>10.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU12" t="n">
         <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AX12" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>14.5</v>
@@ -2841,26 +2841,26 @@
         <v>30</v>
       </c>
       <c r="BB12" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC12" t="n">
         <v>9</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="BD12" t="n">
         <v>32</v>
       </c>
       <c r="BE12" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG12" t="n">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -2894,67 +2894,67 @@
         <v>2.68</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="H13" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="I13" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
         <v>3.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="T13" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="U13" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W13" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X13" t="n">
         <v>90</v>
       </c>
       <c r="Y13" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z13" t="n">
         <v>500</v>
       </c>
-      <c r="Z13" t="n">
-        <v>1000</v>
-      </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
         <v>23</v>
@@ -2963,19 +2963,19 @@
         <v>14</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AH13" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
@@ -2990,7 +2990,7 @@
         <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
         <v>1000</v>
@@ -3008,13 +3008,13 @@
         <v>7.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AV13" t="n">
         <v>7.6</v>
@@ -3023,38 +3023,38 @@
         <v>11.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY13" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="BF13" t="n">
         <v>7.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="G14" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K14" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.4</v>
@@ -3109,37 +3109,37 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V14" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="X14" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="Y14" t="n">
         <v>34</v>
@@ -3148,25 +3148,25 @@
         <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB14" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="AC14" t="n">
         <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AG14" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AH14" t="n">
         <v>60</v>
@@ -3175,10 +3175,10 @@
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK14" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AL14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
         <v>11.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AU14" t="n">
         <v>6.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE14" t="n">
         <v>8.6</v>
       </c>
-      <c r="AX14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD14" t="n">
+      <c r="BF14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG14" t="n">
         <v>8</v>
       </c>
-      <c r="BE14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="G15" t="n">
         <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="I15" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.28</v>
@@ -3309,25 +3309,25 @@
         <v>1.16</v>
       </c>
       <c r="P15" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R15" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="S15" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="U15" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="W15" t="n">
         <v>1.33</v>
@@ -3342,40 +3342,40 @@
         <v>29</v>
       </c>
       <c r="AA15" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AF15" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AG15" t="n">
         <v>38</v>
       </c>
       <c r="AH15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI15" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AJ15" t="n">
         <v>900</v>
       </c>
       <c r="AK15" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AL15" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AM15" t="n">
         <v>500</v>
@@ -3390,59 +3390,59 @@
         <v>21</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AS15" t="n">
         <v>10.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AU15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY15" t="n">
         <v>10.5</v>
       </c>
-      <c r="AX15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA15" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BB15" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE15" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BF15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="G16" t="n">
         <v>2.06</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L16" t="n">
         <v>1.45</v>
@@ -3506,7 +3506,7 @@
         <v>1.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="R16" t="n">
         <v>1.3</v>
@@ -3515,16 +3515,16 @@
         <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U16" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V16" t="n">
         <v>1.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="X16" t="n">
         <v>16</v>
@@ -3542,10 +3542,10 @@
         <v>120</v>
       </c>
       <c r="AC16" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AD16" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
@@ -3554,7 +3554,7 @@
         <v>190</v>
       </c>
       <c r="AG16" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
         <v>160</v>
@@ -3590,7 +3590,7 @@
         <v>12.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="AT16" t="n">
         <v>4.4</v>
@@ -3602,7 +3602,7 @@
         <v>9</v>
       </c>
       <c r="AW16" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="AX16" t="n">
         <v>6.2</v>
@@ -3614,7 +3614,7 @@
         <v>11.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="BB16" t="n">
         <v>11.5</v>
@@ -3623,10 +3623,10 @@
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.5</v>
+        <v>2.62</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.99</v>
+        <v>2.6</v>
       </c>
       <c r="BF16" t="n">
         <v>4.9</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -3667,85 +3667,85 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G17" t="n">
         <v>2.24</v>
       </c>
-      <c r="G17" t="n">
-        <v>2.3</v>
-      </c>
       <c r="H17" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J17" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.58</v>
+        <v>2.76</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="R17" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="T17" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="U17" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W17" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="X17" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Y17" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Z17" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AA17" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AB17" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AD17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
         <v>32</v>
       </c>
       <c r="AF17" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>11.5</v>
@@ -3754,52 +3754,52 @@
         <v>15</v>
       </c>
       <c r="AI17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="AM17" t="n">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="AN17" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AQ17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX17" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>14.5</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
@@ -3808,29 +3808,29 @@
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB17" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BC17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BE17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BF17" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -3864,37 +3864,37 @@
         <v>2.26</v>
       </c>
       <c r="G18" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J18" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="K18" t="n">
         <v>2.86</v>
       </c>
       <c r="L18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="M18" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="N18" t="n">
         <v>2.32</v>
       </c>
       <c r="O18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="P18" t="n">
         <v>1.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
         <v>1.14</v>
@@ -3906,13 +3906,13 @@
         <v>2.42</v>
       </c>
       <c r="U18" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V18" t="n">
         <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X18" t="n">
         <v>6.8</v>
@@ -3921,43 +3921,43 @@
         <v>11</v>
       </c>
       <c r="Z18" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AA18" t="n">
         <v>700</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="AE18" t="n">
         <v>700</v>
       </c>
       <c r="AF18" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="AG18" t="n">
         <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AI18" t="n">
         <v>700</v>
       </c>
       <c r="AJ18" t="n">
-        <v>980</v>
+        <v>80</v>
       </c>
       <c r="AK18" t="n">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="AL18" t="n">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AM18" t="n">
         <v>500</v>
@@ -3969,10 +3969,10 @@
         <v>700</v>
       </c>
       <c r="AP18" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR18" t="n">
         <v>16.5</v>
@@ -3984,47 +3984,47 @@
         <v>5.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX18" t="n">
         <v>10</v>
       </c>
-      <c r="AX18" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AY18" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BA18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB18" t="n">
         <v>15</v>
       </c>
       <c r="BC18" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE18" t="n">
         <v>46</v>
       </c>
-      <c r="BE18" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BF18" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -4055,19 +4055,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="G19" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K19" t="n">
         <v>4.2</v>
@@ -4085,28 +4085,28 @@
         <v>1.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
         <v>1.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S19" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U19" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X19" t="n">
         <v>18.5</v>
@@ -4124,7 +4124,7 @@
         <v>11</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
         <v>18.5</v>
@@ -4136,7 +4136,7 @@
         <v>12</v>
       </c>
       <c r="AG19" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH19" t="n">
         <v>17.5</v>
@@ -4157,22 +4157,22 @@
         <v>85</v>
       </c>
       <c r="AN19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO19" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AP19" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR19" t="n">
         <v>34</v>
       </c>
       <c r="AS19" t="n">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="AT19" t="n">
         <v>9.800000000000001</v>
@@ -4196,7 +4196,7 @@
         <v>15.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BB19" t="n">
         <v>17.5</v>
@@ -4205,10 +4205,10 @@
         <v>15.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE19" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BF19" t="n">
         <v>8.800000000000001</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="H20" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="I20" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="J20" t="n">
         <v>2.9</v>
       </c>
       <c r="K20" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="L20" t="n">
         <v>1.61</v>
@@ -4273,13 +4273,13 @@
         <v>1.14</v>
       </c>
       <c r="N20" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O20" t="n">
         <v>1.57</v>
       </c>
       <c r="P20" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q20" t="n">
         <v>2.82</v>
@@ -4291,43 +4291,43 @@
         <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U20" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="V20" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="X20" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y20" t="n">
         <v>8.6</v>
       </c>
-      <c r="Y20" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="Z20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF20" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG20" t="n">
         <v>14.5</v>
@@ -4336,83 +4336,83 @@
         <v>24</v>
       </c>
       <c r="AI20" t="n">
-        <v>460</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK20" t="n">
         <v>48</v>
       </c>
-      <c r="AK20" t="n">
-        <v>46</v>
-      </c>
       <c r="AL20" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM20" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO20" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ20" t="n">
         <v>7.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV20" t="n">
         <v>12.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="AX20" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AZ20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.800000000000001</v>
+        <v>48</v>
       </c>
       <c r="BB20" t="n">
-        <v>36</v>
+        <v>19.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="BD20" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="BF20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BG20" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -4443,25 +4443,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="G21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I21" t="n">
         <v>1.89</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.92</v>
       </c>
       <c r="J21" t="n">
         <v>3.9</v>
       </c>
       <c r="K21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
@@ -4476,22 +4476,22 @@
         <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V21" t="n">
         <v>2.12</v>
-      </c>
-      <c r="V21" t="n">
-        <v>2.08</v>
       </c>
       <c r="W21" t="n">
         <v>1.27</v>
@@ -4500,7 +4500,7 @@
         <v>15</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z21" t="n">
         <v>11.5</v>
@@ -4509,31 +4509,31 @@
         <v>21</v>
       </c>
       <c r="AB21" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG21" t="n">
         <v>18</v>
       </c>
       <c r="AH21" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
         <v>36</v>
       </c>
       <c r="AJ21" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AK21" t="n">
         <v>60</v>
@@ -4542,7 +4542,7 @@
         <v>65</v>
       </c>
       <c r="AM21" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AN21" t="n">
         <v>60</v>
@@ -4551,62 +4551,62 @@
         <v>12</v>
       </c>
       <c r="AP21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR21" t="n">
         <v>10.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV21" t="n">
         <v>9.4</v>
       </c>
       <c r="AW21" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AX21" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AY21" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BB21" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BC21" t="n">
         <v>36</v>
       </c>
       <c r="BD21" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BE21" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BF21" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="BG21" t="n">
         <v>11</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -4640,19 +4640,19 @@
         <v>1.86</v>
       </c>
       <c r="G22" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H22" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I22" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="n">
         <v>3.6</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.51</v>
@@ -4670,7 +4670,7 @@
         <v>1.69</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
@@ -4691,7 +4691,7 @@
         <v>2.12</v>
       </c>
       <c r="X22" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="Y22" t="n">
         <v>14.5</v>
@@ -4712,19 +4712,19 @@
         <v>21</v>
       </c>
       <c r="AE22" t="n">
-        <v>230</v>
+        <v>90</v>
       </c>
       <c r="AF22" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AG22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AI22" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ22" t="n">
         <v>21</v>
@@ -4739,7 +4739,7 @@
         <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO22" t="n">
         <v>700</v>
@@ -4748,25 +4748,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ22" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR22" t="n">
         <v>34</v>
       </c>
       <c r="AS22" t="n">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="AT22" t="n">
         <v>6.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AW22" t="n">
-        <v>40</v>
+        <v>15.5</v>
       </c>
       <c r="AX22" t="n">
         <v>9</v>
@@ -4775,7 +4775,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA22" t="n">
         <v>29</v>
@@ -4784,7 +4784,7 @@
         <v>18.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD22" t="n">
         <v>36</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
         <v>3.35</v>
       </c>
       <c r="O23" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P23" t="n">
         <v>1.79</v>
@@ -4870,7 +4870,7 @@
         <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T23" t="n">
         <v>1.89</v>
@@ -4879,16 +4879,16 @@
         <v>2.08</v>
       </c>
       <c r="V23" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W23" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X23" t="n">
         <v>11.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z23" t="n">
         <v>15</v>
@@ -4900,7 +4900,7 @@
         <v>11.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD23" t="n">
         <v>11.5</v>
@@ -4927,7 +4927,7 @@
         <v>40</v>
       </c>
       <c r="AL23" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM23" t="n">
         <v>110</v>
@@ -4957,7 +4957,7 @@
         <v>6.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW23" t="n">
         <v>27</v>
@@ -4966,7 +4966,7 @@
         <v>20</v>
       </c>
       <c r="AY23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ23" t="n">
         <v>17</v>
@@ -4990,11 +4990,11 @@
         <v>40</v>
       </c>
       <c r="BG23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -5025,94 +5025,94 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="G24" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="H24" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="I24" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="K24" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="M24" t="n">
         <v>1.13</v>
       </c>
       <c r="N24" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="P24" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="R24" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="V24" t="n">
-        <v>1.98</v>
+        <v>1.71</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="X24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="Z24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB24" t="n">
         <v>10.5</v>
       </c>
-      <c r="AA24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AC24" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF24" t="n">
         <v>28</v>
       </c>
-      <c r="AF24" t="n">
-        <v>42</v>
-      </c>
       <c r="AG24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH24" t="n">
         <v>25</v>
       </c>
-      <c r="AH24" t="n">
-        <v>27</v>
-      </c>
       <c r="AI24" t="n">
-        <v>65</v>
+        <v>460</v>
       </c>
       <c r="AJ24" t="n">
         <v>900</v>
@@ -5130,25 +5130,25 @@
         <v>600</v>
       </c>
       <c r="AO24" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AP24" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AR24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT24" t="n">
         <v>9</v>
       </c>
-      <c r="AS24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>11</v>
-      </c>
       <c r="AU24" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV24" t="n">
         <v>10</v>
@@ -5157,38 +5157,38 @@
         <v>19.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ24" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD24" t="n">
         <v>16.5</v>
       </c>
-      <c r="BA24" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>12</v>
-      </c>
       <c r="BE24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG24" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -5231,16 +5231,16 @@
         <v>11.5</v>
       </c>
       <c r="J25" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K25" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M25" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N25" t="n">
         <v>3.8</v>
@@ -5249,7 +5249,7 @@
         <v>1.34</v>
       </c>
       <c r="P25" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q25" t="n">
         <v>2.04</v>
@@ -5258,13 +5258,13 @@
         <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T25" t="n">
         <v>2.44</v>
       </c>
       <c r="U25" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V25" t="n">
         <v>1.09</v>
@@ -5273,16 +5273,16 @@
         <v>3.5</v>
       </c>
       <c r="X25" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z25" t="n">
         <v>95</v>
       </c>
       <c r="AA25" t="n">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="AB25" t="n">
         <v>6.6</v>
@@ -5294,16 +5294,16 @@
         <v>42</v>
       </c>
       <c r="AE25" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AF25" t="n">
         <v>6.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI25" t="n">
         <v>220</v>
@@ -5318,16 +5318,16 @@
         <v>46</v>
       </c>
       <c r="AM25" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN25" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO25" t="n">
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="AP25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ25" t="n">
         <v>25</v>
@@ -5345,13 +5345,13 @@
         <v>10.5</v>
       </c>
       <c r="AV25" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AW25" t="n">
         <v>210</v>
       </c>
       <c r="AX25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY25" t="n">
         <v>9.800000000000001</v>
@@ -5360,7 +5360,7 @@
         <v>32</v>
       </c>
       <c r="BA25" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="BB25" t="n">
         <v>10</v>
@@ -5369,20 +5369,20 @@
         <v>16</v>
       </c>
       <c r="BD25" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE25" t="n">
         <v>70</v>
       </c>
       <c r="BF25" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -5437,16 +5437,16 @@
         <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O26" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q26" t="n">
         <v>2</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.96</v>
       </c>
       <c r="R26" t="n">
         <v>1.37</v>
@@ -5455,10 +5455,10 @@
         <v>3.55</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U26" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V26" t="n">
         <v>2.68</v>
@@ -5473,25 +5473,25 @@
         <v>7.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA26" t="n">
         <v>14.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AE26" t="n">
         <v>17.5</v>
       </c>
       <c r="AF26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG26" t="n">
         <v>26</v>
@@ -5500,7 +5500,7 @@
         <v>24</v>
       </c>
       <c r="AI26" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ26" t="n">
         <v>220</v>
@@ -5509,7 +5509,7 @@
         <v>110</v>
       </c>
       <c r="AL26" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM26" t="n">
         <v>150</v>
@@ -5518,22 +5518,22 @@
         <v>140</v>
       </c>
       <c r="AO26" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR26" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS26" t="n">
         <v>13.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AU26" t="n">
         <v>9</v>
@@ -5548,35 +5548,35 @@
         <v>50</v>
       </c>
       <c r="AY26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ26" t="n">
         <v>21</v>
       </c>
       <c r="BA26" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB26" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BC26" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BD26" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BE26" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BF26" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
         <v>3.6</v>
       </c>
       <c r="J27" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K27" t="n">
         <v>3.1</v>
@@ -5664,7 +5664,7 @@
         <v>19</v>
       </c>
       <c r="Y27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z27" t="n">
         <v>980</v>
@@ -5715,16 +5715,16 @@
         <v>600</v>
       </c>
       <c r="AP27" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AQ27" t="n">
         <v>5.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.68</v>
+        <v>4.3</v>
       </c>
       <c r="AT27" t="n">
         <v>4.8</v>
@@ -5733,44 +5733,44 @@
         <v>4.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AW27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA27" t="n">
         <v>4</v>
       </c>
-      <c r="AX27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY27" t="n">
+      <c r="BB27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE27" t="n">
         <v>5.6</v>
       </c>
-      <c r="AZ27" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BF27" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="BG27" t="n">
         <v>3.85</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -5801,103 +5801,103 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="G28" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="H28" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="I28" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="J28" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="L28" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M28" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N28" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O28" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P28" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R28" t="n">
         <v>1.23</v>
       </c>
       <c r="S28" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V28" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W28" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="X28" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG28" t="n">
         <v>12</v>
       </c>
-      <c r="Z28" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA28" t="n">
+      <c r="AH28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL28" t="n">
         <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>250</v>
       </c>
       <c r="AM28" t="n">
         <v>580</v>
@@ -5912,59 +5912,59 @@
         <v>8.4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT28" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AW28" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AX28" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB28" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="BG28" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -5995,170 +5995,170 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="G29" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="H29" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="I29" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="J29" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K29" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L29" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M29" t="n">
         <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="O29" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P29" t="n">
         <v>1.94</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="R29" t="n">
         <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
         <v>1.69</v>
       </c>
       <c r="U29" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V29" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="W29" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="X29" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y29" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB29" t="n">
         <v>11</v>
       </c>
       <c r="AC29" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD29" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE29" t="n">
         <v>130</v>
       </c>
       <c r="AF29" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG29" t="n">
         <v>11.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AJ29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK29" t="n">
         <v>26</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>23</v>
       </c>
       <c r="AL29" t="n">
         <v>95</v>
       </c>
       <c r="AM29" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD29" t="n">
         <v>14.5</v>
       </c>
-      <c r="AO29" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS29" t="n">
+      <c r="BE29" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG29" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT29" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>6</v>
-      </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G30" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H30" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J30" t="n">
         <v>2.86</v>
@@ -6207,7 +6207,7 @@
         <v>2.9</v>
       </c>
       <c r="L30" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="M30" t="n">
         <v>1.17</v>
@@ -6222,25 +6222,25 @@
         <v>1.46</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R30" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S30" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="T30" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U30" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X30" t="n">
         <v>7</v>
@@ -6249,13 +6249,13 @@
         <v>10.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="AA30" t="n">
         <v>110</v>
       </c>
       <c r="AB30" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC30" t="n">
         <v>7</v>
@@ -6270,13 +6270,13 @@
         <v>12.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH30" t="n">
         <v>28</v>
       </c>
       <c r="AI30" t="n">
-        <v>420</v>
+        <v>120</v>
       </c>
       <c r="AJ30" t="n">
         <v>34</v>
@@ -6291,7 +6291,7 @@
         <v>500</v>
       </c>
       <c r="AN30" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO30" t="n">
         <v>130</v>
@@ -6300,10 +6300,10 @@
         <v>6.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS30" t="n">
         <v>80</v>
@@ -6318,7 +6318,7 @@
         <v>17.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AX30" t="n">
         <v>11</v>
@@ -6327,10 +6327,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA30" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="BB30" t="n">
         <v>29</v>
@@ -6339,7 +6339,7 @@
         <v>32</v>
       </c>
       <c r="BD30" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="BE30" t="n">
         <v>70</v>
@@ -6348,11 +6348,11 @@
         <v>34</v>
       </c>
       <c r="BG30" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -6383,88 +6383,88 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="G31" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="H31" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I31" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="K31" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="L31" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="M31" t="n">
         <v>1.25</v>
       </c>
       <c r="N31" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="O31" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
         <v>1.27</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="S31" t="n">
         <v>11.5</v>
       </c>
       <c r="T31" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U31" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V31" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W31" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="X31" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="Z31" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AA31" t="n">
         <v>100</v>
       </c>
       <c r="AB31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC31" t="n">
         <v>6.8</v>
       </c>
-      <c r="AC31" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AD31" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AE31" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AF31" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG31" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AH31" t="n">
         <v>70</v>
@@ -6473,10 +6473,10 @@
         <v>500</v>
       </c>
       <c r="AJ31" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AL31" t="n">
         <v>500</v>
@@ -6485,68 +6485,68 @@
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>330</v>
+        <v>250</v>
       </c>
       <c r="AO31" t="n">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR31" t="n">
         <v>16</v>
       </c>
       <c r="AS31" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AU31" t="n">
         <v>6.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AW31" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AX31" t="n">
         <v>12.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BA31" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="BB31" t="n">
         <v>32</v>
       </c>
       <c r="BC31" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="BD31" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BE31" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="BF31" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BG31" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G32" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="H32" t="n">
         <v>5.1</v>
@@ -6592,10 +6592,10 @@
         <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L32" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M32" t="n">
         <v>1.1</v>
@@ -6604,16 +6604,16 @@
         <v>3</v>
       </c>
       <c r="O32" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P32" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R32" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S32" t="n">
         <v>4.7</v>
@@ -6628,16 +6628,16 @@
         <v>1.22</v>
       </c>
       <c r="W32" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X32" t="n">
         <v>10.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Z32" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA32" t="n">
         <v>900</v>
@@ -6655,13 +6655,13 @@
         <v>700</v>
       </c>
       <c r="AF32" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="AG32" t="n">
         <v>21</v>
       </c>
       <c r="AH32" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AI32" t="n">
         <v>700</v>
@@ -6679,22 +6679,22 @@
         <v>580</v>
       </c>
       <c r="AN32" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AO32" t="n">
         <v>700</v>
       </c>
       <c r="AP32" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ32" t="n">
         <v>12</v>
       </c>
       <c r="AR32" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AT32" t="n">
         <v>6.2</v>
@@ -6703,44 +6703,44 @@
         <v>7</v>
       </c>
       <c r="AV32" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AW32" t="n">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="AX32" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY32" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.38</v>
+        <v>13.5</v>
       </c>
       <c r="BB32" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC32" t="n">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="BD32" t="n">
         <v>12</v>
       </c>
       <c r="BE32" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BF32" t="n">
         <v>8.6</v>
       </c>
       <c r="BG32" t="n">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G33" t="n">
         <v>2.7</v>
@@ -6786,7 +6786,7 @@
         <v>2.84</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="L33" t="n">
         <v>1.57</v>
@@ -6813,19 +6813,19 @@
         <v>5</v>
       </c>
       <c r="T33" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
         <v>1.86</v>
       </c>
       <c r="V33" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W33" t="n">
         <v>1.59</v>
       </c>
       <c r="X33" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y33" t="n">
         <v>11</v>
@@ -6846,7 +6846,7 @@
         <v>16.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AF33" t="n">
         <v>16</v>
@@ -6876,13 +6876,13 @@
         <v>38</v>
       </c>
       <c r="AO33" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP33" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR33" t="n">
         <v>20</v>
@@ -6891,25 +6891,25 @@
         <v>10</v>
       </c>
       <c r="AT33" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU33" t="n">
         <v>5.9</v>
       </c>
       <c r="AV33" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AX33" t="n">
         <v>13</v>
       </c>
       <c r="AY33" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA33" t="n">
         <v>26</v>
@@ -6924,17 +6924,17 @@
         <v>24</v>
       </c>
       <c r="BE33" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF33" t="n">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BG33" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H34" t="n">
         <v>2.12</v>
@@ -6983,7 +6983,7 @@
         <v>3.5</v>
       </c>
       <c r="L34" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M34" t="n">
         <v>1.1</v>
@@ -7007,16 +7007,16 @@
         <v>4.4</v>
       </c>
       <c r="T34" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="U34" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="V34" t="n">
         <v>1.83</v>
       </c>
       <c r="W34" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X34" t="n">
         <v>11.5</v>
@@ -7028,22 +7028,22 @@
         <v>13</v>
       </c>
       <c r="AA34" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB34" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="AC34" t="n">
         <v>8</v>
       </c>
       <c r="AD34" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE34" t="n">
         <v>65</v>
       </c>
       <c r="AF34" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AG34" t="n">
         <v>32</v>
@@ -7070,7 +7070,7 @@
         <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="AP34" t="n">
         <v>10</v>
@@ -7082,7 +7082,7 @@
         <v>10.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AT34" t="n">
         <v>10.5</v>
@@ -7094,41 +7094,41 @@
         <v>9.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AY34" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA34" t="n">
         <v>38</v>
       </c>
       <c r="BB34" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC34" t="n">
         <v>23</v>
       </c>
       <c r="BD34" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BE34" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF34" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG34" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -7159,13 +7159,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G35" t="n">
         <v>5</v>
       </c>
       <c r="H35" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I35" t="n">
         <v>2.2</v>
@@ -7174,7 +7174,7 @@
         <v>3.1</v>
       </c>
       <c r="K35" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L35" t="n">
         <v>1.59</v>
@@ -7267,62 +7267,62 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AR35" t="n">
         <v>5</v>
       </c>
       <c r="AS35" t="n">
-        <v>6</v>
+        <v>2.02</v>
       </c>
       <c r="AT35" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AW35" t="n">
-        <v>6</v>
+        <v>2.02</v>
       </c>
       <c r="AX35" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ35" t="n">
         <v>6.2</v>
       </c>
-      <c r="AY35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BA35" t="n">
-        <v>2.08</v>
+        <v>7</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BC35" t="n">
         <v>2.1</v>
       </c>
       <c r="BD35" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BG35" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -7356,10 +7356,10 @@
         <v>3.3</v>
       </c>
       <c r="G36" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H36" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="I36" t="n">
         <v>2.6</v>
@@ -7380,10 +7380,10 @@
         <v>2.88</v>
       </c>
       <c r="O36" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P36" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q36" t="n">
         <v>2.56</v>
@@ -7395,10 +7395,10 @@
         <v>5.2</v>
       </c>
       <c r="T36" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U36" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V36" t="n">
         <v>1.62</v>
@@ -7446,22 +7446,22 @@
         <v>70</v>
       </c>
       <c r="AK36" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AL36" t="n">
         <v>75</v>
       </c>
       <c r="AM36" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN36" t="n">
         <v>60</v>
       </c>
       <c r="AO36" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP36" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ36" t="n">
         <v>7.6</v>
@@ -7470,7 +7470,7 @@
         <v>13</v>
       </c>
       <c r="AS36" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AT36" t="n">
         <v>9</v>
@@ -7482,7 +7482,7 @@
         <v>11</v>
       </c>
       <c r="AW36" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX36" t="n">
         <v>19</v>
@@ -7491,10 +7491,10 @@
         <v>13.5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="BB36" t="n">
         <v>30</v>
@@ -7512,11 +7512,11 @@
         <v>29</v>
       </c>
       <c r="BG36" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -7547,40 +7547,40 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G37" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="H37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I37" t="n">
         <v>4.7</v>
       </c>
-      <c r="I37" t="n">
-        <v>5</v>
-      </c>
       <c r="J37" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K37" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L37" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M37" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N37" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O37" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P37" t="n">
         <v>1.51</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
@@ -7592,25 +7592,25 @@
         <v>2.36</v>
       </c>
       <c r="U37" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V37" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W37" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="X37" t="n">
         <v>8.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z37" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AA37" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AB37" t="n">
         <v>6.4</v>
@@ -7619,37 +7619,37 @@
         <v>7.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE37" t="n">
         <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG37" t="n">
         <v>14</v>
       </c>
       <c r="AH37" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AI37" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ37" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK37" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AL37" t="n">
         <v>1000</v>